--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -832,7 +832,7 @@
         <v>0.0576</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>78.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>0.0556</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>0.039</v>
       </c>
       <c r="P10" s="12" t="n">
-        <v>69.2</v>
+        <v>65.7</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
         <v>0.0384</v>
       </c>
       <c r="P11" s="12" t="n">
-        <v>57.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R11" s="13" t="n">
@@ -1128,11 +1128,11 @@
         <v>0.0243</v>
       </c>
       <c r="P12" s="12" t="n">
-        <v>72.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R12" s="13" t="n">
@@ -1202,11 +1202,11 @@
         <v>0.009899999999999999</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>64.3</v>
+        <v>71.8</v>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="R13" s="13" t="n">
@@ -1276,7 +1276,7 @@
         <v>0.006</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>90.7</v>
+        <v>83.3</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1350,11 +1350,11 @@
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
-        <v>55.7</v>
+        <v>62.7</v>
       </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R15" s="13" t="n">
@@ -1424,7 +1424,7 @@
         <v>-0.0003</v>
       </c>
       <c r="P16" s="12" t="n">
-        <v>60.4</v>
+        <v>63.6</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>-0.0011</v>
       </c>
       <c r="P17" s="12" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
@@ -1572,11 +1572,11 @@
         <v>-0.0025</v>
       </c>
       <c r="P18" s="12" t="n">
-        <v>70.5</v>
+        <v>67.2</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R18" s="13" t="n">
@@ -1646,7 +1646,7 @@
         <v>-0.0108</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>73.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
@@ -1720,11 +1720,11 @@
         <v>-0.0136</v>
       </c>
       <c r="P20" s="12" t="n">
-        <v>54.2</v>
+        <v>65.2</v>
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R20" s="13" t="n">
@@ -1794,7 +1794,7 @@
         <v>-0.0233</v>
       </c>
       <c r="P21" s="12" t="n">
-        <v>28.5</v>
+        <v>45.9</v>
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
@@ -1868,11 +1868,11 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="P22" s="18" t="n">
-        <v>80.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Q22" s="15" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="R22" s="19" t="n">
@@ -1938,11 +1938,11 @@
         <v>0.05889999999999999</v>
       </c>
       <c r="P23" s="24" t="n">
-        <v>86.8</v>
+        <v>76.7</v>
       </c>
       <c r="Q23" s="21" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="R23" s="25" t="n">
@@ -2008,7 +2008,7 @@
         <v>0.0395</v>
       </c>
       <c r="P24" s="18" t="n">
-        <v>90.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q24" s="15" t="inlineStr">
         <is>
@@ -2078,11 +2078,11 @@
         <v>0.0365</v>
       </c>
       <c r="P25" s="18" t="n">
-        <v>58.4</v>
+        <v>63.4</v>
       </c>
       <c r="Q25" s="15" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R25" s="19" t="n">
@@ -2148,7 +2148,7 @@
         <v>0.0334</v>
       </c>
       <c r="P26" s="18" t="n">
-        <v>67.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q26" s="15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>0.031</v>
       </c>
       <c r="P27" s="18" t="n">
-        <v>45.3</v>
+        <v>51.7</v>
       </c>
       <c r="Q27" s="15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>0.03</v>
       </c>
       <c r="P28" s="30" t="n">
-        <v>69.3</v>
+        <v>69.8</v>
       </c>
       <c r="Q28" s="27" t="inlineStr">
         <is>
@@ -2358,11 +2358,11 @@
         <v>0.0296</v>
       </c>
       <c r="P29" s="18" t="n">
-        <v>72.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="Q29" s="15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R29" s="19" t="n">
@@ -2428,7 +2428,7 @@
         <v>0.0203</v>
       </c>
       <c r="P30" s="18" t="n">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="Q30" s="15" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>0.0194</v>
       </c>
       <c r="P31" s="18" t="n">
-        <v>76.3</v>
+        <v>70.5</v>
       </c>
       <c r="Q31" s="15" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>0.0132</v>
       </c>
       <c r="P32" s="18" t="n">
-        <v>67.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Q32" s="15" t="inlineStr">
         <is>
@@ -2638,11 +2638,11 @@
         <v>0.0103</v>
       </c>
       <c r="P33" s="18" t="n">
-        <v>55.8</v>
+        <v>64</v>
       </c>
       <c r="Q33" s="15" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R33" s="19" t="n">
@@ -2708,11 +2708,11 @@
         <v>0.0103</v>
       </c>
       <c r="P34" s="18" t="n">
-        <v>58.7</v>
+        <v>62.5</v>
       </c>
       <c r="Q34" s="15" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R34" s="19" t="n">
@@ -2778,11 +2778,11 @@
         <v>0.0103</v>
       </c>
       <c r="P35" s="24" t="n">
-        <v>55.8</v>
+        <v>64</v>
       </c>
       <c r="Q35" s="21" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R35" s="25" t="n">
@@ -2848,7 +2848,7 @@
         <v>0.0089</v>
       </c>
       <c r="P36" s="18" t="n">
-        <v>80.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q36" s="15" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>0.0077</v>
       </c>
       <c r="P37" s="18" t="n">
-        <v>88.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Q37" s="15" t="inlineStr">
         <is>
@@ -2988,11 +2988,11 @@
         <v>0.0073</v>
       </c>
       <c r="P38" s="18" t="n">
-        <v>54</v>
+        <v>60.2</v>
       </c>
       <c r="Q38" s="15" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R38" s="19" t="n">
@@ -3058,11 +3058,11 @@
         <v>0.0067</v>
       </c>
       <c r="P39" s="18" t="n">
-        <v>62.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q39" s="15" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="R39" s="19" t="n">
@@ -3128,11 +3128,11 @@
         <v>0.0067</v>
       </c>
       <c r="P40" s="18" t="n">
-        <v>62.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q40" s="15" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="R40" s="19" t="n">
@@ -3198,11 +3198,11 @@
         <v>0.0043</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>73.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Q41" s="15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R41" s="19" t="n">
@@ -3268,11 +3268,11 @@
         <v>0.0035</v>
       </c>
       <c r="P42" s="18" t="n">
-        <v>56.3</v>
+        <v>60.8</v>
       </c>
       <c r="Q42" s="15" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R42" s="19" t="n">
@@ -3338,7 +3338,7 @@
         <v>0.0033</v>
       </c>
       <c r="P43" s="18" t="n">
-        <v>45.3</v>
+        <v>59.7</v>
       </c>
       <c r="Q43" s="15" t="inlineStr">
         <is>
@@ -3408,11 +3408,11 @@
         <v>0.0016</v>
       </c>
       <c r="P44" s="18" t="n">
-        <v>51.4</v>
+        <v>61.3</v>
       </c>
       <c r="Q44" s="15" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R44" s="19" t="n">
@@ -3478,11 +3478,11 @@
         <v>-0</v>
       </c>
       <c r="P45" s="30" t="n">
-        <v>84.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="Q45" s="27" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="R45" s="31" t="n">
@@ -3548,7 +3548,7 @@
         <v>-0.0071</v>
       </c>
       <c r="P46" s="18" t="n">
-        <v>39.3</v>
+        <v>56.1</v>
       </c>
       <c r="Q46" s="15" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>-0.008699999999999999</v>
       </c>
       <c r="P47" s="18" t="n">
-        <v>47.3</v>
+        <v>58.9</v>
       </c>
       <c r="Q47" s="15" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>-0.011</v>
       </c>
       <c r="P48" s="18" t="n">
-        <v>89.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="Q48" s="15" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>-0.011</v>
       </c>
       <c r="P49" s="18" t="n">
-        <v>89.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="Q49" s="15" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>-0.0262</v>
       </c>
       <c r="P50" s="18" t="n">
-        <v>78.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="Q50" s="15" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>-0.0318</v>
       </c>
       <c r="P51" s="18" t="n">
-        <v>48.4</v>
+        <v>59.2</v>
       </c>
       <c r="Q51" s="15" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>-0.0327</v>
       </c>
       <c r="P52" s="18" t="n">
-        <v>96.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Q52" s="15" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="AX2" s="34" t="n">
-        <v>89.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AY2" s="34" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="AX3" s="34" t="n">
-        <v>78.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="AY3" s="34" t="inlineStr">
         <is>
@@ -4761,11 +4761,11 @@
         </is>
       </c>
       <c r="AX4" s="35" t="n">
-        <v>58.4</v>
+        <v>63.4</v>
       </c>
       <c r="AY4" s="35" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -4918,11 +4918,11 @@
         </is>
       </c>
       <c r="AX5" s="36" t="n">
-        <v>51.4</v>
+        <v>61.3</v>
       </c>
       <c r="AY5" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5075,11 +5075,11 @@
         </is>
       </c>
       <c r="AX6" s="36" t="n">
-        <v>62.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AY6" s="36" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -5232,11 +5232,11 @@
         </is>
       </c>
       <c r="AX7" s="36" t="n">
-        <v>57.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AY7" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5393,11 +5393,11 @@
         </is>
       </c>
       <c r="AX8" s="36" t="n">
-        <v>55.8</v>
+        <v>64</v>
       </c>
       <c r="AY8" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5554,11 +5554,11 @@
         </is>
       </c>
       <c r="AX9" s="36" t="n">
-        <v>72.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AY9" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AX10" s="36" t="n">
-        <v>69.3</v>
+        <v>69.8</v>
       </c>
       <c r="AY10" s="36" t="inlineStr">
         <is>
@@ -5872,11 +5872,11 @@
         </is>
       </c>
       <c r="AX11" s="36" t="n">
-        <v>80.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AY11" s="36" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="AX12" s="37" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="AY12" s="37" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="AX13" s="37" t="n">
-        <v>73.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="AY13" s="37" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="AX14" s="37" t="n">
-        <v>69.2</v>
+        <v>65.7</v>
       </c>
       <c r="AY14" s="37" t="inlineStr">
         <is>
@@ -6536,11 +6536,11 @@
         </is>
       </c>
       <c r="AX15" s="38" t="n">
-        <v>58.7</v>
+        <v>62.5</v>
       </c>
       <c r="AY15" s="38" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="AX16" s="38" t="n">
-        <v>45.3</v>
+        <v>51.7</v>
       </c>
       <c r="AY16" s="38" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="AX17" s="34" t="n">
-        <v>96.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AY17" s="34" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="AX18" s="34" t="n">
-        <v>88.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AY18" s="34" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="AX19" s="34" t="n">
-        <v>76.3</v>
+        <v>70.5</v>
       </c>
       <c r="AY19" s="34" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         </is>
       </c>
       <c r="AX20" s="34" t="n">
-        <v>45.3</v>
+        <v>59.7</v>
       </c>
       <c r="AY20" s="34" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="AX21" s="35" t="n">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="AY21" s="35" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="AX22" s="35" t="n">
-        <v>39.3</v>
+        <v>56.1</v>
       </c>
       <c r="AY22" s="35" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="AX23" s="36" t="n">
-        <v>67.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AY23" s="36" t="inlineStr">
         <is>
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="AX24" s="35" t="n">
-        <v>56.3</v>
+        <v>60.8</v>
       </c>
       <c r="AY24" s="35" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -8086,11 +8086,11 @@
         </is>
       </c>
       <c r="AX25" s="36" t="n">
-        <v>73.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AY25" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="AX26" s="36" t="n">
-        <v>69.3</v>
+        <v>69.8</v>
       </c>
       <c r="AY26" s="36" t="inlineStr">
         <is>
@@ -8432,11 +8432,11 @@
         </is>
       </c>
       <c r="AX27" s="36" t="n">
-        <v>72.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AY27" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -8601,11 +8601,11 @@
         </is>
       </c>
       <c r="AX28" s="36" t="n">
-        <v>86.8</v>
+        <v>76.7</v>
       </c>
       <c r="AY28" s="36" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="AX29" s="38" t="n">
-        <v>90.7</v>
+        <v>83.3</v>
       </c>
       <c r="AY29" s="38" t="inlineStr">
         <is>
@@ -8943,11 +8943,11 @@
         </is>
       </c>
       <c r="AX30" s="38" t="n">
-        <v>64.3</v>
+        <v>71.8</v>
       </c>
       <c r="AY30" s="38" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="AX31" s="36" t="n">
-        <v>78.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="AY31" s="36" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="AX32" s="38" t="n">
-        <v>80.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="AY32" s="38" t="inlineStr">
         <is>
@@ -9458,11 +9458,11 @@
         </is>
       </c>
       <c r="AX33" s="38" t="n">
-        <v>54.2</v>
+        <v>65.2</v>
       </c>
       <c r="AY33" s="38" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="AX34" s="38" t="n">
-        <v>47.3</v>
+        <v>58.9</v>
       </c>
       <c r="AY34" s="38" t="inlineStr">
         <is>
@@ -9798,11 +9798,11 @@
         </is>
       </c>
       <c r="AX35" s="36" t="n">
-        <v>72.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AY35" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="AX36" s="38" t="n">
-        <v>28.5</v>
+        <v>45.9</v>
       </c>
       <c r="AY36" s="38" t="inlineStr">
         <is>
@@ -10140,11 +10140,11 @@
         </is>
       </c>
       <c r="AX37" s="38" t="n">
-        <v>54</v>
+        <v>60.2</v>
       </c>
       <c r="AY37" s="38" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="AX38" s="38" t="n">
-        <v>60.4</v>
+        <v>63.6</v>
       </c>
       <c r="AY38" s="38" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="AX39" s="34" t="n">
-        <v>88.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AY39" s="34" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="AX40" s="34" t="n">
-        <v>96.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AY40" s="34" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="AX41" s="34" t="n">
-        <v>76.3</v>
+        <v>70.5</v>
       </c>
       <c r="AY41" s="34" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="AX42" s="34" t="n">
-        <v>89.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AY42" s="34" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="AX43" s="34" t="n">
-        <v>45.3</v>
+        <v>59.7</v>
       </c>
       <c r="AY43" s="34" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="AX44" s="35" t="n">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="AY44" s="35" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         </is>
       </c>
       <c r="AX45" s="35" t="n">
-        <v>48.4</v>
+        <v>59.2</v>
       </c>
       <c r="AY45" s="35" t="inlineStr">
         <is>
@@ -11579,11 +11579,11 @@
         </is>
       </c>
       <c r="AX46" s="35" t="n">
-        <v>55.8</v>
+        <v>64</v>
       </c>
       <c r="AY46" s="35" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
         </is>
       </c>
       <c r="AX47" s="36" t="n">
-        <v>67.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AY47" s="36" t="inlineStr">
         <is>
@@ -11897,11 +11897,11 @@
         </is>
       </c>
       <c r="AX48" s="35" t="n">
-        <v>56.3</v>
+        <v>60.8</v>
       </c>
       <c r="AY48" s="35" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -12052,11 +12052,11 @@
         </is>
       </c>
       <c r="AX49" s="36" t="n">
-        <v>73.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AY49" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -12211,11 +12211,11 @@
         </is>
       </c>
       <c r="AX50" s="35" t="n">
-        <v>62.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AY50" s="35" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
         </is>
       </c>
       <c r="AX51" s="36" t="n">
-        <v>78.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="AY51" s="36" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="AX52" s="36" t="n">
-        <v>90.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AY52" s="36" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         </is>
       </c>
       <c r="AX53" s="36" t="n">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="AY53" s="36" t="inlineStr">
         <is>
@@ -12891,11 +12891,11 @@
         </is>
       </c>
       <c r="AX54" s="36" t="n">
-        <v>58.4</v>
+        <v>63.4</v>
       </c>
       <c r="AY54" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -13064,11 +13064,11 @@
         </is>
       </c>
       <c r="AX55" s="36" t="n">
-        <v>55.8</v>
+        <v>64</v>
       </c>
       <c r="AY55" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -13233,11 +13233,11 @@
         </is>
       </c>
       <c r="AX56" s="36" t="n">
-        <v>70.5</v>
+        <v>67.2</v>
       </c>
       <c r="AY56" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -13402,7 +13402,7 @@
         </is>
       </c>
       <c r="AX57" s="36" t="n">
-        <v>67.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AY57" s="36" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         </is>
       </c>
       <c r="AX58" s="34" t="n">
-        <v>69.3</v>
+        <v>69.8</v>
       </c>
       <c r="AY58" s="34" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         </is>
       </c>
       <c r="AX59" s="37" t="n">
-        <v>78.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="AY59" s="37" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         </is>
       </c>
       <c r="AX60" s="36" t="n">
-        <v>78.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="AY60" s="36" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         </is>
       </c>
       <c r="AX61" s="36" t="n">
-        <v>90.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AY61" s="36" t="inlineStr">
         <is>
@@ -14311,11 +14311,11 @@
         </is>
       </c>
       <c r="AX62" s="37" t="n">
-        <v>72.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AY62" s="37" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -14492,11 +14492,11 @@
         </is>
       </c>
       <c r="AX63" s="35" t="n">
-        <v>86.8</v>
+        <v>76.7</v>
       </c>
       <c r="AY63" s="35" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -14677,7 +14677,7 @@
         </is>
       </c>
       <c r="AX64" s="37" t="n">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="AY64" s="37" t="inlineStr">
         <is>
@@ -14854,11 +14854,11 @@
         </is>
       </c>
       <c r="AX65" s="36" t="n">
-        <v>58.4</v>
+        <v>63.4</v>
       </c>
       <c r="AY65" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -15031,11 +15031,11 @@
         </is>
       </c>
       <c r="AX66" s="36" t="n">
-        <v>55.8</v>
+        <v>64</v>
       </c>
       <c r="AY66" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -15204,11 +15204,11 @@
         </is>
       </c>
       <c r="AX67" s="36" t="n">
-        <v>72.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AY67" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -15389,11 +15389,11 @@
         </is>
       </c>
       <c r="AX68" s="37" t="n">
-        <v>70.5</v>
+        <v>67.2</v>
       </c>
       <c r="AY68" s="37" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
         </is>
       </c>
       <c r="AX69" s="36" t="n">
-        <v>67.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AY69" s="36" t="inlineStr">
         <is>
@@ -15751,11 +15751,11 @@
         </is>
       </c>
       <c r="AX70" s="37" t="n">
-        <v>57.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AY70" s="37" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -15926,11 +15926,11 @@
         </is>
       </c>
       <c r="AX71" s="38" t="n">
-        <v>55.7</v>
+        <v>62.7</v>
       </c>
       <c r="AY71" s="38" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -16103,11 +16103,11 @@
         </is>
       </c>
       <c r="AX72" s="34" t="n">
-        <v>84.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="AY72" s="34" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -16264,11 +16264,11 @@
         </is>
       </c>
       <c r="AX73" s="35" t="n">
-        <v>55.8</v>
+        <v>64</v>
       </c>
       <c r="AY73" s="35" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="AX74" s="36" t="n">
-        <v>89.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AY74" s="36" t="inlineStr">
         <is>
@@ -16586,11 +16586,11 @@
         </is>
       </c>
       <c r="AX75" s="36" t="n">
-        <v>51.4</v>
+        <v>61.3</v>
       </c>
       <c r="AY75" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -16749,11 +16749,11 @@
         </is>
       </c>
       <c r="AX76" s="36" t="n">
-        <v>62.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AY76" s="36" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -16908,11 +16908,11 @@
         </is>
       </c>
       <c r="AX77" s="36" t="n">
-        <v>80.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AY77" s="36" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="AX78" s="36" t="n">
-        <v>88.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AY78" s="36" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         </is>
       </c>
       <c r="AX79" s="36" t="n">
-        <v>96.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AY79" s="36" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         </is>
       </c>
       <c r="AX80" s="36" t="n">
-        <v>89.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AY80" s="36" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         </is>
       </c>
       <c r="AX81" s="36" t="n">
-        <v>76.3</v>
+        <v>70.5</v>
       </c>
       <c r="AY81" s="36" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         </is>
       </c>
       <c r="AX82" s="36" t="n">
-        <v>45.3</v>
+        <v>59.7</v>
       </c>
       <c r="AY82" s="36" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="AX83" s="36" t="n">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="AY83" s="36" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="AX84" s="36" t="n">
-        <v>48.4</v>
+        <v>59.2</v>
       </c>
       <c r="AY84" s="36" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         </is>
       </c>
       <c r="AX85" s="36" t="n">
-        <v>67.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AY85" s="36" t="inlineStr">
         <is>
@@ -18231,11 +18231,11 @@
         </is>
       </c>
       <c r="AX86" s="36" t="n">
-        <v>56.3</v>
+        <v>60.8</v>
       </c>
       <c r="AY86" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -18394,11 +18394,11 @@
         </is>
       </c>
       <c r="AX87" s="36" t="n">
-        <v>62.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AY87" s="36" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -18535,11 +18535,11 @@
         </is>
       </c>
       <c r="AX88" s="36" t="n">
-        <v>73.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AY88" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -18680,7 +18680,7 @@
         </is>
       </c>
       <c r="AX89" s="36" t="n">
-        <v>39.3</v>
+        <v>56.1</v>
       </c>
       <c r="AY89" s="36" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="AX90" s="34" t="n">
-        <v>69.3</v>
+        <v>69.8</v>
       </c>
       <c r="AY90" s="34" t="inlineStr">
         <is>
@@ -19046,11 +19046,11 @@
         </is>
       </c>
       <c r="AX91" s="35" t="n">
-        <v>86.8</v>
+        <v>76.7</v>
       </c>
       <c r="AY91" s="35" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
         </is>
       </c>
       <c r="AX92" s="36" t="n">
-        <v>89.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AY92" s="36" t="inlineStr">
         <is>
@@ -19372,11 +19372,11 @@
         </is>
       </c>
       <c r="AX93" s="36" t="n">
-        <v>58.4</v>
+        <v>63.4</v>
       </c>
       <c r="AY93" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -19535,11 +19535,11 @@
         </is>
       </c>
       <c r="AX94" s="36" t="n">
-        <v>51.4</v>
+        <v>61.3</v>
       </c>
       <c r="AY94" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -19698,11 +19698,11 @@
         </is>
       </c>
       <c r="AX95" s="36" t="n">
-        <v>62.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AY95" s="36" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -19861,11 +19861,11 @@
         </is>
       </c>
       <c r="AX96" s="36" t="n">
-        <v>55.8</v>
+        <v>64</v>
       </c>
       <c r="AY96" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -20024,11 +20024,11 @@
         </is>
       </c>
       <c r="AX97" s="36" t="n">
-        <v>80.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AY97" s="36" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -20183,7 +20183,7 @@
         </is>
       </c>
       <c r="AX98" s="36" t="n">
-        <v>78.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="AY98" s="36" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         </is>
       </c>
       <c r="AX99" s="36" t="n">
-        <v>90.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AY99" s="36" t="inlineStr">
         <is>
@@ -20501,11 +20501,11 @@
         </is>
       </c>
       <c r="AX100" s="36" t="n">
-        <v>72.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AY100" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="AX101" s="36" t="n">
-        <v>67.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AY101" s="36" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         </is>
       </c>
       <c r="AX102" s="36" t="n">
-        <v>88.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AY102" s="36" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         </is>
       </c>
       <c r="AX103" s="36" t="n">
-        <v>96.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AY103" s="36" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         </is>
       </c>
       <c r="AX104" s="36" t="n">
-        <v>89.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AY104" s="36" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         </is>
       </c>
       <c r="AX105" s="36" t="n">
-        <v>76.3</v>
+        <v>70.5</v>
       </c>
       <c r="AY105" s="36" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         </is>
       </c>
       <c r="AX106" s="36" t="n">
-        <v>45.3</v>
+        <v>59.7</v>
       </c>
       <c r="AY106" s="36" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         </is>
       </c>
       <c r="AX107" s="36" t="n">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="AY107" s="36" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="AX108" s="36" t="n">
-        <v>48.4</v>
+        <v>59.2</v>
       </c>
       <c r="AY108" s="36" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         </is>
       </c>
       <c r="AX109" s="36" t="n">
-        <v>67.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AY109" s="36" t="inlineStr">
         <is>
@@ -22127,11 +22127,11 @@
         </is>
       </c>
       <c r="AX110" s="36" t="n">
-        <v>56.3</v>
+        <v>60.8</v>
       </c>
       <c r="AY110" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -22290,11 +22290,11 @@
         </is>
       </c>
       <c r="AX111" s="36" t="n">
-        <v>62.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AY111" s="36" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -22449,11 +22449,11 @@
         </is>
       </c>
       <c r="AX112" s="36" t="n">
-        <v>73.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AY112" s="36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -22612,7 +22612,7 @@
         </is>
       </c>
       <c r="AX113" s="36" t="n">
-        <v>39.3</v>
+        <v>56.1</v>
       </c>
       <c r="AY113" s="36" t="inlineStr">
         <is>
@@ -22789,11 +22789,11 @@
         </is>
       </c>
       <c r="AX114" s="34" t="n">
-        <v>84.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="AY114" s="34" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -22950,11 +22950,11 @@
         </is>
       </c>
       <c r="AX115" s="35" t="n">
-        <v>55.8</v>
+        <v>64</v>
       </c>
       <c r="AY115" s="35" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -23131,11 +23131,11 @@
         </is>
       </c>
       <c r="AX116" s="37" t="n">
-        <v>64.3</v>
+        <v>71.8</v>
       </c>
       <c r="AY116" s="37" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -23312,7 +23312,7 @@
         </is>
       </c>
       <c r="AX117" s="37" t="n">
-        <v>90.7</v>
+        <v>83.3</v>
       </c>
       <c r="AY117" s="37" t="inlineStr">
         <is>
@@ -23493,11 +23493,11 @@
         </is>
       </c>
       <c r="AX118" s="37" t="n">
-        <v>54.2</v>
+        <v>65.2</v>
       </c>
       <c r="AY118" s="37" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -23674,11 +23674,11 @@
         </is>
       </c>
       <c r="AX119" s="37" t="n">
-        <v>55.7</v>
+        <v>62.7</v>
       </c>
       <c r="AY119" s="37" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -23855,7 +23855,7 @@
         </is>
       </c>
       <c r="AX120" s="37" t="n">
-        <v>60.4</v>
+        <v>63.6</v>
       </c>
       <c r="AY120" s="37" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="AX121" s="37" t="n">
-        <v>28.5</v>
+        <v>45.9</v>
       </c>
       <c r="AY121" s="37" t="inlineStr">
         <is>
@@ -24199,11 +24199,11 @@
         </is>
       </c>
       <c r="AX122" s="36" t="n">
-        <v>58.7</v>
+        <v>62.5</v>
       </c>
       <c r="AY122" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -24362,7 +24362,7 @@
         </is>
       </c>
       <c r="AX123" s="36" t="n">
-        <v>45.3</v>
+        <v>51.7</v>
       </c>
       <c r="AY123" s="36" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         </is>
       </c>
       <c r="AX124" s="36" t="n">
-        <v>80.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="AY124" s="36" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         </is>
       </c>
       <c r="AX125" s="36" t="n">
-        <v>47.3</v>
+        <v>58.9</v>
       </c>
       <c r="AY125" s="36" t="inlineStr">
         <is>
@@ -24827,11 +24827,11 @@
         </is>
       </c>
       <c r="AX126" s="36" t="n">
-        <v>54</v>
+        <v>60.2</v>
       </c>
       <c r="AY126" s="36" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:X52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -588,21 +588,23 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -725,75 +727,85 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>🎯 Priority</t>
+          <t>🎯 Urgency</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>Inv Quality</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>Investability</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>Final Action</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>Action Note</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
@@ -835,49 +847,59 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>H · PREMATURE EXIT?</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
+          <t>Premature Exit?</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="N8" s="11" t="n">
         <v>73.7</v>
       </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · quality was good · review if premature</t>
-        </is>
-      </c>
-      <c r="M8" s="12" t="n">
+      <c r="O8" s="12" t="n">
         <v>5343.6</v>
       </c>
-      <c r="N8" s="12" t="n">
+      <c r="P8" s="12" t="n">
         <v>5651.5</v>
       </c>
-      <c r="O8" s="12" t="n">
+      <c r="Q8" s="12" t="n">
         <v>5651.5</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="R8" s="13" t="n">
         <v>0.0576</v>
       </c>
-      <c r="Q8" s="12" t="n"/>
-      <c r="R8" s="12" t="n"/>
       <c r="S8" s="12" t="n"/>
-      <c r="T8" s="9" t="inlineStr">
+      <c r="T8" s="12" t="n"/>
+      <c r="U8" s="12" t="n"/>
+      <c r="V8" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U8" s="9" t="inlineStr"/>
-      <c r="V8" s="9" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr"/>
+      <c r="X8" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +10.6pp alpha</t>
         </is>
@@ -919,49 +941,59 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>I · CLOSED · CLEAN</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="N9" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · position closed</t>
-        </is>
-      </c>
-      <c r="M9" s="12" t="n">
+      <c r="O9" s="12" t="n">
         <v>1115</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="P9" s="12" t="n">
         <v>1177</v>
       </c>
-      <c r="O9" s="12" t="n">
+      <c r="Q9" s="12" t="n">
         <v>1177</v>
       </c>
-      <c r="P9" s="13" t="n">
+      <c r="R9" s="13" t="n">
         <v>0.0556</v>
       </c>
-      <c r="Q9" s="12" t="n"/>
-      <c r="R9" s="12" t="n"/>
       <c r="S9" s="12" t="n"/>
-      <c r="T9" s="9" t="inlineStr">
+      <c r="T9" s="12" t="n"/>
+      <c r="U9" s="12" t="n"/>
+      <c r="V9" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U9" s="9" t="inlineStr"/>
-      <c r="V9" s="9" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr"/>
+      <c r="X9" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +11.7pp alpha</t>
         </is>
@@ -1003,49 +1035,59 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>I · CLOSED · CLEAN</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="N10" s="11" t="n">
         <v>65.7</v>
       </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · position closed</t>
-        </is>
-      </c>
-      <c r="M10" s="12" t="n">
+      <c r="O10" s="12" t="n">
         <v>546</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="P10" s="12" t="n">
         <v>567.3</v>
       </c>
-      <c r="O10" s="12" t="n">
+      <c r="Q10" s="12" t="n">
         <v>567.3</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="R10" s="13" t="n">
         <v>0.039</v>
       </c>
-      <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="12" t="n"/>
       <c r="S10" s="12" t="n"/>
-      <c r="T10" s="9" t="inlineStr">
+      <c r="T10" s="12" t="n"/>
+      <c r="U10" s="12" t="n"/>
+      <c r="V10" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U10" s="9" t="inlineStr"/>
-      <c r="V10" s="9" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr"/>
+      <c r="X10" s="9" t="inlineStr">
         <is>
           <t>Rotation → LUPIN.NS (+52.0pp)</t>
         </is>
@@ -1087,49 +1129,59 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>I · CLOSED · CLEAN</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="N11" s="11" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · position closed</t>
-        </is>
-      </c>
-      <c r="M11" s="12" t="n">
+      <c r="O11" s="12" t="n">
         <v>268.5</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="P11" s="12" t="n">
         <v>278.8</v>
       </c>
-      <c r="O11" s="12" t="n">
+      <c r="Q11" s="12" t="n">
         <v>278.8</v>
       </c>
-      <c r="P11" s="13" t="n">
+      <c r="R11" s="13" t="n">
         <v>0.0384</v>
       </c>
-      <c r="Q11" s="12" t="n"/>
-      <c r="R11" s="12" t="n"/>
       <c r="S11" s="12" t="n"/>
-      <c r="T11" s="9" t="inlineStr">
+      <c r="T11" s="12" t="n"/>
+      <c r="U11" s="12" t="n"/>
+      <c r="V11" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U11" s="9" t="inlineStr"/>
-      <c r="V11" s="9" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr"/>
+      <c r="X11" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +11.6pp alpha</t>
         </is>
@@ -1171,49 +1223,59 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>I · CLOSED · CLEAN</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="N12" s="11" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · position closed</t>
-        </is>
-      </c>
-      <c r="M12" s="12" t="n">
+      <c r="O12" s="12" t="n">
         <v>1319.2</v>
       </c>
-      <c r="N12" s="12" t="n">
+      <c r="P12" s="12" t="n">
         <v>1351.3</v>
       </c>
-      <c r="O12" s="12" t="n">
+      <c r="Q12" s="12" t="n">
         <v>1351.3</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="R12" s="13" t="n">
         <v>0.0243</v>
       </c>
-      <c r="Q12" s="12" t="n"/>
-      <c r="R12" s="12" t="n"/>
       <c r="S12" s="12" t="n"/>
-      <c r="T12" s="9" t="inlineStr">
+      <c r="T12" s="12" t="n"/>
+      <c r="U12" s="12" t="n"/>
+      <c r="V12" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U12" s="9" t="inlineStr"/>
-      <c r="V12" s="9" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr"/>
+      <c r="X12" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +7.8pp alpha</t>
         </is>
@@ -1255,49 +1317,59 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>H · PREMATURE EXIT?</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
+          <t>Premature Exit?</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="N13" s="11" t="n">
         <v>71.8</v>
       </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · quality was good · review if premature</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="n">
+      <c r="O13" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="N13" s="12" t="n">
+      <c r="P13" s="12" t="n">
         <v>853.4</v>
       </c>
-      <c r="O13" s="12" t="n">
+      <c r="Q13" s="12" t="n">
         <v>853.4</v>
       </c>
-      <c r="P13" s="13" t="n">
+      <c r="R13" s="13" t="n">
         <v>0.009899999999999999</v>
       </c>
-      <c r="Q13" s="12" t="n"/>
-      <c r="R13" s="12" t="n"/>
       <c r="S13" s="12" t="n"/>
-      <c r="T13" s="9" t="inlineStr">
+      <c r="T13" s="12" t="n"/>
+      <c r="U13" s="12" t="n"/>
+      <c r="V13" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U13" s="9" t="inlineStr"/>
-      <c r="V13" s="9" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr"/>
+      <c r="X13" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +7.4pp alpha</t>
         </is>
@@ -1339,49 +1411,59 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>H · PREMATURE EXIT?</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
+          <t>Premature Exit?</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>🏆 QUALITY</t>
         </is>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="N14" s="11" t="n">
         <v>83.3</v>
       </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · quality was good · review if premature</t>
-        </is>
-      </c>
-      <c r="M14" s="12" t="n">
+      <c r="O14" s="12" t="n">
         <v>6793.5</v>
       </c>
-      <c r="N14" s="12" t="n">
+      <c r="P14" s="12" t="n">
         <v>6834</v>
       </c>
-      <c r="O14" s="12" t="n">
+      <c r="Q14" s="12" t="n">
         <v>6834</v>
       </c>
-      <c r="P14" s="13" t="n">
+      <c r="R14" s="13" t="n">
         <v>0.006</v>
       </c>
-      <c r="Q14" s="12" t="n"/>
-      <c r="R14" s="12" t="n"/>
       <c r="S14" s="12" t="n"/>
-      <c r="T14" s="9" t="inlineStr">
+      <c r="T14" s="12" t="n"/>
+      <c r="U14" s="12" t="n"/>
+      <c r="V14" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U14" s="9" t="inlineStr"/>
-      <c r="V14" s="9" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr"/>
+      <c r="X14" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +8.0pp alpha</t>
         </is>
@@ -1423,49 +1505,59 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>I · CLOSED · CLEAN</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="N15" s="11" t="n">
         <v>62.7</v>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · position closed</t>
-        </is>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>471.2</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>471.2</v>
       </c>
       <c r="O15" s="12" t="n">
         <v>471.2</v>
       </c>
-      <c r="P15" s="13" t="n">
+      <c r="P15" s="12" t="n">
+        <v>471.2</v>
+      </c>
+      <c r="Q15" s="12" t="n">
+        <v>471.2</v>
+      </c>
+      <c r="R15" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="12" t="n"/>
-      <c r="R15" s="12" t="n"/>
       <c r="S15" s="12" t="n"/>
-      <c r="T15" s="9" t="inlineStr">
+      <c r="T15" s="12" t="n"/>
+      <c r="U15" s="12" t="n"/>
+      <c r="V15" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U15" s="9" t="inlineStr"/>
-      <c r="V15" s="9" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr"/>
+      <c r="X15" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +60.7pp alpha</t>
         </is>
@@ -1507,49 +1599,59 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>I · CLOSED · CLEAN</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="N16" s="11" t="n">
         <v>63.6</v>
       </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · position closed</t>
-        </is>
-      </c>
-      <c r="M16" s="12" t="n">
+      <c r="O16" s="12" t="n">
         <v>1595</v>
       </c>
-      <c r="N16" s="12" t="n">
+      <c r="P16" s="12" t="n">
         <v>1594.5</v>
       </c>
-      <c r="O16" s="12" t="n">
+      <c r="Q16" s="12" t="n">
         <v>1594.5</v>
       </c>
-      <c r="P16" s="13" t="n">
+      <c r="R16" s="13" t="n">
         <v>-0.0003</v>
       </c>
-      <c r="Q16" s="12" t="n"/>
-      <c r="R16" s="12" t="n"/>
       <c r="S16" s="12" t="n"/>
-      <c r="T16" s="9" t="inlineStr">
+      <c r="T16" s="12" t="n"/>
+      <c r="U16" s="12" t="n"/>
+      <c r="V16" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U16" s="9" t="inlineStr"/>
-      <c r="V16" s="9" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr"/>
+      <c r="X16" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +62.5pp alpha</t>
         </is>
@@ -1591,49 +1693,59 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>H · PREMATURE EXIT?</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
+          <t>Premature Exit?</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="N17" s="11" t="n">
         <v>70.5</v>
       </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · quality was good · review if premature</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="n">
+      <c r="O17" s="12" t="n">
         <v>425.5</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="P17" s="12" t="n">
         <v>425.05</v>
       </c>
-      <c r="O17" s="12" t="n">
+      <c r="Q17" s="12" t="n">
         <v>425.05</v>
       </c>
-      <c r="P17" s="13" t="n">
+      <c r="R17" s="13" t="n">
         <v>-0.0011</v>
       </c>
-      <c r="Q17" s="12" t="n"/>
-      <c r="R17" s="12" t="n"/>
       <c r="S17" s="12" t="n"/>
-      <c r="T17" s="9" t="inlineStr">
+      <c r="T17" s="12" t="n"/>
+      <c r="U17" s="12" t="n"/>
+      <c r="V17" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U17" s="9" t="inlineStr"/>
-      <c r="V17" s="9" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr"/>
+      <c r="X17" s="9" t="inlineStr">
         <is>
           <t>Rotation → LUPIN.NS (+51.8pp)</t>
         </is>
@@ -1675,49 +1787,59 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>I · CLOSED · CLEAN</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="N18" s="11" t="n">
         <v>67.2</v>
       </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · position closed</t>
-        </is>
-      </c>
-      <c r="M18" s="12" t="n">
+      <c r="O18" s="12" t="n">
         <v>2187.4</v>
       </c>
-      <c r="N18" s="12" t="n">
+      <c r="P18" s="12" t="n">
         <v>2182</v>
       </c>
-      <c r="O18" s="12" t="n">
+      <c r="Q18" s="12" t="n">
         <v>2182</v>
       </c>
-      <c r="P18" s="13" t="n">
+      <c r="R18" s="13" t="n">
         <v>-0.0025</v>
       </c>
-      <c r="Q18" s="12" t="n"/>
-      <c r="R18" s="12" t="n"/>
       <c r="S18" s="12" t="n"/>
-      <c r="T18" s="9" t="inlineStr">
+      <c r="T18" s="12" t="n"/>
+      <c r="U18" s="12" t="n"/>
+      <c r="V18" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U18" s="9" t="inlineStr"/>
-      <c r="V18" s="9" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr"/>
+      <c r="X18" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +59.7pp alpha</t>
         </is>
@@ -1759,49 +1881,59 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>H · PREMATURE EXIT?</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
+          <t>Premature Exit?</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="N19" s="11" t="n">
         <v>72.8</v>
       </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · quality was good · review if premature</t>
-        </is>
-      </c>
-      <c r="M19" s="12" t="n">
+      <c r="O19" s="12" t="n">
         <v>950.2</v>
       </c>
-      <c r="N19" s="12" t="n">
+      <c r="P19" s="12" t="n">
         <v>939.95</v>
       </c>
-      <c r="O19" s="12" t="n">
+      <c r="Q19" s="12" t="n">
         <v>939.95</v>
       </c>
-      <c r="P19" s="13" t="n">
+      <c r="R19" s="13" t="n">
         <v>-0.0108</v>
       </c>
-      <c r="Q19" s="12" t="n"/>
-      <c r="R19" s="12" t="n"/>
       <c r="S19" s="12" t="n"/>
-      <c r="T19" s="9" t="inlineStr">
+      <c r="T19" s="12" t="n"/>
+      <c r="U19" s="12" t="n"/>
+      <c r="V19" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U19" s="9" t="inlineStr"/>
-      <c r="V19" s="9" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr"/>
+      <c r="X19" s="9" t="inlineStr">
         <is>
           <t>Rotation → LUPIN.NS (+51.8pp)</t>
         </is>
@@ -1843,49 +1975,59 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>I · CLOSED · CLEAN</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K20" s="11" t="n">
+      <c r="N20" s="11" t="n">
         <v>65.2</v>
       </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · position closed</t>
-        </is>
-      </c>
-      <c r="M20" s="12" t="n">
+      <c r="O20" s="12" t="n">
         <v>450</v>
       </c>
-      <c r="N20" s="12" t="n">
+      <c r="P20" s="12" t="n">
         <v>443.9</v>
       </c>
-      <c r="O20" s="12" t="n">
+      <c r="Q20" s="12" t="n">
         <v>443.9</v>
       </c>
-      <c r="P20" s="13" t="n">
+      <c r="R20" s="13" t="n">
         <v>-0.0136</v>
       </c>
-      <c r="Q20" s="12" t="n"/>
-      <c r="R20" s="12" t="n"/>
       <c r="S20" s="12" t="n"/>
-      <c r="T20" s="9" t="inlineStr">
+      <c r="T20" s="12" t="n"/>
+      <c r="U20" s="12" t="n"/>
+      <c r="V20" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U20" s="9" t="inlineStr"/>
-      <c r="V20" s="9" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr"/>
+      <c r="X20" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +10.3pp alpha</t>
         </is>
@@ -1927,49 +2069,59 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>I · CLOSED · CLEAN</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>✗ AVOID</t>
         </is>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="N21" s="11" t="n">
         <v>45.9</v>
       </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>⚪ EXITED · position closed</t>
-        </is>
-      </c>
-      <c r="M21" s="12" t="n">
+      <c r="O21" s="12" t="n">
         <v>1327.7</v>
       </c>
-      <c r="N21" s="12" t="n">
+      <c r="P21" s="12" t="n">
         <v>1296.8</v>
       </c>
-      <c r="O21" s="12" t="n">
+      <c r="Q21" s="12" t="n">
         <v>1296.8</v>
       </c>
-      <c r="P21" s="13" t="n">
+      <c r="R21" s="13" t="n">
         <v>-0.0233</v>
       </c>
-      <c r="Q21" s="12" t="n"/>
-      <c r="R21" s="12" t="n"/>
       <c r="S21" s="12" t="n"/>
-      <c r="T21" s="9" t="inlineStr">
+      <c r="T21" s="12" t="n"/>
+      <c r="U21" s="12" t="n"/>
+      <c r="V21" s="9" t="inlineStr">
         <is>
           <t>Sell/rotate today · closed position</t>
         </is>
       </c>
-      <c r="U21" s="9" t="inlineStr"/>
-      <c r="V21" s="9" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr"/>
+      <c r="X21" s="9" t="inlineStr">
         <is>
           <t>→ GNFC.NS · +64.8pp alpha</t>
         </is>
@@ -2007,53 +2159,63 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>D · COMPOUNDER</t>
+          <t>🟢 LOW</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K22" s="16" t="n">
+      <c r="N22" s="16" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="L22" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · quality intact</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="n">
+      <c r="O22" s="17" t="n">
         <v>552.4</v>
       </c>
-      <c r="N22" s="17" t="n">
+      <c r="P22" s="17" t="n">
         <v>597.55</v>
       </c>
-      <c r="O22" s="17" t="n"/>
-      <c r="P22" s="18" t="n">
+      <c r="Q22" s="17" t="n"/>
+      <c r="R22" s="18" t="n">
         <v>0.08169999999999999</v>
       </c>
-      <c r="Q22" s="17" t="n">
+      <c r="S22" s="17" t="n">
         <v>524.78</v>
       </c>
-      <c r="R22" s="17" t="n">
+      <c r="T22" s="17" t="n">
         <v>596.592</v>
       </c>
-      <c r="S22" s="17" t="n">
+      <c r="U22" s="17" t="n">
         <v>635.2599999999999</v>
       </c>
-      <c r="T22" s="14" t="inlineStr">
+      <c r="V22" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U22" s="14" t="inlineStr"/>
-      <c r="V22" s="14" t="inlineStr"/>
+      <c r="W22" s="14" t="inlineStr"/>
+      <c r="X22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
@@ -2087,53 +2249,63 @@
       </c>
       <c r="H23" s="19" t="inlineStr">
         <is>
-          <t>B · CONFIRMED BUY</t>
+          <t>🟠 HIGH</t>
         </is>
       </c>
       <c r="I23" s="19" t="inlineStr">
         <is>
+          <t>Confirmed Buy</t>
+        </is>
+      </c>
+      <c r="J23" s="19" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="K23" s="19" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L23" s="19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="M23" s="19" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K23" s="21" t="n">
+      <c r="N23" s="21" t="n">
         <v>76.7</v>
       </c>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>🟢 BUY · in buy zone · quality confirmed</t>
-        </is>
-      </c>
-      <c r="M23" s="22" t="n">
+      <c r="O23" s="22" t="n">
         <v>11075</v>
       </c>
-      <c r="N23" s="22" t="n">
+      <c r="P23" s="22" t="n">
         <v>11727</v>
       </c>
-      <c r="O23" s="22" t="n"/>
-      <c r="P23" s="23" t="n">
+      <c r="Q23" s="22" t="n"/>
+      <c r="R23" s="23" t="n">
         <v>0.05889999999999999</v>
       </c>
-      <c r="Q23" s="22" t="n">
+      <c r="S23" s="22" t="n">
         <v>11023.38</v>
       </c>
-      <c r="R23" s="22" t="n">
+      <c r="T23" s="22" t="n">
         <v>13134.24</v>
       </c>
-      <c r="S23" s="22" t="n">
+      <c r="U23" s="22" t="n">
         <v>14541.48</v>
       </c>
-      <c r="T23" s="19" t="inlineStr">
+      <c r="V23" s="19" t="inlineStr">
         <is>
           <t>Enter or add · in buy zone</t>
         </is>
       </c>
-      <c r="U23" s="19" t="inlineStr"/>
-      <c r="V23" s="19" t="inlineStr"/>
+      <c r="W23" s="19" t="inlineStr"/>
+      <c r="X23" s="19" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -2167,53 +2339,63 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>D · COMPOUNDER</t>
+          <t>🟢 LOW</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
         <is>
           <t>🏆 QUALITY</t>
         </is>
       </c>
-      <c r="K24" s="16" t="n">
+      <c r="N24" s="16" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="L24" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · patient · both endorse</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="n">
+      <c r="O24" s="17" t="n">
         <v>5322.4</v>
       </c>
-      <c r="N24" s="17" t="n">
+      <c r="P24" s="17" t="n">
         <v>5532.5</v>
       </c>
-      <c r="O24" s="17" t="n"/>
-      <c r="P24" s="18" t="n">
+      <c r="Q24" s="17" t="n"/>
+      <c r="R24" s="18" t="n">
         <v>0.0395</v>
       </c>
-      <c r="Q24" s="17" t="n">
+      <c r="S24" s="17" t="n">
         <v>5056.28</v>
       </c>
-      <c r="R24" s="17" t="n">
+      <c r="T24" s="17" t="n">
         <v>5748.192</v>
       </c>
-      <c r="S24" s="17" t="n">
+      <c r="U24" s="17" t="n">
         <v>6120.759999999999</v>
       </c>
-      <c r="T24" s="14" t="inlineStr">
+      <c r="V24" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U24" s="14" t="inlineStr"/>
-      <c r="V24" s="14" t="inlineStr"/>
+      <c r="W24" s="14" t="inlineStr"/>
+      <c r="X24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -2247,53 +2429,63 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="M25" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K25" s="16" t="n">
+      <c r="N25" s="16" t="n">
         <v>63.4</v>
       </c>
-      <c r="L25" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M25" s="17" t="n">
+      <c r="O25" s="17" t="n">
         <v>443.35</v>
       </c>
-      <c r="N25" s="17" t="n">
+      <c r="P25" s="17" t="n">
         <v>459.55</v>
       </c>
-      <c r="O25" s="17" t="n"/>
-      <c r="P25" s="18" t="n">
+      <c r="Q25" s="17" t="n"/>
+      <c r="R25" s="18" t="n">
         <v>0.0365</v>
       </c>
-      <c r="Q25" s="17" t="n">
+      <c r="S25" s="17" t="n">
         <v>421.1825</v>
       </c>
-      <c r="R25" s="17" t="n">
+      <c r="T25" s="17" t="n">
         <v>478.818</v>
       </c>
-      <c r="S25" s="17" t="n">
+      <c r="U25" s="17" t="n">
         <v>509.8525</v>
       </c>
-      <c r="T25" s="14" t="inlineStr">
+      <c r="V25" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U25" s="14" t="inlineStr"/>
-      <c r="V25" s="14" t="inlineStr"/>
+      <c r="W25" s="14" t="inlineStr"/>
+      <c r="X25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -2327,53 +2519,63 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="M26" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K26" s="16" t="n">
+      <c r="N26" s="16" t="n">
         <v>65.59999999999999</v>
       </c>
-      <c r="L26" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="n">
+      <c r="O26" s="17" t="n">
         <v>494.35</v>
       </c>
-      <c r="N26" s="17" t="n">
+      <c r="P26" s="17" t="n">
         <v>510.85</v>
       </c>
-      <c r="O26" s="17" t="n"/>
-      <c r="P26" s="18" t="n">
+      <c r="Q26" s="17" t="n"/>
+      <c r="R26" s="18" t="n">
         <v>0.0334</v>
       </c>
-      <c r="Q26" s="17" t="n">
+      <c r="S26" s="17" t="n">
         <v>469.6325</v>
       </c>
-      <c r="R26" s="17" t="n">
+      <c r="T26" s="17" t="n">
         <v>533.898</v>
       </c>
-      <c r="S26" s="17" t="n">
+      <c r="U26" s="17" t="n">
         <v>568.5024999999999</v>
       </c>
-      <c r="T26" s="14" t="inlineStr">
+      <c r="V26" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U26" s="14" t="inlineStr"/>
-      <c r="V26" s="14" t="inlineStr"/>
+      <c r="W26" s="14" t="inlineStr"/>
+      <c r="X26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -2407,53 +2609,63 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>F · SIGNAL WARNING</t>
+          <t>🟠 HIGH</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
+          <t>Signal Warning</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="M27" s="14" t="inlineStr">
         <is>
           <t>✗ AVOID</t>
         </is>
       </c>
-      <c r="K27" s="16" t="n">
+      <c r="N27" s="16" t="n">
         <v>51.7</v>
       </c>
-      <c r="L27" s="14" t="inlineStr">
-        <is>
-          <t>🔴 REDUCE / EXIT · quality degraded</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="n">
+      <c r="O27" s="17" t="n">
         <v>709</v>
       </c>
-      <c r="N27" s="17" t="n">
+      <c r="P27" s="17" t="n">
         <v>731</v>
       </c>
-      <c r="O27" s="17" t="n"/>
-      <c r="P27" s="18" t="n">
+      <c r="Q27" s="17" t="n"/>
+      <c r="R27" s="18" t="n">
         <v>0.031</v>
       </c>
-      <c r="Q27" s="17" t="n">
+      <c r="S27" s="17" t="n">
         <v>673.55</v>
       </c>
-      <c r="R27" s="17" t="n">
+      <c r="T27" s="17" t="n">
         <v>765.72</v>
       </c>
-      <c r="S27" s="17" t="n">
+      <c r="U27" s="17" t="n">
         <v>815.3499999999999</v>
       </c>
-      <c r="T27" s="14" t="inlineStr">
+      <c r="V27" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U27" s="14" t="inlineStr"/>
-      <c r="V27" s="14" t="inlineStr"/>
+      <c r="W27" s="14" t="inlineStr"/>
+      <c r="X27" s="14" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
@@ -2487,53 +2699,63 @@
       </c>
       <c r="H28" s="24" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I28" s="24" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L28" s="24" t="inlineStr">
+        <is>
           <t>STRONG BUY</t>
         </is>
       </c>
-      <c r="J28" s="24" t="inlineStr">
+      <c r="M28" s="24" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K28" s="26" t="n">
+      <c r="N28" s="26" t="n">
         <v>69.8</v>
       </c>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>🟡 BUY SMALL · quality borderline</t>
-        </is>
-      </c>
-      <c r="M28" s="27" t="n">
+      <c r="O28" s="27" t="n">
         <v>2351.3</v>
       </c>
-      <c r="N28" s="27" t="n">
+      <c r="P28" s="27" t="n">
         <v>2421.9</v>
       </c>
-      <c r="O28" s="27" t="n"/>
-      <c r="P28" s="28" t="n">
+      <c r="Q28" s="27" t="n"/>
+      <c r="R28" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q28" s="27" t="n">
+      <c r="S28" s="27" t="n">
         <v>2276.59</v>
       </c>
-      <c r="R28" s="27" t="n">
+      <c r="T28" s="27" t="n">
         <v>2712.53</v>
       </c>
-      <c r="S28" s="27" t="n">
+      <c r="U28" s="27" t="n">
         <v>3003.16</v>
       </c>
-      <c r="T28" s="24" t="inlineStr">
+      <c r="V28" s="24" t="inlineStr">
         <is>
           <t>Enter today · top pick · high conviction</t>
         </is>
       </c>
-      <c r="U28" s="24" t="inlineStr"/>
-      <c r="V28" s="24" t="inlineStr"/>
+      <c r="W28" s="24" t="inlineStr"/>
+      <c r="X28" s="24" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -2567,53 +2789,63 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L29" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="M29" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K29" s="16" t="n">
+      <c r="N29" s="16" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="L29" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="n">
+      <c r="O29" s="17" t="n">
         <v>11127</v>
       </c>
-      <c r="N29" s="17" t="n">
+      <c r="P29" s="17" t="n">
         <v>11456</v>
       </c>
-      <c r="O29" s="17" t="n"/>
-      <c r="P29" s="18" t="n">
+      <c r="Q29" s="17" t="n"/>
+      <c r="R29" s="18" t="n">
         <v>0.0296</v>
       </c>
-      <c r="Q29" s="17" t="n">
+      <c r="S29" s="17" t="n">
         <v>10570.65</v>
       </c>
-      <c r="R29" s="17" t="n">
+      <c r="T29" s="17" t="n">
         <v>12017.16</v>
       </c>
-      <c r="S29" s="17" t="n">
+      <c r="U29" s="17" t="n">
         <v>12796.05</v>
       </c>
-      <c r="T29" s="14" t="inlineStr">
+      <c r="V29" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U29" s="14" t="inlineStr"/>
-      <c r="V29" s="14" t="inlineStr"/>
+      <c r="W29" s="14" t="inlineStr"/>
+      <c r="X29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -2647,53 +2879,63 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>D · COMPOUNDER</t>
+          <t>🟢 LOW</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
         <is>
           <t>🏆 QUALITY</t>
         </is>
       </c>
-      <c r="K30" s="16" t="n">
+      <c r="N30" s="16" t="n">
         <v>82.5</v>
       </c>
-      <c r="L30" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · patient · both endorse</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="n">
+      <c r="O30" s="17" t="n">
         <v>389.3</v>
       </c>
-      <c r="N30" s="17" t="n">
+      <c r="P30" s="17" t="n">
         <v>397.2</v>
       </c>
-      <c r="O30" s="17" t="n"/>
-      <c r="P30" s="18" t="n">
+      <c r="Q30" s="17" t="n"/>
+      <c r="R30" s="18" t="n">
         <v>0.0203</v>
       </c>
-      <c r="Q30" s="17" t="n">
+      <c r="S30" s="17" t="n">
         <v>369.835</v>
       </c>
-      <c r="R30" s="17" t="n">
+      <c r="T30" s="17" t="n">
         <v>420.444</v>
       </c>
-      <c r="S30" s="17" t="n">
+      <c r="U30" s="17" t="n">
         <v>447.695</v>
       </c>
-      <c r="T30" s="14" t="inlineStr">
+      <c r="V30" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U30" s="14" t="inlineStr"/>
-      <c r="V30" s="14" t="inlineStr"/>
+      <c r="W30" s="14" t="inlineStr"/>
+      <c r="X30" s="14" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -2727,53 +2969,63 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>D · COMPOUNDER</t>
+          <t>🟢 LOW</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L31" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M31" s="14" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K31" s="16" t="n">
+      <c r="N31" s="16" t="n">
         <v>70.5</v>
       </c>
-      <c r="L31" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · quality intact</t>
-        </is>
-      </c>
-      <c r="M31" s="17" t="n">
+      <c r="O31" s="17" t="n">
         <v>1625.5</v>
       </c>
-      <c r="N31" s="17" t="n">
+      <c r="P31" s="17" t="n">
         <v>1657</v>
       </c>
-      <c r="O31" s="17" t="n"/>
-      <c r="P31" s="18" t="n">
+      <c r="Q31" s="17" t="n"/>
+      <c r="R31" s="18" t="n">
         <v>0.0194</v>
       </c>
-      <c r="Q31" s="17" t="n">
+      <c r="S31" s="17" t="n">
         <v>1544.225</v>
       </c>
-      <c r="R31" s="17" t="n">
+      <c r="T31" s="17" t="n">
         <v>1755.54</v>
       </c>
-      <c r="S31" s="17" t="n">
+      <c r="U31" s="17" t="n">
         <v>1869.325</v>
       </c>
-      <c r="T31" s="14" t="inlineStr">
+      <c r="V31" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U31" s="14" t="inlineStr"/>
-      <c r="V31" s="14" t="inlineStr"/>
+      <c r="W31" s="14" t="inlineStr"/>
+      <c r="X31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -2807,53 +3059,63 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L32" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="M32" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K32" s="16" t="n">
+      <c r="N32" s="16" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="L32" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M32" s="17" t="n">
+      <c r="O32" s="17" t="n">
         <v>1360.5</v>
       </c>
-      <c r="N32" s="17" t="n">
+      <c r="P32" s="17" t="n">
         <v>1378.5</v>
       </c>
-      <c r="O32" s="17" t="n"/>
-      <c r="P32" s="18" t="n">
+      <c r="Q32" s="17" t="n"/>
+      <c r="R32" s="18" t="n">
         <v>0.0132</v>
       </c>
-      <c r="Q32" s="17" t="n">
+      <c r="S32" s="17" t="n">
         <v>1292.475</v>
       </c>
-      <c r="R32" s="17" t="n">
+      <c r="T32" s="17" t="n">
         <v>1469.34</v>
       </c>
-      <c r="S32" s="17" t="n">
+      <c r="U32" s="17" t="n">
         <v>1564.575</v>
       </c>
-      <c r="T32" s="14" t="inlineStr">
+      <c r="V32" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U32" s="14" t="inlineStr"/>
-      <c r="V32" s="14" t="inlineStr"/>
+      <c r="W32" s="14" t="inlineStr"/>
+      <c r="X32" s="14" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -2887,53 +3149,63 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L33" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="M33" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K33" s="16" t="n">
+      <c r="N33" s="16" t="n">
         <v>64</v>
       </c>
-      <c r="L33" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M33" s="17" t="n">
+      <c r="O33" s="17" t="n">
         <v>282.9</v>
       </c>
-      <c r="N33" s="17" t="n">
+      <c r="P33" s="17" t="n">
         <v>285.8</v>
       </c>
-      <c r="O33" s="17" t="n"/>
-      <c r="P33" s="18" t="n">
+      <c r="Q33" s="17" t="n"/>
+      <c r="R33" s="18" t="n">
         <v>0.0103</v>
       </c>
-      <c r="Q33" s="17" t="n">
+      <c r="S33" s="17" t="n">
         <v>268.7549999999999</v>
       </c>
-      <c r="R33" s="17" t="n">
+      <c r="T33" s="17" t="n">
         <v>305.532</v>
       </c>
-      <c r="S33" s="17" t="n">
+      <c r="U33" s="17" t="n">
         <v>325.3349999999999</v>
       </c>
-      <c r="T33" s="14" t="inlineStr">
+      <c r="V33" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U33" s="14" t="inlineStr"/>
-      <c r="V33" s="14" t="inlineStr"/>
+      <c r="W33" s="14" t="inlineStr"/>
+      <c r="X33" s="14" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -2967,53 +3239,63 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="M34" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K34" s="16" t="n">
+      <c r="N34" s="16" t="n">
         <v>62.5</v>
       </c>
-      <c r="L34" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M34" s="17" t="n">
+      <c r="O34" s="17" t="n">
         <v>7454.5</v>
       </c>
-      <c r="N34" s="17" t="n">
+      <c r="P34" s="17" t="n">
         <v>7531.5</v>
       </c>
-      <c r="O34" s="17" t="n"/>
-      <c r="P34" s="18" t="n">
+      <c r="Q34" s="17" t="n"/>
+      <c r="R34" s="18" t="n">
         <v>0.0103</v>
       </c>
-      <c r="Q34" s="17" t="n">
+      <c r="S34" s="17" t="n">
         <v>7081.775</v>
       </c>
-      <c r="R34" s="17" t="n">
+      <c r="T34" s="17" t="n">
         <v>8050.860000000001</v>
       </c>
-      <c r="S34" s="17" t="n">
+      <c r="U34" s="17" t="n">
         <v>8572.674999999999</v>
       </c>
-      <c r="T34" s="14" t="inlineStr">
+      <c r="V34" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U34" s="14" t="inlineStr"/>
-      <c r="V34" s="14" t="inlineStr"/>
+      <c r="W34" s="14" t="inlineStr"/>
+      <c r="X34" s="14" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
@@ -3047,53 +3329,63 @@
       </c>
       <c r="H35" s="19" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I35" s="19" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L35" s="19" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J35" s="19" t="inlineStr">
+      <c r="M35" s="19" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K35" s="21" t="n">
+      <c r="N35" s="21" t="n">
         <v>64</v>
       </c>
-      <c r="L35" s="19" t="inlineStr">
-        <is>
-          <t>🟡 BUY SMALL · watch quality</t>
-        </is>
-      </c>
-      <c r="M35" s="22" t="n">
+      <c r="O35" s="22" t="n">
         <v>282.9</v>
       </c>
-      <c r="N35" s="22" t="n">
+      <c r="P35" s="22" t="n">
         <v>285.8</v>
       </c>
-      <c r="O35" s="22" t="n"/>
-      <c r="P35" s="23" t="n">
+      <c r="Q35" s="22" t="n"/>
+      <c r="R35" s="23" t="n">
         <v>0.0103</v>
       </c>
-      <c r="Q35" s="22" t="n">
+      <c r="S35" s="22" t="n">
         <v>271.51</v>
       </c>
-      <c r="R35" s="22" t="n">
+      <c r="T35" s="22" t="n">
         <v>287</v>
       </c>
-      <c r="S35" s="22" t="n">
+      <c r="U35" s="22" t="n">
         <v>307.09</v>
       </c>
-      <c r="T35" s="19" t="inlineStr">
+      <c r="V35" s="19" t="inlineStr">
         <is>
           <t>Enter or add · in buy zone</t>
         </is>
       </c>
-      <c r="U35" s="19" t="inlineStr"/>
-      <c r="V35" s="19" t="inlineStr"/>
+      <c r="W35" s="19" t="inlineStr"/>
+      <c r="X35" s="19" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -3127,53 +3419,63 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>D · COMPOUNDER</t>
+          <t>🟢 LOW</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L36" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M36" s="14" t="inlineStr">
         <is>
           <t>🏆 QUALITY</t>
         </is>
       </c>
-      <c r="K36" s="16" t="n">
+      <c r="N36" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="L36" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · patient · both endorse</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="n">
+      <c r="O36" s="17" t="n">
         <v>377</v>
       </c>
-      <c r="N36" s="17" t="n">
+      <c r="P36" s="17" t="n">
         <v>380.35</v>
       </c>
-      <c r="O36" s="17" t="n"/>
-      <c r="P36" s="18" t="n">
+      <c r="Q36" s="17" t="n"/>
+      <c r="R36" s="18" t="n">
         <v>0.0089</v>
       </c>
-      <c r="Q36" s="17" t="n">
+      <c r="S36" s="17" t="n">
         <v>358.15</v>
       </c>
-      <c r="R36" s="17" t="n">
+      <c r="T36" s="17" t="n">
         <v>407.16</v>
       </c>
-      <c r="S36" s="17" t="n">
+      <c r="U36" s="17" t="n">
         <v>433.55</v>
       </c>
-      <c r="T36" s="14" t="inlineStr">
+      <c r="V36" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U36" s="14" t="inlineStr"/>
-      <c r="V36" s="14" t="inlineStr"/>
+      <c r="W36" s="14" t="inlineStr"/>
+      <c r="X36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -3207,53 +3509,63 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>D · COMPOUNDER</t>
+          <t>🟢 LOW</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J37" s="14" t="inlineStr">
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L37" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M37" s="14" t="inlineStr">
         <is>
           <t>🏆 QUALITY</t>
         </is>
       </c>
-      <c r="K37" s="16" t="n">
+      <c r="N37" s="16" t="n">
         <v>83.90000000000001</v>
       </c>
-      <c r="L37" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · patient · both endorse</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="n">
+      <c r="O37" s="17" t="n">
         <v>1438.5</v>
       </c>
-      <c r="N37" s="17" t="n">
+      <c r="P37" s="17" t="n">
         <v>1449.6</v>
       </c>
-      <c r="O37" s="17" t="n"/>
-      <c r="P37" s="18" t="n">
+      <c r="Q37" s="17" t="n"/>
+      <c r="R37" s="18" t="n">
         <v>0.0077</v>
       </c>
-      <c r="Q37" s="17" t="n">
+      <c r="S37" s="17" t="n">
         <v>1366.575</v>
       </c>
-      <c r="R37" s="17" t="n">
+      <c r="T37" s="17" t="n">
         <v>1553.58</v>
       </c>
-      <c r="S37" s="17" t="n">
+      <c r="U37" s="17" t="n">
         <v>1654.275</v>
       </c>
-      <c r="T37" s="14" t="inlineStr">
+      <c r="V37" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U37" s="14" t="inlineStr"/>
-      <c r="V37" s="14" t="inlineStr"/>
+      <c r="W37" s="14" t="inlineStr"/>
+      <c r="X37" s="14" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -3287,53 +3599,63 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L38" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="M38" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K38" s="16" t="n">
+      <c r="N38" s="16" t="n">
         <v>60.2</v>
       </c>
-      <c r="L38" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M38" s="17" t="n">
+      <c r="O38" s="17" t="n">
         <v>2744.3</v>
       </c>
-      <c r="N38" s="17" t="n">
+      <c r="P38" s="17" t="n">
         <v>2764.2</v>
       </c>
-      <c r="O38" s="17" t="n"/>
-      <c r="P38" s="18" t="n">
+      <c r="Q38" s="17" t="n"/>
+      <c r="R38" s="18" t="n">
         <v>0.0073</v>
       </c>
-      <c r="Q38" s="17" t="n">
+      <c r="S38" s="17" t="n">
         <v>2607.085</v>
       </c>
-      <c r="R38" s="17" t="n">
+      <c r="T38" s="17" t="n">
         <v>2963.844000000001</v>
       </c>
-      <c r="S38" s="17" t="n">
+      <c r="U38" s="17" t="n">
         <v>3155.945</v>
       </c>
-      <c r="T38" s="14" t="inlineStr">
+      <c r="V38" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U38" s="14" t="inlineStr"/>
-      <c r="V38" s="14" t="inlineStr"/>
+      <c r="W38" s="14" t="inlineStr"/>
+      <c r="X38" s="14" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -3367,53 +3689,63 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>D · COMPOUNDER</t>
+          <t>🟢 LOW</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L39" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M39" s="14" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K39" s="16" t="n">
+      <c r="N39" s="16" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="L39" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · quality intact</t>
-        </is>
-      </c>
-      <c r="M39" s="17" t="n">
+      <c r="O39" s="17" t="n">
         <v>411.3</v>
       </c>
-      <c r="N39" s="17" t="n">
+      <c r="P39" s="17" t="n">
         <v>414.05</v>
       </c>
-      <c r="O39" s="17" t="n"/>
-      <c r="P39" s="18" t="n">
+      <c r="Q39" s="17" t="n"/>
+      <c r="R39" s="18" t="n">
         <v>0.0067</v>
       </c>
-      <c r="Q39" s="17" t="n">
+      <c r="S39" s="17" t="n">
         <v>390.735</v>
       </c>
-      <c r="R39" s="17" t="n">
+      <c r="T39" s="17" t="n">
         <v>444.2040000000001</v>
       </c>
-      <c r="S39" s="17" t="n">
+      <c r="U39" s="17" t="n">
         <v>472.995</v>
       </c>
-      <c r="T39" s="14" t="inlineStr">
+      <c r="V39" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U39" s="14" t="inlineStr"/>
-      <c r="V39" s="14" t="inlineStr"/>
+      <c r="W39" s="14" t="inlineStr"/>
+      <c r="X39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -3447,53 +3779,63 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>D · COMPOUNDER</t>
+          <t>🟢 LOW</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J40" s="14" t="inlineStr">
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L40" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K40" s="16" t="n">
+      <c r="N40" s="16" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="L40" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · quality intact</t>
-        </is>
-      </c>
-      <c r="M40" s="17" t="n">
+      <c r="O40" s="17" t="n">
         <v>411.3</v>
       </c>
-      <c r="N40" s="17" t="n">
+      <c r="P40" s="17" t="n">
         <v>414.05</v>
       </c>
-      <c r="O40" s="17" t="n"/>
-      <c r="P40" s="18" t="n">
+      <c r="Q40" s="17" t="n"/>
+      <c r="R40" s="18" t="n">
         <v>0.0067</v>
       </c>
-      <c r="Q40" s="17" t="n">
+      <c r="S40" s="17" t="n">
         <v>390.735</v>
       </c>
-      <c r="R40" s="17" t="n">
+      <c r="T40" s="17" t="n">
         <v>444.2040000000001</v>
       </c>
-      <c r="S40" s="17" t="n">
+      <c r="U40" s="17" t="n">
         <v>472.995</v>
       </c>
-      <c r="T40" s="14" t="inlineStr">
+      <c r="V40" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U40" s="14" t="inlineStr"/>
-      <c r="V40" s="14" t="inlineStr"/>
+      <c r="W40" s="14" t="inlineStr"/>
+      <c r="X40" s="14" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -3527,53 +3869,63 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L41" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr">
+      <c r="M41" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K41" s="16" t="n">
+      <c r="N41" s="16" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="L41" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M41" s="17" t="n">
+      <c r="O41" s="17" t="n">
         <v>5406</v>
       </c>
-      <c r="N41" s="17" t="n">
+      <c r="P41" s="17" t="n">
         <v>5429</v>
       </c>
-      <c r="O41" s="17" t="n"/>
-      <c r="P41" s="18" t="n">
+      <c r="Q41" s="17" t="n"/>
+      <c r="R41" s="18" t="n">
         <v>0.0043</v>
       </c>
-      <c r="Q41" s="17" t="n">
+      <c r="S41" s="17" t="n">
         <v>5135.7</v>
       </c>
-      <c r="R41" s="17" t="n">
+      <c r="T41" s="17" t="n">
         <v>5838.48</v>
       </c>
-      <c r="S41" s="17" t="n">
+      <c r="U41" s="17" t="n">
         <v>6216.9</v>
       </c>
-      <c r="T41" s="14" t="inlineStr">
+      <c r="V41" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U41" s="14" t="inlineStr"/>
-      <c r="V41" s="14" t="inlineStr"/>
+      <c r="W41" s="14" t="inlineStr"/>
+      <c r="X41" s="14" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
@@ -3607,53 +3959,63 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L42" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J42" s="14" t="inlineStr">
+      <c r="M42" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K42" s="16" t="n">
+      <c r="N42" s="16" t="n">
         <v>60.8</v>
       </c>
-      <c r="L42" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M42" s="17" t="n">
+      <c r="O42" s="17" t="n">
         <v>388.7</v>
       </c>
-      <c r="N42" s="17" t="n">
+      <c r="P42" s="17" t="n">
         <v>390.05</v>
       </c>
-      <c r="O42" s="17" t="n"/>
-      <c r="P42" s="18" t="n">
+      <c r="Q42" s="17" t="n"/>
+      <c r="R42" s="18" t="n">
         <v>0.0035</v>
       </c>
-      <c r="Q42" s="17" t="n">
+      <c r="S42" s="17" t="n">
         <v>369.265</v>
       </c>
-      <c r="R42" s="17" t="n">
+      <c r="T42" s="17" t="n">
         <v>419.796</v>
       </c>
-      <c r="S42" s="17" t="n">
+      <c r="U42" s="17" t="n">
         <v>447.0049999999999</v>
       </c>
-      <c r="T42" s="14" t="inlineStr">
+      <c r="V42" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U42" s="14" t="inlineStr"/>
-      <c r="V42" s="14" t="inlineStr"/>
+      <c r="W42" s="14" t="inlineStr"/>
+      <c r="X42" s="14" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
@@ -3687,53 +4049,63 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>F · SIGNAL WARNING</t>
+          <t>🟠 HIGH</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
+          <t>Signal Warning</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L43" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J43" s="14" t="inlineStr">
+      <c r="M43" s="14" t="inlineStr">
         <is>
           <t>✗ AVOID</t>
         </is>
       </c>
-      <c r="K43" s="16" t="n">
+      <c r="N43" s="16" t="n">
         <v>59.7</v>
       </c>
-      <c r="L43" s="14" t="inlineStr">
-        <is>
-          <t>🔴 REDUCE / EXIT · quality degraded</t>
-        </is>
-      </c>
-      <c r="M43" s="17" t="n">
+      <c r="O43" s="17" t="n">
         <v>345.75</v>
       </c>
-      <c r="N43" s="17" t="n">
+      <c r="P43" s="17" t="n">
         <v>346.9</v>
       </c>
-      <c r="O43" s="17" t="n"/>
-      <c r="P43" s="18" t="n">
+      <c r="Q43" s="17" t="n"/>
+      <c r="R43" s="18" t="n">
         <v>0.0033</v>
       </c>
-      <c r="Q43" s="17" t="n">
+      <c r="S43" s="17" t="n">
         <v>328.4625</v>
       </c>
-      <c r="R43" s="17" t="n">
+      <c r="T43" s="17" t="n">
         <v>373.41</v>
       </c>
-      <c r="S43" s="17" t="n">
+      <c r="U43" s="17" t="n">
         <v>397.6125</v>
       </c>
-      <c r="T43" s="14" t="inlineStr">
+      <c r="V43" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U43" s="14" t="inlineStr"/>
-      <c r="V43" s="14" t="inlineStr"/>
+      <c r="W43" s="14" t="inlineStr"/>
+      <c r="X43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
@@ -3767,53 +4139,63 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>E · WATCH</t>
+          <t>🟡 MEDIUM</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="L44" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J44" s="14" t="inlineStr">
+      <c r="M44" s="14" t="inlineStr">
         <is>
           <t>⚠ MARGINAL</t>
         </is>
       </c>
-      <c r="K44" s="16" t="n">
+      <c r="N44" s="16" t="n">
         <v>61.3</v>
       </c>
-      <c r="L44" s="14" t="inlineStr">
-        <is>
-          <t>🟡 HOLD · tighten stop · watching</t>
-        </is>
-      </c>
-      <c r="M44" s="17" t="n">
+      <c r="O44" s="17" t="n">
         <v>113.36</v>
       </c>
-      <c r="N44" s="17" t="n">
+      <c r="P44" s="17" t="n">
         <v>113.54</v>
       </c>
-      <c r="O44" s="17" t="n"/>
-      <c r="P44" s="18" t="n">
+      <c r="Q44" s="17" t="n"/>
+      <c r="R44" s="18" t="n">
         <v>0.0016</v>
       </c>
-      <c r="Q44" s="17" t="n">
+      <c r="S44" s="17" t="n">
         <v>107.692</v>
       </c>
-      <c r="R44" s="17" t="n">
+      <c r="T44" s="17" t="n">
         <v>122.4288</v>
       </c>
-      <c r="S44" s="17" t="n">
+      <c r="U44" s="17" t="n">
         <v>130.364</v>
       </c>
-      <c r="T44" s="14" t="inlineStr">
+      <c r="V44" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U44" s="14" t="inlineStr"/>
-      <c r="V44" s="14" t="inlineStr"/>
+      <c r="W44" s="14" t="inlineStr"/>
+      <c r="X44" s="14" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
@@ -3847,53 +4229,63 @@
       </c>
       <c r="H45" s="24" t="inlineStr">
         <is>
-          <t>B · CONFIRMED BUY</t>
+          <t>🟠 HIGH</t>
         </is>
       </c>
       <c r="I45" s="24" t="inlineStr">
         <is>
+          <t>Confirmed Buy</t>
+        </is>
+      </c>
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="L45" s="24" t="inlineStr">
+        <is>
           <t>STRONG BUY</t>
         </is>
       </c>
-      <c r="J45" s="24" t="inlineStr">
+      <c r="M45" s="24" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K45" s="26" t="n">
+      <c r="N45" s="26" t="n">
         <v>79.8</v>
       </c>
-      <c r="L45" s="24" t="inlineStr">
-        <is>
-          <t>🟢 BUY · engine + quality aligned</t>
-        </is>
-      </c>
-      <c r="M45" s="27" t="n">
+      <c r="O45" s="27" t="n">
         <v>553.3</v>
       </c>
-      <c r="N45" s="27" t="n">
+      <c r="P45" s="27" t="n">
         <v>553.3</v>
       </c>
-      <c r="O45" s="27" t="n"/>
-      <c r="P45" s="28" t="n">
+      <c r="Q45" s="27" t="n"/>
+      <c r="R45" s="28" t="n">
         <v>-0</v>
       </c>
-      <c r="Q45" s="27" t="n">
+      <c r="S45" s="27" t="n">
         <v>520.1</v>
       </c>
-      <c r="R45" s="27" t="n">
+      <c r="T45" s="27" t="n">
         <v>619.7</v>
       </c>
-      <c r="S45" s="27" t="n">
+      <c r="U45" s="27" t="n">
         <v>686.09</v>
       </c>
-      <c r="T45" s="24" t="inlineStr">
+      <c r="V45" s="24" t="inlineStr">
         <is>
           <t>Enter today · top pick · high conviction</t>
         </is>
       </c>
-      <c r="U45" s="24" t="inlineStr"/>
-      <c r="V45" s="24" t="inlineStr"/>
+      <c r="W45" s="24" t="inlineStr"/>
+      <c r="X45" s="24" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -3927,53 +4319,63 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>G · STRUCTURAL FAILURE</t>
+          <t>🔴 HIGH</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
+          <t>Structural Failure</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>IMMEDIATE</t>
+        </is>
+      </c>
+      <c r="L46" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J46" s="14" t="inlineStr">
+      <c r="M46" s="14" t="inlineStr">
         <is>
           <t>✗ AVOID</t>
         </is>
       </c>
-      <c r="K46" s="16" t="n">
+      <c r="N46" s="16" t="n">
         <v>56.1</v>
       </c>
-      <c r="L46" s="14" t="inlineStr">
-        <is>
-          <t>🔴 REDUCE / EXIT · quality degraded</t>
-        </is>
-      </c>
-      <c r="M46" s="17" t="n">
+      <c r="O46" s="17" t="n">
         <v>381.6</v>
       </c>
-      <c r="N46" s="17" t="n">
+      <c r="P46" s="17" t="n">
         <v>378.9</v>
       </c>
-      <c r="O46" s="17" t="n"/>
-      <c r="P46" s="18" t="n">
+      <c r="Q46" s="17" t="n"/>
+      <c r="R46" s="18" t="n">
         <v>-0.0071</v>
       </c>
-      <c r="Q46" s="17" t="n">
+      <c r="S46" s="17" t="n">
         <v>362.52</v>
       </c>
-      <c r="R46" s="17" t="n">
+      <c r="T46" s="17" t="n">
         <v>412.128</v>
       </c>
-      <c r="S46" s="17" t="n">
+      <c r="U46" s="17" t="n">
         <v>438.84</v>
       </c>
-      <c r="T46" s="14" t="inlineStr">
+      <c r="V46" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U46" s="14" t="inlineStr"/>
-      <c r="V46" s="14" t="inlineStr"/>
+      <c r="W46" s="14" t="inlineStr"/>
+      <c r="X46" s="14" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -4007,53 +4409,63 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>G · STRUCTURAL FAILURE</t>
+          <t>🔴 HIGH</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
+          <t>Structural Failure</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>IMMEDIATE</t>
+        </is>
+      </c>
+      <c r="L47" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J47" s="14" t="inlineStr">
+      <c r="M47" s="14" t="inlineStr">
         <is>
           <t>✗ AVOID</t>
         </is>
       </c>
-      <c r="K47" s="16" t="n">
+      <c r="N47" s="16" t="n">
         <v>58.9</v>
       </c>
-      <c r="L47" s="14" t="inlineStr">
-        <is>
-          <t>🔴 REDUCE / EXIT · quality degraded</t>
-        </is>
-      </c>
-      <c r="M47" s="17" t="n">
+      <c r="O47" s="17" t="n">
         <v>391.3</v>
       </c>
-      <c r="N47" s="17" t="n">
+      <c r="P47" s="17" t="n">
         <v>387.9</v>
       </c>
-      <c r="O47" s="17" t="n"/>
-      <c r="P47" s="18" t="n">
+      <c r="Q47" s="17" t="n"/>
+      <c r="R47" s="18" t="n">
         <v>-0.008699999999999999</v>
       </c>
-      <c r="Q47" s="17" t="n">
+      <c r="S47" s="17" t="n">
         <v>371.735</v>
       </c>
-      <c r="R47" s="17" t="n">
+      <c r="T47" s="17" t="n">
         <v>422.604</v>
       </c>
-      <c r="S47" s="17" t="n">
+      <c r="U47" s="17" t="n">
         <v>449.995</v>
       </c>
-      <c r="T47" s="14" t="inlineStr">
+      <c r="V47" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U47" s="14" t="inlineStr"/>
-      <c r="V47" s="14" t="inlineStr"/>
+      <c r="W47" s="14" t="inlineStr"/>
+      <c r="X47" s="14" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
@@ -4087,53 +4499,63 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>C · QUALITY DIP · ADD</t>
+          <t>🟠 HIGH</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
+          <t>Quality Dip</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="L48" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J48" s="14" t="inlineStr">
+      <c r="M48" s="14" t="inlineStr">
         <is>
           <t>🏆 QUALITY</t>
         </is>
       </c>
-      <c r="K48" s="16" t="n">
+      <c r="N48" s="16" t="n">
         <v>83.8</v>
       </c>
-      <c r="L48" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · patient · both endorse</t>
-        </is>
-      </c>
-      <c r="M48" s="17" t="n">
+      <c r="O48" s="17" t="n">
         <v>2417</v>
       </c>
-      <c r="N48" s="17" t="n">
+      <c r="P48" s="17" t="n">
         <v>2390.4</v>
       </c>
-      <c r="O48" s="17" t="n"/>
-      <c r="P48" s="18" t="n">
+      <c r="Q48" s="17" t="n"/>
+      <c r="R48" s="18" t="n">
         <v>-0.011</v>
       </c>
-      <c r="Q48" s="17" t="n">
+      <c r="S48" s="17" t="n">
         <v>2296.15</v>
       </c>
-      <c r="R48" s="17" t="n">
+      <c r="T48" s="17" t="n">
         <v>2610.36</v>
       </c>
-      <c r="S48" s="17" t="n">
+      <c r="U48" s="17" t="n">
         <v>2779.55</v>
       </c>
-      <c r="T48" s="14" t="inlineStr">
+      <c r="V48" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U48" s="14" t="inlineStr"/>
-      <c r="V48" s="14" t="inlineStr"/>
+      <c r="W48" s="14" t="inlineStr"/>
+      <c r="X48" s="14" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
@@ -4167,53 +4589,63 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>C · QUALITY DIP · ADD</t>
+          <t>🟠 HIGH</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
+          <t>Quality Dip</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="K49" s="14" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="L49" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J49" s="14" t="inlineStr">
+      <c r="M49" s="14" t="inlineStr">
         <is>
           <t>🏆 QUALITY</t>
         </is>
       </c>
-      <c r="K49" s="16" t="n">
+      <c r="N49" s="16" t="n">
         <v>83.8</v>
       </c>
-      <c r="L49" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · patient · both endorse</t>
-        </is>
-      </c>
-      <c r="M49" s="17" t="n">
+      <c r="O49" s="17" t="n">
         <v>2417</v>
       </c>
-      <c r="N49" s="17" t="n">
+      <c r="P49" s="17" t="n">
         <v>2390.4</v>
       </c>
-      <c r="O49" s="17" t="n"/>
-      <c r="P49" s="18" t="n">
+      <c r="Q49" s="17" t="n"/>
+      <c r="R49" s="18" t="n">
         <v>-0.011</v>
       </c>
-      <c r="Q49" s="17" t="n">
+      <c r="S49" s="17" t="n">
         <v>2296.15</v>
       </c>
-      <c r="R49" s="17" t="n">
+      <c r="T49" s="17" t="n">
         <v>2610.36</v>
       </c>
-      <c r="S49" s="17" t="n">
+      <c r="U49" s="17" t="n">
         <v>2779.55</v>
       </c>
-      <c r="T49" s="14" t="inlineStr">
+      <c r="V49" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U49" s="14" t="inlineStr"/>
-      <c r="V49" s="14" t="inlineStr"/>
+      <c r="W49" s="14" t="inlineStr"/>
+      <c r="X49" s="14" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
@@ -4247,53 +4679,63 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>C · QUALITY DIP · ADD</t>
+          <t>🟠 HIGH</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
+          <t>Quality Dip</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="K50" s="14" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="L50" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="M50" s="14" t="inlineStr">
         <is>
           <t>✓ OK</t>
         </is>
       </c>
-      <c r="K50" s="16" t="n">
+      <c r="N50" s="16" t="n">
         <v>76.8</v>
       </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · quality intact</t>
-        </is>
-      </c>
-      <c r="M50" s="17" t="n">
+      <c r="O50" s="17" t="n">
         <v>133.1</v>
       </c>
-      <c r="N50" s="17" t="n">
+      <c r="P50" s="17" t="n">
         <v>129.61</v>
       </c>
-      <c r="O50" s="17" t="n"/>
-      <c r="P50" s="18" t="n">
+      <c r="Q50" s="17" t="n"/>
+      <c r="R50" s="18" t="n">
         <v>-0.0262</v>
       </c>
-      <c r="Q50" s="17" t="n">
+      <c r="S50" s="17" t="n">
         <v>126.445</v>
       </c>
-      <c r="R50" s="17" t="n">
+      <c r="T50" s="17" t="n">
         <v>143.748</v>
       </c>
-      <c r="S50" s="17" t="n">
+      <c r="U50" s="17" t="n">
         <v>153.065</v>
       </c>
-      <c r="T50" s="14" t="inlineStr">
+      <c r="V50" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U50" s="14" t="inlineStr"/>
-      <c r="V50" s="14" t="inlineStr"/>
+      <c r="W50" s="14" t="inlineStr"/>
+      <c r="X50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
@@ -4327,53 +4769,63 @@
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>G · STRUCTURAL FAILURE</t>
+          <t>🔴 HIGH</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
+          <t>Structural Failure</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="inlineStr">
+        <is>
+          <t>IMMEDIATE</t>
+        </is>
+      </c>
+      <c r="L51" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J51" s="14" t="inlineStr">
+      <c r="M51" s="14" t="inlineStr">
         <is>
           <t>✗ AVOID</t>
         </is>
       </c>
-      <c r="K51" s="16" t="n">
+      <c r="N51" s="16" t="n">
         <v>59.2</v>
       </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>🔴 REDUCE / EXIT · quality degraded</t>
-        </is>
-      </c>
-      <c r="M51" s="17" t="n">
+      <c r="O51" s="17" t="n">
         <v>285.9</v>
       </c>
-      <c r="N51" s="17" t="n">
+      <c r="P51" s="17" t="n">
         <v>276.8</v>
       </c>
-      <c r="O51" s="17" t="n"/>
-      <c r="P51" s="18" t="n">
+      <c r="Q51" s="17" t="n"/>
+      <c r="R51" s="18" t="n">
         <v>-0.0318</v>
       </c>
-      <c r="Q51" s="17" t="n">
+      <c r="S51" s="17" t="n">
         <v>271.605</v>
       </c>
-      <c r="R51" s="17" t="n">
+      <c r="T51" s="17" t="n">
         <v>308.772</v>
       </c>
-      <c r="S51" s="17" t="n">
+      <c r="U51" s="17" t="n">
         <v>328.785</v>
       </c>
-      <c r="T51" s="14" t="inlineStr">
+      <c r="V51" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U51" s="14" t="inlineStr"/>
-      <c r="V51" s="14" t="inlineStr"/>
+      <c r="W51" s="14" t="inlineStr"/>
+      <c r="X51" s="14" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
@@ -4407,53 +4859,63 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>C · QUALITY DIP · ADD</t>
+          <t>🟠 HIGH</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
+          <t>Quality Dip</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="K52" s="14" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="L52" s="14" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J52" s="14" t="inlineStr">
+      <c r="M52" s="14" t="inlineStr">
         <is>
           <t>🏆 QUALITY</t>
         </is>
       </c>
-      <c r="K52" s="16" t="n">
+      <c r="N52" s="16" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="L52" s="14" t="inlineStr">
-        <is>
-          <t>🟢 HOLD · patient · both endorse</t>
-        </is>
-      </c>
-      <c r="M52" s="17" t="n">
+      <c r="O52" s="17" t="n">
         <v>2014.8</v>
       </c>
-      <c r="N52" s="17" t="n">
+      <c r="P52" s="17" t="n">
         <v>1949</v>
       </c>
-      <c r="O52" s="17" t="n"/>
-      <c r="P52" s="18" t="n">
+      <c r="Q52" s="17" t="n"/>
+      <c r="R52" s="18" t="n">
         <v>-0.0327</v>
       </c>
-      <c r="Q52" s="17" t="n">
+      <c r="S52" s="17" t="n">
         <v>1914.06</v>
       </c>
-      <c r="R52" s="17" t="n">
+      <c r="T52" s="17" t="n">
         <v>2175.984</v>
       </c>
-      <c r="S52" s="17" t="n">
+      <c r="U52" s="17" t="n">
         <v>2317.02</v>
       </c>
-      <c r="T52" s="14" t="inlineStr">
+      <c r="V52" s="14" t="inlineStr">
         <is>
           <t>Hold · no action needed today</t>
         </is>
       </c>
-      <c r="U52" s="14" t="inlineStr"/>
-      <c r="V52" s="14" t="inlineStr"/>
+      <c r="W52" s="14" t="inlineStr"/>
+      <c r="X52" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -6984,7 +6984,9 @@
       <c r="AK2" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="AL2" s="35" t="n"/>
+      <c r="AL2" s="35" t="n">
+        <v>2398</v>
+      </c>
       <c r="AM2" s="35" t="n">
         <v>-0.59</v>
       </c>
@@ -7187,7 +7189,9 @@
       <c r="AK3" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="AL3" s="35" t="n"/>
+      <c r="AL3" s="35" t="n">
+        <v>5438</v>
+      </c>
       <c r="AM3" s="35" t="n">
         <v>0.6</v>
       </c>
@@ -7390,7 +7394,9 @@
       <c r="AK4" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="AL4" s="36" t="n"/>
+      <c r="AL4" s="36" t="n">
+        <v>444.8</v>
+      </c>
       <c r="AM4" s="36" t="n">
         <v>1.7</v>
       </c>
@@ -7589,7 +7595,9 @@
       <c r="AK5" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL5" s="37" t="n"/>
+      <c r="AL5" s="37" t="n">
+        <v>112.84</v>
+      </c>
       <c r="AM5" s="37" t="n">
         <v>0.46</v>
       </c>
@@ -7786,7 +7794,9 @@
       <c r="AK6" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL6" s="37" t="n"/>
+      <c r="AL6" s="37" t="n">
+        <v>414.75</v>
+      </c>
       <c r="AM6" s="37" t="n">
         <v>0.1</v>
       </c>
@@ -7983,7 +7993,9 @@
       <c r="AK7" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL7" s="37" t="n"/>
+      <c r="AL7" s="37" t="n">
+        <v>267.2</v>
+      </c>
       <c r="AM7" s="37" t="n">
         <v>0.49</v>
       </c>
@@ -8184,7 +8196,9 @@
       <c r="AK8" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL8" s="37" t="n"/>
+      <c r="AL8" s="37" t="n">
+        <v>291.9</v>
+      </c>
       <c r="AM8" s="37" t="n">
         <v>-2.42</v>
       </c>
@@ -8385,7 +8399,9 @@
       <c r="AK9" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL9" s="37" t="n"/>
+      <c r="AL9" s="37" t="n">
+        <v>1348.3</v>
+      </c>
       <c r="AM9" s="37" t="n">
         <v>1.13</v>
       </c>
@@ -8586,7 +8602,9 @@
       <c r="AK10" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL10" s="37" t="n"/>
+      <c r="AL10" s="37" t="n">
+        <v>2393.6</v>
+      </c>
       <c r="AM10" s="37" t="n">
         <v>1.91</v>
       </c>
@@ -8783,7 +8801,9 @@
       <c r="AK11" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL11" s="37" t="n"/>
+      <c r="AL11" s="37" t="n">
+        <v>543.2</v>
+      </c>
       <c r="AM11" s="37" t="n">
         <v>1.69</v>
       </c>
@@ -8990,7 +9010,9 @@
       <c r="AK12" s="38" t="n">
         <v>15</v>
       </c>
-      <c r="AL12" s="38" t="n"/>
+      <c r="AL12" s="38" t="n">
+        <v>425.1</v>
+      </c>
       <c r="AM12" s="38" t="n">
         <v>-0.01</v>
       </c>
@@ -9197,7 +9219,9 @@
       <c r="AK13" s="38" t="n">
         <v>15</v>
       </c>
-      <c r="AL13" s="38" t="n"/>
+      <c r="AL13" s="38" t="n">
+        <v>961.7</v>
+      </c>
       <c r="AM13" s="38" t="n">
         <v>-2.26</v>
       </c>
@@ -9404,7 +9428,9 @@
       <c r="AK14" s="38" t="n">
         <v>15</v>
       </c>
-      <c r="AL14" s="38" t="n"/>
+      <c r="AL14" s="38" t="n">
+        <v>567</v>
+      </c>
       <c r="AM14" s="38" t="n">
         <v>0.05</v>
       </c>
@@ -9595,7 +9621,9 @@
       <c r="AK15" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL15" s="39" t="n"/>
+      <c r="AL15" s="39" t="n">
+        <v>7465</v>
+      </c>
       <c r="AM15" s="39" t="n">
         <v>-0.14</v>
       </c>
@@ -9786,7 +9814,9 @@
       <c r="AK16" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL16" s="39" t="n"/>
+      <c r="AL16" s="39" t="n">
+        <v>699.25</v>
+      </c>
       <c r="AM16" s="39" t="n">
         <v>1.39</v>
       </c>
@@ -9973,7 +10003,9 @@
       <c r="AK17" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="AL17" s="35" t="n"/>
+      <c r="AL17" s="35" t="n">
+        <v>1942.9</v>
+      </c>
       <c r="AM17" s="35" t="n">
         <v>0.64</v>
       </c>
@@ -10168,7 +10200,9 @@
       <c r="AK18" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="AL18" s="35" t="n"/>
+      <c r="AL18" s="35" t="n">
+        <v>1448.3</v>
+      </c>
       <c r="AM18" s="35" t="n">
         <v>0.08</v>
       </c>
@@ -10363,7 +10397,9 @@
       <c r="AK19" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="AL19" s="35" t="n"/>
+      <c r="AL19" s="35" t="n">
+        <v>1633.8</v>
+      </c>
       <c r="AM19" s="35" t="n">
         <v>0.53</v>
       </c>
@@ -10558,7 +10594,9 @@
       <c r="AK20" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="AL20" s="35" t="n"/>
+      <c r="AL20" s="35" t="n">
+        <v>347.55</v>
+      </c>
       <c r="AM20" s="35" t="n">
         <v>-0.09</v>
       </c>
@@ -10749,7 +10787,9 @@
       <c r="AK21" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="AL21" s="36" t="n"/>
+      <c r="AL21" s="36" t="n">
+        <v>392.7</v>
+      </c>
       <c r="AM21" s="36" t="n">
         <v>1.09</v>
       </c>
@@ -10940,7 +10980,9 @@
       <c r="AK22" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="AL22" s="36" t="n"/>
+      <c r="AL22" s="36" t="n">
+        <v>382.25</v>
+      </c>
       <c r="AM22" s="36" t="n">
         <v>-0.17</v>
       </c>
@@ -11131,7 +11173,9 @@
       <c r="AK23" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL23" s="37" t="n"/>
+      <c r="AL23" s="37" t="n">
+        <v>501.4</v>
+      </c>
       <c r="AM23" s="37" t="n">
         <v>1.3</v>
       </c>
@@ -11326,7 +11370,9 @@
       <c r="AK24" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="AL24" s="36" t="n"/>
+      <c r="AL24" s="36" t="n">
+        <v>390.3</v>
+      </c>
       <c r="AM24" s="36" t="n">
         <v>-0.12</v>
       </c>
@@ -11517,7 +11563,9 @@
       <c r="AK25" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL25" s="37" t="n"/>
+      <c r="AL25" s="37" t="n">
+        <v>5452</v>
+      </c>
       <c r="AM25" s="37" t="n">
         <v>0.05</v>
       </c>
@@ -11726,7 +11774,9 @@
       <c r="AK26" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL26" s="37" t="n"/>
+      <c r="AL26" s="37" t="n">
+        <v>2439.4</v>
+      </c>
       <c r="AM26" s="37" t="n">
         <v>0.84</v>
       </c>
@@ -11939,7 +11989,9 @@
       <c r="AK27" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL27" s="37" t="n"/>
+      <c r="AL27" s="37" t="n">
+        <v>1363.6</v>
+      </c>
       <c r="AM27" s="37" t="n">
         <v>0.46</v>
       </c>
@@ -12148,7 +12200,9 @@
       <c r="AK28" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL28" s="37" t="n"/>
+      <c r="AL28" s="37" t="n">
+        <v>11486</v>
+      </c>
       <c r="AM28" s="37" t="n">
         <v>0.99</v>
       </c>
@@ -12359,7 +12413,9 @@
       <c r="AK29" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL29" s="39" t="n"/>
+      <c r="AL29" s="39" t="n">
+        <v>6807</v>
+      </c>
       <c r="AM29" s="39" t="n">
         <v>-0.2</v>
       </c>
@@ -12558,7 +12614,9 @@
       <c r="AK30" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL30" s="39" t="n"/>
+      <c r="AL30" s="39" t="n">
+        <v>841.9</v>
+      </c>
       <c r="AM30" s="39" t="n">
         <v>0.37</v>
       </c>
@@ -12759,7 +12817,9 @@
       <c r="AK31" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL31" s="37" t="n"/>
+      <c r="AL31" s="37" t="n">
+        <v>5470.5</v>
+      </c>
       <c r="AM31" s="37" t="n">
         <v>1.42</v>
       </c>
@@ -12970,7 +13030,9 @@
       <c r="AK32" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL32" s="39" t="n"/>
+      <c r="AL32" s="39" t="n">
+        <v>374</v>
+      </c>
       <c r="AM32" s="39" t="n">
         <v>0.8</v>
       </c>
@@ -13169,7 +13231,9 @@
       <c r="AK33" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL33" s="39" t="n"/>
+      <c r="AL33" s="39" t="n">
+        <v>450.55</v>
+      </c>
       <c r="AM33" s="39" t="n">
         <v>-0.12</v>
       </c>
@@ -13368,12 +13432,14 @@
       <c r="AK34" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL34" s="39" t="n"/>
+      <c r="AL34" s="39" t="n">
+        <v>397.25</v>
+      </c>
       <c r="AM34" s="39" t="n">
         <v>-1.5</v>
       </c>
       <c r="AN34" s="39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO34" s="39" t="n">
         <v>0</v>
@@ -13565,7 +13631,9 @@
       <c r="AK35" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL35" s="37" t="n"/>
+      <c r="AL35" s="37" t="n">
+        <v>11538</v>
+      </c>
       <c r="AM35" s="37" t="n">
         <v>-0.55</v>
       </c>
@@ -13776,12 +13844,14 @@
       <c r="AK36" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL36" s="39" t="n"/>
+      <c r="AL36" s="39" t="n">
+        <v>1333</v>
+      </c>
       <c r="AM36" s="39" t="n">
         <v>-0.4</v>
       </c>
       <c r="AN36" s="39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO36" s="39" t="n">
         <v>0</v>
@@ -13975,7 +14045,9 @@
       <c r="AK37" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL37" s="39" t="n"/>
+      <c r="AL37" s="39" t="n">
+        <v>2783.7</v>
+      </c>
       <c r="AM37" s="39" t="n">
         <v>-1.42</v>
       </c>
@@ -14174,7 +14246,9 @@
       <c r="AK38" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL38" s="39" t="n"/>
+      <c r="AL38" s="39" t="n">
+        <v>1629.9</v>
+      </c>
       <c r="AM38" s="39" t="n">
         <v>-2.14</v>
       </c>
@@ -14365,7 +14439,9 @@
       <c r="AK39" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="AL39" s="35" t="n"/>
+      <c r="AL39" s="35" t="n">
+        <v>1449.5</v>
+      </c>
       <c r="AM39" s="35" t="n">
         <v>0.35</v>
       </c>
@@ -14564,7 +14640,9 @@
       <c r="AK40" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="AL40" s="35" t="n"/>
+      <c r="AL40" s="35" t="n">
+        <v>1955.3</v>
+      </c>
       <c r="AM40" s="35" t="n">
         <v>0.44</v>
       </c>
@@ -14763,7 +14841,9 @@
       <c r="AK41" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="AL41" s="35" t="n"/>
+      <c r="AL41" s="35" t="n">
+        <v>1642.5</v>
+      </c>
       <c r="AM41" s="35" t="n">
         <v>-1.37</v>
       </c>
@@ -14962,7 +15042,9 @@
       <c r="AK42" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="AL42" s="35" t="n"/>
+      <c r="AL42" s="35" t="n">
+        <v>2383.9</v>
+      </c>
       <c r="AM42" s="35" t="n">
         <v>1.09</v>
       </c>
@@ -15161,7 +15243,9 @@
       <c r="AK43" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="AL43" s="35" t="n"/>
+      <c r="AL43" s="35" t="n">
+        <v>347.25</v>
+      </c>
       <c r="AM43" s="35" t="n">
         <v>-1.04</v>
       </c>
@@ -15356,7 +15440,9 @@
       <c r="AK44" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="AL44" s="36" t="n"/>
+      <c r="AL44" s="36" t="n">
+        <v>397</v>
+      </c>
       <c r="AM44" s="36" t="n">
         <v>0.25</v>
       </c>
@@ -15555,7 +15641,9 @@
       <c r="AK45" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="AL45" s="36" t="n"/>
+      <c r="AL45" s="36" t="n">
+        <v>285.85</v>
+      </c>
       <c r="AM45" s="36" t="n">
         <v>-0.86</v>
       </c>
@@ -15746,7 +15834,9 @@
       <c r="AK46" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="AL46" s="36" t="n"/>
+      <c r="AL46" s="36" t="n">
+        <v>284.85</v>
+      </c>
       <c r="AM46" s="36" t="n">
         <v>1.46</v>
       </c>
@@ -15945,7 +16035,9 @@
       <c r="AK47" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL47" s="37" t="n"/>
+      <c r="AL47" s="37" t="n">
+        <v>507.9</v>
+      </c>
       <c r="AM47" s="37" t="n">
         <v>0.46</v>
       </c>
@@ -16144,7 +16236,9 @@
       <c r="AK48" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="AL48" s="36" t="n"/>
+      <c r="AL48" s="36" t="n">
+        <v>389.85</v>
+      </c>
       <c r="AM48" s="36" t="n">
         <v>0.42</v>
       </c>
@@ -16339,7 +16433,9 @@
       <c r="AK49" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL49" s="37" t="n"/>
+      <c r="AL49" s="37" t="n">
+        <v>5454.5</v>
+      </c>
       <c r="AM49" s="37" t="n">
         <v>0.43</v>
       </c>
@@ -16538,7 +16634,9 @@
       <c r="AK50" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="AL50" s="36" t="n"/>
+      <c r="AL50" s="36" t="n">
+        <v>415.15</v>
+      </c>
       <c r="AM50" s="36" t="n">
         <v>0.59</v>
       </c>
@@ -16743,7 +16841,9 @@
       <c r="AK51" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL51" s="37" t="n"/>
+      <c r="AL51" s="37" t="n">
+        <v>127.5</v>
+      </c>
       <c r="AM51" s="37" t="n">
         <v>1.33</v>
       </c>
@@ -16952,7 +17052,9 @@
       <c r="AK52" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL52" s="37" t="n"/>
+      <c r="AL52" s="37" t="n">
+        <v>5485</v>
+      </c>
       <c r="AM52" s="37" t="n">
         <v>0.26</v>
       </c>
@@ -17161,7 +17263,9 @@
       <c r="AK53" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL53" s="37" t="n"/>
+      <c r="AL53" s="37" t="n">
+        <v>1165.1</v>
+      </c>
       <c r="AM53" s="37" t="n">
         <v>0.21</v>
       </c>
@@ -17374,7 +17478,9 @@
       <c r="AK54" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL54" s="37" t="n"/>
+      <c r="AL54" s="37" t="n">
+        <v>452.35</v>
+      </c>
       <c r="AM54" s="37" t="n">
         <v>0.5</v>
       </c>
@@ -17587,7 +17693,9 @@
       <c r="AK55" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL55" s="37" t="n"/>
+      <c r="AL55" s="37" t="n">
+        <v>284.85</v>
+      </c>
       <c r="AM55" s="37" t="n">
         <v>1.46</v>
       </c>
@@ -17796,7 +17904,9 @@
       <c r="AK56" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL56" s="37" t="n"/>
+      <c r="AL56" s="37" t="n">
+        <v>2200.5</v>
+      </c>
       <c r="AM56" s="37" t="n">
         <v>-0.25</v>
       </c>
@@ -18005,7 +18115,9 @@
       <c r="AK57" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL57" s="37" t="n"/>
+      <c r="AL57" s="37" t="n">
+        <v>1405.3</v>
+      </c>
       <c r="AM57" s="37" t="n">
         <v>-1.52</v>
       </c>
@@ -18672,9 +18784,11 @@
       <c r="AK60" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL60" s="37" t="n"/>
+      <c r="AL60" s="37" t="n">
+        <v>129.2</v>
+      </c>
       <c r="AM60" s="37" t="n">
-        <v>1.33</v>
+        <v>0.32</v>
       </c>
       <c r="AN60" s="37" t="n">
         <v>-2.62</v>
@@ -18885,9 +18999,11 @@
       <c r="AK61" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL61" s="37" t="n"/>
+      <c r="AL61" s="37" t="n">
+        <v>5499</v>
+      </c>
       <c r="AM61" s="37" t="n">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="AN61" s="37" t="n">
         <v>3.95</v>
@@ -19753,9 +19869,11 @@
       <c r="AK65" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL65" s="37" t="n"/>
+      <c r="AL65" s="37" t="n">
+        <v>454.6</v>
+      </c>
       <c r="AM65" s="37" t="n">
-        <v>0.5</v>
+        <v>1.09</v>
       </c>
       <c r="AN65" s="37" t="n">
         <v>3.65</v>
@@ -19970,9 +20088,11 @@
       <c r="AK66" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL66" s="37" t="n"/>
+      <c r="AL66" s="37" t="n">
+        <v>289</v>
+      </c>
       <c r="AM66" s="37" t="n">
-        <v>1.46</v>
+        <v>-1.11</v>
       </c>
       <c r="AN66" s="37" t="n">
         <v>1.03</v>
@@ -20183,9 +20303,11 @@
       <c r="AK67" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL67" s="37" t="n"/>
+      <c r="AL67" s="37" t="n">
+        <v>11475</v>
+      </c>
       <c r="AM67" s="37" t="n">
-        <v>-0.55</v>
+        <v>-0.17</v>
       </c>
       <c r="AN67" s="37" t="n">
         <v>2.96</v>
@@ -20609,9 +20731,11 @@
       <c r="AK69" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="AL69" s="37" t="n"/>
+      <c r="AL69" s="37" t="n">
+        <v>1384</v>
+      </c>
       <c r="AM69" s="37" t="n">
-        <v>-1.52</v>
+        <v>-0.4</v>
       </c>
       <c r="AN69" s="37" t="n">
         <v>1.32</v>
@@ -21041,7 +21165,9 @@
       <c r="AK71" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="AL71" s="39" t="n"/>
+      <c r="AL71" s="39" t="n">
+        <v>482</v>
+      </c>
       <c r="AM71" s="39" t="n">
         <v>-2.24</v>
       </c>
@@ -21249,7 +21375,7 @@
         <v>6.46</v>
       </c>
       <c r="AN72" s="35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO72" s="35" t="n">
         <v>0</v>
@@ -24685,10 +24811,10 @@
         <v>27.72</v>
       </c>
       <c r="AL90" s="35" t="n">
-        <v>2460</v>
+        <v>2421.9</v>
       </c>
       <c r="AM90" s="35" t="n">
-        <v>-1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AN90" s="35" t="n">
         <v>4.31</v>
@@ -24906,10 +25032,10 @@
         <v>31.3</v>
       </c>
       <c r="AL91" s="36" t="n">
-        <v>11600</v>
+        <v>11727</v>
       </c>
       <c r="AM91" s="36" t="n">
-        <v>1.09</v>
+        <v>0.67</v>
       </c>
       <c r="AN91" s="36" t="n">
         <v>6.59</v>
@@ -25115,10 +25241,10 @@
         <v>15</v>
       </c>
       <c r="AL92" s="37" t="n">
-        <v>2410</v>
+        <v>2390.4</v>
       </c>
       <c r="AM92" s="37" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.13</v>
       </c>
       <c r="AN92" s="37" t="n">
         <v>-2.21</v>
@@ -25318,10 +25444,10 @@
         <v>15</v>
       </c>
       <c r="AL93" s="37" t="n">
-        <v>454.6</v>
+        <v>459.55</v>
       </c>
       <c r="AM93" s="37" t="n">
-        <v>1.09</v>
+        <v>-1.93</v>
       </c>
       <c r="AN93" s="37" t="n">
         <v>1.66</v>
@@ -25521,10 +25647,10 @@
         <v>15</v>
       </c>
       <c r="AL94" s="37" t="n">
-        <v>113.99</v>
+        <v>113.54</v>
       </c>
       <c r="AM94" s="37" t="n">
-        <v>-0.39</v>
+        <v>1.12</v>
       </c>
       <c r="AN94" s="37" t="n">
         <v>1.28</v>
@@ -25724,10 +25850,10 @@
         <v>15</v>
       </c>
       <c r="AL95" s="37" t="n">
-        <v>417.6</v>
+        <v>414.05</v>
       </c>
       <c r="AM95" s="37" t="n">
-        <v>-0.85</v>
+        <v>0.29</v>
       </c>
       <c r="AN95" s="37" t="n">
         <v>0.96</v>
@@ -25927,10 +26053,10 @@
         <v>15</v>
       </c>
       <c r="AL96" s="37" t="n">
-        <v>289</v>
+        <v>285.8</v>
       </c>
       <c r="AM96" s="37" t="n">
-        <v>-1.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN96" s="37" t="n">
         <v>1.13</v>
@@ -26130,10 +26256,10 @@
         <v>15</v>
       </c>
       <c r="AL97" s="37" t="n">
-        <v>562.9</v>
+        <v>597.55</v>
       </c>
       <c r="AM97" s="37" t="n">
-        <v>6.16</v>
+        <v>0.91</v>
       </c>
       <c r="AN97" s="37" t="n">
         <v>9.16</v>
@@ -26329,10 +26455,10 @@
         <v>15</v>
       </c>
       <c r="AL98" s="37" t="n">
-        <v>129.2</v>
+        <v>129.61</v>
       </c>
       <c r="AM98" s="37" t="n">
-        <v>0.32</v>
+        <v>-1.94</v>
       </c>
       <c r="AN98" s="37" t="n">
         <v>-4.51</v>
@@ -26528,10 +26654,10 @@
         <v>15</v>
       </c>
       <c r="AL99" s="37" t="n">
-        <v>5499</v>
+        <v>5532.5</v>
       </c>
       <c r="AM99" s="37" t="n">
-        <v>0.61</v>
+        <v>-1.04</v>
       </c>
       <c r="AN99" s="37" t="n">
         <v>2.87</v>
@@ -26727,10 +26853,10 @@
         <v>15</v>
       </c>
       <c r="AL100" s="37" t="n">
-        <v>11475</v>
+        <v>11456</v>
       </c>
       <c r="AM100" s="37" t="n">
-        <v>-0.17</v>
+        <v>-1.68</v>
       </c>
       <c r="AN100" s="37" t="n">
         <v>1.22</v>
@@ -26926,10 +27052,10 @@
         <v>15</v>
       </c>
       <c r="AL101" s="37" t="n">
-        <v>1384</v>
+        <v>1378.5</v>
       </c>
       <c r="AM101" s="37" t="n">
-        <v>-0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="AN101" s="37" t="n">
         <v>0.87</v>
@@ -27129,10 +27255,10 @@
         <v>15</v>
       </c>
       <c r="AL102" s="37" t="n">
-        <v>1454.6</v>
+        <v>1449.6</v>
       </c>
       <c r="AM102" s="37" t="n">
-        <v>-0.34</v>
+        <v>-1.97</v>
       </c>
       <c r="AN102" s="37" t="n">
         <v>-1.22</v>
@@ -27332,10 +27458,10 @@
         <v>15</v>
       </c>
       <c r="AL103" s="37" t="n">
-        <v>1964</v>
+        <v>1949</v>
       </c>
       <c r="AM103" s="37" t="n">
-        <v>-0.76</v>
+        <v>-0.21</v>
       </c>
       <c r="AN103" s="37" t="n">
         <v>-3.46</v>
@@ -27535,10 +27661,10 @@
         <v>15</v>
       </c>
       <c r="AL104" s="37" t="n">
-        <v>2410</v>
+        <v>2390.4</v>
       </c>
       <c r="AM104" s="37" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.13</v>
       </c>
       <c r="AN104" s="37" t="n">
         <v>-2.21</v>
@@ -27738,10 +27864,10 @@
         <v>15</v>
       </c>
       <c r="AL105" s="37" t="n">
-        <v>1620</v>
+        <v>1657</v>
       </c>
       <c r="AM105" s="37" t="n">
-        <v>2.28</v>
+        <v>0.18</v>
       </c>
       <c r="AN105" s="37" t="n">
         <v>2.12</v>
@@ -27941,10 +28067,10 @@
         <v>15</v>
       </c>
       <c r="AL106" s="37" t="n">
-        <v>343.65</v>
+        <v>346.9</v>
       </c>
       <c r="AM106" s="37" t="n">
-        <v>0.95</v>
+        <v>-1.27</v>
       </c>
       <c r="AN106" s="37" t="n">
         <v>-0.9399999999999999</v>
@@ -28140,10 +28266,10 @@
         <v>15</v>
       </c>
       <c r="AL107" s="37" t="n">
-        <v>398</v>
+        <v>397.2</v>
       </c>
       <c r="AM107" s="37" t="n">
-        <v>-0.2</v>
+        <v>-1.62</v>
       </c>
       <c r="AN107" s="37" t="n">
         <v>0.37</v>
@@ -28343,10 +28469,10 @@
         <v>15</v>
       </c>
       <c r="AL108" s="37" t="n">
-        <v>283.4</v>
+        <v>276.8</v>
       </c>
       <c r="AM108" s="37" t="n">
-        <v>-2.33</v>
+        <v>-1.88</v>
       </c>
       <c r="AN108" s="37" t="n">
         <v>-5</v>
@@ -28542,10 +28668,10 @@
         <v>15</v>
       </c>
       <c r="AL109" s="37" t="n">
-        <v>510.25</v>
+        <v>510.85</v>
       </c>
       <c r="AM109" s="37" t="n">
-        <v>0.12</v>
+        <v>1.78</v>
       </c>
       <c r="AN109" s="37" t="n">
         <v>5.18</v>
@@ -28745,10 +28871,10 @@
         <v>15</v>
       </c>
       <c r="AL110" s="37" t="n">
-        <v>391.5</v>
+        <v>390.05</v>
       </c>
       <c r="AM110" s="37" t="n">
-        <v>-0.37</v>
+        <v>2.81</v>
       </c>
       <c r="AN110" s="37" t="n">
         <v>3.16</v>
@@ -28948,10 +29074,10 @@
         <v>15</v>
       </c>
       <c r="AL111" s="37" t="n">
-        <v>417.6</v>
+        <v>414.05</v>
       </c>
       <c r="AM111" s="37" t="n">
-        <v>-0.85</v>
+        <v>0.29</v>
       </c>
       <c r="AN111" s="37" t="n">
         <v>0.96</v>
@@ -29147,10 +29273,10 @@
         <v>15</v>
       </c>
       <c r="AL112" s="37" t="n">
-        <v>5478</v>
+        <v>5429</v>
       </c>
       <c r="AM112" s="37" t="n">
-        <v>-0.89</v>
+        <v>1.49</v>
       </c>
       <c r="AN112" s="37" t="n">
         <v>1.92</v>
@@ -29350,10 +29476,10 @@
         <v>15</v>
       </c>
       <c r="AL113" s="37" t="n">
-        <v>380</v>
+        <v>378.9</v>
       </c>
       <c r="AM113" s="37" t="n">
-        <v>-0.29</v>
+        <v>0.44</v>
       </c>
       <c r="AN113" s="37" t="n">
         <v>-0.28</v>
@@ -29557,10 +29683,10 @@
         <v>24</v>
       </c>
       <c r="AL114" s="35" t="n">
-        <v>519.75</v>
+        <v>553.3</v>
       </c>
       <c r="AM114" s="35" t="n">
-        <v>6.46</v>
+        <v>-3.22</v>
       </c>
       <c r="AN114" s="35" t="n">
         <v>-3.22</v>
@@ -29762,10 +29888,10 @@
         <v>8.550000000000001</v>
       </c>
       <c r="AL115" s="36" t="n">
-        <v>289</v>
+        <v>285.8</v>
       </c>
       <c r="AM115" s="36" t="n">
-        <v>-1.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN115" s="36" t="n">
         <v>1.13</v>
@@ -29951,7 +30077,7 @@
         </is>
       </c>
       <c r="AB116" s="38" t="n">
-        <v>853.4</v>
+        <v>889.5</v>
       </c>
       <c r="AC116" s="38" t="n">
         <v>845</v>
@@ -29981,13 +30107,13 @@
         <v>15</v>
       </c>
       <c r="AL116" s="38" t="n">
-        <v>845</v>
+        <v>853.4</v>
       </c>
       <c r="AM116" s="38" t="n">
-        <v>0.99</v>
+        <v>4.23</v>
       </c>
       <c r="AN116" s="38" t="n">
-        <v>0.99</v>
+        <v>5.27</v>
       </c>
       <c r="AO116" s="38" t="n">
         <v>0</v>
@@ -30172,7 +30298,7 @@
         </is>
       </c>
       <c r="AB117" s="38" t="n">
-        <v>6834</v>
+        <v>6774</v>
       </c>
       <c r="AC117" s="38" t="n">
         <v>6793.5</v>
@@ -30202,13 +30328,13 @@
         <v>15</v>
       </c>
       <c r="AL117" s="38" t="n">
-        <v>6793.5</v>
+        <v>6834</v>
       </c>
       <c r="AM117" s="38" t="n">
-        <v>0.6</v>
+        <v>-0.88</v>
       </c>
       <c r="AN117" s="38" t="n">
-        <v>0.6</v>
+        <v>-0.29</v>
       </c>
       <c r="AO117" s="38" t="n">
         <v>0</v>
@@ -30393,7 +30519,7 @@
         </is>
       </c>
       <c r="AB118" s="38" t="n">
-        <v>443.9</v>
+        <v>442.8</v>
       </c>
       <c r="AC118" s="38" t="n">
         <v>450</v>
@@ -30423,13 +30549,13 @@
         <v>15</v>
       </c>
       <c r="AL118" s="38" t="n">
-        <v>450</v>
+        <v>443.9</v>
       </c>
       <c r="AM118" s="38" t="n">
-        <v>-1.36</v>
+        <v>-0.25</v>
       </c>
       <c r="AN118" s="38" t="n">
-        <v>-1.36</v>
+        <v>-1.6</v>
       </c>
       <c r="AO118" s="38" t="n">
         <v>0</v>
@@ -30602,7 +30728,7 @@
         </is>
       </c>
       <c r="AB119" s="38" t="n">
-        <v>471.2</v>
+        <v>473.3</v>
       </c>
       <c r="AC119" s="38" t="n">
         <v>471.2</v>
@@ -30632,13 +30758,13 @@
         <v>15</v>
       </c>
       <c r="AL119" s="38" t="n">
-        <v>482</v>
+        <v>471.2</v>
       </c>
       <c r="AM119" s="38" t="n">
-        <v>-2.24</v>
+        <v>0.45</v>
       </c>
       <c r="AN119" s="38" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AO119" s="38" t="n">
         <v>0</v>
@@ -30811,7 +30937,7 @@
         </is>
       </c>
       <c r="AB120" s="38" t="n">
-        <v>1594.5</v>
+        <v>1584.8</v>
       </c>
       <c r="AC120" s="38" t="n">
         <v>1595</v>
@@ -30841,13 +30967,13 @@
         <v>15</v>
       </c>
       <c r="AL120" s="38" t="n">
-        <v>1595</v>
+        <v>1594.5</v>
       </c>
       <c r="AM120" s="38" t="n">
-        <v>-0.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AN120" s="38" t="n">
-        <v>-0.03</v>
+        <v>-0.64</v>
       </c>
       <c r="AO120" s="38" t="n">
         <v>0</v>
@@ -31020,7 +31146,7 @@
         </is>
       </c>
       <c r="AB121" s="38" t="n">
-        <v>1296.8</v>
+        <v>1285</v>
       </c>
       <c r="AC121" s="38" t="n">
         <v>1327.7</v>
@@ -31050,13 +31176,13 @@
         <v>15</v>
       </c>
       <c r="AL121" s="38" t="n">
-        <v>1327.7</v>
+        <v>1296.8</v>
       </c>
       <c r="AM121" s="38" t="n">
-        <v>-2.33</v>
+        <v>-0.91</v>
       </c>
       <c r="AN121" s="38" t="n">
-        <v>-2.33</v>
+        <v>-3.22</v>
       </c>
       <c r="AO121" s="38" t="n">
         <v>0</v>
@@ -31245,10 +31371,10 @@
         <v>15</v>
       </c>
       <c r="AL122" s="37" t="n">
-        <v>7395</v>
+        <v>7531.5</v>
       </c>
       <c r="AM122" s="37" t="n">
-        <v>1.85</v>
+        <v>-1.28</v>
       </c>
       <c r="AN122" s="37" t="n">
         <v>-0.26</v>
@@ -31448,10 +31574,10 @@
         <v>15</v>
       </c>
       <c r="AL123" s="37" t="n">
-        <v>709.55</v>
+        <v>731</v>
       </c>
       <c r="AM123" s="37" t="n">
-        <v>3.02</v>
+        <v>-1.44</v>
       </c>
       <c r="AN123" s="37" t="n">
         <v>1.62</v>
@@ -31639,10 +31765,10 @@
         <v>15</v>
       </c>
       <c r="AL124" s="37" t="n">
-        <v>377</v>
+        <v>380.35</v>
       </c>
       <c r="AM124" s="37" t="n">
-        <v>0.89</v>
+        <v>0.17</v>
       </c>
       <c r="AN124" s="37" t="n">
         <v>1.06</v>
@@ -31834,10 +31960,10 @@
         <v>15</v>
       </c>
       <c r="AL125" s="37" t="n">
-        <v>391.3</v>
+        <v>387.9</v>
       </c>
       <c r="AM125" s="37" t="n">
-        <v>-0.87</v>
+        <v>1.57</v>
       </c>
       <c r="AN125" s="37" t="n">
         <v>0.6899999999999999</v>
@@ -32025,10 +32151,10 @@
         <v>15</v>
       </c>
       <c r="AL126" s="37" t="n">
-        <v>2744.3</v>
+        <v>2764.2</v>
       </c>
       <c r="AM126" s="37" t="n">
-        <v>0.73</v>
+        <v>0.28</v>
       </c>
       <c r="AN126" s="37" t="n">
         <v>1.01</v>
@@ -32244,10 +32370,10 @@
         <v>29.35</v>
       </c>
       <c r="AL127" s="35" t="n">
-        <v>2421.9</v>
+        <v>2452.7</v>
       </c>
       <c r="AM127" s="35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN127" s="35" t="n">
         <v>4.31</v>
@@ -32276,7 +32402,7 @@
       </c>
       <c r="AU127" s="35" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV127" s="35" t="inlineStr">
@@ -32461,10 +32587,10 @@
         <v>20.01</v>
       </c>
       <c r="AL128" s="35" t="n">
-        <v>553.3</v>
+        <v>535.5</v>
       </c>
       <c r="AM128" s="35" t="n">
-        <v>-3.22</v>
+        <v>0</v>
       </c>
       <c r="AN128" s="35" t="n">
         <v>-3.22</v>
@@ -32493,7 +32619,7 @@
       </c>
       <c r="AU128" s="35" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV128" s="35" t="inlineStr">
@@ -32682,10 +32808,10 @@
         <v>32.17</v>
       </c>
       <c r="AL129" s="36" t="n">
-        <v>11727</v>
+        <v>11805</v>
       </c>
       <c r="AM129" s="36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AN129" s="36" t="n">
         <v>6.59</v>
@@ -32714,7 +32840,7 @@
       </c>
       <c r="AU129" s="36" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV129" s="36" t="inlineStr">
@@ -32905,10 +33031,10 @@
         <v>15</v>
       </c>
       <c r="AL130" s="38" t="n">
-        <v>128.5</v>
+        <v>131.95</v>
       </c>
       <c r="AM130" s="38" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AN130" s="38" t="n">
         <v>0</v>
@@ -33108,10 +33234,10 @@
         <v>15</v>
       </c>
       <c r="AL131" s="38" t="n">
-        <v>176.1</v>
+        <v>183.6</v>
       </c>
       <c r="AM131" s="38" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="AN131" s="38" t="n">
         <v>0</v>
@@ -33311,10 +33437,10 @@
         <v>15</v>
       </c>
       <c r="AL132" s="38" t="n">
-        <v>5020.5</v>
+        <v>4924</v>
       </c>
       <c r="AM132" s="38" t="n">
-        <v>-1.92</v>
+        <v>0</v>
       </c>
       <c r="AN132" s="38" t="n">
         <v>0</v>
@@ -33522,10 +33648,10 @@
         <v>15</v>
       </c>
       <c r="AL133" s="38" t="n">
-        <v>7531.5</v>
+        <v>7435</v>
       </c>
       <c r="AM133" s="38" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="AN133" s="38" t="n">
         <v>-0.26</v>
@@ -33717,10 +33843,10 @@
         <v>11.35</v>
       </c>
       <c r="AL134" s="35" t="n">
-        <v>1449.6</v>
+        <v>1421</v>
       </c>
       <c r="AM134" s="35" t="n">
-        <v>-1.97</v>
+        <v>0</v>
       </c>
       <c r="AN134" s="35" t="n">
         <v>-1.22</v>
@@ -33922,10 +34048,10 @@
         <v>8.02</v>
       </c>
       <c r="AL135" s="35" t="n">
-        <v>1949</v>
+        <v>1945</v>
       </c>
       <c r="AM135" s="35" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="AN135" s="35" t="n">
         <v>-3.46</v>
@@ -34127,10 +34253,10 @@
         <v>10.78</v>
       </c>
       <c r="AL136" s="35" t="n">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="AM136" s="35" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="AN136" s="35" t="n">
         <v>2.12</v>
@@ -34332,10 +34458,10 @@
         <v>13</v>
       </c>
       <c r="AL137" s="35" t="n">
-        <v>2390.4</v>
+        <v>2363.5</v>
       </c>
       <c r="AM137" s="35" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="AN137" s="35" t="n">
         <v>-2.21</v>
@@ -34537,10 +34663,10 @@
         <v>16.01</v>
       </c>
       <c r="AL138" s="35" t="n">
-        <v>397.2</v>
+        <v>390.75</v>
       </c>
       <c r="AM138" s="35" t="n">
-        <v>-1.62</v>
+        <v>0</v>
       </c>
       <c r="AN138" s="35" t="n">
         <v>0.37</v>
@@ -34742,10 +34868,10 @@
         <v>14.47</v>
       </c>
       <c r="AL139" s="36" t="n">
-        <v>346.9</v>
+        <v>342.5</v>
       </c>
       <c r="AM139" s="36" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="AN139" s="36" t="n">
         <v>-0.9399999999999999</v>
@@ -34943,10 +35069,10 @@
         <v>19.22</v>
       </c>
       <c r="AL140" s="36" t="n">
-        <v>390.05</v>
+        <v>401</v>
       </c>
       <c r="AM140" s="36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AN140" s="36" t="n">
         <v>3.16</v>
@@ -35152,10 +35278,10 @@
         <v>9.779999999999999</v>
       </c>
       <c r="AL141" s="36" t="n">
-        <v>276.8</v>
+        <v>271.6</v>
       </c>
       <c r="AM141" s="36" t="n">
-        <v>-1.88</v>
+        <v>0</v>
       </c>
       <c r="AN141" s="36" t="n">
         <v>-5</v>
@@ -35353,10 +35479,10 @@
         <v>21.56</v>
       </c>
       <c r="AL142" s="37" t="n">
-        <v>510.85</v>
+        <v>519.95</v>
       </c>
       <c r="AM142" s="37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AN142" s="37" t="n">
         <v>5.18</v>
@@ -35554,10 +35680,10 @@
         <v>8.550000000000001</v>
       </c>
       <c r="AL143" s="36" t="n">
-        <v>285.8</v>
+        <v>286.1</v>
       </c>
       <c r="AM143" s="36" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN143" s="36" t="n">
         <v>1.13</v>
@@ -35582,7 +35708,7 @@
       </c>
       <c r="AU143" s="36" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV143" s="36" t="inlineStr">
@@ -35759,10 +35885,10 @@
         <v>16.66</v>
       </c>
       <c r="AL144" s="36" t="n">
-        <v>414.05</v>
+        <v>415.25</v>
       </c>
       <c r="AM144" s="36" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="AN144" s="36" t="n">
         <v>0.96</v>
@@ -35960,10 +36086,10 @@
         <v>17.78</v>
       </c>
       <c r="AL145" s="37" t="n">
-        <v>5429</v>
+        <v>5510</v>
       </c>
       <c r="AM145" s="37" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AN145" s="37" t="n">
         <v>1.92</v>
@@ -36165,10 +36291,10 @@
         <v>15</v>
       </c>
       <c r="AL146" s="37" t="n">
-        <v>2390.4</v>
+        <v>2363.5</v>
       </c>
       <c r="AM146" s="37" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="AN146" s="37" t="n">
         <v>-2.21</v>
@@ -36191,7 +36317,7 @@
       </c>
       <c r="AU146" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV146" s="37" t="inlineStr">
@@ -36368,10 +36494,10 @@
         <v>15</v>
       </c>
       <c r="AL147" s="37" t="n">
-        <v>459.55</v>
+        <v>450.7</v>
       </c>
       <c r="AM147" s="37" t="n">
-        <v>-1.93</v>
+        <v>0</v>
       </c>
       <c r="AN147" s="37" t="n">
         <v>1.66</v>
@@ -36394,7 +36520,7 @@
       </c>
       <c r="AU147" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV147" s="37" t="inlineStr">
@@ -36571,10 +36697,10 @@
         <v>15</v>
       </c>
       <c r="AL148" s="37" t="n">
-        <v>113.54</v>
+        <v>114.81</v>
       </c>
       <c r="AM148" s="37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AN148" s="37" t="n">
         <v>1.28</v>
@@ -36597,7 +36723,7 @@
       </c>
       <c r="AU148" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV148" s="37" t="inlineStr">
@@ -36774,10 +36900,10 @@
         <v>15</v>
       </c>
       <c r="AL149" s="37" t="n">
-        <v>414.05</v>
+        <v>415.25</v>
       </c>
       <c r="AM149" s="37" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="AN149" s="37" t="n">
         <v>0.96</v>
@@ -36800,7 +36926,7 @@
       </c>
       <c r="AU149" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV149" s="37" t="inlineStr">
@@ -36977,10 +37103,10 @@
         <v>15</v>
       </c>
       <c r="AL150" s="37" t="n">
-        <v>285.8</v>
+        <v>286.1</v>
       </c>
       <c r="AM150" s="37" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN150" s="37" t="n">
         <v>1.13</v>
@@ -37003,7 +37129,7 @@
       </c>
       <c r="AU150" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV150" s="37" t="inlineStr">
@@ -37180,10 +37306,10 @@
         <v>15</v>
       </c>
       <c r="AL151" s="37" t="n">
-        <v>597.55</v>
+        <v>603</v>
       </c>
       <c r="AM151" s="37" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="AN151" s="37" t="n">
         <v>9.16</v>
@@ -37206,7 +37332,7 @@
       </c>
       <c r="AU151" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV151" s="37" t="inlineStr">
@@ -37383,10 +37509,10 @@
         <v>15</v>
       </c>
       <c r="AL152" s="37" t="n">
-        <v>731</v>
+        <v>720.5</v>
       </c>
       <c r="AM152" s="37" t="n">
-        <v>-1.44</v>
+        <v>0</v>
       </c>
       <c r="AN152" s="37" t="n">
         <v>1.62</v>
@@ -37409,7 +37535,7 @@
       </c>
       <c r="AU152" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV152" s="37" t="inlineStr">
@@ -37578,10 +37704,10 @@
         <v>15</v>
       </c>
       <c r="AL153" s="37" t="n">
-        <v>129.61</v>
+        <v>127.1</v>
       </c>
       <c r="AM153" s="37" t="n">
-        <v>-1.94</v>
+        <v>0</v>
       </c>
       <c r="AN153" s="37" t="n">
         <v>-4.51</v>
@@ -37604,7 +37730,7 @@
       </c>
       <c r="AU153" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV153" s="37" t="inlineStr">
@@ -37777,10 +37903,10 @@
         <v>15</v>
       </c>
       <c r="AL154" s="37" t="n">
-        <v>5532.5</v>
+        <v>5475</v>
       </c>
       <c r="AM154" s="37" t="n">
-        <v>-1.04</v>
+        <v>0</v>
       </c>
       <c r="AN154" s="37" t="n">
         <v>2.87</v>
@@ -37803,7 +37929,7 @@
       </c>
       <c r="AU154" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV154" s="37" t="inlineStr">
@@ -37976,10 +38102,10 @@
         <v>15</v>
       </c>
       <c r="AL155" s="37" t="n">
-        <v>11456</v>
+        <v>11263</v>
       </c>
       <c r="AM155" s="37" t="n">
-        <v>-1.68</v>
+        <v>0</v>
       </c>
       <c r="AN155" s="37" t="n">
         <v>1.22</v>
@@ -38002,7 +38128,7 @@
       </c>
       <c r="AU155" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV155" s="37" t="inlineStr">
@@ -38175,10 +38301,10 @@
         <v>15</v>
       </c>
       <c r="AL156" s="37" t="n">
-        <v>1378.5</v>
+        <v>1372.4</v>
       </c>
       <c r="AM156" s="37" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="AN156" s="37" t="n">
         <v>0.87</v>
@@ -38201,7 +38327,7 @@
       </c>
       <c r="AU156" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV156" s="37" t="inlineStr">
@@ -38370,10 +38496,10 @@
         <v>15</v>
       </c>
       <c r="AL157" s="37" t="n">
-        <v>380.35</v>
+        <v>381</v>
       </c>
       <c r="AM157" s="37" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AN157" s="37" t="n">
         <v>1.06</v>
@@ -38396,7 +38522,7 @@
       </c>
       <c r="AU157" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV157" s="37" t="inlineStr">
@@ -38565,10 +38691,10 @@
         <v>15</v>
       </c>
       <c r="AL158" s="37" t="n">
-        <v>387.9</v>
+        <v>394</v>
       </c>
       <c r="AM158" s="37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN158" s="37" t="n">
         <v>0.6899999999999999</v>
@@ -38591,7 +38717,7 @@
       </c>
       <c r="AU158" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV158" s="37" t="inlineStr">
@@ -38756,10 +38882,10 @@
         <v>15</v>
       </c>
       <c r="AL159" s="37" t="n">
-        <v>2764.2</v>
+        <v>2772</v>
       </c>
       <c r="AM159" s="37" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AN159" s="37" t="n">
         <v>1.01</v>
@@ -38782,7 +38908,7 @@
       </c>
       <c r="AU159" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV159" s="37" t="inlineStr">
@@ -38959,10 +39085,10 @@
         <v>15</v>
       </c>
       <c r="AL160" s="37" t="n">
-        <v>1449.6</v>
+        <v>1421</v>
       </c>
       <c r="AM160" s="37" t="n">
-        <v>-1.97</v>
+        <v>0</v>
       </c>
       <c r="AN160" s="37" t="n">
         <v>-1.22</v>
@@ -38985,7 +39111,7 @@
       </c>
       <c r="AU160" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV160" s="37" t="inlineStr">
@@ -39162,10 +39288,10 @@
         <v>15</v>
       </c>
       <c r="AL161" s="37" t="n">
-        <v>1949</v>
+        <v>1945</v>
       </c>
       <c r="AM161" s="37" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="AN161" s="37" t="n">
         <v>-3.46</v>
@@ -39188,7 +39314,7 @@
       </c>
       <c r="AU161" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV161" s="37" t="inlineStr">
@@ -39365,10 +39491,10 @@
         <v>15</v>
       </c>
       <c r="AL162" s="37" t="n">
-        <v>2390.4</v>
+        <v>2363.5</v>
       </c>
       <c r="AM162" s="37" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="AN162" s="37" t="n">
         <v>-2.21</v>
@@ -39391,7 +39517,7 @@
       </c>
       <c r="AU162" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV162" s="37" t="inlineStr">
@@ -39568,10 +39694,10 @@
         <v>15</v>
       </c>
       <c r="AL163" s="37" t="n">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="AM163" s="37" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="AN163" s="37" t="n">
         <v>2.12</v>
@@ -39594,7 +39720,7 @@
       </c>
       <c r="AU163" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV163" s="37" t="inlineStr">
@@ -39771,10 +39897,10 @@
         <v>15</v>
       </c>
       <c r="AL164" s="37" t="n">
-        <v>346.9</v>
+        <v>342.5</v>
       </c>
       <c r="AM164" s="37" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="AN164" s="37" t="n">
         <v>-0.9399999999999999</v>
@@ -39797,7 +39923,7 @@
       </c>
       <c r="AU164" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV164" s="37" t="inlineStr">
@@ -39970,10 +40096,10 @@
         <v>15</v>
       </c>
       <c r="AL165" s="37" t="n">
-        <v>397.2</v>
+        <v>390.75</v>
       </c>
       <c r="AM165" s="37" t="n">
-        <v>-1.62</v>
+        <v>0</v>
       </c>
       <c r="AN165" s="37" t="n">
         <v>0.37</v>
@@ -39996,7 +40122,7 @@
       </c>
       <c r="AU165" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV165" s="37" t="inlineStr">
@@ -40173,10 +40299,10 @@
         <v>15</v>
       </c>
       <c r="AL166" s="37" t="n">
-        <v>276.8</v>
+        <v>271.6</v>
       </c>
       <c r="AM166" s="37" t="n">
-        <v>-1.88</v>
+        <v>0</v>
       </c>
       <c r="AN166" s="37" t="n">
         <v>-5</v>
@@ -40199,7 +40325,7 @@
       </c>
       <c r="AU166" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV166" s="37" t="inlineStr">
@@ -40372,10 +40498,10 @@
         <v>15</v>
       </c>
       <c r="AL167" s="37" t="n">
-        <v>510.85</v>
+        <v>519.95</v>
       </c>
       <c r="AM167" s="37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AN167" s="37" t="n">
         <v>5.18</v>
@@ -40398,7 +40524,7 @@
       </c>
       <c r="AU167" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV167" s="37" t="inlineStr">
@@ -40575,10 +40701,10 @@
         <v>15</v>
       </c>
       <c r="AL168" s="37" t="n">
-        <v>390.05</v>
+        <v>401</v>
       </c>
       <c r="AM168" s="37" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AN168" s="37" t="n">
         <v>3.16</v>
@@ -40601,7 +40727,7 @@
       </c>
       <c r="AU168" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV168" s="37" t="inlineStr">
@@ -40778,10 +40904,10 @@
         <v>15</v>
       </c>
       <c r="AL169" s="37" t="n">
-        <v>414.05</v>
+        <v>415.25</v>
       </c>
       <c r="AM169" s="37" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="AN169" s="37" t="n">
         <v>0.96</v>
@@ -40804,7 +40930,7 @@
       </c>
       <c r="AU169" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV169" s="37" t="inlineStr">
@@ -40977,10 +41103,10 @@
         <v>15</v>
       </c>
       <c r="AL170" s="37" t="n">
-        <v>5429</v>
+        <v>5510</v>
       </c>
       <c r="AM170" s="37" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AN170" s="37" t="n">
         <v>1.92</v>
@@ -41003,7 +41129,7 @@
       </c>
       <c r="AU170" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV170" s="37" t="inlineStr">
@@ -41180,10 +41306,10 @@
         <v>15</v>
       </c>
       <c r="AL171" s="37" t="n">
-        <v>378.9</v>
+        <v>380.55</v>
       </c>
       <c r="AM171" s="37" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AN171" s="37" t="n">
         <v>-0.28</v>
@@ -41206,7 +41332,7 @@
       </c>
       <c r="AU171" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:40</t>
+          <t>2026-08-10 05:58</t>
         </is>
       </c>
       <c r="AV171" s="37" t="inlineStr">

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -98,12 +98,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCC66"/>
-        <bgColor rgb="00FFCC66"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D6DCE4"/>
         <bgColor rgb="00D6DCE4"/>
       </patternFill>
@@ -112,6 +106,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00A9D08E"/>
         <bgColor rgb="00A9D08E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCC66"/>
+        <bgColor rgb="00FFCC66"/>
       </patternFill>
     </fill>
     <fill>
@@ -876,12 +876,12 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>🟢 ACTIVE</t>
+          <t>🟡 REVIEWING</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr"/>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr"/>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr"/>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr"/>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>🟢 ACTIVE</t>
+          <t>🟡 REVIEWING</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>🟢 ACTIVE</t>
+          <t>🟡 REVIEWING</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr"/>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr"/>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr"/>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr"/>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr"/>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>🟢 ACTIVE</t>
+          <t>🟡 REVIEWING</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr"/>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>🟢 ACTIVE</t>
+          <t>🟡 REVIEWING</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -2710,12 +2710,12 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr"/>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr"/>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>🔴 EXIT NOW</t>
+          <t>🔴 EXIT</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B49" s="29" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="C49" s="28" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="B51" s="29" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="C51" s="28" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="B53" s="29" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="C53" s="28" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AZ2" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA2" s="35" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="AZ12" s="38" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="BA12" s="38" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="AZ13" s="38" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="BA13" s="38" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="AZ14" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA14" s="38" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="AZ15" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA15" s="39" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="AZ16" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA16" s="39" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="AZ17" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA17" s="35" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AZ18" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA18" s="35" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AZ29" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA29" s="39" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AZ30" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA30" s="39" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="AZ32" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA32" s="39" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="AZ33" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA33" s="39" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AZ34" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA34" s="39" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="AZ36" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA36" s="39" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="AZ37" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA37" s="39" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="AZ38" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA38" s="39" t="inlineStr">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="AZ39" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA39" s="35" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="AZ40" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA40" s="35" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="AZ42" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA42" s="35" t="inlineStr">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="AZ59" s="38" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="BA59" s="38" t="inlineStr">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="AZ62" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA62" s="38" t="inlineStr">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="AZ64" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA64" s="38" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="AZ68" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA68" s="38" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="AZ70" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA70" s="38" t="inlineStr">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="AZ71" s="39" t="inlineStr">
         <is>
-          <t>⚪ IGNORED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA71" s="39" t="inlineStr">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AZ84" s="37" t="inlineStr">
         <is>
-          <t>🔴 EXIT NOW</t>
+          <t>🔴 EXIT</t>
         </is>
       </c>
       <c r="BA84" s="37" t="inlineStr">
@@ -24645,7 +24645,7 @@
       </c>
       <c r="AZ89" s="37" t="inlineStr">
         <is>
-          <t>🔴 EXIT NOW</t>
+          <t>🔴 EXIT</t>
         </is>
       </c>
       <c r="BA89" s="37" t="inlineStr">
@@ -30160,7 +30160,7 @@
       </c>
       <c r="AZ116" s="38" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="BA116" s="38" t="inlineStr">
@@ -30381,7 +30381,7 @@
       </c>
       <c r="AZ117" s="38" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="BA117" s="38" t="inlineStr">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="AZ118" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA118" s="38" t="inlineStr">
@@ -30811,7 +30811,7 @@
       </c>
       <c r="AZ119" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA119" s="38" t="inlineStr">
@@ -31020,7 +31020,7 @@
       </c>
       <c r="AZ120" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA120" s="38" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="AZ121" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA121" s="38" t="inlineStr">
@@ -32402,7 +32402,7 @@
       </c>
       <c r="AU127" s="35" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV127" s="35" t="inlineStr">
@@ -32619,7 +32619,7 @@
       </c>
       <c r="AU128" s="35" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV128" s="35" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="AU129" s="36" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV129" s="36" t="inlineStr">
@@ -33078,7 +33078,7 @@
       <c r="AY130" s="38" t="inlineStr"/>
       <c r="AZ130" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA130" s="38" t="inlineStr">
@@ -33281,7 +33281,7 @@
       <c r="AY131" s="38" t="inlineStr"/>
       <c r="AZ131" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA131" s="38" t="inlineStr">
@@ -33484,7 +33484,7 @@
       <c r="AY132" s="38" t="inlineStr"/>
       <c r="AZ132" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA132" s="38" t="inlineStr">
@@ -33701,7 +33701,7 @@
       </c>
       <c r="AZ133" s="38" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA133" s="38" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="AZ134" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA134" s="35" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="AZ135" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA135" s="35" t="inlineStr">
@@ -34509,7 +34509,7 @@
       </c>
       <c r="AZ137" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA137" s="35" t="inlineStr">
@@ -34714,7 +34714,7 @@
       </c>
       <c r="AZ138" s="35" t="inlineStr">
         <is>
-          <t>🟢 BUY BIG</t>
+          <t>🟢 BUY</t>
         </is>
       </c>
       <c r="BA138" s="35" t="inlineStr">
@@ -35708,7 +35708,7 @@
       </c>
       <c r="AU143" s="36" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV143" s="36" t="inlineStr">
@@ -36317,7 +36317,7 @@
       </c>
       <c r="AU146" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV146" s="37" t="inlineStr">
@@ -36520,7 +36520,7 @@
       </c>
       <c r="AU147" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV147" s="37" t="inlineStr">
@@ -36723,7 +36723,7 @@
       </c>
       <c r="AU148" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV148" s="37" t="inlineStr">
@@ -36926,7 +36926,7 @@
       </c>
       <c r="AU149" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV149" s="37" t="inlineStr">
@@ -37129,7 +37129,7 @@
       </c>
       <c r="AU150" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV150" s="37" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="AU151" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV151" s="37" t="inlineStr">
@@ -37535,7 +37535,7 @@
       </c>
       <c r="AU152" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV152" s="37" t="inlineStr">
@@ -37730,7 +37730,7 @@
       </c>
       <c r="AU153" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV153" s="37" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AU154" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV154" s="37" t="inlineStr">
@@ -38128,7 +38128,7 @@
       </c>
       <c r="AU155" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV155" s="37" t="inlineStr">
@@ -38327,7 +38327,7 @@
       </c>
       <c r="AU156" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV156" s="37" t="inlineStr">
@@ -38522,7 +38522,7 @@
       </c>
       <c r="AU157" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV157" s="37" t="inlineStr">
@@ -38717,7 +38717,7 @@
       </c>
       <c r="AU158" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV158" s="37" t="inlineStr">
@@ -38908,7 +38908,7 @@
       </c>
       <c r="AU159" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV159" s="37" t="inlineStr">
@@ -39111,7 +39111,7 @@
       </c>
       <c r="AU160" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV160" s="37" t="inlineStr">
@@ -39314,7 +39314,7 @@
       </c>
       <c r="AU161" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV161" s="37" t="inlineStr">
@@ -39517,7 +39517,7 @@
       </c>
       <c r="AU162" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV162" s="37" t="inlineStr">
@@ -39720,7 +39720,7 @@
       </c>
       <c r="AU163" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV163" s="37" t="inlineStr">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="AU164" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV164" s="37" t="inlineStr">
@@ -40122,7 +40122,7 @@
       </c>
       <c r="AU165" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV165" s="37" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="AU166" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV166" s="37" t="inlineStr">
@@ -40524,7 +40524,7 @@
       </c>
       <c r="AU167" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV167" s="37" t="inlineStr">
@@ -40727,7 +40727,7 @@
       </c>
       <c r="AU168" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV168" s="37" t="inlineStr">
@@ -40930,7 +40930,7 @@
       </c>
       <c r="AU169" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV169" s="37" t="inlineStr">
@@ -41129,7 +41129,7 @@
       </c>
       <c r="AU170" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV170" s="37" t="inlineStr">
@@ -41332,7 +41332,7 @@
       </c>
       <c r="AU171" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:58</t>
+          <t>2026-08-10 06:13</t>
         </is>
       </c>
       <c r="AV171" s="37" t="inlineStr">

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="AZ14" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA14" s="38" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="AZ15" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA15" s="39" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="AZ16" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA16" s="39" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AZ29" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA29" s="39" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AZ30" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA30" s="39" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="AZ32" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA32" s="39" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="AZ33" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA33" s="39" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AZ34" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA34" s="39" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="AZ36" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA36" s="39" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="AZ37" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA37" s="39" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="AZ38" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA38" s="39" t="inlineStr">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="AZ62" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA62" s="38" t="inlineStr">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="AZ64" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA64" s="38" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="AZ68" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA68" s="38" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="AZ70" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA70" s="38" t="inlineStr">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="AZ71" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="BA71" s="39" t="inlineStr">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="AZ118" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA118" s="38" t="inlineStr">
@@ -30811,7 +30811,7 @@
       </c>
       <c r="AZ119" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA119" s="38" t="inlineStr">
@@ -31020,7 +31020,7 @@
       </c>
       <c r="AZ120" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA120" s="38" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="AZ121" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA121" s="38" t="inlineStr">
@@ -32402,7 +32402,7 @@
       </c>
       <c r="AU127" s="35" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV127" s="35" t="inlineStr">
@@ -32619,7 +32619,7 @@
       </c>
       <c r="AU128" s="35" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV128" s="35" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="AU129" s="36" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV129" s="36" t="inlineStr">
@@ -33078,7 +33078,7 @@
       <c r="AY130" s="38" t="inlineStr"/>
       <c r="AZ130" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA130" s="38" t="inlineStr">
@@ -33281,7 +33281,7 @@
       <c r="AY131" s="38" t="inlineStr"/>
       <c r="AZ131" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA131" s="38" t="inlineStr">
@@ -33484,7 +33484,7 @@
       <c r="AY132" s="38" t="inlineStr"/>
       <c r="AZ132" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA132" s="38" t="inlineStr">
@@ -33701,7 +33701,7 @@
       </c>
       <c r="AZ133" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA133" s="38" t="inlineStr">
@@ -35708,7 +35708,7 @@
       </c>
       <c r="AU143" s="36" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV143" s="36" t="inlineStr">
@@ -36317,7 +36317,7 @@
       </c>
       <c r="AU146" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV146" s="37" t="inlineStr">
@@ -36520,7 +36520,7 @@
       </c>
       <c r="AU147" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV147" s="37" t="inlineStr">
@@ -36723,7 +36723,7 @@
       </c>
       <c r="AU148" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV148" s="37" t="inlineStr">
@@ -36926,7 +36926,7 @@
       </c>
       <c r="AU149" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV149" s="37" t="inlineStr">
@@ -37129,7 +37129,7 @@
       </c>
       <c r="AU150" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV150" s="37" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="AU151" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV151" s="37" t="inlineStr">
@@ -37535,7 +37535,7 @@
       </c>
       <c r="AU152" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV152" s="37" t="inlineStr">
@@ -37730,7 +37730,7 @@
       </c>
       <c r="AU153" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV153" s="37" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AU154" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV154" s="37" t="inlineStr">
@@ -38128,7 +38128,7 @@
       </c>
       <c r="AU155" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV155" s="37" t="inlineStr">
@@ -38327,7 +38327,7 @@
       </c>
       <c r="AU156" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV156" s="37" t="inlineStr">
@@ -38522,7 +38522,7 @@
       </c>
       <c r="AU157" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV157" s="37" t="inlineStr">
@@ -38717,7 +38717,7 @@
       </c>
       <c r="AU158" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV158" s="37" t="inlineStr">
@@ -38908,7 +38908,7 @@
       </c>
       <c r="AU159" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV159" s="37" t="inlineStr">
@@ -39111,7 +39111,7 @@
       </c>
       <c r="AU160" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV160" s="37" t="inlineStr">
@@ -39314,7 +39314,7 @@
       </c>
       <c r="AU161" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV161" s="37" t="inlineStr">
@@ -39517,7 +39517,7 @@
       </c>
       <c r="AU162" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV162" s="37" t="inlineStr">
@@ -39720,7 +39720,7 @@
       </c>
       <c r="AU163" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV163" s="37" t="inlineStr">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="AU164" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV164" s="37" t="inlineStr">
@@ -40122,7 +40122,7 @@
       </c>
       <c r="AU165" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV165" s="37" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="AU166" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV166" s="37" t="inlineStr">
@@ -40524,7 +40524,7 @@
       </c>
       <c r="AU167" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV167" s="37" t="inlineStr">
@@ -40727,7 +40727,7 @@
       </c>
       <c r="AU168" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV168" s="37" t="inlineStr">
@@ -40930,7 +40930,7 @@
       </c>
       <c r="AU169" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV169" s="37" t="inlineStr">
@@ -41129,7 +41129,7 @@
       </c>
       <c r="AU170" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV170" s="37" t="inlineStr">
@@ -41332,7 +41332,7 @@
       </c>
       <c r="AU171" s="37" t="inlineStr">
         <is>
-          <t>2026-08-10 06:13</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
       <c r="AV171" s="37" t="inlineStr">

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -47,7 +47,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -100,6 +100,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6DCE4"/>
         <bgColor rgb="00D6DCE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -637,7 +643,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA PORTFOLIO · as of 2026-08-10</t>
+          <t>AEGIS INDIA PORTFOLIO · as of 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1814,12 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr"/>
@@ -1859,12 +1865,12 @@
       </c>
       <c r="O16" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P16" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q16" s="9" t="inlineStr">
@@ -1914,12 +1920,12 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr"/>
@@ -1965,12 +1971,12 @@
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q17" s="9" t="inlineStr">
@@ -2020,12 +2026,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr"/>
@@ -2071,12 +2077,12 @@
       </c>
       <c r="O18" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P18" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q18" s="9" t="inlineStr">
@@ -2984,7 +2990,7 @@
       </c>
       <c r="L26" s="16" t="n"/>
       <c r="M26" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
@@ -3104,7 +3110,7 @@
       </c>
       <c r="L27" s="22" t="n"/>
       <c r="M27" s="24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N27" s="22" t="inlineStr">
         <is>
@@ -3224,7 +3230,7 @@
       </c>
       <c r="L28" s="16" t="n"/>
       <c r="M28" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
@@ -3344,7 +3350,7 @@
       </c>
       <c r="L29" s="28" t="n"/>
       <c r="M29" s="30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N29" s="28" t="inlineStr">
         <is>
@@ -3464,7 +3470,7 @@
       </c>
       <c r="L30" s="22" t="n"/>
       <c r="M30" s="24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N30" s="22" t="inlineStr">
         <is>
@@ -3584,7 +3590,7 @@
       </c>
       <c r="L31" s="16" t="n"/>
       <c r="M31" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N31" s="16" t="inlineStr">
         <is>
@@ -3704,7 +3710,7 @@
       </c>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N32" s="28" t="inlineStr">
         <is>
@@ -3824,7 +3830,7 @@
       </c>
       <c r="L33" s="16" t="n"/>
       <c r="M33" s="18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N33" s="16" t="inlineStr">
         <is>
@@ -3944,7 +3950,7 @@
       </c>
       <c r="L34" s="16" t="n"/>
       <c r="M34" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N34" s="16" t="inlineStr">
         <is>
@@ -4060,7 +4066,7 @@
       </c>
       <c r="L35" s="16" t="n"/>
       <c r="M35" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N35" s="16" t="inlineStr">
         <is>
@@ -4180,7 +4186,7 @@
       </c>
       <c r="L36" s="16" t="n"/>
       <c r="M36" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N36" s="16" t="inlineStr">
         <is>
@@ -4300,7 +4306,7 @@
       </c>
       <c r="L37" s="16" t="n"/>
       <c r="M37" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
@@ -4420,7 +4426,7 @@
       </c>
       <c r="L38" s="16" t="n"/>
       <c r="M38" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N38" s="16" t="inlineStr">
         <is>
@@ -4540,7 +4546,7 @@
       </c>
       <c r="L39" s="22" t="n"/>
       <c r="M39" s="24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N39" s="22" t="inlineStr">
         <is>
@@ -4660,7 +4666,7 @@
       </c>
       <c r="L40" s="16" t="n"/>
       <c r="M40" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
@@ -4780,7 +4786,7 @@
       </c>
       <c r="L41" s="16" t="n"/>
       <c r="M41" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
@@ -4900,7 +4906,7 @@
       </c>
       <c r="L42" s="16" t="n"/>
       <c r="M42" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N42" s="16" t="inlineStr">
         <is>
@@ -5020,7 +5026,7 @@
       </c>
       <c r="L43" s="22" t="n"/>
       <c r="M43" s="24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N43" s="22" t="inlineStr">
         <is>
@@ -5140,7 +5146,7 @@
       </c>
       <c r="L44" s="16" t="n"/>
       <c r="M44" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N44" s="16" t="inlineStr">
         <is>
@@ -5256,7 +5262,7 @@
       </c>
       <c r="L45" s="16" t="n"/>
       <c r="M45" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N45" s="16" t="inlineStr">
         <is>
@@ -5376,7 +5382,7 @@
       </c>
       <c r="L46" s="28" t="n"/>
       <c r="M46" s="30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N46" s="28" t="inlineStr">
         <is>
@@ -5496,7 +5502,7 @@
       </c>
       <c r="L47" s="16" t="n"/>
       <c r="M47" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
@@ -5612,7 +5618,7 @@
       </c>
       <c r="L48" s="22" t="n"/>
       <c r="M48" s="24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N48" s="22" t="inlineStr">
         <is>
@@ -5732,7 +5738,7 @@
       </c>
       <c r="L49" s="28" t="n"/>
       <c r="M49" s="30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N49" s="28" t="inlineStr">
         <is>
@@ -5852,7 +5858,7 @@
       </c>
       <c r="L50" s="16" t="n"/>
       <c r="M50" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N50" s="16" t="inlineStr">
         <is>
@@ -5972,7 +5978,7 @@
       </c>
       <c r="L51" s="28" t="n"/>
       <c r="M51" s="30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N51" s="28" t="inlineStr">
         <is>
@@ -6092,7 +6098,7 @@
       </c>
       <c r="L52" s="28" t="n"/>
       <c r="M52" s="30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N52" s="28" t="inlineStr">
         <is>
@@ -6212,7 +6218,7 @@
       </c>
       <c r="L53" s="28" t="n"/>
       <c r="M53" s="30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N53" s="28" t="inlineStr">
         <is>
@@ -6332,7 +6338,7 @@
       </c>
       <c r="L54" s="16" t="n"/>
       <c r="M54" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N54" s="16" t="inlineStr">
         <is>
@@ -6448,7 +6454,7 @@
       </c>
       <c r="L55" s="22" t="n"/>
       <c r="M55" s="24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N55" s="22" t="inlineStr">
         <is>
@@ -6528,7 +6534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG171"/>
+  <dimension ref="A1:BG212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -41390,6 +41396,8331 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="35" t="inlineStr">
+        <is>
+          <t>TCS_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B172" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C172" s="35" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D172" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E172" s="35" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="F172" s="35" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="G172" s="35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H172" s="35" t="n"/>
+      <c r="I172" s="35" t="n"/>
+      <c r="J172" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="L172" s="35" t="n">
+        <v>-8</v>
+      </c>
+      <c r="M172" s="35" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="N172" s="35" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O172" s="35" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="P172" s="35" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q172" s="35" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+47 more) → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R172" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 9→1 · Conf 39% · band HOLD · 16d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S172" s="35" t="n"/>
+      <c r="T172" s="35" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U172" s="35" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V172" s="35" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="W172" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="X172" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y172" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z172" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA172" s="35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB172" s="35" t="n">
+        <v>2452.7</v>
+      </c>
+      <c r="AC172" s="35" t="n">
+        <v>2351.3</v>
+      </c>
+      <c r="AD172" s="35" t="n">
+        <v>2428.17</v>
+      </c>
+      <c r="AE172" s="35" t="n">
+        <v>2477.23</v>
+      </c>
+      <c r="AF172" s="35" t="n">
+        <v>2305.54</v>
+      </c>
+      <c r="AG172" s="35" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="AH172" s="35" t="n">
+        <v>2747.02</v>
+      </c>
+      <c r="AI172" s="35" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="AJ172" s="35" t="n">
+        <v>3041.35</v>
+      </c>
+      <c r="AK172" s="35" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="AL172" s="35" t="n">
+        <v>2452.7</v>
+      </c>
+      <c r="AM172" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN172" s="35" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AO172" s="35" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AP172" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ172" s="35" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Momentum</t>
+        </is>
+      </c>
+      <c r="AR172" s="35" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="AS172" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT172" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV172" s="35" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW172" s="35" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX172" s="35" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AY172" s="35" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ172" s="35" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA172" s="35" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB172" s="35" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC172" s="35" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD172" s="35" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE172" s="35" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 2305.54</t>
+        </is>
+      </c>
+      <c r="BF172" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG172" s="35" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="35" t="inlineStr">
+        <is>
+          <t>GNFC_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B173" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C173" s="35" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D173" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E173" s="35" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="F173" s="35" t="n"/>
+      <c r="G173" s="35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H173" s="35" t="n"/>
+      <c r="I173" s="35" t="n"/>
+      <c r="J173" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K173" s="35" t="n"/>
+      <c r="L173" s="35" t="n"/>
+      <c r="M173" s="35" t="n">
+        <v>73</v>
+      </c>
+      <c r="N173" s="35" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O173" s="35" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P173" s="35" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q173" s="35" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+47 more) → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R173" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 34% · band HOLD · 17d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S173" s="35" t="n"/>
+      <c r="T173" s="35" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="U173" s="35" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V173" s="35" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="W173" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X173" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y173" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z173" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA173" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AB173" s="35" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="AC173" s="35" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="AD173" s="35" t="n">
+        <v>530.14</v>
+      </c>
+      <c r="AE173" s="35" t="n">
+        <v>540.86</v>
+      </c>
+      <c r="AF173" s="35" t="n">
+        <v>503.37</v>
+      </c>
+      <c r="AG173" s="35" t="n">
+        <v>-9.02</v>
+      </c>
+      <c r="AH173" s="35" t="n">
+        <v>599.76</v>
+      </c>
+      <c r="AI173" s="35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AJ173" s="35" t="n">
+        <v>664.02</v>
+      </c>
+      <c r="AK173" s="35" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="AL173" s="35" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="AM173" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN173" s="35" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="AO173" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP173" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ173" s="35" t="inlineStr">
+        <is>
+          <t>Value · Growth · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AR173" s="35" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="AS173" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT173" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV173" s="35" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW173" s="35" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX173" s="35" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="AY173" s="35" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+      <c r="AZ173" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY</t>
+        </is>
+      </c>
+      <c r="BA173" s="35" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB173" s="35" t="inlineStr">
+        <is>
+          <t>Confirmed Buy</t>
+        </is>
+      </c>
+      <c r="BC173" s="35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="BD173" s="35" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE173" s="35" t="inlineStr">
+        <is>
+          <t>Target 1 @ 599.76</t>
+        </is>
+      </c>
+      <c r="BF173" s="35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG173" s="35" t="inlineStr">
+        <is>
+          <t>🟢 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="36" t="inlineStr">
+        <is>
+          <t>OFSS_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B174" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C174" s="36" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D174" s="36" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E174" s="36" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="F174" s="36" t="n"/>
+      <c r="G174" s="36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H174" s="36" t="n"/>
+      <c r="I174" s="36" t="n"/>
+      <c r="J174" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="L174" s="36" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M174" s="36" t="n">
+        <v>74</v>
+      </c>
+      <c r="N174" s="36" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O174" s="36" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="P174" s="36" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q174" s="36" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+47 more) → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R174" s="36" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 6→3 · Conf 46% · band HOLD · 16d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S174" s="36" t="n"/>
+      <c r="T174" s="36" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="U174" s="36" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V174" s="36" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="W174" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="X174" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y174" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z174" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA174" s="36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB174" s="36" t="n">
+        <v>11805</v>
+      </c>
+      <c r="AC174" s="36" t="n">
+        <v>11075</v>
+      </c>
+      <c r="AD174" s="36" t="n">
+        <v>11686.95</v>
+      </c>
+      <c r="AE174" s="36" t="n">
+        <v>11923.05</v>
+      </c>
+      <c r="AF174" s="36" t="n">
+        <v>11096.7</v>
+      </c>
+      <c r="AG174" s="36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH174" s="36" t="n">
+        <v>13221.6</v>
+      </c>
+      <c r="AI174" s="36" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="AJ174" s="36" t="n">
+        <v>14638.2</v>
+      </c>
+      <c r="AK174" s="36" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="AL174" s="36" t="n">
+        <v>11805</v>
+      </c>
+      <c r="AM174" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN174" s="36" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="AO174" s="36" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AP174" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ174" s="36" t="inlineStr">
+        <is>
+          <t>Quality · Growth · Momentum</t>
+        </is>
+      </c>
+      <c r="AR174" s="36" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="AS174" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT174" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV174" s="36" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW174" s="36" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX174" s="36" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="AY174" s="36" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+      <c r="AZ174" s="36" t="inlineStr">
+        <is>
+          <t>🟢 BUY</t>
+        </is>
+      </c>
+      <c r="BA174" s="36" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB174" s="36" t="inlineStr">
+        <is>
+          <t>Confirmed Buy</t>
+        </is>
+      </c>
+      <c r="BC174" s="36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="BD174" s="36" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE174" s="36" t="inlineStr">
+        <is>
+          <t>Target 1 @ 13221.60</t>
+        </is>
+      </c>
+      <c r="BF174" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG174" s="36" t="inlineStr">
+        <is>
+          <t>🟢 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="35" t="inlineStr">
+        <is>
+          <t>ICICIBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B175" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C175" s="35" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D175" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E175" s="35" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="F175" s="35" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="G175" s="35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H175" s="35" t="n"/>
+      <c r="I175" s="35" t="n"/>
+      <c r="J175" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L175" s="35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M175" s="35" t="n"/>
+      <c r="N175" s="35" t="n"/>
+      <c r="O175" s="35" t="n"/>
+      <c r="P175" s="35" t="n"/>
+      <c r="Q175" s="35" t="n"/>
+      <c r="R175" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 82% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S175" s="35" t="n"/>
+      <c r="T175" s="35" t="n">
+        <v>82</v>
+      </c>
+      <c r="U175" s="35" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V175" s="35" t="n">
+        <v>76</v>
+      </c>
+      <c r="W175" s="35" t="n"/>
+      <c r="X175" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y175" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z175" s="35" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA175" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB175" s="35" t="n">
+        <v>1421</v>
+      </c>
+      <c r="AC175" s="35" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="AD175" s="35" t="n">
+        <v>1382</v>
+      </c>
+      <c r="AE175" s="35" t="n">
+        <v>1460</v>
+      </c>
+      <c r="AF175" s="35" t="n">
+        <v>1349.95</v>
+      </c>
+      <c r="AG175" s="35" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="AH175" s="35" t="n">
+        <v>1497</v>
+      </c>
+      <c r="AI175" s="35" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AJ175" s="35" t="n">
+        <v>1601.79</v>
+      </c>
+      <c r="AK175" s="35" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="AL175" s="35" t="n">
+        <v>1421</v>
+      </c>
+      <c r="AM175" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN175" s="35" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="AO175" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP175" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ175" s="35" t="n"/>
+      <c r="AR175" s="35" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AS175" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT175" s="35" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AU175" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV175" s="35" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW175" s="35" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX175" s="35" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="AY175" s="35" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ175" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY</t>
+        </is>
+      </c>
+      <c r="BA175" s="35" t="inlineStr">
+        <is>
+          <t>🔴 HIGH</t>
+        </is>
+      </c>
+      <c r="BB175" s="35" t="inlineStr">
+        <is>
+          <t>Conviction Buy</t>
+        </is>
+      </c>
+      <c r="BC175" s="35" t="inlineStr">
+        <is>
+          <t>BUY BIG</t>
+        </is>
+      </c>
+      <c r="BD175" s="35" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE175" s="35" t="inlineStr">
+        <is>
+          <t>Target 1 @ 1497.00</t>
+        </is>
+      </c>
+      <c r="BF175" s="35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG175" s="35" t="inlineStr">
+        <is>
+          <t>🟢 Normal window · 10:00-14:30 IST · staged entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="35" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B176" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C176" s="35" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D176" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E176" s="35" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="F176" s="35" t="inlineStr">
+        <is>
+          <t>Sun Pharma</t>
+        </is>
+      </c>
+      <c r="G176" s="35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H176" s="35" t="n"/>
+      <c r="I176" s="35" t="n"/>
+      <c r="J176" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K176" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L176" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" s="35" t="n"/>
+      <c r="N176" s="35" t="n"/>
+      <c r="O176" s="35" t="n"/>
+      <c r="P176" s="35" t="n"/>
+      <c r="Q176" s="35" t="n"/>
+      <c r="R176" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 1→2 · Conf 88% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S176" s="35" t="n"/>
+      <c r="T176" s="35" t="n">
+        <v>88</v>
+      </c>
+      <c r="U176" s="35" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V176" s="35" t="n">
+        <v>74</v>
+      </c>
+      <c r="W176" s="35" t="n"/>
+      <c r="X176" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y176" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z176" s="35" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA176" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB176" s="35" t="n">
+        <v>1945</v>
+      </c>
+      <c r="AC176" s="35" t="n">
+        <v>2014.8</v>
+      </c>
+      <c r="AD176" s="35" t="n">
+        <v>1893</v>
+      </c>
+      <c r="AE176" s="35" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AF176" s="35" t="n">
+        <v>1847.75</v>
+      </c>
+      <c r="AG176" s="35" t="n">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="AH176" s="35" t="n">
+        <v>2034</v>
+      </c>
+      <c r="AI176" s="35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ176" s="35" t="n">
+        <v>2176.38</v>
+      </c>
+      <c r="AK176" s="35" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="AL176" s="35" t="n">
+        <v>1945</v>
+      </c>
+      <c r="AM176" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN176" s="35" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="AO176" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP176" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ176" s="35" t="n"/>
+      <c r="AR176" s="35" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AS176" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT176" s="35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AU176" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV176" s="35" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW176" s="35" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX176" s="35" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="AY176" s="35" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ176" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY</t>
+        </is>
+      </c>
+      <c r="BA176" s="35" t="inlineStr">
+        <is>
+          <t>🔴 HIGH</t>
+        </is>
+      </c>
+      <c r="BB176" s="35" t="inlineStr">
+        <is>
+          <t>Conviction Buy</t>
+        </is>
+      </c>
+      <c r="BC176" s="35" t="inlineStr">
+        <is>
+          <t>BUY BIG</t>
+        </is>
+      </c>
+      <c r="BD176" s="35" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE176" s="35" t="inlineStr">
+        <is>
+          <t>Target 1 @ 2034.00</t>
+        </is>
+      </c>
+      <c r="BF176" s="35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG176" s="35" t="inlineStr">
+        <is>
+          <t>🟢 Normal window · 10:00-14:30 IST · staged entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="35" t="inlineStr">
+        <is>
+          <t>PIDILITIND_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B177" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C177" s="35" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D177" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E177" s="35" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="F177" s="35" t="inlineStr">
+        <is>
+          <t>Pidilite</t>
+        </is>
+      </c>
+      <c r="G177" s="35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H177" s="35" t="n"/>
+      <c r="I177" s="35" t="n"/>
+      <c r="J177" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L177" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="35" t="n"/>
+      <c r="N177" s="35" t="n"/>
+      <c r="O177" s="35" t="n"/>
+      <c r="P177" s="35" t="n"/>
+      <c r="Q177" s="35" t="n"/>
+      <c r="R177" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.1%) · Rank → 3→3 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S177" s="35" t="n"/>
+      <c r="T177" s="35" t="n">
+        <v>86</v>
+      </c>
+      <c r="U177" s="35" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V177" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="W177" s="35" t="n"/>
+      <c r="X177" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y177" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z177" s="35" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA177" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB177" s="35" t="n">
+        <v>1660</v>
+      </c>
+      <c r="AC177" s="35" t="n">
+        <v>1625.5</v>
+      </c>
+      <c r="AD177" s="35" t="n">
+        <v>1607</v>
+      </c>
+      <c r="AE177" s="35" t="n">
+        <v>1713</v>
+      </c>
+      <c r="AF177" s="35" t="n">
+        <v>1577</v>
+      </c>
+      <c r="AG177" s="35" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="AH177" s="35" t="n">
+        <v>1683</v>
+      </c>
+      <c r="AI177" s="35" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AJ177" s="35" t="n">
+        <v>1800.81</v>
+      </c>
+      <c r="AK177" s="35" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AL177" s="35" t="n">
+        <v>1660</v>
+      </c>
+      <c r="AM177" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN177" s="35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO177" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP177" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ177" s="35" t="n"/>
+      <c r="AR177" s="35" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="AS177" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT177" s="35" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AU177" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV177" s="35" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW177" s="35" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX177" s="35" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AY177" s="35" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+      <c r="AZ177" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY</t>
+        </is>
+      </c>
+      <c r="BA177" s="35" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB177" s="35" t="inlineStr">
+        <is>
+          <t>Confirmed Buy</t>
+        </is>
+      </c>
+      <c r="BC177" s="35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="BD177" s="35" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE177" s="35" t="inlineStr">
+        <is>
+          <t>Target 1 @ 1683.00</t>
+        </is>
+      </c>
+      <c r="BF177" s="35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG177" s="35" t="inlineStr">
+        <is>
+          <t>🟢 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="35" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B178" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C178" s="35" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D178" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E178" s="35" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F178" s="35" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G178" s="35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H178" s="35" t="n"/>
+      <c r="I178" s="35" t="n"/>
+      <c r="J178" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K178" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L178" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" s="35" t="n"/>
+      <c r="N178" s="35" t="n"/>
+      <c r="O178" s="35" t="n"/>
+      <c r="P178" s="35" t="n"/>
+      <c r="Q178" s="35" t="n"/>
+      <c r="R178" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 3→4 · Conf 71% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S178" s="35" t="n"/>
+      <c r="T178" s="35" t="n">
+        <v>71</v>
+      </c>
+      <c r="U178" s="35" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V178" s="35" t="n">
+        <v>69</v>
+      </c>
+      <c r="W178" s="35" t="n"/>
+      <c r="X178" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y178" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z178" s="35" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA178" s="35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB178" s="35" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AC178" s="35" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AD178" s="35" t="n">
+        <v>2303</v>
+      </c>
+      <c r="AE178" s="35" t="n">
+        <v>2424</v>
+      </c>
+      <c r="AF178" s="35" t="n">
+        <v>2245.325</v>
+      </c>
+      <c r="AG178" s="35" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="AH178" s="35" t="n">
+        <v>2552.58</v>
+      </c>
+      <c r="AI178" s="35" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AJ178" s="35" t="n">
+        <v>2731.260600000001</v>
+      </c>
+      <c r="AK178" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL178" s="35" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AM178" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN178" s="35" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="AO178" s="35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP178" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ178" s="35" t="n"/>
+      <c r="AR178" s="35" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AS178" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT178" s="35" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AU178" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV178" s="35" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW178" s="35" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX178" s="35" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AY178" s="35" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ178" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY</t>
+        </is>
+      </c>
+      <c r="BA178" s="35" t="inlineStr">
+        <is>
+          <t>🔴 HIGH</t>
+        </is>
+      </c>
+      <c r="BB178" s="35" t="inlineStr">
+        <is>
+          <t>Conviction Buy</t>
+        </is>
+      </c>
+      <c r="BC178" s="35" t="inlineStr">
+        <is>
+          <t>BUY BIG</t>
+        </is>
+      </c>
+      <c r="BD178" s="35" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE178" s="35" t="inlineStr">
+        <is>
+          <t>Target 1 @ 2552.58</t>
+        </is>
+      </c>
+      <c r="BF178" s="35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG178" s="35" t="inlineStr">
+        <is>
+          <t>🟢 Normal window · 10:00-14:30 IST · staged entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="35" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B179" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C179" s="35" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D179" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E179" s="35" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="F179" s="35" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="G179" s="35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H179" s="35" t="n"/>
+      <c r="I179" s="35" t="n"/>
+      <c r="J179" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K179" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L179" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="35" t="n"/>
+      <c r="N179" s="35" t="n"/>
+      <c r="O179" s="35" t="n"/>
+      <c r="P179" s="35" t="n"/>
+      <c r="Q179" s="35" t="n"/>
+      <c r="R179" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.8%) · Rank → 5→5 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S179" s="35" t="n"/>
+      <c r="T179" s="35" t="n">
+        <v>72</v>
+      </c>
+      <c r="U179" s="35" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V179" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="W179" s="35" t="n"/>
+      <c r="X179" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y179" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z179" s="35" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA179" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB179" s="35" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="AC179" s="35" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="AD179" s="35" t="n">
+        <v>379</v>
+      </c>
+      <c r="AE179" s="35" t="n">
+        <v>402</v>
+      </c>
+      <c r="AF179" s="35" t="n">
+        <v>371.26</v>
+      </c>
+      <c r="AG179" s="35" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="AH179" s="35" t="n">
+        <v>422.064</v>
+      </c>
+      <c r="AI179" s="35" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AJ179" s="35" t="n">
+        <v>451.60848</v>
+      </c>
+      <c r="AK179" s="35" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="AL179" s="35" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="AM179" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="35" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AO179" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP179" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ179" s="35" t="n"/>
+      <c r="AR179" s="35" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AS179" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT179" s="35" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AU179" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV179" s="35" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW179" s="35" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX179" s="35" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="AY179" s="35" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ179" s="35" t="inlineStr">
+        <is>
+          <t>🟢 BUY</t>
+        </is>
+      </c>
+      <c r="BA179" s="35" t="inlineStr">
+        <is>
+          <t>🔴 HIGH</t>
+        </is>
+      </c>
+      <c r="BB179" s="35" t="inlineStr">
+        <is>
+          <t>Conviction Buy</t>
+        </is>
+      </c>
+      <c r="BC179" s="35" t="inlineStr">
+        <is>
+          <t>BUY BIG</t>
+        </is>
+      </c>
+      <c r="BD179" s="35" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE179" s="35" t="inlineStr">
+        <is>
+          <t>Target 1 @ 422.06</t>
+        </is>
+      </c>
+      <c r="BF179" s="35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG179" s="35" t="inlineStr">
+        <is>
+          <t>🟢 Normal window · 10:00-14:30 IST · staged entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="36" t="inlineStr">
+        <is>
+          <t>NTPC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B180" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C180" s="36" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D180" s="36" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E180" s="36" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F180" s="36" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="G180" s="36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H180" s="36" t="n"/>
+      <c r="I180" s="36" t="n"/>
+      <c r="J180" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="K180" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L180" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" s="36" t="n"/>
+      <c r="N180" s="36" t="n"/>
+      <c r="O180" s="36" t="n"/>
+      <c r="P180" s="36" t="n"/>
+      <c r="Q180" s="36" t="n"/>
+      <c r="R180" s="36" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.4%) · Rank ↓ 4→6 · Conf 72% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S180" s="36" t="n"/>
+      <c r="T180" s="36" t="n">
+        <v>72</v>
+      </c>
+      <c r="U180" s="36" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V180" s="36" t="n">
+        <v>64</v>
+      </c>
+      <c r="W180" s="36" t="n"/>
+      <c r="X180" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y180" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z180" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA180" s="36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB180" s="36" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="AC180" s="36" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="AD180" s="36" t="n">
+        <v>334</v>
+      </c>
+      <c r="AE180" s="36" t="n">
+        <v>351</v>
+      </c>
+      <c r="AF180" s="36" t="n">
+        <v>325.375</v>
+      </c>
+      <c r="AG180" s="36" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="AH180" s="36" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="AI180" s="36" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="AJ180" s="36" t="n">
+        <v>395.7930000000001</v>
+      </c>
+      <c r="AK180" s="36" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AL180" s="36" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="AM180" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN180" s="36" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AO180" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP180" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ180" s="36" t="n"/>
+      <c r="AR180" s="36" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AS180" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT180" s="36" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="AU180" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV180" s="36" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW180" s="36" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX180" s="36" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="AY180" s="36" t="inlineStr">
+        <is>
+          <t>✗ AVOID</t>
+        </is>
+      </c>
+      <c r="AZ180" s="36" t="inlineStr">
+        <is>
+          <t>⚫ SKIP</t>
+        </is>
+      </c>
+      <c r="BA180" s="36" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB180" s="36" t="inlineStr">
+        <is>
+          <t>Signal Warning</t>
+        </is>
+      </c>
+      <c r="BC180" s="36" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="BD180" s="36" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE180" s="36" t="inlineStr"/>
+      <c r="BF180" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG180" s="36" t="inlineStr">
+        <is>
+          <t>⚫ Do not enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="36" t="inlineStr">
+        <is>
+          <t>BEL_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B181" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C181" s="36" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D181" s="36" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E181" s="36" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="F181" s="36" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="G181" s="36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H181" s="36" t="n"/>
+      <c r="I181" s="36" t="n"/>
+      <c r="J181" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K181" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="L181" s="36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M181" s="36" t="n"/>
+      <c r="N181" s="36" t="n"/>
+      <c r="O181" s="36" t="n"/>
+      <c r="P181" s="36" t="n"/>
+      <c r="Q181" s="36" t="n"/>
+      <c r="R181" s="36" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.1%) · Rank ↑ 8→7 · Conf 65% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S181" s="36" t="n"/>
+      <c r="T181" s="36" t="n">
+        <v>65</v>
+      </c>
+      <c r="U181" s="36" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V181" s="36" t="n">
+        <v>56</v>
+      </c>
+      <c r="W181" s="36" t="n"/>
+      <c r="X181" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y181" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z181" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA181" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB181" s="36" t="n">
+        <v>401</v>
+      </c>
+      <c r="AC181" s="36" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="AD181" s="36" t="n">
+        <v>388</v>
+      </c>
+      <c r="AE181" s="36" t="n">
+        <v>414</v>
+      </c>
+      <c r="AF181" s="36" t="n">
+        <v>380.95</v>
+      </c>
+      <c r="AG181" s="36" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="AH181" s="36" t="n">
+        <v>433.08</v>
+      </c>
+      <c r="AI181" s="36" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="AJ181" s="36" t="n">
+        <v>463.3956000000001</v>
+      </c>
+      <c r="AK181" s="36" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="AL181" s="36" t="n">
+        <v>401</v>
+      </c>
+      <c r="AM181" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN181" s="36" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AO181" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP181" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ181" s="36" t="n"/>
+      <c r="AR181" s="36" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="AS181" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT181" s="36" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="AU181" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV181" s="36" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW181" s="36" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX181" s="36" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="AY181" s="36" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ181" s="36" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA181" s="36" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB181" s="36" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC181" s="36" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD181" s="36" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE181" s="36" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 380.95</t>
+        </is>
+      </c>
+      <c r="BF181" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG181" s="36" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="36" t="inlineStr">
+        <is>
+          <t>POWERGRID_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B182" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C182" s="36" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D182" s="36" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E182" s="36" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="F182" s="36" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="G182" s="36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H182" s="36" t="n"/>
+      <c r="I182" s="36" t="n"/>
+      <c r="J182" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="K182" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="L182" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" s="36" t="n"/>
+      <c r="N182" s="36" t="n"/>
+      <c r="O182" s="36" t="n"/>
+      <c r="P182" s="36" t="n"/>
+      <c r="Q182" s="36" t="n"/>
+      <c r="R182" s="36" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.3%) · Rank ↓ 7→8 · Conf 68% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S182" s="36" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T182" s="36" t="n">
+        <v>68</v>
+      </c>
+      <c r="U182" s="36" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V182" s="36" t="n">
+        <v>55</v>
+      </c>
+      <c r="W182" s="36" t="n"/>
+      <c r="X182" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y182" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z182" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA182" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB182" s="36" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="AC182" s="36" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="AD182" s="36" t="n">
+        <v>265</v>
+      </c>
+      <c r="AE182" s="36" t="n">
+        <v>278</v>
+      </c>
+      <c r="AF182" s="36" t="n">
+        <v>258.02</v>
+      </c>
+      <c r="AG182" s="36" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="AH182" s="36" t="n">
+        <v>293.328</v>
+      </c>
+      <c r="AI182" s="36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ182" s="36" t="n">
+        <v>313.86096</v>
+      </c>
+      <c r="AK182" s="36" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AL182" s="36" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="AM182" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN182" s="36" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AO182" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP182" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ182" s="36" t="n"/>
+      <c r="AR182" s="36" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AS182" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT182" s="36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU182" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV182" s="36" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW182" s="36" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX182" s="36" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="AY182" s="36" t="inlineStr">
+        <is>
+          <t>✗ AVOID</t>
+        </is>
+      </c>
+      <c r="AZ182" s="36" t="inlineStr">
+        <is>
+          <t>⚫ SKIP</t>
+        </is>
+      </c>
+      <c r="BA182" s="36" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB182" s="36" t="inlineStr">
+        <is>
+          <t>Signal Warning</t>
+        </is>
+      </c>
+      <c r="BC182" s="36" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="BD182" s="36" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE182" s="36" t="inlineStr"/>
+      <c r="BF182" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG182" s="36" t="inlineStr">
+        <is>
+          <t>⚫ Do not enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="37" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B183" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C183" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D183" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E183" s="37" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F183" s="37" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G183" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H183" s="37" t="n"/>
+      <c r="I183" s="37" t="n"/>
+      <c r="J183" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="K183" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="L183" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" s="37" t="n"/>
+      <c r="N183" s="37" t="n"/>
+      <c r="O183" s="37" t="n"/>
+      <c r="P183" s="37" t="n"/>
+      <c r="Q183" s="37" t="n"/>
+      <c r="R183" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 7→9 · Conf 68% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S183" s="37" t="n"/>
+      <c r="T183" s="37" t="n">
+        <v>68</v>
+      </c>
+      <c r="U183" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V183" s="37" t="n">
+        <v>55</v>
+      </c>
+      <c r="W183" s="37" t="n"/>
+      <c r="X183" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y183" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z183" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA183" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB183" s="37" t="n">
+        <v>519.95</v>
+      </c>
+      <c r="AC183" s="37" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="AD183" s="37" t="n">
+        <v>504</v>
+      </c>
+      <c r="AE183" s="37" t="n">
+        <v>536</v>
+      </c>
+      <c r="AF183" s="37" t="n">
+        <v>494</v>
+      </c>
+      <c r="AG183" s="37" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AH183" s="37" t="n">
+        <v>561.6</v>
+      </c>
+      <c r="AI183" s="37" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AJ183" s="37" t="n">
+        <v>600.912</v>
+      </c>
+      <c r="AK183" s="37" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AL183" s="37" t="n">
+        <v>519.95</v>
+      </c>
+      <c r="AM183" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN183" s="37" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AO183" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP183" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ183" s="37" t="n"/>
+      <c r="AR183" s="37" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="AS183" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT183" s="37" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AU183" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV183" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW183" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX183" s="37" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="AY183" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ183" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA183" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB183" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC183" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD183" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE183" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 494.00</t>
+        </is>
+      </c>
+      <c r="BF183" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG183" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="36" t="inlineStr">
+        <is>
+          <t>ITC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B184" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C184" s="36" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D184" s="36" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E184" s="36" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F184" s="36" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G184" s="36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H184" s="36" t="n"/>
+      <c r="I184" s="36" t="n"/>
+      <c r="J184" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="K184" s="36" t="n"/>
+      <c r="L184" s="36" t="n"/>
+      <c r="M184" s="36" t="n"/>
+      <c r="N184" s="36" t="n"/>
+      <c r="O184" s="36" t="n"/>
+      <c r="P184" s="36" t="n"/>
+      <c r="Q184" s="36" t="n"/>
+      <c r="R184" s="36" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.4%) · Rank #10 · Conf 72% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S184" s="36" t="n"/>
+      <c r="T184" s="36" t="n">
+        <v>72</v>
+      </c>
+      <c r="U184" s="36" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V184" s="36" t="n">
+        <v>54</v>
+      </c>
+      <c r="W184" s="36" t="n"/>
+      <c r="X184" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y184" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z184" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA184" s="36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB184" s="36" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="AC184" s="36" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="AD184" s="36" t="n">
+        <v>279</v>
+      </c>
+      <c r="AE184" s="36" t="n">
+        <v>293</v>
+      </c>
+      <c r="AF184" s="36" t="n">
+        <v>271.795</v>
+      </c>
+      <c r="AG184" s="36" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="AH184" s="36" t="n">
+        <v>287</v>
+      </c>
+      <c r="AI184" s="36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ184" s="36" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="AK184" s="36" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="AL184" s="36" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="AM184" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN184" s="36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO184" s="36" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AP184" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ184" s="36" t="n"/>
+      <c r="AR184" s="36" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AS184" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT184" s="36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU184" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV184" s="36" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW184" s="36" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX184" s="36" t="n">
+        <v>64</v>
+      </c>
+      <c r="AY184" s="36" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ184" s="36" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA184" s="36" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB184" s="36" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC184" s="36" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD184" s="36" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE184" s="36" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 271.80</t>
+        </is>
+      </c>
+      <c r="BF184" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG184" s="36" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="36" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B185" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C185" s="36" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D185" s="36" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E185" s="36" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F185" s="36" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G185" s="36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H185" s="36" t="n"/>
+      <c r="I185" s="36" t="n"/>
+      <c r="J185" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="K185" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="L185" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" s="36" t="n"/>
+      <c r="N185" s="36" t="n"/>
+      <c r="O185" s="36" t="n"/>
+      <c r="P185" s="36" t="n"/>
+      <c r="Q185" s="36" t="n"/>
+      <c r="R185" s="36" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 10→11 · Conf 67% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S185" s="36" t="n"/>
+      <c r="T185" s="36" t="n">
+        <v>67</v>
+      </c>
+      <c r="U185" s="36" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V185" s="36" t="n">
+        <v>53</v>
+      </c>
+      <c r="W185" s="36" t="n"/>
+      <c r="X185" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y185" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z185" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA185" s="36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB185" s="36" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AC185" s="36" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AD185" s="36" t="n">
+        <v>403</v>
+      </c>
+      <c r="AE185" s="36" t="n">
+        <v>428</v>
+      </c>
+      <c r="AF185" s="36" t="n">
+        <v>394.44</v>
+      </c>
+      <c r="AG185" s="36" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="AH185" s="36" t="n">
+        <v>448.416</v>
+      </c>
+      <c r="AI185" s="36" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="AJ185" s="36" t="n">
+        <v>479.80512</v>
+      </c>
+      <c r="AK185" s="36" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="AL185" s="36" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AM185" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN185" s="36" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AO185" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP185" s="36" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ185" s="36" t="n"/>
+      <c r="AR185" s="36" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="AS185" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT185" s="36" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="AU185" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV185" s="36" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW185" s="36" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX185" s="36" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AY185" s="36" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+      <c r="AZ185" s="36" t="inlineStr">
+        <is>
+          <t>🟢 BUY</t>
+        </is>
+      </c>
+      <c r="BA185" s="36" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB185" s="36" t="inlineStr">
+        <is>
+          <t>Confirmed Buy</t>
+        </is>
+      </c>
+      <c r="BC185" s="36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="BD185" s="36" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE185" s="36" t="inlineStr">
+        <is>
+          <t>Target 1 @ 448.42</t>
+        </is>
+      </c>
+      <c r="BF185" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG185" s="36" t="inlineStr">
+        <is>
+          <t>🟢 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="37" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B186" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C186" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D186" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E186" s="37" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F186" s="37" t="n"/>
+      <c r="G186" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H186" s="37" t="n"/>
+      <c r="I186" s="37" t="n"/>
+      <c r="J186" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="K186" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="L186" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="M186" s="37" t="n"/>
+      <c r="N186" s="37" t="n"/>
+      <c r="O186" s="37" t="n"/>
+      <c r="P186" s="37" t="n"/>
+      <c r="Q186" s="37" t="n"/>
+      <c r="R186" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 9→12 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S186" s="37" t="n"/>
+      <c r="T186" s="37" t="n">
+        <v>66</v>
+      </c>
+      <c r="U186" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V186" s="37" t="n">
+        <v>52</v>
+      </c>
+      <c r="W186" s="37" t="n"/>
+      <c r="X186" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y186" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z186" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA186" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB186" s="37" t="n">
+        <v>5510</v>
+      </c>
+      <c r="AC186" s="37" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AD186" s="37" t="n">
+        <v>5366</v>
+      </c>
+      <c r="AE186" s="37" t="n">
+        <v>5654</v>
+      </c>
+      <c r="AF186" s="37" t="n">
+        <v>5234.5</v>
+      </c>
+      <c r="AG186" s="37" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="AH186" s="37" t="n">
+        <v>5950.8</v>
+      </c>
+      <c r="AI186" s="37" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="AJ186" s="37" t="n">
+        <v>6367.356000000001</v>
+      </c>
+      <c r="AK186" s="37" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AL186" s="37" t="n">
+        <v>5510</v>
+      </c>
+      <c r="AM186" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN186" s="37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO186" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP186" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ186" s="37" t="n"/>
+      <c r="AR186" s="37" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AS186" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT186" s="37" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="AU186" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:07</t>
+        </is>
+      </c>
+      <c r="AV186" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW186" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX186" s="37" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AY186" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ186" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA186" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB186" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC186" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD186" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE186" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 5234.50</t>
+        </is>
+      </c>
+      <c r="BF186" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG186" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="37" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B187" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C187" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D187" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E187" s="37" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F187" s="37" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G187" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H187" s="37" t="n"/>
+      <c r="I187" s="37" t="n"/>
+      <c r="J187" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L187" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" s="37" t="n"/>
+      <c r="N187" s="37" t="n"/>
+      <c r="O187" s="37" t="n"/>
+      <c r="P187" s="37" t="n"/>
+      <c r="Q187" s="37" t="n"/>
+      <c r="R187" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S187" s="37" t="n"/>
+      <c r="T187" s="37" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="U187" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V187" s="37" t="n">
+        <v>26</v>
+      </c>
+      <c r="W187" s="37" t="n"/>
+      <c r="X187" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y187" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z187" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA187" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB187" s="37" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AC187" s="37" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AD187" s="37" t="n">
+        <v>2392.83</v>
+      </c>
+      <c r="AE187" s="37" t="n">
+        <v>2441.17</v>
+      </c>
+      <c r="AF187" s="37" t="n">
+        <v>2296.15</v>
+      </c>
+      <c r="AG187" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH187" s="37" t="n">
+        <v>2610.36</v>
+      </c>
+      <c r="AI187" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ187" s="37" t="n">
+        <v>2779.55</v>
+      </c>
+      <c r="AK187" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL187" s="37" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AM187" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="37" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="AO187" s="37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP187" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ187" s="37" t="n"/>
+      <c r="AR187" s="37" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="AS187" s="37" t="n"/>
+      <c r="AT187" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU187" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV187" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW187" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX187" s="37" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AY187" s="37" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ187" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA187" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB187" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC187" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD187" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE187" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 2610.36</t>
+        </is>
+      </c>
+      <c r="BF187" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG187" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="37" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B188" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C188" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D188" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E188" s="37" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="F188" s="37" t="inlineStr">
+        <is>
+          <t>Chambal Fert.</t>
+        </is>
+      </c>
+      <c r="G188" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H188" s="37" t="n"/>
+      <c r="I188" s="37" t="n"/>
+      <c r="J188" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="K188" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L188" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="M188" s="37" t="n"/>
+      <c r="N188" s="37" t="n"/>
+      <c r="O188" s="37" t="n"/>
+      <c r="P188" s="37" t="n"/>
+      <c r="Q188" s="37" t="n"/>
+      <c r="R188" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S188" s="37" t="n"/>
+      <c r="T188" s="37" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U188" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V188" s="37" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W188" s="37" t="n"/>
+      <c r="X188" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y188" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z188" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA188" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB188" s="37" t="n">
+        <v>450.7</v>
+      </c>
+      <c r="AC188" s="37" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="AD188" s="37" t="n">
+        <v>438.92</v>
+      </c>
+      <c r="AE188" s="37" t="n">
+        <v>447.78</v>
+      </c>
+      <c r="AF188" s="37" t="n">
+        <v>421.1825</v>
+      </c>
+      <c r="AG188" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH188" s="37" t="n">
+        <v>478.818</v>
+      </c>
+      <c r="AI188" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ188" s="37" t="n">
+        <v>509.8525</v>
+      </c>
+      <c r="AK188" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL188" s="37" t="n">
+        <v>450.7</v>
+      </c>
+      <c r="AM188" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN188" s="37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO188" s="37" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AP188" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ188" s="37" t="n"/>
+      <c r="AR188" s="37" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="AS188" s="37" t="n"/>
+      <c r="AT188" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU188" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV188" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW188" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX188" s="37" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="AY188" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ188" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA188" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB188" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC188" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD188" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE188" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 421.18</t>
+        </is>
+      </c>
+      <c r="BF188" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG188" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="37" t="inlineStr">
+        <is>
+          <t>PNB_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B189" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C189" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D189" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E189" s="37" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="F189" s="37" t="inlineStr">
+        <is>
+          <t>Punjab Natl. Bank</t>
+        </is>
+      </c>
+      <c r="G189" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H189" s="37" t="n"/>
+      <c r="I189" s="37" t="n"/>
+      <c r="J189" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K189" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L189" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" s="37" t="n"/>
+      <c r="N189" s="37" t="n"/>
+      <c r="O189" s="37" t="n"/>
+      <c r="P189" s="37" t="n"/>
+      <c r="Q189" s="37" t="n"/>
+      <c r="R189" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S189" s="37" t="n"/>
+      <c r="T189" s="37" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="U189" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V189" s="37" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W189" s="37" t="n"/>
+      <c r="X189" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y189" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z189" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA189" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB189" s="37" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="AC189" s="37" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="AD189" s="37" t="n">
+        <v>112.23</v>
+      </c>
+      <c r="AE189" s="37" t="n">
+        <v>114.49</v>
+      </c>
+      <c r="AF189" s="37" t="n">
+        <v>107.692</v>
+      </c>
+      <c r="AG189" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH189" s="37" t="n">
+        <v>122.4288</v>
+      </c>
+      <c r="AI189" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ189" s="37" t="n">
+        <v>130.364</v>
+      </c>
+      <c r="AK189" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL189" s="37" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="AM189" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN189" s="37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AO189" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP189" s="37" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="AQ189" s="37" t="n"/>
+      <c r="AR189" s="37" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="AS189" s="37" t="n"/>
+      <c r="AT189" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU189" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV189" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW189" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX189" s="37" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="AY189" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ189" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA189" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB189" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC189" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD189" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE189" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 107.69</t>
+        </is>
+      </c>
+      <c r="BF189" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG189" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="37" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B190" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C190" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D190" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E190" s="37" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F190" s="37" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G190" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H190" s="37" t="n"/>
+      <c r="I190" s="37" t="n"/>
+      <c r="J190" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K190" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L190" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" s="37" t="n"/>
+      <c r="N190" s="37" t="n"/>
+      <c r="O190" s="37" t="n"/>
+      <c r="P190" s="37" t="n"/>
+      <c r="Q190" s="37" t="n"/>
+      <c r="R190" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S190" s="37" t="n"/>
+      <c r="T190" s="37" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="U190" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V190" s="37" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W190" s="37" t="n"/>
+      <c r="X190" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y190" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z190" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA190" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB190" s="37" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AC190" s="37" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AD190" s="37" t="n">
+        <v>407.19</v>
+      </c>
+      <c r="AE190" s="37" t="n">
+        <v>415.41</v>
+      </c>
+      <c r="AF190" s="37" t="n">
+        <v>390.735</v>
+      </c>
+      <c r="AG190" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH190" s="37" t="n">
+        <v>444.2040000000001</v>
+      </c>
+      <c r="AI190" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ190" s="37" t="n">
+        <v>472.995</v>
+      </c>
+      <c r="AK190" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL190" s="37" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AM190" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="37" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AO190" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP190" s="37" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ190" s="37" t="n"/>
+      <c r="AR190" s="37" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="AS190" s="37" t="n"/>
+      <c r="AT190" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU190" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV190" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW190" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX190" s="37" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AY190" s="37" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+      <c r="AZ190" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA190" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB190" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC190" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD190" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE190" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 444.20</t>
+        </is>
+      </c>
+      <c r="BF190" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG190" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="37" t="inlineStr">
+        <is>
+          <t>ITC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B191" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C191" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D191" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E191" s="37" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F191" s="37" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G191" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H191" s="37" t="n"/>
+      <c r="I191" s="37" t="n"/>
+      <c r="J191" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="K191" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="L191" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M191" s="37" t="n"/>
+      <c r="N191" s="37" t="n"/>
+      <c r="O191" s="37" t="n"/>
+      <c r="P191" s="37" t="n"/>
+      <c r="Q191" s="37" t="n"/>
+      <c r="R191" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S191" s="37" t="n"/>
+      <c r="T191" s="37" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U191" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V191" s="37" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W191" s="37" t="n"/>
+      <c r="X191" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y191" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z191" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA191" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB191" s="37" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="AC191" s="37" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="AD191" s="37" t="n">
+        <v>280.07</v>
+      </c>
+      <c r="AE191" s="37" t="n">
+        <v>285.73</v>
+      </c>
+      <c r="AF191" s="37" t="n">
+        <v>268.7549999999999</v>
+      </c>
+      <c r="AG191" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH191" s="37" t="n">
+        <v>305.532</v>
+      </c>
+      <c r="AI191" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ191" s="37" t="n">
+        <v>325.3349999999999</v>
+      </c>
+      <c r="AK191" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL191" s="37" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="AM191" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN191" s="37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO191" s="37" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AP191" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ191" s="37" t="n"/>
+      <c r="AR191" s="37" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="AS191" s="37" t="n"/>
+      <c r="AT191" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU191" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV191" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW191" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX191" s="37" t="n">
+        <v>64</v>
+      </c>
+      <c r="AY191" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ191" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA191" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB191" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC191" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD191" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE191" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 268.75</t>
+        </is>
+      </c>
+      <c r="BF191" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG191" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="37" t="inlineStr">
+        <is>
+          <t>HINDZINC_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B192" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C192" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D192" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E192" s="37" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="F192" s="37" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc</t>
+        </is>
+      </c>
+      <c r="G192" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H192" s="37" t="n"/>
+      <c r="I192" s="37" t="n"/>
+      <c r="J192" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="K192" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L192" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" s="37" t="n"/>
+      <c r="N192" s="37" t="n"/>
+      <c r="O192" s="37" t="n"/>
+      <c r="P192" s="37" t="n"/>
+      <c r="Q192" s="37" t="n"/>
+      <c r="R192" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S192" s="37" t="n"/>
+      <c r="T192" s="37" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U192" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V192" s="37" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W192" s="37" t="n"/>
+      <c r="X192" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y192" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z192" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA192" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB192" s="37" t="n">
+        <v>603</v>
+      </c>
+      <c r="AC192" s="37" t="n">
+        <v>552.4</v>
+      </c>
+      <c r="AD192" s="37" t="n">
+        <v>546.88</v>
+      </c>
+      <c r="AE192" s="37" t="n">
+        <v>557.92</v>
+      </c>
+      <c r="AF192" s="37" t="n">
+        <v>524.78</v>
+      </c>
+      <c r="AG192" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH192" s="37" t="n">
+        <v>596.592</v>
+      </c>
+      <c r="AI192" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ192" s="37" t="n">
+        <v>635.2599999999999</v>
+      </c>
+      <c r="AK192" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL192" s="37" t="n">
+        <v>603</v>
+      </c>
+      <c r="AM192" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN192" s="37" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="AO192" s="37" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="AP192" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ192" s="37" t="n"/>
+      <c r="AR192" s="37" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="AS192" s="37" t="n"/>
+      <c r="AT192" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU192" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV192" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW192" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX192" s="37" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AY192" s="37" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+      <c r="AZ192" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA192" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB192" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC192" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD192" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE192" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 596.59</t>
+        </is>
+      </c>
+      <c r="BF192" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG192" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="37" t="inlineStr">
+        <is>
+          <t>BATAINDIA_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B193" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C193" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D193" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E193" s="37" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="F193" s="37" t="inlineStr">
+        <is>
+          <t>Bata India</t>
+        </is>
+      </c>
+      <c r="G193" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H193" s="37" t="n"/>
+      <c r="I193" s="37" t="n"/>
+      <c r="J193" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="K193" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="L193" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" s="37" t="n"/>
+      <c r="N193" s="37" t="n"/>
+      <c r="O193" s="37" t="n"/>
+      <c r="P193" s="37" t="n"/>
+      <c r="Q193" s="37" t="n"/>
+      <c r="R193" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S193" s="37" t="n"/>
+      <c r="T193" s="37" t="n">
+        <v>24</v>
+      </c>
+      <c r="U193" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V193" s="37" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="W193" s="37" t="n"/>
+      <c r="X193" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y193" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z193" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA193" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB193" s="37" t="n">
+        <v>720.5</v>
+      </c>
+      <c r="AC193" s="37" t="n">
+        <v>709</v>
+      </c>
+      <c r="AD193" s="37" t="n">
+        <v>701.91</v>
+      </c>
+      <c r="AE193" s="37" t="n">
+        <v>716.09</v>
+      </c>
+      <c r="AF193" s="37" t="n">
+        <v>673.55</v>
+      </c>
+      <c r="AG193" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH193" s="37" t="n">
+        <v>765.72</v>
+      </c>
+      <c r="AI193" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ193" s="37" t="n">
+        <v>815.3499999999999</v>
+      </c>
+      <c r="AK193" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL193" s="37" t="n">
+        <v>720.5</v>
+      </c>
+      <c r="AM193" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN193" s="37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO193" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP193" s="37" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AQ193" s="37" t="n"/>
+      <c r="AR193" s="37" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="AS193" s="37" t="n"/>
+      <c r="AT193" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU193" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV193" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW193" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX193" s="37" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="AY193" s="37" t="inlineStr">
+        <is>
+          <t>✗ AVOID</t>
+        </is>
+      </c>
+      <c r="AZ193" s="37" t="inlineStr">
+        <is>
+          <t>⚫ SKIP</t>
+        </is>
+      </c>
+      <c r="BA193" s="37" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB193" s="37" t="inlineStr">
+        <is>
+          <t>Signal Warning</t>
+        </is>
+      </c>
+      <c r="BC193" s="37" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="BD193" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE193" s="37" t="inlineStr"/>
+      <c r="BF193" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG193" s="37" t="inlineStr">
+        <is>
+          <t>⚫ Do not enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="37" t="inlineStr">
+        <is>
+          <t>IEX_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B194" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C194" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D194" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E194" s="37" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="F194" s="37" t="n"/>
+      <c r="G194" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H194" s="37" t="n"/>
+      <c r="I194" s="37" t="n"/>
+      <c r="J194" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L194" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" s="37" t="n"/>
+      <c r="N194" s="37" t="n"/>
+      <c r="O194" s="37" t="n"/>
+      <c r="P194" s="37" t="n"/>
+      <c r="Q194" s="37" t="n"/>
+      <c r="R194" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 39% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S194" s="37" t="n"/>
+      <c r="T194" s="37" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U194" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V194" s="37" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W194" s="37" t="n"/>
+      <c r="X194" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y194" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z194" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA194" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB194" s="37" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="AC194" s="37" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="AD194" s="37" t="n">
+        <v>131.77</v>
+      </c>
+      <c r="AE194" s="37" t="n">
+        <v>134.43</v>
+      </c>
+      <c r="AF194" s="37" t="n">
+        <v>126.445</v>
+      </c>
+      <c r="AG194" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH194" s="37" t="n">
+        <v>143.748</v>
+      </c>
+      <c r="AI194" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ194" s="37" t="n">
+        <v>153.065</v>
+      </c>
+      <c r="AK194" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL194" s="37" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="AM194" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN194" s="37" t="n">
+        <v>-4.51</v>
+      </c>
+      <c r="AO194" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP194" s="37" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="AQ194" s="37" t="n"/>
+      <c r="AR194" s="37" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="AS194" s="37" t="n"/>
+      <c r="AT194" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU194" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV194" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW194" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX194" s="37" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AY194" s="37" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+      <c r="AZ194" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA194" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB194" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC194" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD194" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE194" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 143.75</t>
+        </is>
+      </c>
+      <c r="BF194" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG194" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="37" t="inlineStr">
+        <is>
+          <t>PERSISTENT_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B195" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C195" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D195" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E195" s="37" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="F195" s="37" t="n"/>
+      <c r="G195" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H195" s="37" t="n"/>
+      <c r="I195" s="37" t="n"/>
+      <c r="J195" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K195" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L195" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" s="37" t="n"/>
+      <c r="N195" s="37" t="n"/>
+      <c r="O195" s="37" t="n"/>
+      <c r="P195" s="37" t="n"/>
+      <c r="Q195" s="37" t="n"/>
+      <c r="R195" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S195" s="37" t="n"/>
+      <c r="T195" s="37" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="U195" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V195" s="37" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="W195" s="37" t="n"/>
+      <c r="X195" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y195" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z195" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA195" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB195" s="37" t="n">
+        <v>5475</v>
+      </c>
+      <c r="AC195" s="37" t="n">
+        <v>5322.4</v>
+      </c>
+      <c r="AD195" s="37" t="n">
+        <v>5269.18</v>
+      </c>
+      <c r="AE195" s="37" t="n">
+        <v>5375.62</v>
+      </c>
+      <c r="AF195" s="37" t="n">
+        <v>5056.28</v>
+      </c>
+      <c r="AG195" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH195" s="37" t="n">
+        <v>5748.192</v>
+      </c>
+      <c r="AI195" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ195" s="37" t="n">
+        <v>6120.759999999999</v>
+      </c>
+      <c r="AK195" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL195" s="37" t="n">
+        <v>5475</v>
+      </c>
+      <c r="AM195" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN195" s="37" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AO195" s="37" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AP195" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ195" s="37" t="n"/>
+      <c r="AR195" s="37" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="AS195" s="37" t="n"/>
+      <c r="AT195" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU195" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV195" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW195" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX195" s="37" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="AY195" s="37" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ195" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA195" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB195" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC195" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD195" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE195" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 5748.19</t>
+        </is>
+      </c>
+      <c r="BF195" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG195" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="37" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B196" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C196" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D196" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E196" s="37" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="F196" s="37" t="n"/>
+      <c r="G196" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H196" s="37" t="n"/>
+      <c r="I196" s="37" t="n"/>
+      <c r="J196" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="K196" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L196" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" s="37" t="n"/>
+      <c r="N196" s="37" t="n"/>
+      <c r="O196" s="37" t="n"/>
+      <c r="P196" s="37" t="n"/>
+      <c r="Q196" s="37" t="n"/>
+      <c r="R196" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S196" s="37" t="n"/>
+      <c r="T196" s="37" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U196" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V196" s="37" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W196" s="37" t="n"/>
+      <c r="X196" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y196" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z196" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA196" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB196" s="37" t="n">
+        <v>11263</v>
+      </c>
+      <c r="AC196" s="37" t="n">
+        <v>11127</v>
+      </c>
+      <c r="AD196" s="37" t="n">
+        <v>11015.73</v>
+      </c>
+      <c r="AE196" s="37" t="n">
+        <v>11238.27</v>
+      </c>
+      <c r="AF196" s="37" t="n">
+        <v>10570.65</v>
+      </c>
+      <c r="AG196" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH196" s="37" t="n">
+        <v>12017.16</v>
+      </c>
+      <c r="AI196" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ196" s="37" t="n">
+        <v>12796.05</v>
+      </c>
+      <c r="AK196" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL196" s="37" t="n">
+        <v>11263</v>
+      </c>
+      <c r="AM196" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN196" s="37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO196" s="37" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AP196" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ196" s="37" t="n"/>
+      <c r="AR196" s="37" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="AS196" s="37" t="n"/>
+      <c r="AT196" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU196" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV196" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW196" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX196" s="37" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AY196" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ196" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA196" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB196" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC196" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD196" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE196" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 10570.65</t>
+        </is>
+      </c>
+      <c r="BF196" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG196" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="37" t="inlineStr">
+        <is>
+          <t>ADANIGREEN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B197" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C197" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D197" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E197" s="37" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="F197" s="37" t="n"/>
+      <c r="G197" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H197" s="37" t="n"/>
+      <c r="I197" s="37" t="n"/>
+      <c r="J197" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="K197" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="L197" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" s="37" t="n"/>
+      <c r="N197" s="37" t="n"/>
+      <c r="O197" s="37" t="n"/>
+      <c r="P197" s="37" t="n"/>
+      <c r="Q197" s="37" t="n"/>
+      <c r="R197" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 28% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S197" s="37" t="n"/>
+      <c r="T197" s="37" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="U197" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V197" s="37" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="W197" s="37" t="n"/>
+      <c r="X197" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y197" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z197" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA197" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB197" s="37" t="n">
+        <v>1372.4</v>
+      </c>
+      <c r="AC197" s="37" t="n">
+        <v>1360.5</v>
+      </c>
+      <c r="AD197" s="37" t="n">
+        <v>1346.89</v>
+      </c>
+      <c r="AE197" s="37" t="n">
+        <v>1374.11</v>
+      </c>
+      <c r="AF197" s="37" t="n">
+        <v>1292.475</v>
+      </c>
+      <c r="AG197" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH197" s="37" t="n">
+        <v>1469.34</v>
+      </c>
+      <c r="AI197" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ197" s="37" t="n">
+        <v>1564.575</v>
+      </c>
+      <c r="AK197" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL197" s="37" t="n">
+        <v>1372.4</v>
+      </c>
+      <c r="AM197" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN197" s="37" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AO197" s="37" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AP197" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ197" s="37" t="n"/>
+      <c r="AR197" s="37" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="AS197" s="37" t="n"/>
+      <c r="AT197" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU197" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV197" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW197" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX197" s="37" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AY197" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ197" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA197" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB197" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC197" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD197" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE197" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 1292.47</t>
+        </is>
+      </c>
+      <c r="BF197" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG197" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="37" t="inlineStr">
+        <is>
+          <t>NATIONALUM_IND_20260805</t>
+        </is>
+      </c>
+      <c r="B198" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C198" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D198" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E198" s="37" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="F198" s="37" t="n"/>
+      <c r="G198" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H198" s="37" t="n"/>
+      <c r="I198" s="37" t="n"/>
+      <c r="J198" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="K198" s="37" t="n"/>
+      <c r="L198" s="37" t="n"/>
+      <c r="M198" s="37" t="n"/>
+      <c r="N198" s="37" t="n"/>
+      <c r="O198" s="37" t="n"/>
+      <c r="P198" s="37" t="n"/>
+      <c r="Q198" s="37" t="n"/>
+      <c r="R198" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #10 · Conf 41% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S198" s="37" t="n"/>
+      <c r="T198" s="37" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="U198" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V198" s="37" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="W198" s="37" t="n"/>
+      <c r="X198" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y198" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z198" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA198" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB198" s="37" t="n">
+        <v>381</v>
+      </c>
+      <c r="AC198" s="37" t="n">
+        <v>377</v>
+      </c>
+      <c r="AD198" s="37" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="AE198" s="37" t="n">
+        <v>380.77</v>
+      </c>
+      <c r="AF198" s="37" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="AG198" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH198" s="37" t="n">
+        <v>407.16</v>
+      </c>
+      <c r="AI198" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ198" s="37" t="n">
+        <v>433.55</v>
+      </c>
+      <c r="AK198" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL198" s="37" t="n">
+        <v>381</v>
+      </c>
+      <c r="AM198" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN198" s="37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AO198" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP198" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ198" s="37" t="n"/>
+      <c r="AR198" s="37" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="AS198" s="37" t="n"/>
+      <c r="AT198" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU198" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV198" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW198" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX198" s="37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AY198" s="37" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ198" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA198" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB198" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC198" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD198" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE198" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 407.16</t>
+        </is>
+      </c>
+      <c r="BF198" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG198" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="37" t="inlineStr">
+        <is>
+          <t>LICI_IND_20260805</t>
+        </is>
+      </c>
+      <c r="B199" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C199" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D199" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E199" s="37" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="F199" s="37" t="n"/>
+      <c r="G199" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H199" s="37" t="n"/>
+      <c r="I199" s="37" t="n"/>
+      <c r="J199" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="K199" s="37" t="n"/>
+      <c r="L199" s="37" t="n"/>
+      <c r="M199" s="37" t="n"/>
+      <c r="N199" s="37" t="n"/>
+      <c r="O199" s="37" t="n"/>
+      <c r="P199" s="37" t="n"/>
+      <c r="Q199" s="37" t="n"/>
+      <c r="R199" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S199" s="37" t="n"/>
+      <c r="T199" s="37" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="U199" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V199" s="37" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="W199" s="37" t="n"/>
+      <c r="X199" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y199" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z199" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA199" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB199" s="37" t="n">
+        <v>394</v>
+      </c>
+      <c r="AC199" s="37" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="AD199" s="37" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="AE199" s="37" t="n">
+        <v>395.21</v>
+      </c>
+      <c r="AF199" s="37" t="n">
+        <v>371.735</v>
+      </c>
+      <c r="AG199" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH199" s="37" t="n">
+        <v>422.604</v>
+      </c>
+      <c r="AI199" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ199" s="37" t="n">
+        <v>449.995</v>
+      </c>
+      <c r="AK199" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL199" s="37" t="n">
+        <v>394</v>
+      </c>
+      <c r="AM199" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN199" s="37" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO199" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP199" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ199" s="37" t="n"/>
+      <c r="AR199" s="37" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="AS199" s="37" t="n"/>
+      <c r="AT199" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU199" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV199" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW199" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX199" s="37" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AY199" s="37" t="inlineStr">
+        <is>
+          <t>✗ AVOID</t>
+        </is>
+      </c>
+      <c r="AZ199" s="37" t="inlineStr">
+        <is>
+          <t>⚫ SKIP</t>
+        </is>
+      </c>
+      <c r="BA199" s="37" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB199" s="37" t="inlineStr">
+        <is>
+          <t>Signal Warning</t>
+        </is>
+      </c>
+      <c r="BC199" s="37" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="BD199" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE199" s="37" t="inlineStr"/>
+      <c r="BF199" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG199" s="37" t="inlineStr">
+        <is>
+          <t>⚫ Do not enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="37" t="inlineStr">
+        <is>
+          <t>TIINDIA_IND_20260805</t>
+        </is>
+      </c>
+      <c r="B200" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C200" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D200" s="37" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E200" s="37" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="F200" s="37" t="n"/>
+      <c r="G200" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H200" s="37" t="n"/>
+      <c r="I200" s="37" t="n"/>
+      <c r="J200" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="K200" s="37" t="n"/>
+      <c r="L200" s="37" t="n"/>
+      <c r="M200" s="37" t="n"/>
+      <c r="N200" s="37" t="n"/>
+      <c r="O200" s="37" t="n"/>
+      <c r="P200" s="37" t="n"/>
+      <c r="Q200" s="37" t="n"/>
+      <c r="R200" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S200" s="37" t="n"/>
+      <c r="T200" s="37" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="U200" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V200" s="37" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="W200" s="37" t="n"/>
+      <c r="X200" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y200" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z200" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA200" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB200" s="37" t="n">
+        <v>2772</v>
+      </c>
+      <c r="AC200" s="37" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="AD200" s="37" t="n">
+        <v>2716.86</v>
+      </c>
+      <c r="AE200" s="37" t="n">
+        <v>2771.74</v>
+      </c>
+      <c r="AF200" s="37" t="n">
+        <v>2607.085</v>
+      </c>
+      <c r="AG200" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH200" s="37" t="n">
+        <v>2963.844000000001</v>
+      </c>
+      <c r="AI200" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ200" s="37" t="n">
+        <v>3155.945</v>
+      </c>
+      <c r="AK200" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL200" s="37" t="n">
+        <v>2772</v>
+      </c>
+      <c r="AM200" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AO200" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP200" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ200" s="37" t="n"/>
+      <c r="AR200" s="37" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="AS200" s="37" t="n"/>
+      <c r="AT200" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU200" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV200" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW200" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX200" s="37" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="AY200" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ200" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA200" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB200" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC200" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD200" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE200" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 2607.09</t>
+        </is>
+      </c>
+      <c r="BF200" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG200" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="37" t="inlineStr">
+        <is>
+          <t>ICICIBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B201" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C201" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D201" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E201" s="37" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="F201" s="37" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="G201" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H201" s="37" t="n"/>
+      <c r="I201" s="37" t="n"/>
+      <c r="J201" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K201" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L201" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" s="37" t="n"/>
+      <c r="N201" s="37" t="n"/>
+      <c r="O201" s="37" t="n"/>
+      <c r="P201" s="37" t="n"/>
+      <c r="Q201" s="37" t="n"/>
+      <c r="R201" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 83% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S201" s="37" t="n"/>
+      <c r="T201" s="37" t="n">
+        <v>83</v>
+      </c>
+      <c r="U201" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V201" s="37" t="n">
+        <v>77</v>
+      </c>
+      <c r="W201" s="37" t="n"/>
+      <c r="X201" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y201" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z201" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA201" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB201" s="37" t="n">
+        <v>1421</v>
+      </c>
+      <c r="AC201" s="37" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="AD201" s="37" t="n">
+        <v>1424.12</v>
+      </c>
+      <c r="AE201" s="37" t="n">
+        <v>1452.88</v>
+      </c>
+      <c r="AF201" s="37" t="n">
+        <v>1366.575</v>
+      </c>
+      <c r="AG201" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH201" s="37" t="n">
+        <v>1553.58</v>
+      </c>
+      <c r="AI201" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ201" s="37" t="n">
+        <v>1654.275</v>
+      </c>
+      <c r="AK201" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL201" s="37" t="n">
+        <v>1421</v>
+      </c>
+      <c r="AM201" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN201" s="37" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="AO201" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP201" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ201" s="37" t="n"/>
+      <c r="AR201" s="37" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="AS201" s="37" t="n"/>
+      <c r="AT201" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU201" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV201" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW201" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX201" s="37" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="AY201" s="37" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ201" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA201" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB201" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC201" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD201" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE201" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 1553.58</t>
+        </is>
+      </c>
+      <c r="BF201" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG201" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="37" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B202" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C202" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D202" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E202" s="37" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="F202" s="37" t="inlineStr">
+        <is>
+          <t>Sun Pharma</t>
+        </is>
+      </c>
+      <c r="G202" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H202" s="37" t="n"/>
+      <c r="I202" s="37" t="n"/>
+      <c r="J202" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L202" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" s="37" t="n"/>
+      <c r="N202" s="37" t="n"/>
+      <c r="O202" s="37" t="n"/>
+      <c r="P202" s="37" t="n"/>
+      <c r="Q202" s="37" t="n"/>
+      <c r="R202" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 90% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S202" s="37" t="n"/>
+      <c r="T202" s="37" t="n">
+        <v>90</v>
+      </c>
+      <c r="U202" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V202" s="37" t="n">
+        <v>77</v>
+      </c>
+      <c r="W202" s="37" t="n"/>
+      <c r="X202" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y202" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z202" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA202" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB202" s="37" t="n">
+        <v>1945</v>
+      </c>
+      <c r="AC202" s="37" t="n">
+        <v>2014.8</v>
+      </c>
+      <c r="AD202" s="37" t="n">
+        <v>1994.65</v>
+      </c>
+      <c r="AE202" s="37" t="n">
+        <v>2034.95</v>
+      </c>
+      <c r="AF202" s="37" t="n">
+        <v>1914.06</v>
+      </c>
+      <c r="AG202" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH202" s="37" t="n">
+        <v>2175.984</v>
+      </c>
+      <c r="AI202" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ202" s="37" t="n">
+        <v>2317.02</v>
+      </c>
+      <c r="AK202" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL202" s="37" t="n">
+        <v>1945</v>
+      </c>
+      <c r="AM202" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN202" s="37" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="AO202" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP202" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ202" s="37" t="n"/>
+      <c r="AR202" s="37" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="AS202" s="37" t="n"/>
+      <c r="AT202" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU202" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV202" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW202" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX202" s="37" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="AY202" s="37" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ202" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA202" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB202" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC202" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD202" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE202" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 2175.98</t>
+        </is>
+      </c>
+      <c r="BF202" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG202" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="37" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B203" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C203" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D203" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E203" s="37" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F203" s="37" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G203" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H203" s="37" t="n"/>
+      <c r="I203" s="37" t="n"/>
+      <c r="J203" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L203" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" s="37" t="n"/>
+      <c r="N203" s="37" t="n"/>
+      <c r="O203" s="37" t="n"/>
+      <c r="P203" s="37" t="n"/>
+      <c r="Q203" s="37" t="n"/>
+      <c r="R203" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S203" s="37" t="n"/>
+      <c r="T203" s="37" t="n">
+        <v>72</v>
+      </c>
+      <c r="U203" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V203" s="37" t="n">
+        <v>71</v>
+      </c>
+      <c r="W203" s="37" t="n"/>
+      <c r="X203" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y203" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z203" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA203" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB203" s="37" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AC203" s="37" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AD203" s="37" t="n">
+        <v>2392.83</v>
+      </c>
+      <c r="AE203" s="37" t="n">
+        <v>2441.17</v>
+      </c>
+      <c r="AF203" s="37" t="n">
+        <v>2296.15</v>
+      </c>
+      <c r="AG203" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH203" s="37" t="n">
+        <v>2610.36</v>
+      </c>
+      <c r="AI203" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ203" s="37" t="n">
+        <v>2779.55</v>
+      </c>
+      <c r="AK203" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL203" s="37" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AM203" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN203" s="37" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="AO203" s="37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP203" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ203" s="37" t="n"/>
+      <c r="AR203" s="37" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="AS203" s="37" t="n"/>
+      <c r="AT203" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU203" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV203" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW203" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX203" s="37" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AY203" s="37" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ203" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA203" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB203" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC203" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD203" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE203" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 2610.36</t>
+        </is>
+      </c>
+      <c r="BF203" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG203" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="37" t="inlineStr">
+        <is>
+          <t>PIDILITIND_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B204" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C204" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D204" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E204" s="37" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="F204" s="37" t="inlineStr">
+        <is>
+          <t>Pidilite</t>
+        </is>
+      </c>
+      <c r="G204" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H204" s="37" t="n"/>
+      <c r="I204" s="37" t="n"/>
+      <c r="J204" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L204" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" s="37" t="n"/>
+      <c r="N204" s="37" t="n"/>
+      <c r="O204" s="37" t="n"/>
+      <c r="P204" s="37" t="n"/>
+      <c r="Q204" s="37" t="n"/>
+      <c r="R204" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S204" s="37" t="n"/>
+      <c r="T204" s="37" t="n">
+        <v>87</v>
+      </c>
+      <c r="U204" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V204" s="37" t="n">
+        <v>71</v>
+      </c>
+      <c r="W204" s="37" t="n"/>
+      <c r="X204" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y204" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z204" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA204" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB204" s="37" t="n">
+        <v>1660</v>
+      </c>
+      <c r="AC204" s="37" t="n">
+        <v>1625.5</v>
+      </c>
+      <c r="AD204" s="37" t="n">
+        <v>1609.24</v>
+      </c>
+      <c r="AE204" s="37" t="n">
+        <v>1641.76</v>
+      </c>
+      <c r="AF204" s="37" t="n">
+        <v>1544.225</v>
+      </c>
+      <c r="AG204" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH204" s="37" t="n">
+        <v>1755.54</v>
+      </c>
+      <c r="AI204" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ204" s="37" t="n">
+        <v>1869.325</v>
+      </c>
+      <c r="AK204" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL204" s="37" t="n">
+        <v>1660</v>
+      </c>
+      <c r="AM204" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN204" s="37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO204" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP204" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ204" s="37" t="n"/>
+      <c r="AR204" s="37" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="AS204" s="37" t="n"/>
+      <c r="AT204" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU204" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV204" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW204" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX204" s="37" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AY204" s="37" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+      <c r="AZ204" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA204" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB204" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC204" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD204" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE204" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 1755.54</t>
+        </is>
+      </c>
+      <c r="BF204" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG204" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="37" t="inlineStr">
+        <is>
+          <t>NTPC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B205" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C205" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D205" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E205" s="37" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F205" s="37" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="G205" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H205" s="37" t="n"/>
+      <c r="I205" s="37" t="n"/>
+      <c r="J205" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K205" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L205" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" s="37" t="n"/>
+      <c r="N205" s="37" t="n"/>
+      <c r="O205" s="37" t="n"/>
+      <c r="P205" s="37" t="n"/>
+      <c r="Q205" s="37" t="n"/>
+      <c r="R205" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S205" s="37" t="n"/>
+      <c r="T205" s="37" t="n">
+        <v>72</v>
+      </c>
+      <c r="U205" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V205" s="37" t="n">
+        <v>65</v>
+      </c>
+      <c r="W205" s="37" t="n"/>
+      <c r="X205" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y205" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z205" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA205" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB205" s="37" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="AC205" s="37" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="AD205" s="37" t="n">
+        <v>342.29</v>
+      </c>
+      <c r="AE205" s="37" t="n">
+        <v>349.21</v>
+      </c>
+      <c r="AF205" s="37" t="n">
+        <v>328.4625</v>
+      </c>
+      <c r="AG205" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH205" s="37" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="AI205" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ205" s="37" t="n">
+        <v>397.6125</v>
+      </c>
+      <c r="AK205" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL205" s="37" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="AM205" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN205" s="37" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AO205" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP205" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ205" s="37" t="n"/>
+      <c r="AR205" s="37" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="AS205" s="37" t="n"/>
+      <c r="AT205" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU205" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV205" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW205" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX205" s="37" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="AY205" s="37" t="inlineStr">
+        <is>
+          <t>✗ AVOID</t>
+        </is>
+      </c>
+      <c r="AZ205" s="37" t="inlineStr">
+        <is>
+          <t>⚫ SKIP</t>
+        </is>
+      </c>
+      <c r="BA205" s="37" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB205" s="37" t="inlineStr">
+        <is>
+          <t>Signal Warning</t>
+        </is>
+      </c>
+      <c r="BC205" s="37" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="BD205" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE205" s="37" t="inlineStr"/>
+      <c r="BF205" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG205" s="37" t="inlineStr">
+        <is>
+          <t>⚫ Do not enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="37" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B206" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C206" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D206" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E206" s="37" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="F206" s="37" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="G206" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H206" s="37" t="n"/>
+      <c r="I206" s="37" t="n"/>
+      <c r="J206" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K206" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L206" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" s="37" t="n"/>
+      <c r="N206" s="37" t="n"/>
+      <c r="O206" s="37" t="n"/>
+      <c r="P206" s="37" t="n"/>
+      <c r="Q206" s="37" t="n"/>
+      <c r="R206" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S206" s="37" t="n"/>
+      <c r="T206" s="37" t="n">
+        <v>71</v>
+      </c>
+      <c r="U206" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V206" s="37" t="n">
+        <v>63</v>
+      </c>
+      <c r="W206" s="37" t="n"/>
+      <c r="X206" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y206" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z206" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA206" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB206" s="37" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="AC206" s="37" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="AD206" s="37" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="AE206" s="37" t="n">
+        <v>393.19</v>
+      </c>
+      <c r="AF206" s="37" t="n">
+        <v>369.835</v>
+      </c>
+      <c r="AG206" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH206" s="37" t="n">
+        <v>420.444</v>
+      </c>
+      <c r="AI206" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ206" s="37" t="n">
+        <v>447.695</v>
+      </c>
+      <c r="AK206" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL206" s="37" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="AM206" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN206" s="37" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AO206" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP206" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ206" s="37" t="n"/>
+      <c r="AR206" s="37" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="AS206" s="37" t="n"/>
+      <c r="AT206" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU206" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV206" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW206" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX206" s="37" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="AY206" s="37" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ206" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA206" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB206" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC206" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD206" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE206" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 420.44</t>
+        </is>
+      </c>
+      <c r="BF206" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG206" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="37" t="inlineStr">
+        <is>
+          <t>POWERGRID_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B207" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C207" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D207" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E207" s="37" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="F207" s="37" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="G207" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H207" s="37" t="n"/>
+      <c r="I207" s="37" t="n"/>
+      <c r="J207" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="K207" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="L207" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" s="37" t="n"/>
+      <c r="N207" s="37" t="n"/>
+      <c r="O207" s="37" t="n"/>
+      <c r="P207" s="37" t="n"/>
+      <c r="Q207" s="37" t="n"/>
+      <c r="R207" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 69% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S207" s="37" t="n"/>
+      <c r="T207" s="37" t="n">
+        <v>69</v>
+      </c>
+      <c r="U207" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V207" s="37" t="n">
+        <v>58</v>
+      </c>
+      <c r="W207" s="37" t="n"/>
+      <c r="X207" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y207" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z207" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA207" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB207" s="37" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="AC207" s="37" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="AD207" s="37" t="n">
+        <v>283.04</v>
+      </c>
+      <c r="AE207" s="37" t="n">
+        <v>288.76</v>
+      </c>
+      <c r="AF207" s="37" t="n">
+        <v>271.605</v>
+      </c>
+      <c r="AG207" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH207" s="37" t="n">
+        <v>308.772</v>
+      </c>
+      <c r="AI207" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ207" s="37" t="n">
+        <v>328.785</v>
+      </c>
+      <c r="AK207" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL207" s="37" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="AM207" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AO207" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP207" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ207" s="37" t="n"/>
+      <c r="AR207" s="37" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="AS207" s="37" t="n"/>
+      <c r="AT207" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU207" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV207" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW207" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX207" s="37" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="AY207" s="37" t="inlineStr">
+        <is>
+          <t>✗ AVOID</t>
+        </is>
+      </c>
+      <c r="AZ207" s="37" t="inlineStr">
+        <is>
+          <t>⚫ SKIP</t>
+        </is>
+      </c>
+      <c r="BA207" s="37" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB207" s="37" t="inlineStr">
+        <is>
+          <t>Signal Warning</t>
+        </is>
+      </c>
+      <c r="BC207" s="37" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="BD207" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE207" s="37" t="inlineStr"/>
+      <c r="BF207" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG207" s="37" t="inlineStr">
+        <is>
+          <t>⚫ Do not enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="37" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B208" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C208" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D208" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E208" s="37" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F208" s="37" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G208" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H208" s="37" t="n"/>
+      <c r="I208" s="37" t="n"/>
+      <c r="J208" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="K208" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="L208" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" s="37" t="n"/>
+      <c r="N208" s="37" t="n"/>
+      <c r="O208" s="37" t="n"/>
+      <c r="P208" s="37" t="n"/>
+      <c r="Q208" s="37" t="n"/>
+      <c r="R208" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S208" s="37" t="n"/>
+      <c r="T208" s="37" t="n">
+        <v>67</v>
+      </c>
+      <c r="U208" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V208" s="37" t="n">
+        <v>54</v>
+      </c>
+      <c r="W208" s="37" t="n"/>
+      <c r="X208" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y208" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z208" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA208" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB208" s="37" t="n">
+        <v>519.95</v>
+      </c>
+      <c r="AC208" s="37" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="AD208" s="37" t="n">
+        <v>489.41</v>
+      </c>
+      <c r="AE208" s="37" t="n">
+        <v>499.29</v>
+      </c>
+      <c r="AF208" s="37" t="n">
+        <v>469.6325</v>
+      </c>
+      <c r="AG208" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH208" s="37" t="n">
+        <v>533.898</v>
+      </c>
+      <c r="AI208" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ208" s="37" t="n">
+        <v>568.5024999999999</v>
+      </c>
+      <c r="AK208" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL208" s="37" t="n">
+        <v>519.95</v>
+      </c>
+      <c r="AM208" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN208" s="37" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AO208" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP208" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ208" s="37" t="n"/>
+      <c r="AR208" s="37" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="AS208" s="37" t="n"/>
+      <c r="AT208" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU208" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV208" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW208" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX208" s="37" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="AY208" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ208" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA208" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB208" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC208" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD208" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE208" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 469.63</t>
+        </is>
+      </c>
+      <c r="BF208" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG208" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="37" t="inlineStr">
+        <is>
+          <t>BEL_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B209" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C209" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D209" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E209" s="37" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="F209" s="37" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="G209" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H209" s="37" t="n"/>
+      <c r="I209" s="37" t="n"/>
+      <c r="J209" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="K209" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="L209" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" s="37" t="n"/>
+      <c r="N209" s="37" t="n"/>
+      <c r="O209" s="37" t="n"/>
+      <c r="P209" s="37" t="n"/>
+      <c r="Q209" s="37" t="n"/>
+      <c r="R209" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 8→8 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S209" s="37" t="n"/>
+      <c r="T209" s="37" t="n">
+        <v>64</v>
+      </c>
+      <c r="U209" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V209" s="37" t="n">
+        <v>53</v>
+      </c>
+      <c r="W209" s="37" t="n"/>
+      <c r="X209" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y209" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z209" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA209" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB209" s="37" t="n">
+        <v>401</v>
+      </c>
+      <c r="AC209" s="37" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="AD209" s="37" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="AE209" s="37" t="n">
+        <v>392.59</v>
+      </c>
+      <c r="AF209" s="37" t="n">
+        <v>369.265</v>
+      </c>
+      <c r="AG209" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH209" s="37" t="n">
+        <v>419.796</v>
+      </c>
+      <c r="AI209" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ209" s="37" t="n">
+        <v>447.0049999999999</v>
+      </c>
+      <c r="AK209" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL209" s="37" t="n">
+        <v>401</v>
+      </c>
+      <c r="AM209" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN209" s="37" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AO209" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP209" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ209" s="37" t="n"/>
+      <c r="AR209" s="37" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="AS209" s="37" t="n"/>
+      <c r="AT209" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU209" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV209" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW209" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX209" s="37" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="AY209" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ209" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA209" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB209" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC209" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD209" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE209" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 369.26</t>
+        </is>
+      </c>
+      <c r="BF209" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG209" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="37" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B210" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C210" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D210" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E210" s="37" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F210" s="37" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G210" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H210" s="37" t="n"/>
+      <c r="I210" s="37" t="n"/>
+      <c r="J210" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="K210" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L210" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" s="37" t="n"/>
+      <c r="N210" s="37" t="n"/>
+      <c r="O210" s="37" t="n"/>
+      <c r="P210" s="37" t="n"/>
+      <c r="Q210" s="37" t="n"/>
+      <c r="R210" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S210" s="37" t="n"/>
+      <c r="T210" s="37" t="n">
+        <v>66</v>
+      </c>
+      <c r="U210" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V210" s="37" t="n">
+        <v>50</v>
+      </c>
+      <c r="W210" s="37" t="n"/>
+      <c r="X210" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y210" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z210" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA210" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB210" s="37" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AC210" s="37" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AD210" s="37" t="n">
+        <v>407.19</v>
+      </c>
+      <c r="AE210" s="37" t="n">
+        <v>415.41</v>
+      </c>
+      <c r="AF210" s="37" t="n">
+        <v>390.735</v>
+      </c>
+      <c r="AG210" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH210" s="37" t="n">
+        <v>444.2040000000001</v>
+      </c>
+      <c r="AI210" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ210" s="37" t="n">
+        <v>472.995</v>
+      </c>
+      <c r="AK210" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL210" s="37" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AM210" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN210" s="37" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AO210" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP210" s="37" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ210" s="37" t="n"/>
+      <c r="AR210" s="37" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="AS210" s="37" t="n"/>
+      <c r="AT210" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU210" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV210" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW210" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX210" s="37" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AY210" s="37" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+      <c r="AZ210" s="37" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA210" s="37" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB210" s="37" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC210" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD210" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE210" s="37" t="inlineStr">
+        <is>
+          <t>Watching @ 444.20</t>
+        </is>
+      </c>
+      <c r="BF210" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG210" s="37" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="37" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B211" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C211" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D211" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E211" s="37" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F211" s="37" t="n"/>
+      <c r="G211" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H211" s="37" t="n"/>
+      <c r="I211" s="37" t="n"/>
+      <c r="J211" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="K211" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="L211" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" s="37" t="n"/>
+      <c r="N211" s="37" t="n"/>
+      <c r="O211" s="37" t="n"/>
+      <c r="P211" s="37" t="n"/>
+      <c r="Q211" s="37" t="n"/>
+      <c r="R211" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S211" s="37" t="n"/>
+      <c r="T211" s="37" t="n">
+        <v>66</v>
+      </c>
+      <c r="U211" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V211" s="37" t="n">
+        <v>52</v>
+      </c>
+      <c r="W211" s="37" t="n"/>
+      <c r="X211" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y211" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z211" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA211" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB211" s="37" t="n">
+        <v>5510</v>
+      </c>
+      <c r="AC211" s="37" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AD211" s="37" t="n">
+        <v>5351.94</v>
+      </c>
+      <c r="AE211" s="37" t="n">
+        <v>5460.06</v>
+      </c>
+      <c r="AF211" s="37" t="n">
+        <v>5135.7</v>
+      </c>
+      <c r="AG211" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH211" s="37" t="n">
+        <v>5838.48</v>
+      </c>
+      <c r="AI211" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ211" s="37" t="n">
+        <v>6216.9</v>
+      </c>
+      <c r="AK211" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL211" s="37" t="n">
+        <v>5510</v>
+      </c>
+      <c r="AM211" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN211" s="37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO211" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP211" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ211" s="37" t="n"/>
+      <c r="AR211" s="37" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="AS211" s="37" t="n"/>
+      <c r="AT211" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU211" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV211" s="37" t="inlineStr">
+        <is>
+          <t>LargeCap</t>
+        </is>
+      </c>
+      <c r="AW211" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX211" s="37" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AY211" s="37" t="inlineStr">
+        <is>
+          <t>⚠ MARGINAL</t>
+        </is>
+      </c>
+      <c r="AZ211" s="37" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA211" s="37" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB211" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC211" s="37" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD211" s="37" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE211" s="37" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 5135.70</t>
+        </is>
+      </c>
+      <c r="BF211" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG211" s="37" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="37" t="inlineStr">
+        <is>
+          <t>TATAPOWER_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B212" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C212" s="37" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D212" s="37" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E212" s="37" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="F212" s="37" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="G212" s="37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H212" s="37" t="n"/>
+      <c r="I212" s="37" t="n"/>
+      <c r="J212" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="K212" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="L212" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" s="37" t="n"/>
+      <c r="N212" s="37" t="n"/>
+      <c r="O212" s="37" t="n"/>
+      <c r="P212" s="37" t="n"/>
+      <c r="Q212" s="37" t="n"/>
+      <c r="R212" s="37" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S212" s="37" t="n"/>
+      <c r="T212" s="37" t="n">
+        <v>64</v>
+      </c>
+      <c r="U212" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V212" s="37" t="n">
+        <v>54</v>
+      </c>
+      <c r="W212" s="37" t="n"/>
+      <c r="X212" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y212" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z212" s="37" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA212" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB212" s="37" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="AC212" s="37" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="AD212" s="37" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="AE212" s="37" t="n">
+        <v>385.42</v>
+      </c>
+      <c r="AF212" s="37" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="AG212" s="37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH212" s="37" t="n">
+        <v>412.128</v>
+      </c>
+      <c r="AI212" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ212" s="37" t="n">
+        <v>438.84</v>
+      </c>
+      <c r="AK212" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL212" s="37" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="AM212" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN212" s="37" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AO212" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP212" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ212" s="37" t="n"/>
+      <c r="AR212" s="37" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="AS212" s="37" t="n"/>
+      <c r="AT212" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU212" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:12</t>
+        </is>
+      </c>
+      <c r="AV212" s="37" t="inlineStr">
+        <is>
+          <t>MidCap</t>
+        </is>
+      </c>
+      <c r="AW212" s="37" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="AX212" s="37" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="AY212" s="37" t="inlineStr">
+        <is>
+          <t>✗ AVOID</t>
+        </is>
+      </c>
+      <c r="AZ212" s="37" t="inlineStr">
+        <is>
+          <t>⚫ SKIP</t>
+        </is>
+      </c>
+      <c r="BA212" s="37" t="inlineStr">
+        <is>
+          <t>🟠 HIGH</t>
+        </is>
+      </c>
+      <c r="BB212" s="37" t="inlineStr">
+        <is>
+          <t>Signal Warning</t>
+        </is>
+      </c>
+      <c r="BC212" s="37" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="BD212" s="37" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE212" s="37" t="inlineStr"/>
+      <c r="BF212" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG212" s="37" t="inlineStr">
+        <is>
+          <t>⚫ Do not enter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -489,9 +489,11 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -551,17 +553,27 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>Dynamic Stop</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Engine Verdict</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Would-Have-Exited-On</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>As-Of</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Provenance</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -598,19 +610,27 @@
       <c r="H5" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="n">
+        <v>545.1072</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -647,19 +667,27 @@
       <c r="H6" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="n">
+        <v>11017</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -696,19 +724,27 @@
       <c r="H7" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="n">
+        <v>399.7929</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -745,19 +781,27 @@
       <c r="H8" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="n">
+        <v>5402.5</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -794,19 +838,27 @@
       <c r="H9" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="n">
+        <v>2619.7713</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -843,19 +895,27 @@
       <c r="H10" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="n">
+        <v>636.7429</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -892,19 +952,27 @@
       <c r="H11" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -941,19 +1009,27 @@
       <c r="H12" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="n">
+        <v>258.25</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -990,19 +1066,27 @@
       <c r="H13" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="n">
+        <v>109.8471</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -1034,14 +1118,38 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Dynamic Stop = today's stop level from the coded exit engine (dynamic_risk_v2 ATR-based, else recommendation entry_zone.stop_loss, else entry × 0.94).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Engine Verdict = what the coded lifecycle engine (evaluate_position) says today. HOLD if no trigger. EXIT_STOP / EXIT_TARGET / EXIT_HORIZON if triggered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Would-Have-Exited-On = if the engine says exit today, this is the first date the position crossed the trigger. Positions are NOT retroactively closed in the current release · this is audit-only until the wiring is enforced.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A17:K17"/>
+  <mergeCells count="9">
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A16:M16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -661,10 +661,10 @@
         <v>11475</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11333</v>
+        <v>11310</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-1.24</v>
+        <v>-1.44</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>28</v>
@@ -720,10 +720,10 @@
         <v>391.3</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>413.95</v>
+        <v>412.15</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>5.79</v>
+        <v>5.33</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>28</v>
@@ -779,10 +779,10 @@
         <v>5499</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5625.5</v>
+        <v>5800</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2.3</v>
+        <v>5.47</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>28</v>
@@ -838,10 +838,10 @@
         <v>2744.3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2775.8999</v>
+        <v>2763.2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>28</v>
@@ -897,10 +897,10 @@
         <v>709</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>676.2</v>
+        <v>677.35</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-4.63</v>
+        <v>-4.46</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>29</v>
@@ -956,10 +956,10 @@
         <v>452.35</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>413.55</v>
+        <v>412.3</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-8.58</v>
+        <v>-8.85</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>29</v>
@@ -1015,10 +1015,10 @@
         <v>284.85</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>264.9</v>
+        <v>266.6</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-7</v>
+        <v>-6.41</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>29</v>
@@ -1074,10 +1074,10 @@
         <v>113.36</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>113.33</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>-0.03</v>
+        <v>115.22</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.64</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>29</v>
@@ -1179,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1205,7 +1205,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📅 Today's R2 decisions/recommendations · ✓ ledger fresh for 2026-09-02 · scanned universe=0 · by_state={} · sorted acceptance tier</t>
+          <t>📅 Today's R2 decisions/recommendations · ✓ ledger fresh for 2026-09-02 · scanned universe=3 · by_state={'ACCEPTED': 0, 'WATCH': 2, 'REJECTED': 1, 'NO_EVIDENCE': 0} · sorted acceptance tier</t>
         </is>
       </c>
     </row>
@@ -1267,42 +1267,188 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No R2 decisions/recommendations for 2026-09-02 </t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Today + Momentum shows ONLY the current reporting date's R2 decisions/recommendations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Terminal states · ACCEPTED · WATCH · REJECTED · NO_EVIDENCE (quality unavailable).</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>SUSTAINED_UP</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>verdict=MOMENTUM_WATCH · quality=QUALITY · quality-confirmed momentum · BUT weak</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>canonical:momentum_ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>SUSTAINED_UP</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>verdict=MOMENTUM_WATCH · quality=OK · quality + momentum · BUT overbought · wait</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>canonical:momentum_ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>QUICK_RISE</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>verdict=PUMP_RISK · big move on low-quality name · pump-and-dump risk · avoid</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>canonical:momentum_ledger</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday's rows forward.</t>
+          <t>Today + Momentum shows ONLY the current reporting date's R2 decisions/recommendations.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>A recommendation does NOT automatically become a Portfolio holding · only canonical lifecycle transitions move a stock into 01_Portfolio.</t>
+          <t>Terminal states · ACCEPTED · WATCH · REJECTED · NO_EVIDENCE (quality unavailable).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday's rows forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>A recommendation does NOT automatically become a Portfolio holding · only canonical lifecycle transitions move a stock into 01_Portfolio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Only the active production runner (R2) appears in this workbook.</t>
         </is>
@@ -1314,9 +1460,9 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1328,21 +1474,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1355,7 +1502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📕 R2 closed positions (last 90d): 37 · latest exit first · realized P&amp;L only</t>
+          <t>📕 Closed positions (last 90d): 38 · latest exit first · realized P&amp;L only · historical accountability incl. retired runners</t>
         </is>
       </c>
     </row>
@@ -1367,55 +1514,60 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Ticker</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Runner</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Exit Date</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Holding Days</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Realized P&amp;L %</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Provenance</t>
         </is>
@@ -1424,52 +1576,57 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R2-ADANIENT-20260902-51452a</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>27</v>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2383.8999</v>
+        <v>0</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2160.2</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+13.0pp)</t>
-        </is>
+        <v>2863.8999</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>2863.8999</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+57.0pp)</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1478,52 +1635,57 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" s="4" t="n">
-        <v>398.8</v>
+        <v>27</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>398.8</v>
+        <v>2383.8999</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+52.9pp)</t>
-        </is>
+        <v>2160.2</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>-9.380000000000001</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+13.0pp)</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1532,52 +1694,57 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>24</v>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>415.15</v>
+        <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>402.55</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>-3.04</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+14.3pp)</t>
-        </is>
+        <v>398.8</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>398.8</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+52.9pp)</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1586,52 +1753,57 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARICO-20260826-1c5a1c</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0</v>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>847.5</v>
+        <v>24</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>847.5</v>
+        <v>415.15</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+56.7pp)</t>
-        </is>
+        <v>402.55</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-3.04</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+14.3pp)</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1640,52 +1812,57 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
+          <t>IND-R2-MARICO-20260826-1c5a1c</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>1702.7</v>
-      </c>
       <c r="I9" s="4" t="n">
-        <v>1702.7</v>
+        <v>847.5</v>
       </c>
       <c r="J9" s="4" t="n">
+        <v>847.5</v>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+57.6pp)</t>
-        </is>
-      </c>
       <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+56.7pp)</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1694,52 +1871,57 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260824-89850d</t>
+          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>244.55</v>
-      </c>
       <c r="I10" s="4" t="n">
-        <v>244.55</v>
+        <v>1702.7</v>
       </c>
       <c r="J10" s="4" t="n">
+        <v>1702.7</v>
+      </c>
+      <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+10.1pp)</t>
-        </is>
-      </c>
       <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+57.6pp)</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1748,52 +1930,57 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
+          <t>IND-R2-JIOFIN-20260824-89850d</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n">
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>402.8</v>
-      </c>
       <c r="I11" s="4" t="n">
-        <v>402.8</v>
+        <v>244.55</v>
       </c>
       <c r="J11" s="4" t="n">
+        <v>244.55</v>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+13.3pp)</t>
-        </is>
-      </c>
       <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+10.1pp)</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1802,52 +1989,57 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260821-142d93</t>
+          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>1114.2</v>
-      </c>
       <c r="I12" s="4" t="n">
-        <v>1114.2</v>
+        <v>402.8</v>
       </c>
       <c r="J12" s="4" t="n">
+        <v>402.8</v>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+14.5pp)</t>
-        </is>
-      </c>
       <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+13.3pp)</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1856,52 +2048,57 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
+          <t>IND-R2-MGL-20260821-142d93</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>8693</v>
-      </c>
       <c r="I13" s="4" t="n">
-        <v>8693</v>
+        <v>1114.2</v>
       </c>
       <c r="J13" s="4" t="n">
+        <v>1114.2</v>
+      </c>
+      <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+61.4pp)</t>
-        </is>
-      </c>
       <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+14.5pp)</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1910,52 +2107,57 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260820-80f37d</t>
+          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>174.9</v>
-      </c>
       <c r="I14" s="4" t="n">
-        <v>174.9</v>
+        <v>8693</v>
       </c>
       <c r="J14" s="4" t="n">
+        <v>8693</v>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +11.8pp alpha</t>
-        </is>
-      </c>
       <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+61.4pp)</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1964,52 +2166,57 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-SAIL-20260820-80f37d</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>14</v>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>552.4</v>
+        <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>558</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +14.7pp alpha</t>
-        </is>
+        <v>174.9</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +11.8pp alpha</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2018,52 +2225,57 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="H16" s="4" t="n">
-        <v>129.2</v>
+        <v>14</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>-3.72</v>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +12.2pp alpha</t>
-        </is>
+        <v>552.4</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>558</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.01</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +14.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2072,52 +2284,57 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" s="4" t="n">
-        <v>5220</v>
+        <v>13</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5220</v>
+        <v>129.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +60.0pp alpha</t>
-        </is>
+        <v>124.4</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>-3.72</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +12.2pp alpha</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2126,52 +2343,57 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>12</v>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1384</v>
+        <v>0</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1327.6</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +56.7pp alpha</t>
-        </is>
+        <v>5220</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>5220</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +60.0pp alpha</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2180,52 +2402,57 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H19" s="4" t="n">
-        <v>377</v>
-      </c>
       <c r="I19" s="4" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +9.8pp alpha</t>
-        </is>
+        <v>1384</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>1327.6</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>-4.08</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +56.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2234,52 +2461,57 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>9</v>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>11600</v>
+        <v>12</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11828</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +6.6pp alpha</t>
-        </is>
+        <v>377</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>387.55</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>2.8</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +9.8pp alpha</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2288,52 +2520,57 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" s="4" t="n">
-        <v>3940</v>
+        <v>9</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3940</v>
+        <v>11600</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +7.5pp alpha</t>
-        </is>
+        <v>11828</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>1.97</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +6.6pp alpha</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2342,52 +2579,57 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>10</v>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2439.3999</v>
+        <v>0</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2361</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>-3.21</v>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +6.7pp alpha</t>
-        </is>
+        <v>3940</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>3940</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.5pp alpha</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2396,52 +2638,57 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1779.2</v>
+        <v>10</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1779.2</v>
+        <v>2439.3999</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +8.1pp alpha</t>
-        </is>
+        <v>2361</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>-3.21</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +6.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2450,52 +2697,57 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>6</v>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7454.5</v>
+        <v>0</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7095</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>-4.82</v>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>→ TCS.NS · +62.1pp alpha</t>
-        </is>
+        <v>1779.2</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>1779.2</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +8.1pp alpha</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2504,52 +2756,57 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260810-788da8</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" s="4" t="n">
-        <v>129</v>
+        <v>6</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>129</v>
+        <v>7454.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>→ TCS.NS · +6.5pp alpha</t>
-        </is>
+        <v>7095</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>-4.82</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +62.1pp alpha</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2558,52 +2815,57 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
+          <t>IND-R2-CANBK-20260810-788da8</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="4" t="n">
-        <v>4924</v>
-      </c>
       <c r="I26" s="4" t="n">
-        <v>4924</v>
+        <v>129</v>
       </c>
       <c r="J26" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="K26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>→ TCS.NS · +60.1pp alpha</t>
-        </is>
-      </c>
       <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +6.5pp alpha</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2612,52 +2874,57 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
+          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>181.14</v>
-      </c>
       <c r="I27" s="4" t="n">
-        <v>181.14</v>
+        <v>4924</v>
       </c>
       <c r="J27" s="4" t="n">
+        <v>4924</v>
+      </c>
+      <c r="K27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>→ TCS.NS · +9.4pp alpha</t>
-        </is>
-      </c>
       <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +60.1pp alpha</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2666,52 +2933,57 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>2</v>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6793.5</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6774</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +8.0pp alpha</t>
-        </is>
+        <v>181.14</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>181.14</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +9.4pp alpha</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2720,52 +2992,57 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="H29" s="4" t="n">
-        <v>471.2</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +60.7pp alpha</t>
-        </is>
+        <v>6793.5</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>6774</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +8.0pp alpha</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2774,52 +3051,57 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H30" s="4" t="n">
-        <v>845</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>889.5</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +7.4pp alpha</t>
-        </is>
+        <v>471.2</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>473.3</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.45</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +60.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2828,52 +3110,57 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="4" t="n">
-        <v>450</v>
-      </c>
       <c r="I31" s="4" t="n">
-        <v>442.8</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +10.3pp alpha</t>
-        </is>
+        <v>845</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>889.5</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>5.27</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.4pp alpha</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2882,52 +3169,57 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="4" t="n">
-        <v>1595</v>
-      </c>
       <c r="I32" s="4" t="n">
-        <v>1584.8</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +62.5pp alpha</t>
-        </is>
+        <v>450</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>442.8</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>-1.6</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +10.3pp alpha</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2936,52 +3228,57 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>1327.7</v>
-      </c>
       <c r="I33" s="4" t="n">
-        <v>1285</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +64.8pp alpha</t>
-        </is>
+        <v>1595</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>1584.8</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>-0.64</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +62.5pp alpha</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2990,52 +3287,57 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>1</v>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2195</v>
+        <v>2</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +59.7pp alpha</t>
-        </is>
+        <v>1327.7</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>1285</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>-3.22</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +64.8pp alpha</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3044,52 +3346,57 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H35" s="4" t="n">
-        <v>1363.6</v>
+        <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1351.3</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +7.8pp alpha</t>
-        </is>
+        <v>2195</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>2182</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>-0.59</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +59.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3098,52 +3405,57 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>5470.5</v>
-      </c>
       <c r="I36" s="4" t="n">
-        <v>5651.5</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +10.6pp alpha</t>
-        </is>
+        <v>1363.6</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>1351.3</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>-0.9</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.8pp alpha</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3152,52 +3464,57 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="H37" s="4" t="n">
-        <v>1167.5</v>
+        <v>2</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1177</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +11.7pp alpha</t>
-        </is>
+        <v>5470.5</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>5651.5</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>3.31</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +10.6pp alpha</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3206,52 +3523,57 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260804-563905</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H38" s="4" t="n">
-        <v>268.5</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>278.8</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +11.6pp alpha</t>
-        </is>
+        <v>1167.5</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>1177</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +11.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3260,52 +3582,57 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BIOCON-20260804-954a24</t>
+          <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>425.05</v>
+        <v>2</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>425.05</v>
+        <v>268.5</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → LUPIN.NS (+51.8pp)</t>
-        </is>
+        <v>278.8</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>3.84</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +11.6pp alpha</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3314,52 +3641,57 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+          <t>IND-R2-BIOCON-20260804-954a24</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="4" t="n">
-        <v>939.95</v>
-      </c>
       <c r="I40" s="4" t="n">
-        <v>939.95</v>
+        <v>425.05</v>
       </c>
       <c r="J40" s="4" t="n">
+        <v>425.05</v>
+      </c>
+      <c r="K40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>Rotation → LUPIN.NS (+51.8pp)</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3368,93 +3700,157 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>939.95</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>939.95</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>IND-R2-JSWENERGY-20260804-1210a0</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>JSWENERGY</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="I42" s="4" t="n">
         <v>567.3</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="J42" s="4" t="n">
         <v>567.3</v>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="K42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>Rotation → LUPIN.NS (+52.0pp)</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Priced: 37 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Realized P&amp;L % · (Exit − Entry) / Entry · positive=green · negative=red · zero/N/A=neutral.</t>
+          <t>Priced: 38 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>This sheet accumulates closed R2 positions via Registry CLOSED events · latest exit first · 90-day rolling window.</t>
+          <t>Realized P&amp;L % · (Exit − Entry) / Entry · positive=green · negative=red · zero/N/A=neutral.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
+          <t>This sheet accumulates closed R2 positions via Registry CLOSED events · latest exit first · 90-day rolling window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
           <t>This sheet shows the production runner (R2) closed lifecycle only · historical evidence for retired runners lives in canonical audit files only.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A47:L47"/>
-    <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A46:L46"/>
-    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A46:M46"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A47:M47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.0pp)</t>
+          <t>Rotation swap · +57.0 pp</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.0pp)</t>
+          <t>Rotation swap · +13.0 pp</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+52.9pp)</t>
+          <t>Rotation swap · +52.9 pp</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.3pp)</t>
+          <t>Rotation swap · +14.3 pp</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+56.7pp)</t>
+          <t>Rotation swap · +56.7 pp</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.6pp)</t>
+          <t>Rotation swap · +57.6 pp</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+10.1pp)</t>
+          <t>Rotation swap · +10.1 pp</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.3pp)</t>
+          <t>Rotation swap · +13.3 pp</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.5pp)</t>
+          <t>Rotation swap · +14.5 pp</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+61.4pp)</t>
+          <t>Rotation swap · +61.4 pp</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.8pp alpha</t>
+          <t>Outperformance exit · +11.8 pp</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +14.7pp alpha</t>
+          <t>Outperformance exit · +14.7 pp</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +12.2pp alpha</t>
+          <t>Outperformance exit · +12.2 pp</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.0pp alpha</t>
+          <t>Outperformance exit · +60.0 pp</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +56.7pp alpha</t>
+          <t>Outperformance exit · +56.7 pp</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +9.8pp alpha</t>
+          <t>Outperformance exit · +9.8 pp</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.6pp alpha</t>
+          <t>Outperformance exit · +6.6 pp</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.5pp alpha</t>
+          <t>Outperformance exit · +7.5 pp</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.7pp alpha</t>
+          <t>Outperformance exit · +6.7 pp</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.1pp alpha</t>
+          <t>Outperformance exit · +8.1 pp</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +62.1pp alpha</t>
+          <t>Outperformance exit · +62.1 pp</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +6.5pp alpha</t>
+          <t>Outperformance exit · +6.5 pp</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +60.1pp alpha</t>
+          <t>Outperformance exit · +60.1 pp</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +9.4pp alpha</t>
+          <t>Outperformance exit · +9.4 pp</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.0pp alpha</t>
+          <t>Outperformance exit · +8.0 pp</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.7pp alpha</t>
+          <t>Outperformance exit · +60.7 pp</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.4pp alpha</t>
+          <t>Outperformance exit · +7.4 pp</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.3pp alpha</t>
+          <t>Outperformance exit · +10.3 pp</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +62.5pp alpha</t>
+          <t>Outperformance exit · +62.5 pp</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +64.8pp alpha</t>
+          <t>Outperformance exit · +64.8 pp</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +59.7pp alpha</t>
+          <t>Outperformance exit · +59.7 pp</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.8pp alpha</t>
+          <t>Outperformance exit · +7.8 pp</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.6pp alpha</t>
+          <t>Outperformance exit · +10.6 pp</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.7pp alpha</t>
+          <t>Outperformance exit · +11.7 pp</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.6pp alpha</t>
+          <t>Outperformance exit · +11.6 pp</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+          <t>Rotation swap · +51.8 pp</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+          <t>Rotation swap · +51.8 pp</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+52.0pp)</t>
+          <t>Rotation swap · +52.0 pp</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -490,10 +490,11 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,22 +559,27 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>Stop Type</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>Engine Verdict</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Would-Have-Exited-On</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>As-Of</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Provenance</t>
         </is>
       </c>
     </row>
@@ -610,29 +616,32 @@
       <c r="H5" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I5" s="4" t="n">
+        <v>545.1072</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 4.7% below</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -669,29 +678,32 @@
       <c r="H6" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I6" s="4" t="n">
+        <v>10989.5714</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 2.8% below</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -728,29 +740,32 @@
       <c r="H7" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I7" s="4" t="n">
+        <v>397.1429</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 3.6% below</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -787,29 +802,32 @@
       <c r="H8" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I8" s="4" t="n">
+        <v>5557.5714</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 4.2% below</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -846,29 +864,32 @@
       <c r="H9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I9" s="4" t="n">
+        <v>2604.7285</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 5.7% below</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -905,29 +926,32 @@
       <c r="H10" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I10" s="4" t="n">
+        <v>638.4714</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 5.7% below</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -964,29 +988,32 @@
       <c r="H11" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I11" s="4" t="n">
+        <v>399.5571</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 3.1% below</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -1023,29 +1050,32 @@
       <c r="H12" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I12" s="4" t="n">
+        <v>258.9929</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 2.9% below</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -1082,29 +1112,32 @@
       <c r="H13" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I13" s="4" t="n">
+        <v>111.2957</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 3.4% below</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -1159,15 +1192,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A21:M21"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A18:N18"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A19:N19"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1179,20 +1212,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1205,264 +1240,239 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📅 Today's R2 decisions/recommendations · ✓ ledger fresh for 2026-09-02 · scanned universe=3 · by_state={'ACCEPTED': 0, 'WATCH': 2, 'REJECTED': 1, 'NO_EVIDENCE': 0} · sorted acceptance tier</t>
+          <t>📅 Today's R2 momentum scan · ✓ ledger fresh for 2026-09-02 · scanned universe=2 · Actions: {'INVEST': 0, 'WATCH': 0, 'AVOID': 2, 'NO EVIDENCE': 0}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Quality Band</t>
-        </is>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Terminal State</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Entry Zone</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Return 1d %</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Return 5d %</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Return 20d %</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Return 1d %</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Return 5d %</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Return 20d %</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>As-Of</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Attribution</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Provenance</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>AVOID</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SUSTAINED_UP</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>QUICK_FALL</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>verdict=MOMENTUM_WATCH · quality=QUALITY · quality-confirmed momentum · BUT weak</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>2863.8999</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>-6.41</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>verdict=AVOID · low quality + falling · structural failure · stay away</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>canonical:momentum_ledger</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>AVOID</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
+          <t>JINDALSAW</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
           <t>SUSTAINED_UP</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>verdict=MOMENTUM_WATCH · quality=OK · quality + momentum · BUT overbought · wait</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>309.75</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>verdict=PUMP_RISK · big move on low-quality name · pump-and-dump risk · avoid</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>canonical:momentum_ledger</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>QUICK_RISE</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>AVOID</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>verdict=PUMP_RISK · big move on low-quality name · pump-and-dump risk · avoid</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>canonical:momentum_ledger</t>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Action → INVEST (eligible for new R2 entry today) · WATCH (monitor · do not enter) · AVOID (do not initiate) · NO EVIDENCE (insufficient data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Today + Momentum shows ONLY the current reporting date's R2 decisions/recommendations.</t>
+          <t>Current Price · from canonical parquet close on As-Of · never fabricated.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Terminal states · ACCEPTED · WATCH · REJECTED · NO_EVIDENCE (quality unavailable).</t>
+          <t>Entry Zone / Stop / Confidence · populated when the canonical decision engine provides them · UNAVAILABLE otherwise · zero-fabrication invariant.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday's rows forward.</t>
+          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday forward.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>A recommendation does NOT automatically become a Portfolio holding · only canonical lifecycle transitions move a stock into 01_Portfolio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Only the active production runner (R2) appears in this workbook.</t>
+          <t>An INVEST recommendation is a signal · it becomes a Portfolio holding only after canonical lifecycle transition creates a Registry ACTIVE position.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1474,7 +1484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1488,8 +1498,9 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1502,7 +1513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📕 Closed positions (last 90d): 38 · latest exit first · realized P&amp;L only · historical accountability incl. retired runners</t>
+          <t>📕 Realized production exits (last 90d): 20 · latest exit first · realized P&amp;L only · 18 administrative/same-day events filtered to canonical audit</t>
         </is>
       </c>
     </row>
@@ -1569,6 +1580,11 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
+          <t>Relative Opportunity pp</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>Provenance</t>
         </is>
       </c>
@@ -1576,17 +1592,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIENT-20260902-51452a</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1601,32 +1617,35 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2863.8999</v>
+        <v>2383.8999</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>2863.8999</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>2160.2</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>-9.380000000000001</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +57.0 pp</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1635,17 +1654,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1665,27 +1684,30 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2383.8999</v>
+        <v>415.15</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2160.2</v>
+        <v>402.55</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-9.380000000000001</v>
+        <v>-3.04</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +13.0 pp</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1694,17 +1716,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1719,32 +1741,35 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>398.8</v>
+        <v>552.4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>398.8</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>558</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.01</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +52.9 pp</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1753,17 +1778,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1778,32 +1803,35 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>415.15</v>
+        <v>129.2</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>402.55</v>
+        <v>124.4</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-3.04</v>
+        <v>-3.72</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +14.3 pp</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1812,17 +1840,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARICO-20260826-1c5a1c</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1837,32 +1865,35 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>847.5</v>
+        <v>1384</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>847.5</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>1327.6</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>-4.08</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +56.7 pp</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1871,17 +1902,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1896,32 +1927,35 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1702.7</v>
+        <v>377</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1702.7</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>387.55</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>2.8</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +57.6 pp</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1930,17 +1964,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260824-89850d</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1955,32 +1989,35 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>244.55</v>
+        <v>11600</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>244.55</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>11828</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.97</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +10.1 pp</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1989,17 +2026,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2014,32 +2051,35 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>402.8</v>
+        <v>2439.3999</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>402.8</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>2361</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-3.21</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +13.3 pp</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2048,17 +2088,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260821-142d93</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -2073,32 +2113,35 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1114.2</v>
+        <v>7454.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1114.2</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>7095</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>-4.82</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +14.5 pp</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2107,17 +2150,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -2132,32 +2175,35 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8693</v>
+        <v>6793.5</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>8693</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>6774</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +61.4 pp</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2166,17 +2212,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260820-80f37d</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -2191,32 +2237,35 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>174.9</v>
+        <v>471.2</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>473.3</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.45</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +11.8 pp</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2225,17 +2274,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -2250,32 +2299,35 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>552.4</v>
+        <v>845</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>558</v>
+        <v>889.5</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1.01</v>
+        <v>5.27</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +14.7 pp</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2284,17 +2336,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2314,27 +2366,30 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>129.2</v>
+        <v>450</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>124.4</v>
+        <v>442.8</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-3.72</v>
+        <v>-1.6</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +12.2 pp</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2343,17 +2398,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2368,32 +2423,35 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5220</v>
+        <v>1595</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>5220</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>1584.8</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>-0.64</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +60.0 pp</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2402,17 +2460,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2432,27 +2490,30 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1384</v>
+        <v>1327.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1327.6</v>
+        <v>1285</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-4.08</v>
+        <v>-3.22</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +56.7 pp</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2461,17 +2522,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2491,27 +2552,30 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>377</v>
+        <v>2195</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>2.8</v>
+        <v>2182</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>-0.59</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +9.8 pp</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2520,12 +2584,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2545,32 +2609,35 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>11600</v>
+        <v>1363.6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>11828</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>1.97</v>
+        <v>1351.3</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>-0.9</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +6.6 pp</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2579,17 +2646,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2604,32 +2671,35 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3940</v>
+        <v>5470.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3940</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>5651.5</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>3.31</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +7.5 pp</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2638,12 +2708,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2663,32 +2733,35 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2439.3999</v>
+        <v>1167.5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2361</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>-3.21</v>
+        <v>1177</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +6.7 pp</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2697,12 +2770,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
+          <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2722,1135 +2795,84 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1779.2</v>
+        <v>268.5</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1779.2</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>278.8</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>3.84</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +8.1 pp</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>7454.5</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>7095</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>-4.82</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +62.1 pp</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-CANBK-20260810-788da8</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +6.5 pp</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>4924</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>4924</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +60.1 pp</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Priced: 20 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>181.14</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>181.14</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +9.4 pp</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Realized P&amp;L % · (Exit − Entry) / Entry · own-trade result · positive=green · negative=red.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>ATUL</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>6793.5</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>6774</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +8.0 pp</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Relative Opportunity pp · alpha/rotation benefit vs the closed position (pp = percentage points) · this is NOT the trade's own P&amp;L · shown separately so it cannot be misread.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>471.2</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +60.7 pp</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>18 same-day / registry-sync administrative events filtered from this operator-facing view · they remain in the canonical Registry JSONL for audit.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>845</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>889.5</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +7.4 pp</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>442.8</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +10.3 pp</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>PRESTIGE</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>1595</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>1584.8</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +62.5 pp</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>1327.7</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>1285</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +64.8 pp</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>2195</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +59.7 pp</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>HCLTECH</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>1363.6</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>1351.3</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +7.8 pp</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>5470.5</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>5651.5</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +10.6 pp</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>1167.5</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>1177</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +11.7 pp</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-VEDL-20260804-563905</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>VEDL</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>268.5</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>278.8</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +11.6 pp</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-BIOCON-20260804-954a24</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>BIOCON</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>425.05</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>425.05</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>Rotation swap · +51.8 pp</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>FORTIS</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>939.95</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>939.95</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>Rotation swap · +51.8 pp</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-JSWENERGY-20260804-1210a0</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>567.3</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>567.3</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>Rotation swap · +52.0 pp</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Priced: 38 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Realized P&amp;L % · (Exit − Entry) / Entry · positive=green · negative=red · zero/N/A=neutral.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>This sheet accumulates closed R2 positions via Registry CLOSED events · latest exit first · 90-day rolling window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>This sheet shows the production runner (R2) closed lifecycle only · historical evidence for retired runners lives in canonical audit files only.</t>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>This sheet contains ONLY realized production exits · 90-day rolling window.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A46:M46"/>
-    <mergeCell ref="A45:M45"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A47:M47"/>
+  <mergeCells count="7">
+    <mergeCell ref="A27:N27"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A29:N29"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -658,15 +658,19 @@
       <c r="I5" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>545.1072</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>4.68</v>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -686,12 +690,12 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 4.68% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr">
@@ -748,15 +752,19 @@
       <c r="I6" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>10989.5714</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>2.83</v>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -776,12 +784,12 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 2.83% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
@@ -838,15 +846,19 @@
       <c r="I7" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>397.1429</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>3.64</v>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -866,12 +878,12 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.64% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
@@ -928,15 +940,19 @@
       <c r="I8" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>5557.5714</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>4.18</v>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -956,12 +972,12 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 4.18% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
@@ -1018,15 +1034,19 @@
       <c r="I9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>2604.7285</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>5.74</v>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1046,12 +1066,12 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 5.74% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
@@ -1108,15 +1128,19 @@
       <c r="I10" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>638.4714</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>5.74</v>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1136,12 +1160,12 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 5.74% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -1198,15 +1222,19 @@
       <c r="I11" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>399.5571</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>3.09</v>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1226,12 +1254,12 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.09% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
@@ -1288,15 +1316,19 @@
       <c r="I12" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>258.9929</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>2.85</v>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1316,12 +1348,12 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 2.85% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
@@ -1378,15 +1410,19 @@
       <c r="I13" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>111.2957</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>3.41</v>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1406,12 +1442,12 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.41% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
@@ -21281,22 +21317,24 @@
       <c r="I298" s="6" t="n">
         <v>-1.44</v>
       </c>
-      <c r="J298" s="4" t="n">
-        <v>10989.5714</v>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K298" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21340,22 +21378,24 @@
       <c r="I299" s="6" t="n">
         <v>-4.46</v>
       </c>
-      <c r="J299" s="4" t="n">
-        <v>638.4714</v>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K299" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L299" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21399,22 +21439,24 @@
       <c r="I300" s="6" t="n">
         <v>-8.85</v>
       </c>
-      <c r="J300" s="4" t="n">
-        <v>399.5571</v>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K300" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21458,22 +21500,24 @@
       <c r="I301" s="5" t="n">
         <v>3.36</v>
       </c>
-      <c r="J301" s="4" t="n">
-        <v>545.1072</v>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L301" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M301" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21517,22 +21561,24 @@
       <c r="I302" s="6" t="n">
         <v>-6.41</v>
       </c>
-      <c r="J302" s="4" t="n">
-        <v>258.9929</v>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21576,22 +21622,24 @@
       <c r="I303" s="5" t="n">
         <v>5.33</v>
       </c>
-      <c r="J303" s="4" t="n">
-        <v>397.1429</v>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M303" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21635,22 +21683,24 @@
       <c r="I304" s="5" t="n">
         <v>5.47</v>
       </c>
-      <c r="J304" s="4" t="n">
-        <v>5557.5714</v>
+      <c r="J304" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21694,22 +21744,24 @@
       <c r="I305" s="5" t="n">
         <v>1.64</v>
       </c>
-      <c r="J305" s="4" t="n">
-        <v>111.2957</v>
+      <c r="J305" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M305" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21753,22 +21805,24 @@
       <c r="I306" s="5" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J306" s="4" t="n">
-        <v>2604.7285</v>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M306" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -658,19 +658,15 @@
       <c r="I5" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J5" s="4" t="n">
+        <v>545.1072</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>4.68</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -690,12 +686,12 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 4.68% below</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr">
@@ -752,19 +748,15 @@
       <c r="I6" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J6" s="4" t="n">
+        <v>10989.5714</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>2.83</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -784,12 +776,12 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 2.83% below</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
@@ -846,19 +838,15 @@
       <c r="I7" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J7" s="4" t="n">
+        <v>397.1429</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>3.64</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -878,12 +866,12 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.64% below</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
@@ -940,19 +928,15 @@
       <c r="I8" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J8" s="4" t="n">
+        <v>5557.5714</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>4.18</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -972,12 +956,12 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 4.18% below</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
@@ -1034,19 +1018,15 @@
       <c r="I9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J9" s="4" t="n">
+        <v>2604.7285</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>5.74</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1066,12 +1046,12 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 5.74% below</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
@@ -1128,19 +1108,15 @@
       <c r="I10" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J10" s="4" t="n">
+        <v>638.4714</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>5.74</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1160,12 +1136,12 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 5.74% below</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -1222,19 +1198,15 @@
       <c r="I11" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J11" s="4" t="n">
+        <v>399.5571</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>3.09</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1254,12 +1226,12 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.09% below</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
@@ -1316,19 +1288,15 @@
       <c r="I12" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J12" s="4" t="n">
+        <v>258.9929</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>2.85</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1348,12 +1316,12 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 2.85% below</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
@@ -1410,19 +1378,15 @@
       <c r="I13" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J13" s="4" t="n">
+        <v>111.2957</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>3.41</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1442,12 +1406,12 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.41% below</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
@@ -1934,7 +1898,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📕 Realized production exits (last 90d): 20 · latest exit first · realized P&amp;L only · 18 administrative/same-day events filtered to canonical audit</t>
+          <t>📕 Realized production exits (last 90d): 20 · latest exit first · realized P&amp;L only · 18 admin (same-day/zero-Δ) + 5 retired-runner events routed to canonical audit sink (orphan_audit_india.jsonl)</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3238,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>18 same-day / registry-sync administrative events filtered from this operator-facing view · they remain in the canonical Registry JSONL for audit.</t>
+          <t>18 same-day / zero-Δ administrative events + 5 retired-runner events filtered from this operator-facing view · they remain in the canonical Registry JSONL and orphan_audit sink for audit.</t>
         </is>
       </c>
     </row>
@@ -21317,24 +21281,22 @@
       <c r="I298" s="6" t="n">
         <v>-1.44</v>
       </c>
-      <c r="J298" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J298" s="4" t="n">
+        <v>10989.5714</v>
       </c>
       <c r="K298" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21378,24 +21340,22 @@
       <c r="I299" s="6" t="n">
         <v>-4.46</v>
       </c>
-      <c r="J299" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J299" s="4" t="n">
+        <v>638.4714</v>
       </c>
       <c r="K299" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L299" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21439,24 +21399,22 @@
       <c r="I300" s="6" t="n">
         <v>-8.85</v>
       </c>
-      <c r="J300" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J300" s="4" t="n">
+        <v>399.5571</v>
       </c>
       <c r="K300" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21500,24 +21458,22 @@
       <c r="I301" s="5" t="n">
         <v>3.36</v>
       </c>
-      <c r="J301" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J301" s="4" t="n">
+        <v>545.1072</v>
       </c>
       <c r="K301" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L301" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M301" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21561,24 +21517,22 @@
       <c r="I302" s="6" t="n">
         <v>-6.41</v>
       </c>
-      <c r="J302" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J302" s="4" t="n">
+        <v>258.9929</v>
       </c>
       <c r="K302" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21622,24 +21576,22 @@
       <c r="I303" s="5" t="n">
         <v>5.33</v>
       </c>
-      <c r="J303" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J303" s="4" t="n">
+        <v>397.1429</v>
       </c>
       <c r="K303" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M303" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21683,24 +21635,22 @@
       <c r="I304" s="5" t="n">
         <v>5.47</v>
       </c>
-      <c r="J304" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J304" s="4" t="n">
+        <v>5557.5714</v>
       </c>
       <c r="K304" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21744,24 +21694,22 @@
       <c r="I305" s="5" t="n">
         <v>1.64</v>
       </c>
-      <c r="J305" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J305" s="4" t="n">
+        <v>111.2957</v>
       </c>
       <c r="K305" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M305" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21805,24 +21753,22 @@
       <c r="I306" s="5" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J306" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J306" s="4" t="n">
+        <v>2604.7285</v>
       </c>
       <c r="K306" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M306" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -507,7 +507,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · PORTFOLIO · current active holdings as of 2026-09-02</t>
+          <t>AEGIS INDIA · PORTFOLIO · current active holdings as of 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
         <v>553.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>571.9</v>
+        <v>576.95</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>3.36</v>
+        <v>4.27</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>545.1072</v>
+        <v>548.0143</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4.68</v>
+        <v>5.02</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 4.68% below</t>
+          <t>HOLD · stop 5.02% below</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -746,7 +746,7 @@
         <v>-1.44</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>10989.5714</v>
@@ -830,19 +830,19 @@
         <v>391.3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>412.15</v>
+        <v>408.25</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>5.33</v>
+        <v>4.33</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>397.1429</v>
+        <v>393.6429</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.64% below</t>
+          <t>HOLD · stop 3.58% below</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -920,19 +920,19 @@
         <v>5499</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5800</v>
+        <v>5690</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>5.47</v>
+        <v>3.47</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5557.5714</v>
+        <v>5425.6429</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.18</v>
+        <v>4.65</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 4.18% below</t>
+          <t>HOLD · stop 4.65% below</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -1010,19 +1010,19 @@
         <v>2744.3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2763.2</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>2720</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.89</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2604.7285</v>
+        <v>2559.2857</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.74</v>
+        <v>5.91</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 5.74% below</t>
+          <t>HOLD · stop 5.91% below</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1100,19 +1100,19 @@
         <v>709</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>677.35</v>
+        <v>670.45</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-4.46</v>
+        <v>-5.44</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>638.4714</v>
+        <v>634.2929</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.74</v>
+        <v>5.39</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 5.74% below</t>
+          <t>HOLD · stop 5.39% below</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -1196,7 +1196,7 @@
         <v>-8.85</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>399.5571</v>
@@ -1280,19 +1280,19 @@
         <v>284.85</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>266.6</v>
+        <v>266.3</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-6.41</v>
+        <v>-6.51</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>258.9929</v>
+        <v>258.2071</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 2.85% below</t>
+          <t>HOLD · stop 3.04% below</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -1370,19 +1370,19 @@
         <v>113.36</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>115.22</v>
+        <v>117</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1.64</v>
+        <v>3.21</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>111.2957</v>
+        <v>113.2557</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.41% below</t>
+          <t>HOLD · stop 3.2% below</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1558,14 +1558,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · TODAY + MOMENTUM · reporting date 2026-09-02</t>
+          <t>AEGIS INDIA · TODAY + MOMENTUM · reporting date 2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📅 Today's R2 momentum scan · ✓ ledger fresh for 2026-09-02 · scanned universe=2 · Actions: {'INVEST': 0, 'WATCH': 0, 'AVOID': 2, 'NO EVIDENCE': 0}</t>
+          <t>📅 Today's R2 momentum scan · ✓ ledger fresh for 2026-09-03 · scanned universe=3 · Actions: {'INVEST': 0, 'WATCH': 2, 'AVOID': 1, 'NO EVIDENCE': 0}</t>
         </is>
       </c>
     </row>
@@ -1659,31 +1659,31 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>AVOID</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>QUICK_FALL</t>
+          <t>SUSTAINED_UP</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2863.8999</v>
+        <v>3286</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-6.45</v>
+        <v>-0.46</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-4.85</v>
+        <v>10.33</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>-6.41</v>
+        <v>18.8</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>verdict=AVOID · low quality + falling · structural failure · stay away</t>
+          <t>verdict=MOMENTUM_WATCH · quality=QUALITY · quality-confirmed momentum · BUT weak</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -1738,112 +1738,191 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SUSTAINED_UP</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1619</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>verdict=MOMENTUM_WATCH · quality=OK · quality + momentum · BUT overbought · wait</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>canonical:momentum_ledger+prices+sector_cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
           <t>AVOID</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>JINDALSAW</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>SUSTAINED_UP</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>MARGINAL</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>309.75</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>20.81</v>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>QUICK_RISE</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2891.8</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>verdict=PUMP_RISK · big move on low-quality name · pump-and-dump risk · avoid</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>canonical:momentum_ledger+prices+sector_cache</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Action → INVEST (eligible for new R2 entry today) · WATCH (monitor · do not enter) · AVOID (do not initiate) · NO EVIDENCE (insufficient data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Current Price · from canonical parquet close on As-Of · never fabricated.</t>
+          <t>Action → INVEST (eligible for new R2 entry today) · WATCH (monitor · do not enter) · AVOID (do not initiate) · NO EVIDENCE (insufficient data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Entry Zone / Stop / Confidence · populated when the canonical decision engine provides them · UNAVAILABLE otherwise · zero-fabrication invariant.</t>
+          <t>Current Price · from canonical parquet close on As-Of · never fabricated.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday forward.</t>
+          <t>Entry Zone / Stop / Confidence · populated when the canonical decision engine provides them · UNAVAILABLE otherwise · zero-fabrication invariant.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>An INVEST recommendation is a signal · it becomes a Portfolio holding only after canonical lifecycle transition creates a Registry ACTIVE position.</t>
         </is>
@@ -1852,8 +1931,8 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A14:M14"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A9:M9"/>
     <mergeCell ref="A12:M12"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A11:M11"/>
@@ -1891,7 +1970,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · realized · as of 2026-09-02</t>
+          <t>AEGIS INDIA · EXIT HISTORY · realized · as of 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M313"/>
+  <dimension ref="A1:M322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3290,14 +3369,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · DAILY PORTFOLIO HISTORY · reconstructed from canonical Registry as of 2026-09-02</t>
+          <t>AEGIS INDIA · DAILY PORTFOLIO HISTORY · reconstructed from canonical Registry as of 2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📅 Reconstructed from Registry · 29 genuine R2 positions · trading days 2026-08-04 → 2026-09-02 · excludes same-day admin events</t>
+          <t>📅 Reconstructed from Registry · 29 genuine R2 positions · trading days 2026-08-04 → 2026-09-03 · excludes same-day admin events</t>
         </is>
       </c>
     </row>
@@ -20910,10 +20989,10 @@
         <v>553.3</v>
       </c>
       <c r="H292" s="4" t="n">
-        <v>571.9</v>
+        <v>576</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
@@ -21281,22 +21360,24 @@
       <c r="I298" s="6" t="n">
         <v>-1.44</v>
       </c>
-      <c r="J298" s="4" t="n">
-        <v>10989.5714</v>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K298" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21335,27 +21416,29 @@
         <v>709</v>
       </c>
       <c r="H299" s="4" t="n">
-        <v>677.35</v>
+        <v>670.45</v>
       </c>
       <c r="I299" s="6" t="n">
-        <v>-4.46</v>
-      </c>
-      <c r="J299" s="4" t="n">
-        <v>638.4714</v>
+        <v>-5.44</v>
+      </c>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K299" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L299" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21399,22 +21482,24 @@
       <c r="I300" s="6" t="n">
         <v>-8.85</v>
       </c>
-      <c r="J300" s="4" t="n">
-        <v>399.5571</v>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K300" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21453,27 +21538,29 @@
         <v>553.3</v>
       </c>
       <c r="H301" s="4" t="n">
-        <v>571.9</v>
+        <v>576.95</v>
       </c>
       <c r="I301" s="5" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="J301" s="4" t="n">
-        <v>545.1072</v>
+        <v>4.27</v>
+      </c>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L301" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M301" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21512,27 +21599,29 @@
         <v>284.85</v>
       </c>
       <c r="H302" s="4" t="n">
-        <v>266.6</v>
+        <v>266.3</v>
       </c>
       <c r="I302" s="6" t="n">
-        <v>-6.41</v>
-      </c>
-      <c r="J302" s="4" t="n">
-        <v>258.9929</v>
+        <v>-6.51</v>
+      </c>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21571,27 +21660,29 @@
         <v>391.3</v>
       </c>
       <c r="H303" s="4" t="n">
-        <v>412.15</v>
+        <v>408.25</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="J303" s="4" t="n">
-        <v>397.1429</v>
+        <v>4.33</v>
+      </c>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M303" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21630,27 +21721,29 @@
         <v>5499</v>
       </c>
       <c r="H304" s="4" t="n">
-        <v>5800</v>
+        <v>5690</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="J304" s="4" t="n">
-        <v>5557.5714</v>
+        <v>3.47</v>
+      </c>
+      <c r="J304" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21689,27 +21782,29 @@
         <v>113.36</v>
       </c>
       <c r="H305" s="4" t="n">
-        <v>115.22</v>
+        <v>117</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="J305" s="4" t="n">
-        <v>111.2957</v>
+        <v>3.21</v>
+      </c>
+      <c r="J305" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M305" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21748,60 +21843,593 @@
         <v>2744.3</v>
       </c>
       <c r="H306" s="4" t="n">
-        <v>2763.2</v>
-      </c>
-      <c r="I306" s="5" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J306" s="4" t="n">
-        <v>2604.7285</v>
+        <v>2720</v>
+      </c>
+      <c r="I306" s="6" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
         <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L306" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="M306" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E307" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G307" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="H307" s="4" t="n">
+        <v>11310</v>
+      </c>
+      <c r="I307" s="6" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="J307" s="4" t="n">
+        <v>10989.5714</v>
+      </c>
+      <c r="K307" s="4" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="L306" s="4" t="inlineStr">
+      <c r="L307" s="4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M306" s="4" t="inlineStr">
+      <c r="M307" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E308" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G308" s="4" t="n">
+        <v>709</v>
+      </c>
+      <c r="H308" s="4" t="n">
+        <v>670.45</v>
+      </c>
+      <c r="I308" s="6" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="J308" s="4" t="n">
+        <v>634.2929</v>
+      </c>
+      <c r="K308" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L308" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M308" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
     <row r="309">
-      <c r="A309" s="7" t="inlineStr">
+      <c r="A309" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+        </is>
+      </c>
+      <c r="C309" s="4" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="D309" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E309" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G309" s="4" t="n">
+        <v>452.35</v>
+      </c>
+      <c r="H309" s="4" t="n">
+        <v>412.3</v>
+      </c>
+      <c r="I309" s="6" t="n">
+        <v>-8.85</v>
+      </c>
+      <c r="J309" s="4" t="n">
+        <v>399.5571</v>
+      </c>
+      <c r="K309" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L309" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M309" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="D310" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E310" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F310" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G310" s="4" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="H310" s="4" t="n">
+        <v>576.95</v>
+      </c>
+      <c r="I310" s="5" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J310" s="4" t="n">
+        <v>548.0143</v>
+      </c>
+      <c r="K310" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L310" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M310" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-ITC-20260804-e0ebbb</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E311" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F311" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G311" s="4" t="n">
+        <v>284.85</v>
+      </c>
+      <c r="H311" s="4" t="n">
+        <v>266.3</v>
+      </c>
+      <c r="I311" s="6" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="J311" s="4" t="n">
+        <v>258.2071</v>
+      </c>
+      <c r="K311" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L311" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M311" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-LICI-20260805-035a2d</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E312" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F312" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G312" s="4" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="H312" s="4" t="n">
+        <v>408.25</v>
+      </c>
+      <c r="I312" s="5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J312" s="4" t="n">
+        <v>393.6429</v>
+      </c>
+      <c r="K312" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L312" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M312" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E313" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G313" s="4" t="n">
+        <v>5499</v>
+      </c>
+      <c r="H313" s="4" t="n">
+        <v>5690</v>
+      </c>
+      <c r="I313" s="5" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="J313" s="4" t="n">
+        <v>5425.6429</v>
+      </c>
+      <c r="K313" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L313" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M313" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E314" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F314" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G314" s="4" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="H314" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="I314" s="5" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J314" s="4" t="n">
+        <v>113.2557</v>
+      </c>
+      <c r="K314" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L314" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M314" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B315" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E315" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F315" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G315" s="4" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="H315" s="4" t="n">
+        <v>2720</v>
+      </c>
+      <c r="I315" s="6" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="J315" s="4" t="n">
+        <v>2559.2857</v>
+      </c>
+      <c r="K315" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L315" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M315" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="7" t="inlineStr">
         <is>
           <t>Reconstructed daily active-portfolio history from canonical Registry.</t>
         </is>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" s="7" t="inlineStr">
+    <row r="319">
+      <c r="A319" s="7" t="inlineStr">
         <is>
           <t>One row per position per trading day while the position was genuinely active.</t>
         </is>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" s="7" t="inlineStr">
+    <row r="320">
+      <c r="A320" s="7" t="inlineStr">
         <is>
           <t>Excludes same-day administrative Registry records (entry_date == exit_date).</t>
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" s="7" t="inlineStr">
+    <row r="321">
+      <c r="A321" s="7" t="inlineStr">
         <is>
           <t>Dynamic Stop is populated ONLY for the current as-of date · historical dynamic stops are UNAVAILABLE because dynamic_risk_v2 stores only the current snapshot.</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" s="7" t="inlineStr">
+    <row r="322">
+      <c r="A322" s="7" t="inlineStr">
         <is>
           <t>Never fabricated · UNAVAILABLE means the canonical source has no value for that day.</t>
         </is>
@@ -21809,13 +22437,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A322:M322"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A309:M309"/>
-    <mergeCell ref="A312:M312"/>
-    <mergeCell ref="A311:M311"/>
-    <mergeCell ref="A310:M310"/>
+    <mergeCell ref="A321:M321"/>
+    <mergeCell ref="A320:M320"/>
+    <mergeCell ref="A319:M319"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A313:M313"/>
+    <mergeCell ref="A318:M318"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -22663,7 +22663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -22717,6 +22717,457 @@
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Advisory Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1389 - 1464</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.2%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1881 - 1982</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 79/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>322 - 338</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.6%) • sector strength 36/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>989 - 1053</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.7%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>261 - 273</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 36/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>394 - 418</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.2%) • sector strength 64/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>230 - 245</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 57/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>260 - 273</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 29/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>406 - 430</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.5%) • sector strength 21/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>178 - 190</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.4%) • sector strength 21/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>459 - 486</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-17.1%) • sector strength 7/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION de</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -484,13 +484,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INVESTMENTS · daily operator view · NEW opportunities + ACTIVE holdings across all runners · Dynamic Stop mandatory · R1 rows tagged SUGGESTED (no auto-exit per V2 §18)</t>
+          <t>AEGIS INVESTMENTS · daily operator view · NEW opportunities + ACTIVE holdings across all runners · Dynamic Stop mandatory · R1 rows tagged SUGGESTED · ⚠ R1 POSITIONS CARRY NO DYNAMIC-EXIT PROTECTION · advisory only · no auto-exit enforcement (per AEGIS Master v2 §R1.9 Stage 1 requirement)</t>
         </is>
       </c>
     </row>
@@ -1106,58 +1106,55 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5499</v>
+        <v>397</v>
       </c>
       <c r="H16" t="n">
-        <v>5657</v>
+        <v>421.15</v>
       </c>
       <c r="I16" t="n">
-        <v>2.87</v>
+        <v>6.08</v>
       </c>
       <c r="J16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5195.5001</t>
+          <t>386.4571 · SUGGESTED</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5954.2499</v>
+        <v>412.8143</v>
       </c>
       <c r="M16" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.64</v>
+        <v>8.24</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1166,13 +1163,13 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>R2 · 5-fc13a0</t>
+          <t>R1 ADVISORY · 4-4429c0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1181,12 +1178,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1196,34 +1193,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>113.36</v>
+        <v>5499</v>
       </c>
       <c r="H17" t="n">
-        <v>116.32</v>
+        <v>5657</v>
       </c>
       <c r="I17" t="n">
-        <v>2.61</v>
+        <v>2.87</v>
       </c>
       <c r="J17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>109.6843</t>
+          <t>5195.5001</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>118.8736</v>
+        <v>5954.2499</v>
       </c>
       <c r="M17" t="n">
-        <v>5.7</v>
+        <v>8.16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.38</v>
+        <v>0.64</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1232,13 +1229,13 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>R2 · 4-ffee9e</t>
+          <t>R2 · 5-fc13a0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1247,12 +1244,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1262,34 +1259,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2744.3</v>
+        <v>113.36</v>
       </c>
       <c r="H18" t="n">
-        <v>2735.3999</v>
+        <v>116.32</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.32</v>
+        <v>2.61</v>
       </c>
       <c r="J18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2607.1858</t>
+          <t>109.6843</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2949.9715</v>
+        <v>118.8736</v>
       </c>
       <c r="M18" t="n">
-        <v>4.69</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>0.38</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1298,27 +1295,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>R2 · 5-7e40ba</t>
+          <t>R2 · 4-ffee9e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EXIT · stop hit</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1332,27 +1329,30 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>11475</v>
+        <v>2744.3</v>
       </c>
       <c r="H19" t="n">
-        <v>11100</v>
+        <v>2735.3999</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.27</v>
+        <v>-0.32</v>
       </c>
       <c r="J19" t="n">
         <v>30</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11144.7143</t>
+          <t>2607.1858</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>11970.4286</v>
+        <v>2949.9715</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4</v>
+        <v>4.69</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.67</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1361,61 +1361,64 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>R2 · 5-b3d435</t>
+          <t>R2 · 5-7e40ba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EXIT · stop hit</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>709</v>
+        <v>417.6</v>
       </c>
       <c r="H20" t="n">
-        <v>677.4</v>
+        <v>420.05</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.46</v>
+        <v>0.59</v>
       </c>
       <c r="J20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>682.2286</t>
+          <t>407.3714 · SUGGESTED</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>749.1571</v>
+        <v>432.9429</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.71</v>
+        <v>3.02</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.02</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1424,22 +1427,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>R2 · 4-a68e4b</t>
+          <t>R1 ADVISORY · 5-9349c5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EXIT · stop hit</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1449,7 +1452,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1458,27 +1461,30 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>452.35</v>
+        <v>1642.5</v>
       </c>
       <c r="H21" t="n">
-        <v>418.3</v>
+        <v>1638.3</v>
       </c>
       <c r="I21" t="n">
-        <v>-7.53</v>
+        <v>-0.26</v>
       </c>
       <c r="J21" t="n">
         <v>31</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>435.5929</t>
+          <t>1594.6857 · SUGGESTED</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>477.4857</v>
+        <v>1714.2215</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.13</v>
+        <v>2.66</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.74</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1487,145 +1493,976 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>R2 · 4-893fdf</t>
+          <t>R1 ADVISORY · 4-cf5c6a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1413.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1412.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1382.3857 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1460.1715</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 8-d46712</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>27</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>187.46</v>
+      </c>
+      <c r="H23" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>181.8114 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>195.9329</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 8-c215bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>26</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>377.5071 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>396.6143</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 8-be7819</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1048.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1023.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="J25" t="n">
+        <v>14</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1011.5999 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1104.35</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 1-b637f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EXIT · stop hit</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>11475</v>
+      </c>
+      <c r="H26" t="n">
+        <v>11100</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="J26" t="n">
+        <v>30</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>11144.7143</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>11970.4286</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>R2 · 5-b3d435</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EXIT · stop hit</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>709</v>
+      </c>
+      <c r="H27" t="n">
+        <v>677.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="J27" t="n">
+        <v>31</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>682.2286</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>749.1571</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>R2 · 4-a68e4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="J28" t="n">
+        <v>31</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>369.75 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>399.375</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 4-29907f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1191</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1143</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="J29" t="n">
+        <v>24</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1149.2286 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1253.6571</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 1-58636b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2064.8999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1962</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="J30" t="n">
+        <v>23</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1990.457 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2176.5643</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 2-08d1f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>5454.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5130</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="J31" t="n">
+        <v>31</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>5283.7143 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>5710.6786</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 4-3de31c</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>18</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>507.9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>474.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-6.56</v>
+      </c>
+      <c r="J32" t="n">
+        <v>31</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>493.3286 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>529.7572</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 4-afbb8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>17</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>EXIT · stop hit</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>452.35</v>
+      </c>
+      <c r="H33" t="n">
+        <v>418.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-7.53</v>
+      </c>
+      <c r="J33" t="n">
+        <v>31</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>435.5929</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>477.4857</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>R2 · 4-893fdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EXIT · stop hit</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="G34" t="n">
         <v>284.85</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H34" t="n">
         <v>263</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I34" t="n">
         <v>-7.67</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J34" t="n">
         <v>31</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>276.1</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="L34" t="n">
         <v>297.975</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M34" t="n">
         <v>-4.98</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>R2 · 4-e0ebbb</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="n">
+        <v>13</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2410</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2132</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-11.54</v>
+      </c>
+      <c r="J35" t="n">
+        <v>30</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2314.8285 · SUGGESTED</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>2552.7572</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-8.58</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · 5-71abab</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Score · unified 0-100 · higher = better · combines confidence + P&amp;L trend + safety margin</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Action · BUY (new) · HOLD (active above stop) · EXIT (stop hit) · REVIEW (data error)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Runner · which engine produced the signal · R1=advisory · R2=production · Composite=research</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Dynamic Stop · MANDATORY on every row · trichotomy:</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  ₹XXX                        = valid dynamic stop (R2 · ATR-14 · k=2)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  ₹XXX · SUGGESTED           = R1 advisory · no auto-exit per V2 §18</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  N/A · advisory · no auto-exit = R1 with no ATR available</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  DATA_ERROR · &lt;reason&gt;       = engine/data failure · never blank</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Entry Date · from Registry for active positions · today for new BUY</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Holding Days · active positions only · calendar days since Registry entry</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>R:R · Reward/Risk · (Target − Current) / (Current − Stop) · only when both present</t>
         </is>
@@ -1633,18 +2470,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A28:P28"/>
-    <mergeCell ref="A32:P32"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="A42:P42"/>
+    <mergeCell ref="A46:P46"/>
+    <mergeCell ref="A44:P44"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A27:P27"/>
-    <mergeCell ref="A31:P31"/>
-    <mergeCell ref="A34:P34"/>
-    <mergeCell ref="A35:P35"/>
-    <mergeCell ref="A26:P26"/>
-    <mergeCell ref="A30:P30"/>
-    <mergeCell ref="A29:P29"/>
-    <mergeCell ref="A25:P25"/>
-    <mergeCell ref="A33:P33"/>
+    <mergeCell ref="A40:P40"/>
+    <mergeCell ref="A45:P45"/>
+    <mergeCell ref="A39:P39"/>
+    <mergeCell ref="A48:P48"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A43:P43"/>
+    <mergeCell ref="A41:P41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1656,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1704,10 +2541,8 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="C5" t="n">
+        <v>500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1731,10 +2566,8 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="C6" t="n">
+        <v>500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1758,10 +2591,8 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="C7" t="n">
+        <v>230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1785,10 +2616,8 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="C8" t="n">
+        <v>15</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,10 +2641,8 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="C9" t="n">
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1839,10 +2666,8 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="C10" t="n">
+        <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1868,7 +2693,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>S2_universe_actual→S3_data_present</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1878,14 +2703,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>dropped 0 tickers</t>
+          <t>dropped 270 tickers</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MVS relaxation budget</t>
+          <t>Momentum scanned/raw</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1893,42 +2718,173 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>15</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2/230</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>used 0 of 15 · rolling 90d</t>
+          <t>M4/M1 · severe collapse if scanned &lt;&lt; raw</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Momentum bottleneck</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M3_after_out_of_universe_drop→M4_actually_scanned</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>dropped 228 tickers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P0 exit-bridge gate</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>n=20 · delta=0.0075</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MVS relaxation budget</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>used 0 of 15 · rolling 90d</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Outcome Dataset</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>68</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>non-admin closed: 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Signal Ledger</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>snapshots: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Price parquet freshness</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>india</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>230 files · newest mtime 0d ago</t>
         </is>
@@ -2127,15 +3083,19 @@
       <c r="I5" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>555.7785</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>5.38</v>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
@@ -2149,12 +3109,12 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>HOLD · stop 5.38% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -2162,8 +3122,10 @@
           <t>2026-10-05 (~31d)</t>
         </is>
       </c>
-      <c r="S5" s="6" t="n">
-        <v>0.01</v>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
@@ -2209,15 +3171,19 @@
       <c r="I6" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>10749</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>3.16</v>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M6" s="6" t="n">
@@ -2231,12 +3197,12 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.16% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -2244,8 +3210,10 @@
           <t>2026-10-04 (~30d)</t>
         </is>
       </c>
-      <c r="S6" s="6" t="n">
-        <v>2.48</v>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -2291,15 +3259,19 @@
       <c r="I7" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>5375</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>4.98</v>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
@@ -2313,12 +3285,12 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>HOLD · stop 4.98% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -2326,8 +3298,10 @@
           <t>2026-10-04 (~30d)</t>
         </is>
       </c>
-      <c r="S7" s="6" t="n">
-        <v>1.05</v>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -2373,15 +3347,19 @@
       <c r="I8" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>2589.5427</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>5.33</v>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M8" s="6" t="n">
@@ -2395,12 +3373,12 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>HOLD · stop 5.33% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -2408,8 +3386,10 @@
           <t>2026-10-04 (~30d)</t>
         </is>
       </c>
-      <c r="S8" s="6" t="n">
-        <v>1.47</v>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -2455,15 +3435,19 @@
       <c r="I9" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>642.7071999999999</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>5.12</v>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M9" s="6" t="n">
@@ -2477,12 +3461,12 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>HOLD · stop 5.12% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -2490,8 +3474,10 @@
           <t>2026-10-03 (~29d)</t>
         </is>
       </c>
-      <c r="S9" s="6" t="n">
-        <v>2.07</v>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -2537,15 +3523,19 @@
       <c r="I10" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>403.0428</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>3.65</v>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
@@ -2559,12 +3549,12 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.65% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -2572,8 +3562,10 @@
           <t>2026-10-03 (~29d)</t>
         </is>
       </c>
-      <c r="S10" s="6" t="n">
-        <v>3.88</v>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -2619,15 +3611,19 @@
       <c r="I11" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>254.5</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>3.23</v>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
@@ -2641,12 +3637,12 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.23% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -2654,8 +3650,10 @@
           <t>2026-10-03 (~29d)</t>
         </is>
       </c>
-      <c r="S11" s="6" t="n">
-        <v>4.11</v>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -2701,15 +3699,19 @@
       <c r="I12" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="J12" s="6" t="n">
-        <v>112.5257</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>3.26</v>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
@@ -2723,12 +3725,12 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.26% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -2736,8 +3738,10 @@
           <t>2026-10-03 (~29d)</t>
         </is>
       </c>
-      <c r="S12" s="6" t="n">
-        <v>0.67</v>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -2880,7 +3884,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>📅 Today's R2 momentum scan · ✓ ledger fresh for 2026-09-04 · scanned universe=1 · Actions: {'INVEST': 0, 'WATCH': 0, 'AVOID': 1, 'NO EVIDENCE': 0}</t>
+          <t>📅 Today's R2 momentum scan · ✓ ledger fresh for 2026-09-04 · scanned universe=0 · Actions: {'INVEST': 0, 'WATCH': 0, 'AVOID': 0, 'NO EVIDENCE': 0}</t>
         </is>
       </c>
     </row>
@@ -2972,81 +3976,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>AVOID</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>QUICK_RISE</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>AVOID</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>2901</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>verdict=PUMP_RISK · big move on low-quality name · pump-and-dump risk · avoid</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>canonical:momentum_ledger+prices+sector_cache</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No R2 decisions/recommendations for 2026-09-04 </t>
         </is>
       </c>
     </row>
@@ -23701,22 +24633,24 @@
       <c r="I316" s="8" t="n">
         <v>-3.27</v>
       </c>
-      <c r="J316" s="6" t="n">
-        <v>10749</v>
+      <c r="J316" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K316" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L316" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M316" s="6" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -23760,22 +24694,24 @@
       <c r="I317" s="8" t="n">
         <v>-4.46</v>
       </c>
-      <c r="J317" s="6" t="n">
-        <v>642.7071999999999</v>
+      <c r="J317" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M317" s="6" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -23819,22 +24755,24 @@
       <c r="I318" s="8" t="n">
         <v>-7.53</v>
       </c>
-      <c r="J318" s="6" t="n">
-        <v>403.0428</v>
+      <c r="J318" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K318" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L318" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M318" s="6" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -23878,22 +24816,24 @@
       <c r="I319" s="7" t="n">
         <v>6.15</v>
       </c>
-      <c r="J319" s="6" t="n">
-        <v>555.7785</v>
+      <c r="J319" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M319" s="6" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -23937,22 +24877,24 @@
       <c r="I320" s="8" t="n">
         <v>-7.67</v>
       </c>
-      <c r="J320" s="6" t="n">
-        <v>254.5</v>
+      <c r="J320" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K320" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L320" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M320" s="6" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -23996,22 +24938,24 @@
       <c r="I321" s="7" t="n">
         <v>2.87</v>
       </c>
-      <c r="J321" s="6" t="n">
-        <v>5375</v>
+      <c r="J321" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M321" s="6" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -24055,22 +24999,24 @@
       <c r="I322" s="7" t="n">
         <v>2.61</v>
       </c>
-      <c r="J322" s="6" t="n">
-        <v>112.5257</v>
+      <c r="J322" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K322" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L322" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M322" s="6" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -24114,22 +25060,24 @@
       <c r="I323" s="8" t="n">
         <v>-0.32</v>
       </c>
-      <c r="J323" s="6" t="n">
-        <v>2589.5427</v>
+      <c r="J323" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M323" s="6" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -24833,7 +25781,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -24841,7 +25789,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.236</v>
+        <v>-0.2682</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -24880,7 +25828,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -24888,7 +25836,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2415</v>
+        <v>-0.2804</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -24927,7 +25875,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24935,7 +25883,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1861</v>
+        <v>-0.2889</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -24974,7 +25922,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -24982,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2074</v>
+        <v>0.2507</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -25021,7 +25969,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -25029,7 +25977,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2169</v>
+        <v>0.2133</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -25076,7 +26024,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3603</v>
+        <v>0.2332</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -25115,7 +26063,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -25123,7 +26071,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2301</v>
+        <v>0.2677</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -25162,7 +26110,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -25170,7 +26118,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2401</v>
+        <v>0.2849</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -25209,7 +26157,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -25217,7 +26165,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2101</v>
+        <v>0.2354</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -25256,7 +26204,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -25264,7 +26212,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1892</v>
+        <v>-0.2779</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -25303,7 +26251,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -25311,7 +26259,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2523</v>
+        <v>-0.3021</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -25350,7 +26298,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -25358,7 +26306,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2422</v>
+        <v>0.2302</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -25397,7 +26345,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -25405,7 +26353,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2649</v>
+        <v>0.2667</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -25444,7 +26392,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -25452,7 +26400,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2437</v>
+        <v>0.302</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -25499,7 +26447,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2677</v>
+        <v>0.2832</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -2493,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2887,6 +2887,83 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>230 files · newest mtime 0d ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fundamentals PIT freshness</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>trading_age=1d · unique_asof=1 (≥60 needed for F01-05 OOS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fundamentals substrate maturity</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Substrate-before-sophistication rule · F01-05 OOS unblock at 60 asof-dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WORKED_LEGACY remediation queue</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>19 schedulable · 7 blocked by substrate rule</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🟢 NEW OPPORTUNITIES · 2026-09-04 · sorted by Score ↓</t>
+          <t>🟢 NEW OPPORTUNITIES · 2026-09-07 · sorted by Score ↓</t>
         </is>
       </c>
     </row>
@@ -609,38 +609,38 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1430</v>
+        <v>1423.199951171875</v>
       </c>
       <c r="H5" t="n">
-        <v>1430</v>
+        <v>1423.199951171875</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1399.2571 · SUGGESTED</t>
+          <t>1392.4142 · SUGGESTED</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1476.1143</v>
+        <v>1469.3785</v>
       </c>
       <c r="M5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="N5" t="n">
         <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.4%) • outperforming Ni</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.9%) • outperforming Ni</t>
         </is>
       </c>
     </row>
@@ -670,28 +670,28 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1916</v>
+        <v>1899</v>
       </c>
       <c r="H6" t="n">
-        <v>1916</v>
+        <v>1899</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1859.0429 · SUGGESTED</t>
+          <t>1848.7714 · SUGGESTED</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2001.4357</v>
+        <v>1974.3429</v>
       </c>
       <c r="M6" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="N6" t="n">
         <v>1.5</v>
@@ -701,13 +701,13 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-risk Pharma holding (low vol) • above 200-dma (+6.4%) • outperforming Nifty </t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.4%) • sector strength 64/1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -731,38 +731,38 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>330.8999938964844</v>
+        <v>332.5</v>
       </c>
       <c r="H7" t="n">
-        <v>330.8999938964844</v>
+        <v>332.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>320.8071 · SUGGESTED</t>
+          <t>322.4571 · SUGGESTED</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>346.0393</v>
+        <v>347.5643</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="N7" t="n">
         <v>1.5</v>
       </c>
       <c r="O7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.4%) • sector strength 8/100</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.9%) • sector strength 7/100</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -792,28 +792,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>265.6000061035156</v>
+        <v>1385</v>
       </c>
       <c r="H8" t="n">
-        <v>265.6000061035156</v>
+        <v>1385</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>256.7071 · SUGGESTED</t>
+          <t>1349.1429 · SUGGESTED</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>278.9393</v>
+        <v>1438.7857</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>2.59</v>
       </c>
       <c r="N8" t="n">
         <v>1.5</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.6%) • sector strength 8/100</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.6%) • sector strength 64/1</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -853,28 +853,28 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="H9" t="n">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>229.9143 · SUGGESTED</t>
+          <t>257.15 · SUGGESTED</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>245.1286</v>
+        <v>279.275</v>
       </c>
       <c r="M9" t="n">
-        <v>2.58</v>
+        <v>3.33</v>
       </c>
       <c r="N9" t="n">
         <v>1.5</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.4%) • sector strength 54/1</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.5%) • sector strength 7/100</t>
         </is>
       </c>
     </row>
@@ -914,28 +914,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>408.6000061035156</v>
+        <v>405.3500061035156</v>
       </c>
       <c r="H10" t="n">
-        <v>408.6000061035156</v>
+        <v>405.3500061035156</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>397.6 · SUGGESTED</t>
+          <t>393.9357 · SUGGESTED</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>425.1</v>
+        <v>422.4715</v>
       </c>
       <c r="M10" t="n">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="N10" t="n">
         <v>1.5</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.5%) • sector strength</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.3%) • sector strength</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1071,13 +1071,13 @@
         <v>553.3</v>
       </c>
       <c r="H15" t="n">
-        <v>587.35</v>
+        <v>596.7</v>
       </c>
       <c r="I15" t="n">
-        <v>6.15</v>
+        <v>7.84</v>
       </c>
       <c r="J15" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1088,10 +1088,7 @@
         <v>587.6713999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.01</v>
+        <v>11.11</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1106,7 +1103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1137,13 +1134,13 @@
         <v>397</v>
       </c>
       <c r="H16" t="n">
-        <v>421.15</v>
+        <v>424.5</v>
       </c>
       <c r="I16" t="n">
-        <v>6.08</v>
+        <v>6.93</v>
       </c>
       <c r="J16" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1154,7 +1151,7 @@
         <v>412.8143</v>
       </c>
       <c r="M16" t="n">
-        <v>8.24</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1169,7 +1166,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1200,13 +1197,13 @@
         <v>5499</v>
       </c>
       <c r="H17" t="n">
-        <v>5657</v>
+        <v>5643</v>
       </c>
       <c r="I17" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="J17" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1217,10 +1214,10 @@
         <v>5954.2499</v>
       </c>
       <c r="M17" t="n">
-        <v>8.16</v>
+        <v>7.93</v>
       </c>
       <c r="N17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1235,7 +1232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1266,13 +1263,13 @@
         <v>113.36</v>
       </c>
       <c r="H18" t="n">
-        <v>116.32</v>
+        <v>117</v>
       </c>
       <c r="I18" t="n">
-        <v>2.61</v>
+        <v>3.21</v>
       </c>
       <c r="J18" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1283,10 +1280,10 @@
         <v>118.8736</v>
       </c>
       <c r="M18" t="n">
-        <v>5.7</v>
+        <v>6.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1301,58 +1298,58 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2744.3</v>
+        <v>187.46</v>
       </c>
       <c r="H19" t="n">
-        <v>2735.3999</v>
+        <v>188.79</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.32</v>
+        <v>0.71</v>
       </c>
       <c r="J19" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2607.1858</t>
+          <t>181.8114 · SUGGESTED</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2949.9715</v>
+        <v>195.9329</v>
       </c>
       <c r="M19" t="n">
-        <v>4.69</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1361,64 +1358,64 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>R2 · 5-7e40ba</t>
+          <t>R1 ADVISORY · 8-c215bb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>32</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2698</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="J20" t="n">
         <v>33</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>HOLD · R1 ADVISORY</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>417.6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>420.05</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J20" t="n">
-        <v>30</v>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>407.3714 · SUGGESTED</t>
+          <t>2607.1858</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>432.9429</v>
+        <v>2949.9715</v>
       </c>
       <c r="M20" t="n">
-        <v>3.02</v>
+        <v>3.37</v>
       </c>
       <c r="N20" t="n">
-        <v>1.02</v>
+        <v>2.77</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1427,13 +1424,13 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 5-9349c5</t>
+          <t>R2 · 5-7e40ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1464,13 +1461,13 @@
         <v>1642.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1638.3</v>
+        <v>1629.5</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.26</v>
+        <v>-0.79</v>
       </c>
       <c r="J21" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1481,10 +1478,10 @@
         <v>1714.2215</v>
       </c>
       <c r="M21" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="N21" t="n">
-        <v>1.74</v>
+        <v>2.43</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1499,7 +1496,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1508,12 +1505,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1523,34 +1520,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1413.5</v>
+        <v>417.6</v>
       </c>
       <c r="H22" t="n">
-        <v>1412.8</v>
+        <v>415.35</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.05</v>
+        <v>-0.54</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1382.3857 · SUGGESTED</t>
+          <t>407.3714 · SUGGESTED</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1460.1715</v>
+        <v>432.9429</v>
       </c>
       <c r="M22" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="N22" t="n">
-        <v>1.56</v>
+        <v>2.21</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1559,64 +1556,64 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 8-d46712</t>
+          <t>R1 ADVISORY · 5-9349c5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>26</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HOLD · R1 ADVISORY</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>239.45</v>
+      </c>
+      <c r="H23" t="n">
+        <v>234.65</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J23" t="n">
         <v>27</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HOLD · R1 ADVISORY</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="H23" t="n">
-        <v>184.2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7</v>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>181.8114 · SUGGESTED</t>
+          <t>232.2186 · SUGGESTED</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>195.9329</v>
+        <v>250.2971</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>4.91</v>
+        <v>6.44</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1625,7 +1622,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 8-c215bb</t>
+          <t>R1 ADVISORY · 1-326ea2</t>
         </is>
       </c>
     </row>
@@ -1662,13 +1659,13 @@
         <v>385.15</v>
       </c>
       <c r="H24" t="n">
-        <v>380.7</v>
+        <v>380.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.16</v>
+        <v>-1.1</v>
       </c>
       <c r="J24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1679,10 +1676,10 @@
         <v>396.6143</v>
       </c>
       <c r="M24" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="N24" t="n">
-        <v>4.98</v>
+        <v>4.63</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1697,16 +1694,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HOLD · R1 ADVISORY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1716,39 +1713,39 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1048.7</v>
+        <v>11475</v>
       </c>
       <c r="H25" t="n">
-        <v>1023.4</v>
+        <v>11162</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.41</v>
+        <v>-2.73</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1011.5999 · SUGGESTED</t>
+          <t>11144.7143</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1104.35</v>
+        <v>11970.4286</v>
       </c>
       <c r="M25" t="n">
-        <v>1.15</v>
+        <v>0.15</v>
       </c>
       <c r="N25" t="n">
-        <v>6.86</v>
+        <v>46.77</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1757,22 +1754,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 1-b637f4</t>
+          <t>R2 · 5-b3d435</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EXIT · stop hit</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1782,36 +1779,39 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>11475</v>
+        <v>1048.7</v>
       </c>
       <c r="H26" t="n">
-        <v>11100</v>
+        <v>1016.1</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.27</v>
+        <v>-3.11</v>
       </c>
       <c r="J26" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>11144.7143</t>
+          <t>1011.5999 · SUGGESTED</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>11970.4286</v>
+        <v>1104.35</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4</v>
+        <v>0.44</v>
+      </c>
+      <c r="N26" t="n">
+        <v>19.61</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>R2 · 5-b3d435</t>
+          <t>R1 ADVISORY · 1-b637f4</t>
         </is>
       </c>
     </row>
@@ -1830,51 +1830,51 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EXIT · stop hit</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>709</v>
+        <v>2064.8999</v>
       </c>
       <c r="H27" t="n">
-        <v>677.4</v>
+        <v>1973.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.46</v>
+        <v>-4.43</v>
       </c>
       <c r="J27" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>682.2286</t>
+          <t>1990.457 · SUGGESTED</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>749.1571</v>
+        <v>2176.5643</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.71</v>
+        <v>-0.86</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>R2 · 4-a68e4b</t>
+          <t>R1 ADVISORY · 2-08d1f5</t>
         </is>
       </c>
     </row>
@@ -1920,13 +1920,13 @@
         <v>381.6</v>
       </c>
       <c r="H28" t="n">
-        <v>365.7</v>
+        <v>368</v>
       </c>
       <c r="I28" t="n">
-        <v>-4.17</v>
+        <v>-3.56</v>
       </c>
       <c r="J28" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>399.375</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.11</v>
+        <v>-0.48</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1952,55 +1952,55 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HOLD · R1 ADVISORY</t>
+          <t>EXIT · stop hit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1191</v>
+        <v>709</v>
       </c>
       <c r="H29" t="n">
-        <v>1143</v>
+        <v>672.75</v>
       </c>
       <c r="I29" t="n">
-        <v>-4.03</v>
+        <v>-5.11</v>
       </c>
       <c r="J29" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1149.2286 · SUGGESTED</t>
+          <t>682.2286</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1253.6571</v>
+        <v>749.1571</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.54</v>
+        <v>-1.41</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2009,13 +2009,13 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 1-58636b</t>
+          <t>R2 · 4-a68e4b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2039,31 +2039,31 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2064.8999</v>
+        <v>5454.5</v>
       </c>
       <c r="H30" t="n">
-        <v>1962</v>
+        <v>5101.5</v>
       </c>
       <c r="I30" t="n">
-        <v>-4.98</v>
+        <v>-6.47</v>
       </c>
       <c r="J30" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1990.457 · SUGGESTED</t>
+          <t>5283.7143 · SUGGESTED</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2176.5643</v>
+        <v>5710.6786</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.45</v>
+        <v>-3.57</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 2-08d1f5</t>
+          <t>R1 ADVISORY · 4-3de31c</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2106,27 +2106,27 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>5454.5</v>
+        <v>507.9</v>
       </c>
       <c r="H31" t="n">
-        <v>5130</v>
+        <v>476.05</v>
       </c>
       <c r="I31" t="n">
-        <v>-5.95</v>
+        <v>-6.27</v>
       </c>
       <c r="J31" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5283.7143 · SUGGESTED</t>
+          <t>493.3286 · SUGGESTED</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5710.6786</v>
+        <v>529.7572</v>
       </c>
       <c r="M31" t="n">
-        <v>-3</v>
+        <v>-3.63</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2135,13 +2135,13 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 4-3de31c</t>
+          <t>R1 ADVISORY · 4-afbb8f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2165,31 +2165,31 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>507.9</v>
+        <v>1191</v>
       </c>
       <c r="H32" t="n">
-        <v>474.6</v>
+        <v>1120</v>
       </c>
       <c r="I32" t="n">
-        <v>-6.56</v>
+        <v>-5.96</v>
       </c>
       <c r="J32" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>493.3286 · SUGGESTED</t>
+          <t>1149.2286 · SUGGESTED</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>529.7572</v>
+        <v>1253.6571</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.95</v>
+        <v>-2.61</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2198,13 +2198,13 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 4-afbb8f</t>
+          <t>R1 ADVISORY · 1-58636b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2235,13 +2235,13 @@
         <v>452.35</v>
       </c>
       <c r="H33" t="n">
-        <v>418.3</v>
+        <v>419.05</v>
       </c>
       <c r="I33" t="n">
-        <v>-7.53</v>
+        <v>-7.36</v>
       </c>
       <c r="J33" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>477.4857</v>
       </c>
       <c r="M33" t="n">
-        <v>-4.13</v>
+        <v>-3.95</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2298,13 +2298,13 @@
         <v>284.85</v>
       </c>
       <c r="H34" t="n">
-        <v>263</v>
+        <v>264.1</v>
       </c>
       <c r="I34" t="n">
-        <v>-7.67</v>
+        <v>-7.28</v>
       </c>
       <c r="J34" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>297.975</v>
       </c>
       <c r="M34" t="n">
-        <v>-4.98</v>
+        <v>-4.54</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2361,13 +2361,13 @@
         <v>2410</v>
       </c>
       <c r="H35" t="n">
-        <v>2132</v>
+        <v>2110</v>
       </c>
       <c r="I35" t="n">
-        <v>-11.54</v>
+        <v>-12.45</v>
       </c>
       <c r="J35" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>2552.7572</v>
       </c>
       <c r="M35" t="n">
-        <v>-8.58</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2541,8 +2541,10 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>500</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2566,8 +2568,10 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>500</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2591,8 +2595,10 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>230</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2616,8 +2622,10 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>15</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2641,8 +2649,10 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2666,8 +2676,10 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2693,7 +2705,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S2_universe_actual→S3_data_present</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2703,14 +2715,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>dropped 270 tickers</t>
+          <t>dropped 0 tickers</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Momentum scanned/raw</t>
+          <t>MVS relaxation budget</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2718,26 +2730,24 @@
           <t>india</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2/230</t>
-        </is>
+      <c r="C12" t="n">
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>M4/M1 · severe collapse if scanned &lt;&lt; raw</t>
+          <t>used 0 of 15 · rolling 90d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Momentum bottleneck</t>
+          <t>Price parquet freshness</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2747,24 +2757,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M3_after_out_of_universe_drop→M4_actually_scanned</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>dropped 228 tickers</t>
+          <t>230 files · newest mtime 0d ago</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P0 exit-bridge gate</t>
+          <t>Fundamentals PIT freshness</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2774,24 +2784,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>n=20 · delta=0.0075</t>
+          <t>trading_age=0d · unique_asof=3 (≥60 needed for F01-05 OOS)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MVS relaxation budget</t>
+          <t>Fundamentals substrate maturity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2800,23 +2810,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>used 0 of 15 · rolling 90d</t>
+          <t>Substrate-before-sophistication rule · F01-05 OOS unblock at 60 asof-dates</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Outcome Dataset</t>
+          <t>WORKED_LEGACY remediation queue</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2825,145 +2835,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non-admin closed: 24</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Signal Ledger</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>india</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>snapshots: 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Price parquet freshness</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>india</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>230 files · newest mtime 0d ago</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fundamentals PIT freshness</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>india</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>trading_age=1d · unique_asof=1 (≥60 needed for F01-05 OOS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fundamentals substrate maturity</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>india</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Substrate-before-sophistication rule · F01-05 OOS unblock at 60 asof-dates</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>WORKED_LEGACY remediation queue</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>india</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>19</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>19 schedulable · 7 blocked by substrate rule</t>
+          <t>16 schedulable · 6 blocked by substrate rule</t>
         </is>
       </c>
     </row>
@@ -3009,7 +2890,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · PORTFOLIO · current active holdings as of 2026-09-04</t>
+          <t>AEGIS INDIA · PORTFOLIO · current active holdings as of 2026-09-07</t>
         </is>
       </c>
     </row>
@@ -3152,51 +3033,47 @@
         <v>553.3</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>587.35</v>
+        <v>596.7</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>6.15</v>
+        <v>7.84</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>566.1643</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>5.12</v>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
         <v>587.6713999999999</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.05</v>
+        <v>-1.51</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>60</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 5.12% below</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-05 (~31d)</t>
+          <t>2026-10-05 (~28d)</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -3240,57 +3117,51 @@
         <v>11475</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>11100</v>
+        <v>11162</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-3.27</v>
+        <v>-2.73</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>10771.7143</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>3.5</v>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M6" s="6" t="n">
         <v>11970.4286</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>7.84</v>
+        <v>7.24</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>60</v>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.5% below</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04 (~30d)</t>
-        </is>
-      </c>
-      <c r="S6" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+          <t>2026-10-04 (~27d)</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>2.07</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -3328,57 +3199,51 @@
         <v>5499</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>5657</v>
+        <v>5643</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>5372.5714</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>4.79</v>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
         <v>5954.2499</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>5.25</v>
+        <v>5.52</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>60</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 4.79% below</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04 (~30d)</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+          <t>2026-10-04 (~27d)</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>1.15</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -3416,57 +3281,51 @@
         <v>2744.3</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>2735.3999</v>
+        <v>2698</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.32</v>
+        <v>-1.69</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>2556.9857</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>5.23</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M8" s="6" t="n">
         <v>2949.9715</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>7.84</v>
+        <v>9.34</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>60</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 5.23% below</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04 (~30d)</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+          <t>2026-10-04 (~27d)</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>1.79</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -3504,57 +3363,51 @@
         <v>709</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>677.4</v>
+        <v>672.75</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-4.46</v>
+        <v>-5.11</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>644.0286</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>4.27</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M9" s="6" t="n">
         <v>749.1571</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>10.59</v>
+        <v>11.36</v>
       </c>
       <c r="O9" s="6" t="n">
         <v>60</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 4.27% below</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03 (~29d)</t>
-        </is>
-      </c>
-      <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+          <t>2026-10-03 (~26d)</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>2.66</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -3592,57 +3445,51 @@
         <v>452.35</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>418.3</v>
+        <v>419.05</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-7.53</v>
+        <v>-7.36</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>403.5857</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>3.69</v>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
         <v>477.4857</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>14.15</v>
+        <v>13.94</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>60</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.69% below</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03 (~29d)</t>
-        </is>
-      </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+          <t>2026-10-03 (~26d)</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>3.78</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -3680,57 +3527,51 @@
         <v>284.85</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>263</v>
+        <v>264.1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>-7.67</v>
+        <v>-7.28</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>255.8286</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>3.13</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
         <v>297.975</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>13.3</v>
+        <v>12.83</v>
       </c>
       <c r="O11" s="6" t="n">
         <v>60</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.13% below</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03 (~29d)</t>
-        </is>
-      </c>
-      <c r="S11" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+          <t>2026-10-03 (~26d)</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>4.1</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -3768,57 +3609,51 @@
         <v>113.36</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>116.32</v>
+        <v>117</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>2.61</v>
+        <v>3.21</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>3.12</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
         <v>118.8736</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>60</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.12% below</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03 (~29d)</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+          <t>2026-10-03 (~26d)</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0.51</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -3954,14 +3789,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · TODAY + MOMENTUM · reporting date 2026-09-04</t>
+          <t>AEGIS INDIA · TODAY + MOMENTUM · reporting date 2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>📅 Today's R2 momentum scan · ✓ ledger fresh for 2026-09-04 · scanned universe=0 · Actions: {'INVEST': 0, 'WATCH': 0, 'AVOID': 0, 'NO EVIDENCE': 0}</t>
+          <t>📅 Today's R2 momentum scan · ✓ ledger fresh for 2026-09-07 · scanned universe=1 · Actions: {'INVEST': 0, 'WATCH': 0, 'AVOID': 1, 'NO EVIDENCE': 0}</t>
         </is>
       </c>
     </row>
@@ -4053,9 +3888,81 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No R2 decisions/recommendations for 2026-09-04 </t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>QUICK_RISE</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2938</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>verdict=PUMP_RISK · big move on low-quality name · pump-and-dump risk · avoid</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>canonical:momentum_ledger+prices+sector_cache</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4059,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · realized · as of 2026-09-04</t>
+          <t>AEGIS INDIA · EXIT HISTORY · realized · as of 2026-09-07</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4073,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Excluded (routed to orphan_audit_india.jsonl · not P&amp;L): 18 administrative (same-day/zero-Δ) · 5 retired-runner</t>
+          <t xml:space="preserve">    Excluded (routed to orphan_audit_india.jsonl · not P&amp;L): 19 administrative (same-day/zero-Δ) · 5 retired-runner</t>
         </is>
       </c>
     </row>
@@ -4285,10 +4192,10 @@
         <v>391.3</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>416.9</v>
+        <v>415.35</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>6.54</v>
+        <v>6.15</v>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
@@ -5568,7 +5475,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>18 same-day / zero-Δ administrative events + 5 retired-runner events filtered from this operator-facing view · they remain in the canonical Registry JSONL and orphan_audit sink for audit.</t>
+          <t>19 same-day / zero-Δ administrative events + 5 retired-runner events filtered from this operator-facing view · they remain in the canonical Registry JSONL and orphan_audit sink for audit.</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M330"/>
+  <dimension ref="A1:M338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5621,14 +5528,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · DAILY PORTFOLIO HISTORY · reconstructed from canonical Registry as of 2026-09-04</t>
+          <t>AEGIS INDIA · DAILY PORTFOLIO HISTORY · reconstructed from canonical Registry as of 2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>📅 Reconstructed from Registry · 29 genuine R2 positions · trading days 2026-08-04 → 2026-09-04 · excludes same-day admin events</t>
+          <t>📅 Reconstructed from Registry · 29 genuine R2 positions · trading days 2026-08-04 → 2026-09-07 · excludes same-day admin events</t>
         </is>
       </c>
     </row>
@@ -24156,10 +24063,10 @@
         <v>11475</v>
       </c>
       <c r="H307" s="6" t="n">
-        <v>11100</v>
+        <v>11165</v>
       </c>
       <c r="I307" s="8" t="n">
-        <v>-3.27</v>
+        <v>-2.7</v>
       </c>
       <c r="J307" s="6" t="inlineStr">
         <is>
@@ -24705,10 +24612,10 @@
         <v>11475</v>
       </c>
       <c r="H316" s="6" t="n">
-        <v>11100</v>
+        <v>11162</v>
       </c>
       <c r="I316" s="8" t="n">
-        <v>-3.27</v>
+        <v>-2.73</v>
       </c>
       <c r="J316" s="6" t="inlineStr">
         <is>
@@ -24717,12 +24624,12 @@
       </c>
       <c r="K316" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L316" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M316" s="6" t="inlineStr">
@@ -24766,10 +24673,10 @@
         <v>709</v>
       </c>
       <c r="H317" s="6" t="n">
-        <v>677.4</v>
+        <v>672.75</v>
       </c>
       <c r="I317" s="8" t="n">
-        <v>-4.46</v>
+        <v>-5.11</v>
       </c>
       <c r="J317" s="6" t="inlineStr">
         <is>
@@ -24778,12 +24685,12 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M317" s="6" t="inlineStr">
@@ -24827,10 +24734,10 @@
         <v>452.35</v>
       </c>
       <c r="H318" s="6" t="n">
-        <v>418.3</v>
+        <v>419.05</v>
       </c>
       <c r="I318" s="8" t="n">
-        <v>-7.53</v>
+        <v>-7.36</v>
       </c>
       <c r="J318" s="6" t="inlineStr">
         <is>
@@ -24839,12 +24746,12 @@
       </c>
       <c r="K318" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L318" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M318" s="6" t="inlineStr">
@@ -24888,10 +24795,10 @@
         <v>553.3</v>
       </c>
       <c r="H319" s="6" t="n">
-        <v>587.35</v>
+        <v>596.7</v>
       </c>
       <c r="I319" s="7" t="n">
-        <v>6.15</v>
+        <v>7.84</v>
       </c>
       <c r="J319" s="6" t="inlineStr">
         <is>
@@ -24900,12 +24807,12 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M319" s="6" t="inlineStr">
@@ -24949,10 +24856,10 @@
         <v>284.85</v>
       </c>
       <c r="H320" s="6" t="n">
-        <v>263</v>
+        <v>264.1</v>
       </c>
       <c r="I320" s="8" t="n">
-        <v>-7.67</v>
+        <v>-7.28</v>
       </c>
       <c r="J320" s="6" t="inlineStr">
         <is>
@@ -24961,12 +24868,12 @@
       </c>
       <c r="K320" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L320" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M320" s="6" t="inlineStr">
@@ -25010,10 +24917,10 @@
         <v>5499</v>
       </c>
       <c r="H321" s="6" t="n">
-        <v>5657</v>
+        <v>5643</v>
       </c>
       <c r="I321" s="7" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="J321" s="6" t="inlineStr">
         <is>
@@ -25022,12 +24929,12 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M321" s="6" t="inlineStr">
@@ -25071,10 +24978,10 @@
         <v>113.36</v>
       </c>
       <c r="H322" s="6" t="n">
-        <v>116.32</v>
+        <v>117</v>
       </c>
       <c r="I322" s="7" t="n">
-        <v>2.61</v>
+        <v>3.21</v>
       </c>
       <c r="J322" s="6" t="inlineStr">
         <is>
@@ -25083,12 +24990,12 @@
       </c>
       <c r="K322" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L322" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M322" s="6" t="inlineStr">
@@ -25132,10 +25039,10 @@
         <v>2744.3</v>
       </c>
       <c r="H323" s="6" t="n">
-        <v>2735.3999</v>
+        <v>2698</v>
       </c>
       <c r="I323" s="8" t="n">
-        <v>-0.32</v>
+        <v>-1.69</v>
       </c>
       <c r="J323" s="6" t="inlineStr">
         <is>
@@ -25144,12 +25051,12 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M323" s="6" t="inlineStr">
@@ -25158,36 +25065,508 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
+        <is>
+          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+        </is>
+      </c>
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E324" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G324" s="6" t="n">
+        <v>11475</v>
+      </c>
+      <c r="H324" s="6" t="n">
+        <v>11162</v>
+      </c>
+      <c r="I324" s="8" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="J324" s="6" t="n">
+        <v>10771.7143</v>
+      </c>
+      <c r="K324" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L324" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M324" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
+        <is>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+        </is>
+      </c>
+      <c r="C325" s="6" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E325" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G325" s="6" t="n">
+        <v>709</v>
+      </c>
+      <c r="H325" s="6" t="n">
+        <v>672.75</v>
+      </c>
+      <c r="I325" s="8" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="J325" s="6" t="n">
+        <v>644.0286</v>
+      </c>
+      <c r="K325" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L325" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M325" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
     <row r="326">
-      <c r="A326" s="4" t="inlineStr">
+      <c r="A326" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B326" s="6" t="inlineStr">
+        <is>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+        </is>
+      </c>
+      <c r="C326" s="6" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="D326" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E326" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F326" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G326" s="6" t="n">
+        <v>452.35</v>
+      </c>
+      <c r="H326" s="6" t="n">
+        <v>419.05</v>
+      </c>
+      <c r="I326" s="8" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="J326" s="6" t="n">
+        <v>403.5857</v>
+      </c>
+      <c r="K326" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L326" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M326" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B327" s="6" t="inlineStr">
+        <is>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
+        </is>
+      </c>
+      <c r="C327" s="6" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="D327" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E327" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F327" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G327" s="6" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="H327" s="6" t="n">
+        <v>596.7</v>
+      </c>
+      <c r="I327" s="7" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="J327" s="6" t="n">
+        <v>566.1643</v>
+      </c>
+      <c r="K327" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L327" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M327" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B328" s="6" t="inlineStr">
+        <is>
+          <t>IND-R2-ITC-20260804-e0ebbb</t>
+        </is>
+      </c>
+      <c r="C328" s="6" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D328" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E328" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F328" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G328" s="6" t="n">
+        <v>284.85</v>
+      </c>
+      <c r="H328" s="6" t="n">
+        <v>264.1</v>
+      </c>
+      <c r="I328" s="8" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="J328" s="6" t="n">
+        <v>255.8286</v>
+      </c>
+      <c r="K328" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L328" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M328" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B329" s="6" t="inlineStr">
+        <is>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+        </is>
+      </c>
+      <c r="C329" s="6" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D329" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E329" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F329" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G329" s="6" t="n">
+        <v>5499</v>
+      </c>
+      <c r="H329" s="6" t="n">
+        <v>5643</v>
+      </c>
+      <c r="I329" s="7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J329" s="6" t="n">
+        <v>5372.5714</v>
+      </c>
+      <c r="K329" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L329" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M329" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
+        </is>
+      </c>
+      <c r="C330" s="6" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D330" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E330" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F330" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G330" s="6" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="H330" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="I330" s="7" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J330" s="6" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="K330" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L330" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M330" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B331" s="6" t="inlineStr">
+        <is>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+        </is>
+      </c>
+      <c r="C331" s="6" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="D331" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E331" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F331" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G331" s="6" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="H331" s="6" t="n">
+        <v>2698</v>
+      </c>
+      <c r="I331" s="8" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="J331" s="6" t="n">
+        <v>2556.9857</v>
+      </c>
+      <c r="K331" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L331" s="6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M331" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="inlineStr">
         <is>
           <t>Reconstructed daily active-portfolio history from canonical Registry.</t>
         </is>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" s="4" t="inlineStr">
+    <row r="335">
+      <c r="A335" s="4" t="inlineStr">
         <is>
           <t>One row per position per trading day while the position was genuinely active.</t>
         </is>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" s="4" t="inlineStr">
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
         <is>
           <t>Excludes same-day administrative Registry records (entry_date == exit_date).</t>
         </is>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" s="4" t="inlineStr">
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
         <is>
           <t>Dynamic Stop is populated ONLY for the current as-of date · historical dynamic stops are UNAVAILABLE because dynamic_risk_v2 stores only the current snapshot.</t>
         </is>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" s="4" t="inlineStr">
+    <row r="338">
+      <c r="A338" s="4" t="inlineStr">
         <is>
           <t>Never fabricated · UNAVAILABLE means the canonical source has no value for that day.</t>
         </is>
@@ -25195,13 +25574,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A330:M330"/>
-    <mergeCell ref="A326:M326"/>
+    <mergeCell ref="A334:M334"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A329:M329"/>
-    <mergeCell ref="A328:M328"/>
-    <mergeCell ref="A327:M327"/>
+    <mergeCell ref="A338:M338"/>
+    <mergeCell ref="A336:M336"/>
+    <mergeCell ref="A337:M337"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A335:M335"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25213,7 +25592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -25291,12 +25670,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1393 - 1467</t>
+          <t>1387 - 1460</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.4%) • outperforming Nifty • sector strength 85/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.9%) • outperforming Nifty • sector strength 79/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -25332,12 +25711,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1866 - 1966</t>
+          <t>1849 - 1949</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.4%) • outperforming Nifty • sector strength 69/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.4%) • sector strength 64/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -25373,12 +25752,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>323 - 339</t>
+          <t>325 - 340</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.4%) • sector strength 8/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.9%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -25414,12 +25793,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>397 - 420</t>
+          <t>394 - 417</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.5%) • sector strength 77/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.3%) • sector strength 71/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -25437,12 +25816,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -25455,12 +25834,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>259 - 272</t>
+          <t>1343 - 1427</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.6%) • sector strength 8/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.6%) • sector strength 64/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -25478,12 +25857,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -25496,12 +25875,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>229 - 243</t>
+          <t>260 - 272</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.4%) • sector strength 54/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.5%) • sector strength 7/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -25537,12 +25916,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>408 - 432</t>
+          <t>403 - 427</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.0%) • sector strength 38/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.1%) • sector strength 43/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -25560,12 +25939,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -25578,12 +25957,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>257 - 269</t>
+          <t>183 - 195</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.1%) • sector strength 23/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.9%) • sector strength 43/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -25601,12 +25980,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -25619,12 +25998,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>179 - 190</t>
+          <t>228 - 242</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.9%) • sector strength 36/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -25642,7 +26021,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -25660,12 +26039,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>369 - 393</t>
+          <t>258 - 270</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.6%) • sector strength 23/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.5%) • sector strength 14/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -25683,17 +26062,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -25701,12 +26080,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>461 - 488</t>
+          <t>369 - 393</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.6%) • sector strength 15/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION d</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.4%) • sector strength 14/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -25716,6 +26095,47 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>463 - 489</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.2%) • sector strength 57/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION d</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>no dynamic-exit protection</t>
         </is>
@@ -25858,7 +26278,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -25866,7 +26286,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2682</v>
+        <v>-0.2474</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -25905,7 +26325,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -25913,7 +26333,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2804</v>
+        <v>0.2125</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -25952,7 +26372,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25960,7 +26380,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2889</v>
+        <v>0.1861</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -25999,7 +26419,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -26007,7 +26427,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2507</v>
+        <v>0.3676</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -26046,7 +26466,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -26054,7 +26474,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2133</v>
+        <v>0.2225</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -26093,7 +26513,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -26101,7 +26521,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2332</v>
+        <v>0.2042</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -26140,7 +26560,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -26148,7 +26568,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2677</v>
+        <v>-0.2286</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -26187,7 +26607,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -26195,7 +26615,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2849</v>
+        <v>0.1789</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -26234,7 +26654,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -26242,7 +26662,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2354</v>
+        <v>0.1907</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -26281,7 +26701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -26289,7 +26709,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2779</v>
+        <v>0.239</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -26328,7 +26748,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -26336,7 +26756,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3021</v>
+        <v>-0.2753</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -26375,7 +26795,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -26383,7 +26803,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2302</v>
+        <v>0.1854</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -26422,7 +26842,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -26430,7 +26850,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2667</v>
+        <v>-0.2332</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -26469,7 +26889,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -26477,7 +26897,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.302</v>
+        <v>-0.2889</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -26524,7 +26944,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2832</v>
+        <v>0.2517</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Held: 16 · today's advisory BUY signals: 30 · needing review (stop breach or deep loss): 6</t>
+          <t>Held: 16 · today's advisory BUY signals: 6 · needing review (stop breach or deep loss): 6</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="M6" s="4" t="n">
-        <v>100</v>
+        <v>49.1</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -722,12 +722,14 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>100</v>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -791,11 +793,11 @@
         </is>
       </c>
       <c r="M8" s="4" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -858,12 +860,14 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>100</v>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -926,12 +930,14 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="M10" s="4" t="n">
-        <v>100</v>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -994,12 +1000,14 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>100</v>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1062,12 +1070,14 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>100</v>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1131,11 +1141,11 @@
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1199,11 +1209,11 @@
         </is>
       </c>
       <c r="M14" s="4" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1267,11 +1277,11 @@
         </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1335,11 +1345,11 @@
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1402,12 +1412,14 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="M17" s="4" t="n">
-        <v>100</v>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1471,7 +1483,7 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>88</v>
+        <v>40.6</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -1539,11 +1551,11 @@
         </is>
       </c>
       <c r="M19" s="4" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1607,11 +1619,11 @@
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1674,12 +1686,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M21" s="4" t="n">
-        <v>100</v>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -1703,7 +1717,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1713,7 +1727,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1725,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1965.3</v>
+        <v>1423.2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1965.3</v>
+        <v>1423.2</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
@@ -1752,20 +1766,20 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>ADVISORY BUY</t>
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:83.5 · high_confidence:1.00</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.9%) • outperforming Nifty • sect</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -1777,7 +1791,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1787,7 +1801,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1799,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>598.8</v>
+        <v>1899</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>598.8</v>
+        <v>1899</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1826,20 +1840,20 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>ADVISORY BUY</t>
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:81.9 · high_confidence:1.00</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.4%) • sector strength 64/100 • regim</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -1851,7 +1865,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1861,7 +1875,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1873,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1222</v>
+        <v>332.5</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1222</v>
+        <v>332.5</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -1900,20 +1914,20 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>NEW · BUY</t>
+          <t>ADVISORY BUY</t>
         </is>
       </c>
       <c r="M26" s="4" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:76.3 · high_confidence:1.00</t>
+          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.9%) • sector strength 7/100 • regime </t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -1925,7 +1939,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1935,7 +1949,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1947,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2932.4</v>
+        <v>405.35</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2932.4</v>
+        <v>405.35</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -1974,20 +1988,20 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>NEW · BUY</t>
+          <t>ADVISORY BUY</t>
         </is>
       </c>
       <c r="M27" s="4" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>company_score_bullish:73.1 · high_confidence:1.00</t>
+          <t xml:space="preserve">Low-risk Industrials holding (low vol) • below 200-dma (-3.3%) • sector strength 71/100 • </t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -1999,7 +2013,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2009,7 +2023,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2021,10 +2035,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>789</v>
+        <v>1385</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>789</v>
+        <v>1385</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -2048,20 +2062,20 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>ADVISORY BUY</t>
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:80.6 · high_confidence:1.00</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.6%) • sector strength 64/100 • regim</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -2073,7 +2087,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2083,7 +2097,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2095,10 +2109,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>424.35</v>
+        <v>266</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>424.35</v>
+        <v>266</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -2122,20 +2136,20 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>ADVISORY BUY</t>
         </is>
       </c>
       <c r="M29" s="4" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:78.1 · high_confidence:1.00</t>
+          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.5%) • sector strength 7/100 • regime </t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -2144,1826 +2158,50 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>1120</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>1120</v>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O30" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:75.6 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Realty</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>1982</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>1982</v>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:71.8 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>1840</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1840</v>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:66.5 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>R1 is RETIRED_ADVISORY · shown for operator awareness · it opens and closes nothing automatically.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>AJANTPHARM</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>3464.8</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>3464.8</v>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:66.0 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Suggested Stop · Entry − 2×ATR14 at entry · a SUGGESTION · it is NOT the canonical dynamic_risk_v2 stop and is not enforced.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Realty</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>1942</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>1942</v>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:67.0 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Review State · 🟢 NORMAL · 🟡 WATCH (within 3.0% of stop or ≤-8.0% P&amp;L) · 🔴 STOP BREACH (price at/below suggested stop) · 🔴 DEEP LOSS (≤-15.0% P&amp;L).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>1899</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>1899</v>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:70.7 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Action never exceeds REVIEW · R1 auto-exit is prohibited by V2 §18.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>BIOCON</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>397.4</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>397.4</v>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:63.2 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>R1 P&amp;L is never mixed into R2 production performance.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>4494</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>4494</v>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:77.9 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.491 · mean 0.349 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>ABBOTINDIA</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>26065</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>26065</v>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:61.2 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>RELAXO</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Consumption</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>344.75</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>344.75</v>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:68.3 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>4857</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>4857</v>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:65.4 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>APOLLOHOSP</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>8650</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>8650</v>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:73.6 · high_confidence:0.92</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>1956</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>1956</v>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:64.1 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:69.1 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>1319.8</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>1319.8</v>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O44" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:68.9 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>457.9</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>457.9</v>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N45" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O45" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:68.2 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Consumption</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>5020</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>5020</v>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O46" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:69.9 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>1653.1</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>1653.1</v>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N47" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O47" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:61.0 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>2938</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>2938</v>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N48" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O48" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:69.4 · high_confidence:1.00</t>
-        </is>
-      </c>
-      <c r="P48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>1423.2</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>1423.2</v>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY BUY</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
-        </is>
-      </c>
-      <c r="O49" s="4" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.9%) • outperforming Nifty • sect</t>
-        </is>
-      </c>
-      <c r="P49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY BUY</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
-        </is>
-      </c>
-      <c r="O50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.9%) • sector strength 7/100 • regime </t>
-        </is>
-      </c>
-      <c r="P50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>405.35</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>405.35</v>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY BUY</t>
-        </is>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
-        </is>
-      </c>
-      <c r="O51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low-risk Industrials holding (low vol) • below 200-dma (-3.3%) • sector strength 71/100 • </t>
-        </is>
-      </c>
-      <c r="P51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>CIPLA</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>1385</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>1385</v>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY BUY</t>
-        </is>
-      </c>
-      <c r="M52" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="N52" s="4" t="inlineStr">
-        <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
-        </is>
-      </c>
-      <c r="O52" s="4" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.6%) • sector strength 64/100 • regim</t>
-        </is>
-      </c>
-      <c r="P52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY BUY</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="N53" s="4" t="inlineStr">
-        <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
-        </is>
-      </c>
-      <c r="O53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.5%) • sector strength 7/100 • regime </t>
-        </is>
-      </c>
-      <c r="P53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>R1 is RETIRED_ADVISORY · shown for operator awareness · it opens and closes nothing automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Suggested Stop · Entry − 2×ATR14 at entry · a SUGGESTION · it is NOT the canonical dynamic_risk_v2 stop and is not enforced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>Review State · 🟢 NORMAL · 🟡 WATCH (within 3.0% of stop or ≤-8.0% P&amp;L) · 🔴 STOP BREACH (price at/below suggested stop) · 🔴 DEEP LOSS (≤-15.0% P&amp;L).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Action never exceeds REVIEW · R1 auto-exit is prohibited by V2 §18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>R1 P&amp;L is never mixed into R2 production performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. ⚠ SATURATED: range 0.88–1.0 · mean 0.978 · 76.0% of scored names sit at the maximum · a high value here means the engine did not separate this name from the rest, not that the call is certain. Treat it as low-information until the engine is recalibrated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Confidence Source · names exactly where the number came from · a value with no stated source is not trustworthy.</t>
         </is>
@@ -3971,16 +2209,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A60:P60"/>
+    <mergeCell ref="A32:P32"/>
+    <mergeCell ref="A36:P36"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A23:P23"/>
-    <mergeCell ref="A56:P56"/>
-    <mergeCell ref="A61:P61"/>
-    <mergeCell ref="A58:P58"/>
-    <mergeCell ref="A62:P62"/>
+    <mergeCell ref="A37:P37"/>
+    <mergeCell ref="A34:P34"/>
+    <mergeCell ref="A35:P35"/>
     <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A59:P59"/>
-    <mergeCell ref="A57:P57"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A33:P33"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4210,12 +2448,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="n">
-        <v>100</v>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
@@ -4297,12 +2537,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="n">
-        <v>88</v>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S7" s="4" t="inlineStr">
@@ -4384,12 +2626,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>100</v>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr">
@@ -4471,12 +2715,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="n">
-        <v>92</v>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr">
@@ -4558,12 +2804,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="n">
-        <v>100</v>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr">
@@ -4645,12 +2893,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="n">
-        <v>100</v>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S11" s="4" t="inlineStr">
@@ -4732,12 +2982,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="n">
-        <v>100</v>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
@@ -4822,7 +3074,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>100</v>
+        <v>39.3</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -4897,7 +3149,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. ⚠ SATURATED: range 0.88–1.0 · mean 0.978 · 76.0% of scored names sit at the maximum · a high value here means the engine did not separate this name from the rest, not that the call is certain. Treat it as low-information until the engine is recalibrated.</t>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.491 · mean 0.349 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
@@ -5652,7 +3904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5680,14 +3932,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>50 row(s) · 6 position(s) need attention (stop breach or deep loss) · R2 production 8 · R1 advisory 16 · momentum candidates 0</t>
+          <t>27 row(s) · 6 position(s) need attention (stop breach or deep loss) · R2 production 8 · R1 advisory 16 · momentum candidates 0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Daily recommendations · as-of 2026-09-07 · 208 scored · 51 investable (NEW_POSITION) · 🟢 FRESH</t>
+          <t>Daily recommendations · as-of 2026-09-07 · 15 scored · 0 investable (NEW_POSITION) · 🟢 FRESH</t>
         </is>
       </c>
     </row>
@@ -5811,8 +4063,10 @@
           <t>R2 ACTIVE · held 34 d</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>100</v>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
@@ -5866,8 +4120,10 @@
           <t>R2 ACTIVE · held 34 d</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n">
-        <v>88</v>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
@@ -5921,8 +4177,10 @@
           <t>R2 ACTIVE · held 34 d</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n">
-        <v>100</v>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
@@ -5976,8 +4234,10 @@
           <t>R2 ACTIVE · held 33 d</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n">
-        <v>92</v>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
@@ -6031,8 +4291,10 @@
           <t>R2 ACTIVE · held 33 d</t>
         </is>
       </c>
-      <c r="L10" s="4" t="n">
-        <v>100</v>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
@@ -6086,8 +4348,10 @@
           <t>R2 ACTIVE · held 33 d</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n">
-        <v>100</v>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -6141,8 +4405,10 @@
           <t>R2 ACTIVE · held 34 d</t>
         </is>
       </c>
-      <c r="L12" s="4" t="n">
-        <v>100</v>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
@@ -6197,7 +4463,7 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>100</v>
+        <v>39.3</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
@@ -6254,7 +4520,7 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>100</v>
+        <v>49.1</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
@@ -6310,8 +4576,10 @@
           <t>R1 ADVISORY · held 34 d</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n">
-        <v>100</v>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
@@ -6368,7 +4636,7 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
@@ -6424,8 +4692,10 @@
           <t>R1 ADVISORY · held 27 d</t>
         </is>
       </c>
-      <c r="L17" s="4" t="n">
-        <v>100</v>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
@@ -6481,8 +4751,10 @@
           <t>R1 ADVISORY · held 26 d</t>
         </is>
       </c>
-      <c r="L18" s="4" t="n">
-        <v>100</v>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -6538,8 +4810,10 @@
           <t>R1 ADVISORY · held 34 d</t>
         </is>
       </c>
-      <c r="L19" s="4" t="n">
-        <v>100</v>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -6595,8 +4869,10 @@
           <t>R1 ADVISORY · held 17 d</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n">
-        <v>100</v>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -6653,7 +4929,7 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -6710,7 +4986,7 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -6767,7 +5043,7 @@
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -6824,7 +5100,7 @@
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
@@ -6880,8 +5156,10 @@
           <t>R1 ADVISORY · held 34 d</t>
         </is>
       </c>
-      <c r="L25" s="4" t="n">
-        <v>100</v>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
@@ -6938,7 +5216,7 @@
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>88</v>
+        <v>40.6</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
@@ -6995,7 +5273,7 @@
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
@@ -7052,7 +5330,7 @@
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
@@ -7108,8 +5386,10 @@
           <t>R1 ADVISORY · held 34 d</t>
         </is>
       </c>
-      <c r="L29" s="4" t="n">
-        <v>100</v>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
@@ -7125,7 +5405,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -7139,7 +5419,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1965.3</v>
+        <v>1899</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
@@ -7163,7 +5443,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · REVIEW</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -7172,11 +5452,11 @@
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:83.5 · high_confidence:1.00</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.4%) • sector strength 64/100 • regim</t>
         </is>
       </c>
     </row>
@@ -7188,12 +5468,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -7202,7 +5482,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>598.8</v>
+        <v>332.5</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -7226,7 +5506,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · REVIEW</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -7235,11 +5515,11 @@
         </is>
       </c>
       <c r="L31" s="4" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:81.9 · high_confidence:1.00</t>
+          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.9%) • sector strength 7/100 • regime </t>
         </is>
       </c>
     </row>
@@ -7251,12 +5531,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -7265,7 +5545,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1222</v>
+        <v>266</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
@@ -7289,7 +5569,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>NEW · BUY</t>
+          <t>NEW · REVIEW</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -7298,1663 +5578,214 @@
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:76.3 · high_confidence:1.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>2932.4</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:73.1 · high_confidence:1.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>789</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:80.6 · high_confidence:1.00</t>
+          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.5%) • sector strength 7/100 • regime </t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>EXIDEIND</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>424.35</v>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:78.1 · high_confidence:1.00</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>MOMENTUM → R2 LIFECYCLE RECONCILIATION</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Realty</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>1982</v>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:71.8 · high_confidence:1.00</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Where the rest went</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>1840</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:66.5 · high_confidence:1.00</t>
-        </is>
-      </c>
+          <t>1 · Declared universe</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>AJANTPHARM</t>
-        </is>
+          <t>2 · Actually evaluated</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>230</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>3464.8</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:66.0 · high_confidence:1.00</t>
+          <t>unreadable=0 · insufficient history=0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
+          <t>3 · Momentum candidates</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Realty</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>1942</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:67.0 · high_confidence:1.00</t>
+          <t>225 evaluated tickers showed no momentum signal</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
+          <t>4 · In production universe</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>1899</v>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:70.7 · high_confidence:1.00</t>
+          <t>5 candidate(s) dropped as outside the 50-name production universe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>BIOCON</t>
-        </is>
+          <t>5 · ACCEPTED by ledger</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>397.4</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:63.2 · high_confidence:1.00</t>
+          <t>WATCH=0 · REJECTED=0 · NO_EVIDENCE=0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
+          <t>6 · Registry R2 NEW today</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>4494</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:77.9 · high_confidence:1.00</t>
+          <t>accepted momentum tickers not opened: none</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>ABBOTINDIA</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>26065</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:61.2 · high_confidence:1.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>RELAXO</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Consumption</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>344.75</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M44" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:68.3 · high_confidence:1.00</t>
-        </is>
-      </c>
+          <t>7 · R2 sheet ACTIVE</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>4857</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M45" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:65.4 · high_confidence:1.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>APOLLOHOSP</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>8650</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="M46" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:73.6 · high_confidence:0.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>1956</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M47" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:64.1 · high_confidence:1.00</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>✅ No unexplained losses between momentum and R2.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M48" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:69.1 · high_confidence:1.00</t>
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>1319.8</v>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M49" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:68.9 · high_confidence:1.00</t>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>457.9</v>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M50" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:68.2 · high_confidence:1.00</t>
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Consumption</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>5020</v>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M51" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:69.9 · high_confidence:1.00</t>
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>1653.1</v>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M52" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:61.0 · high_confidence:1.00</t>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>2938</v>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>NEW · BUY</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M53" s="4" t="inlineStr">
-        <is>
-          <t>company_score_bullish:69.4 · high_confidence:1.00</t>
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>NEW · REVIEW</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="M54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.9%) • sector strength 7/100 • regime </t>
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>NEW · REVIEW</t>
-        </is>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="M55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.5%) • sector strength 7/100 • regime </t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>MOMENTUM → R2 LIFECYCLE RECONCILIATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Where the rest went</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>1 · Declared universe</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>230</v>
-      </c>
-      <c r="C60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>2 · Actually evaluated</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n">
-        <v>230</v>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>unreadable=0 · insufficient history=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>3 · Momentum candidates</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>225 evaluated tickers showed no momentum signal</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>4 · In production universe</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>5 candidate(s) dropped as outside the 50-name production universe</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>5 · ACCEPTED by ledger</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>WATCH=0 · REJECTED=0 · NO_EVIDENCE=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>6 · Registry R2 NEW today</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>accepted momentum tickers not opened: none</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>7 · R2 sheet ACTIVE</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C66" s="4" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>✅ No unexplained losses between momentum and R2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. ⚠ SATURATED: range 0.88–1.0 · mean 0.978 · 76.0% of scored names sit at the maximum · a high value here means the engine did not separate this name from the rest, not that the call is certain. Treat it as low-information until the engine is recalibrated.</t>
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.491 · mean 0.349 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A76:M76"/>
-    <mergeCell ref="A68:M68"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A75:M75"/>
-    <mergeCell ref="A58:M58"/>
-    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A35:M35"/>
     <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A48:M48"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A78:M78"/>
-    <mergeCell ref="A77:M77"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A73:M73"/>
+    <mergeCell ref="A50:M50"/>
+    <mergeCell ref="A53:M53"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="A55:M55"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A71:M71"/>
+    <mergeCell ref="A49:M49"/>
+    <mergeCell ref="A52:M52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · R1 · ADVISORY ONLY · as of 2026-09-07</t>
+          <t>AEGIS INDIA · R1 · ADVISORY ONLY · as of 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Held: 16 · today's advisory BUY signals: 6 · needing review (stop breach or deep loss): 6</t>
+          <t>Held: 16 · today's advisory BUY signals: 11 · needing review (stop breach or deep loss): 8</t>
         </is>
       </c>
     </row>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>2410</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-12.45</v>
+        <v>-12.66</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>2314.8285</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="M6" s="4" t="n">
-        <v>49.1</v>
+        <v>40.6</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>5454.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5101.5</v>
+        <v>5042.5</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-6.47</v>
+        <v>-7.55</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>5283.7143</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.57</v>
+        <v>-4.78</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>507.9</v>
@@ -792,12 +792,14 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="M8" s="4" t="n">
-        <v>66</v>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -814,7 +816,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -824,31 +826,31 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
         <v>27</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1191</v>
+        <v>2064.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1120</v>
+        <v>1973.4</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-5.96</v>
+        <v>-4.43</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1149.2286</v>
+        <v>1990.457</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.61</v>
+        <v>-0.86</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -877,14 +879,14 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
+          <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -894,31 +896,31 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2064.9</v>
+        <v>381.6</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1973.4</v>
+        <v>365.7</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-4.43</v>
+        <v>-4.17</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1990.457</v>
+        <v>369.75</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.86</v>
+        <v>-1.11</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -930,14 +932,12 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+      <c r="M10" s="4" t="n">
+        <v>63</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>NOT CAPTURED</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -947,14 +947,14 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
+          <t>IND-R1-TATAPOWER-20260804-29907f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>381.6</v>
+        <v>1642.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>368</v>
+        <v>1575</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-3.56</v>
+        <v>-4.11</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>369.75</v>
+        <v>1594.6857</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.48</v>
+        <v>-1.25</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATAPOWER-20260804-29907f</t>
+          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
         </is>
       </c>
     </row>
@@ -1043,46 +1043,44 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>1048.7</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1016.1</v>
+        <v>1005.9</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-3.11</v>
+        <v>-4.08</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>1011.5999</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.44</v>
+        <v>-0.57</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>🟡 WATCH</t>
+          <t>🔴 STOP BREACH</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>71</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>NOT CAPTURED</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>R1 approaching advisory stop</t>
+          <t>R1 advisory stop breached · no auto-exit</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -1094,7 +1092,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1104,7 +1102,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1113,35 +1111,35 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1413.5</v>
+        <v>385.15</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1385</v>
+        <v>375.5</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-2.02</v>
+        <v>-2.51</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1382.3857</v>
+        <v>377.5071</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.19</v>
+        <v>-0.53</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>🟡 WATCH</t>
+          <t>🔴 STOP BREACH</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
@@ -1150,19 +1148,19 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>R1 approaching advisory stop</t>
+          <t>R1 advisory stop breached · no auto-exit</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R1-DABUR-20260828-be7819</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1172,7 +1170,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1181,22 +1179,22 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>239.45</v>
+        <v>1191</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>234.65</v>
+        <v>1156.9</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-2</v>
+        <v>-2.86</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>232.2186</v>
+        <v>1149.2286</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1208,12 +1206,14 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="M14" s="4" t="n">
-        <v>67</v>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1223,14 +1223,14 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1240,31 +1240,31 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1449.5</v>
+        <v>239.45</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1423.2</v>
+        <v>233.7</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-1.81</v>
+        <v>-2.4</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1412.0571</v>
+        <v>232.2186</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1317,22 +1317,22 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>385.15</v>
+        <v>1413.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>380.9</v>
+        <v>1385</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-1.1</v>
+        <v>-2.02</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>377.5071</v>
+        <v>1382.3857</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.89</v>
+        <v>0.19</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1344,12 +1344,14 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="M16" s="4" t="n">
-        <v>62</v>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1359,14 +1361,14 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-DABUR-20260828-be7819</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1376,7 +1378,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1385,22 +1387,22 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1642.5</v>
+        <v>1449.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1629.5</v>
+        <v>1427.5</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.79</v>
+        <v>-1.52</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1594.6857</v>
+        <v>1412.0571</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.14</v>
+        <v>1.08</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1412,14 +1414,12 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+      <c r="M17" s="4" t="n">
+        <v>83</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>NOT CAPTURED</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1446,31 +1446,31 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>417.6</v>
+        <v>187.46</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>415.35</v>
+        <v>185.61</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.54</v>
+        <v>-0.99</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>407.3714</v>
+        <v>181.8114</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1483,11 +1483,11 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>40.6</v>
+        <v>65</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1497,14 +1497,14 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1514,58 +1514,58 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>187.46</v>
+        <v>417.6</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>188.79</v>
+        <v>418.85</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>181.8114</v>
+        <v>407.3714</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.7</v>
+        <v>2.74</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>🟢 NORMAL</t>
+          <t>🟡 WATCH</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="M19" s="4" t="n">
-        <v>64</v>
+        <v>33.3</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
+          <t>recommendations.json:confidence</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>R1 advisory · within suggested stop</t>
+          <t>R1 approaching advisory stop</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
     </row>
@@ -1591,22 +1591,22 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>389.85</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>405.35</v>
+        <v>404</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3.98</v>
+        <v>3.63</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>378.3286</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>6.67</v>
+        <v>6.35</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -1659,22 +1659,22 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>397</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>424.5</v>
+        <v>422.1</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>6.93</v>
+        <v>6.32</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>386.4571</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>8.960000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1727,22 +1727,22 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1423.2</v>
+        <v>597.9</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1423.2</v>
+        <v>597.9</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
@@ -1766,20 +1766,20 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY BUY</t>
+          <t>NEW · STRONG BUY</t>
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>83</v>
+        <v>34.1</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
+          <t>recommendations.json:confidence</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.9%) • outperforming Nifty • sect</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -1791,7 +1791,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1801,22 +1801,22 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1899</v>
+        <v>186.04</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1899</v>
+        <v>186.04</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1840,20 +1840,20 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY BUY</t>
+          <t>NEW · STRONG BUY</t>
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>88</v>
+        <v>30.3</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
+          <t>recommendations.json:confidence</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.4%) • sector strength 64/100 • regim</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -1865,7 +1865,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>332.5</v>
+        <v>117.5</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>332.5</v>
+        <v>117.5</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -1914,20 +1914,20 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M26" s="4" t="n">
-        <v>72</v>
+        <v>30.3</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
+          <t>recommendations.json:confidence</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.9%) • sector strength 7/100 • regime </t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1949,22 +1949,22 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>405.35</v>
+        <v>1427.5</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>405.35</v>
+        <v>1427.5</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="M27" s="4" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-risk Industrials holding (low vol) • below 200-dma (-3.3%) • sector strength 71/100 • </t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.2%) • outperforming Nifty • sect</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -2013,7 +2013,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2028,17 +2028,17 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1385</v>
+        <v>1895</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1385</v>
+        <v>1895</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.6%) • sector strength 64/100 • regim</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.1%) • outperforming Nifty • sector s</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2102,17 +2102,17 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>266</v>
+        <v>332</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>266</v>
+        <v>332</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -2140,85 +2140,455 @@
         </is>
       </c>
       <c r="M29" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>r1_daily_picks:Rec Confidence %</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.1%) • sector strength 15/100 • regime</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1005.9</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1005.9</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY SIGNAL</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY BUY</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>r1_daily_picks:Rec Confidence %</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.2%) • sector strength 77/100 • r</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>418.85</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>418.85</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY SIGNAL</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY BUY</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.5%) • sector strength 7/100 • regime </t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.3%) • sector strength 46/100 • regime</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>R1 is RETIRED_ADVISORY · shown for operator awareness · it opens and closes nothing automatically.</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY SIGNAL</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY BUY</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>r1_daily_picks:Rec Confidence %</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low-risk Industrials holding (low vol) • below 200-dma (-3.6%) • sector strength 38/100 • </t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Suggested Stop · Entry − 2×ATR14 at entry · a SUGGESTION · it is NOT the canonical dynamic_risk_v2 stop and is not enforced.</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY SIGNAL</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY BUY</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>r1_daily_picks:Rec Confidence %</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.2%) • sector strength 62/100 • regim</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Review State · 🟢 NORMAL · 🟡 WATCH (within 3.0% of stop or ≤-8.0% P&amp;L) · 🔴 STOP BREACH (price at/below suggested stop) · 🔴 DEEP LOSS (≤-15.0% P&amp;L).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Action never exceeds REVIEW · R1 auto-exit is prohibited by V2 §18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>R1 P&amp;L is never mixed into R2 production performance.</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>185.61</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>185.61</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY SIGNAL</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>ADVISORY BUY</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>r1_daily_picks:Rec Confidence %</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.5%) • sector strength 46/100 • regime</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.491 · mean 0.349 · 0.0% of scored names sit at the maximum.</t>
+          <t>R1 is RETIRED_ADVISORY · shown for operator awareness · it opens and closes nothing automatically.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
+          <t>Suggested Stop · Entry − 2×ATR14 at entry · a SUGGESTION · it is NOT the canonical dynamic_risk_v2 stop and is not enforced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Review State · 🟢 NORMAL · 🟡 WATCH (within 3.0% of stop or ≤-8.0% P&amp;L) · 🔴 STOP BREACH (price at/below suggested stop) · 🔴 DEEP LOSS (≤-15.0% P&amp;L).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Action never exceeds REVIEW · R1 auto-exit is prohibited by V2 §18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>R1 P&amp;L is never mixed into R2 production performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.309 · 0.0% of scored names sit at the maximum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
           <t>Confidence Source · names exactly where the number came from · a value with no stated source is not trustworthy.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A32:P32"/>
-    <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A42:P42"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A23:P23"/>
     <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A34:P34"/>
-    <mergeCell ref="A35:P35"/>
+    <mergeCell ref="A40:P40"/>
+    <mergeCell ref="A39:P39"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A33:P33"/>
+    <mergeCell ref="A43:P43"/>
+    <mergeCell ref="A41:P41"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2260,7 +2630,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · R2 · PRODUCTION · as of 2026-09-07</t>
+          <t>AEGIS INDIA · R2 · PRODUCTION · as of 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2758,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -2398,7 +2768,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2407,19 +2777,19 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>452.35</v>
+        <v>284.85</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>419.05</v>
+        <v>263.5</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-7.36</v>
+        <v>-7.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>403.5857</v>
+        <v>255.5857</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -2427,20 +2797,20 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.69</v>
+        <v>3</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>477.49</v>
+        <v>297.98</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.94</v>
+        <v>13.08</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.78</v>
+        <v>4.36</v>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>🟢 NORMAL</t>
+          <t>🟡 WATCH</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -2460,12 +2830,12 @@
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>canonical dynamic stop intact</t>
+          <t>approaching canonical stop</t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+          <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr">
@@ -2477,7 +2847,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2487,7 +2857,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2496,19 +2866,19 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>284.85</v>
+        <v>452.35</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>264.1</v>
+        <v>419.05</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-7.28</v>
+        <v>-7.36</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>255.8286</v>
+        <v>403.5857</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -2516,16 +2886,16 @@
         </is>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.13</v>
+        <v>3.69</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>297.98</v>
+        <v>477.49</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.83</v>
+        <v>13.94</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -2554,7 +2924,7 @@
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ITC-20260804-e0ebbb</t>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
         </is>
       </c>
       <c r="U7" s="4" t="inlineStr">
@@ -2585,19 +2955,19 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>709</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>672.75</v>
+        <v>669.45</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-5.11</v>
+        <v>-5.58</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>644.0286</v>
+        <v>643.1072</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -2605,16 +2975,16 @@
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.27</v>
+        <v>3.93</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>749.16</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>11.36</v>
+        <v>11.91</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.66</v>
+        <v>3.03</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -2674,19 +3044,19 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>11475</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>11162</v>
+        <v>10956</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-2.73</v>
+        <v>-4.52</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10771.7143</v>
+        <v>10569.1429</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -2694,16 +3064,16 @@
         </is>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>11970.43</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.24</v>
+        <v>9.26</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -2763,7 +3133,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>2744.3</v>
@@ -2852,19 +3222,19 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>5499</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5643</v>
+        <v>5540</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2.62</v>
+        <v>0.75</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5372.5714</v>
+        <v>5265.5714</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -2872,16 +3242,16 @@
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.79</v>
+        <v>4.95</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>5954.25</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.52</v>
+        <v>7.48</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -2941,19 +3311,19 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>113.36</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>117</v>
+        <v>115.6</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>113.35</v>
+        <v>111.9314</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -2961,16 +3331,16 @@
         </is>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="L12" s="4" t="n">
         <v>118.87</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.6</v>
+        <v>2.83</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.51</v>
+        <v>0.89</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -3030,19 +3400,19 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>553.3</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>596.7</v>
+        <v>597.9</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>7.84</v>
+        <v>8.06</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>566.1643</v>
+        <v>570.8357</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -3050,13 +3420,13 @@
         </is>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.12</v>
+        <v>4.53</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>587.67</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.51</v>
+        <v>-1.71</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
@@ -3074,7 +3444,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>39.3</v>
+        <v>34.1</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -3149,7 +3519,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.491 · mean 0.349 · 0.0% of scored names sit at the maximum.</t>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.309 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3207,14 +3577,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · MOMENTUM · upstream research · as of 2026-09-07</t>
+          <t>AEGIS INDIA · MOMENTUM · upstream research · as of 2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Producer as-of: 2026-09-07 · reporting as-of: 2026-09-07 · 🟢 FRESH</t>
+          <t>Producer as-of: 2026-09-08 · reporting as-of: 2026-09-08 · 🟢 FRESH</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3686,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -3331,7 +3701,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -3361,7 +3731,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -3540,7 +3910,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CANDIDATES FOUND BUT OUTSIDE THE PRODUCTION UNIVERSE · 5 · real momentum · not R2-tradable · shown so a zero above is never mistaken for a quiet market</t>
+          <t>CANDIDATES FOUND BUT OUTSIDE THE PRODUCTION UNIVERSE · 4 · real momentum · not R2-tradable · shown so a zero above is never mistaken for a quiet market</t>
         </is>
       </c>
     </row>
@@ -3727,7 +4097,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3737,7 +4107,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>QUICK_FALL</t>
+          <t>SUSTAINED_DOWN</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -3746,22 +4116,22 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.76</v>
+        <v>-3.01</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-6.69</v>
+        <v>-9.01</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-8.15</v>
+        <v>-14.07</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-10.2</v>
+        <v>-16.89</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.1</v>
+        <v>15</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.7</v>
+        <v>2.51</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -3784,96 +4154,36 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>KEI</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>QUICK_FALL</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>-9.31</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>-12.06</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>-13.39</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>AVOID</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>NOT CLASSIFIED</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>unknown quality + falling · not a value play</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>'Declared universe' is NOT 'scanned' · only ACTUALLY EVALUATED counts tickers that were genuinely scored.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>'Declared universe' is NOT 'scanned' · only ACTUALLY EVALUATED counts tickers that were genuinely scored.</t>
+          <t>Thresholds are UNCHANGED production values and are never lowered to manufacture candidates: {"1d_rise_pct": 4.0, "3d_rise_pct": 8.0, "5d_rise_pct": 12.0, "1d_fall_pct": -4.0, "3d_fall_pct": -8.0, "5d_fall_pct": -12.0, "volume_confirm_multiplier": 1.5, "rsi_overbought": 70, "rsi_oversold": 30, "vol_adjust_cap": 2.0}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Thresholds are UNCHANGED production values and are never lowered to manufacture candidates: {"1d_rise_pct": 4.0, "3d_rise_pct": 8.0, "5d_rise_pct": 12.0, "1d_fall_pct": -4.0, "3d_fall_pct": -8.0, "5d_fall_pct": -12.0, "volume_confirm_multiplier": 1.5, "rsi_overbought": 70, "rsi_oversold": 30, "vol_adjust_cap": 2.0}</t>
+          <t>Momentum never opens a position · production_impact is null by design.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Momentum never opens a position · production_impact is null by design.</t>
+          <t>A candidate reaches R2 only through R2 eligibility · see the reconciliation block on DAILY RECOMMENDATION.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>A candidate reaches R2 only through R2 eligibility · see the reconciliation block on DAILY RECOMMENDATION.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>STALE means the producer's as-of date is older than this report's as-of date · the rows are not today's market.</t>
         </is>
@@ -3883,7 +4193,7 @@
   <mergeCells count="12">
     <mergeCell ref="A27:N27"/>
     <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A34:N34"/>
     <mergeCell ref="A35:N35"/>
     <mergeCell ref="A21:N21"/>
     <mergeCell ref="A2:N2"/>
@@ -3904,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3925,21 +4235,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · DAILY RECOMMENDATION · what to do today · 2026-09-07</t>
+          <t>AEGIS INDIA · DAILY RECOMMENDATION · what to do today · 2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>27 row(s) · 6 position(s) need attention (stop breach or deep loss) · R2 production 8 · R1 advisory 16 · momentum candidates 0</t>
+          <t>28 row(s) · 8 position(s) need attention (stop breach or deep loss) · R2 production 8 · R1 advisory 16 · momentum candidates 0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Daily recommendations · as-of 2026-09-07 · 15 scored · 0 investable (NEW_POSITION) · 🟢 FRESH</t>
+          <t>Daily recommendations · as-of 2026-09-08 · 15 scored · 3 investable (NEW_POSITION) · 🟢 FRESH</t>
         </is>
       </c>
     </row>
@@ -4025,33 +4335,33 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>🟢 NORMAL</t>
+          <t>🟡 WATCH</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>419.05</v>
+        <v>263.5</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-7.36</v>
+        <v>-7.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>403.5857</v>
+        <v>255.5857</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.69</v>
+        <v>3</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>477.49</v>
+        <v>297.98</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -4060,7 +4370,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 34 d</t>
+          <t>R2 ACTIVE · held 35 d</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -4070,7 +4380,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>canonical dynamic stop intact</t>
+          <t>approaching canonical stop</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4392,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4096,19 +4406,19 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>264.1</v>
+        <v>419.05</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-7.28</v>
+        <v>-7.36</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>255.8286</v>
+        <v>403.5857</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.13</v>
+        <v>3.69</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>297.98</v>
+        <v>477.49</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -4117,7 +4427,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 34 d</t>
+          <t>R2 ACTIVE · held 35 d</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -4153,16 +4463,16 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>672.75</v>
+        <v>669.45</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-5.11</v>
+        <v>-5.58</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>644.0286</v>
+        <v>643.1072</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.27</v>
+        <v>3.93</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>749.16</v>
@@ -4174,7 +4484,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 34 d</t>
+          <t>R2 ACTIVE · held 35 d</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -4210,16 +4520,16 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>11162</v>
+        <v>10956</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-2.73</v>
+        <v>-4.52</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>10771.7143</v>
+        <v>10569.1429</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>11970.43</v>
@@ -4231,7 +4541,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 33 d</t>
+          <t>R2 ACTIVE · held 34 d</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -4288,7 +4598,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 33 d</t>
+          <t>R2 ACTIVE · held 34 d</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -4324,16 +4634,16 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5643</v>
+        <v>5540</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2.62</v>
+        <v>0.75</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5372.5714</v>
+        <v>5265.5714</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.79</v>
+        <v>4.95</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>5954.25</v>
@@ -4345,7 +4655,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 33 d</t>
+          <t>R2 ACTIVE · held 34 d</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -4381,16 +4691,16 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>117</v>
+        <v>115.6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>113.35</v>
+        <v>111.9314</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>118.87</v>
@@ -4402,7 +4712,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 34 d</t>
+          <t>R2 ACTIVE · held 35 d</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -4438,16 +4748,16 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>596.7</v>
+        <v>597.9</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>7.84</v>
+        <v>8.06</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>566.1643</v>
+        <v>570.8357</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.12</v>
+        <v>4.53</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>587.67</v>
@@ -4459,11 +4769,11 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 32 d</t>
+          <t>R2 ACTIVE · held 33 d</t>
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>39.3</v>
+        <v>34.1</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
@@ -4493,16 +4803,16 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-12.45</v>
+        <v>-12.66</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>2314.8285</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -4516,11 +4826,11 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 33 d</t>
+          <t>R1 ADVISORY · held 34 d</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>49.1</v>
+        <v>40.6</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
@@ -4550,16 +4860,16 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5101.5</v>
+        <v>5042.5</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-6.47</v>
+        <v>-7.55</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>5283.7143</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.57</v>
+        <v>-4.78</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -4573,7 +4883,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 34 d</t>
+          <t>R1 ADVISORY · held 35 d</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4632,11 +4942,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 34 d</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>66</v>
+          <t>R1 ADVISORY · held 35 d</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
@@ -4652,12 +4964,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -4666,16 +4978,16 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1120</v>
+        <v>1973.4</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-5.96</v>
+        <v>-4.43</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1149.2286</v>
+        <v>1990.457</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.61</v>
+        <v>-0.86</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -4711,12 +5023,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -4725,16 +5037,16 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1973.4</v>
+        <v>365.7</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-4.43</v>
+        <v>-4.17</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1990.457</v>
+        <v>369.75</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.86</v>
+        <v>-1.11</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -4748,13 +5060,11 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 26 d</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 35 d</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>63</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -4770,12 +5080,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -4784,16 +5094,16 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>368</v>
+        <v>1575</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-3.56</v>
+        <v>-4.11</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>369.75</v>
+        <v>1594.6857</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.48</v>
+        <v>-1.25</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -4807,7 +5117,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 34 d</t>
+          <t>R1 ADVISORY · held 35 d</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -4839,20 +5149,20 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>🟡 WATCH</t>
+          <t>🔴 STOP BREACH</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1016.1</v>
+        <v>1005.9</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-3.11</v>
+        <v>-4.08</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>1011.5999</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.44</v>
+        <v>-0.57</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -4861,22 +5171,20 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 17 d</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 18 d</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>71</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>R1 approaching advisory stop</t>
+          <t>R1 advisory stop breached · no auto-exit</t>
         </is>
       </c>
     </row>
@@ -4888,30 +5196,30 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>🟡 WATCH</t>
+          <t>🔴 STOP BREACH</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1385</v>
+        <v>375.5</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-2.02</v>
+        <v>-2.51</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1382.3857</v>
+        <v>377.5071</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.19</v>
+        <v>-0.53</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -4920,20 +5228,20 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 10 d</t>
+          <t>R1 ADVISORY · held 11 d</t>
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>R1 approaching advisory stop</t>
+          <t>R1 advisory stop breached · no auto-exit</t>
         </is>
       </c>
     </row>
@@ -4945,12 +5253,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -4959,16 +5267,16 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>234.65</v>
+        <v>1156.9</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-2</v>
+        <v>-2.86</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>232.2186</v>
+        <v>1149.2286</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -4982,11 +5290,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 27 d</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>67</v>
+          <t>R1 ADVISORY · held 28 d</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -5002,12 +5312,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -5016,16 +5326,16 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1423.2</v>
+        <v>233.7</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-1.81</v>
+        <v>-2.4</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1412.0571</v>
+        <v>232.2186</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -5039,11 +5349,11 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 34 d</t>
+          <t>R1 ADVISORY · held 28 d</t>
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -5059,12 +5369,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -5073,16 +5383,16 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>380.9</v>
+        <v>1385</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-1.1</v>
+        <v>-2.02</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>377.5071</v>
+        <v>1382.3857</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.89</v>
+        <v>0.19</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -5096,11 +5406,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 10 d</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>62</v>
+          <t>R1 ADVISORY · held 11 d</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
@@ -5116,12 +5428,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -5130,16 +5442,16 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1629.5</v>
+        <v>1427.5</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-0.79</v>
+        <v>-1.52</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1594.6857</v>
+        <v>1412.0571</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.14</v>
+        <v>1.08</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -5153,13 +5465,11 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 34 d</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 35 d</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>83</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
@@ -5175,12 +5485,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -5189,16 +5499,16 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>415.35</v>
+        <v>185.61</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.54</v>
+        <v>-0.99</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>407.3714</v>
+        <v>181.8114</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -5212,11 +5522,11 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 33 d</t>
+          <t>R1 ADVISORY · held 11 d</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>40.6</v>
+        <v>65</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
@@ -5232,30 +5542,30 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>🟢 NORMAL</t>
+          <t>🟡 WATCH</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>188.79</v>
+        <v>418.85</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>181.8114</v>
+        <v>407.3714</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.7</v>
+        <v>2.74</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -5264,20 +5574,20 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 10 d</t>
+          <t>R1 ADVISORY · held 34 d</t>
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>64</v>
+        <v>33.3</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>R1 advisory · within suggested stop</t>
+          <t>R1 approaching advisory stop</t>
         </is>
       </c>
     </row>
@@ -5303,16 +5613,16 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>405.35</v>
+        <v>404</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3.98</v>
+        <v>3.63</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>378.3286</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.67</v>
+        <v>6.35</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -5326,11 +5636,11 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 34 d</t>
+          <t>R1 ADVISORY · held 35 d</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
@@ -5360,16 +5670,16 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>424.5</v>
+        <v>422.1</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>6.93</v>
+        <v>6.32</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>386.4571</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.960000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -5383,7 +5693,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 34 d</t>
+          <t>R1 ADVISORY · held 35 d</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -5405,12 +5715,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -5419,7 +5729,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1899</v>
+        <v>186.04</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
@@ -5443,7 +5753,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>NEW · REVIEW</t>
+          <t>NEW · STRONG BUY</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -5452,11 +5762,11 @@
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>88</v>
+        <v>30.3</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.4%) • sector strength 64/100 • regim</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
     </row>
@@ -5468,12 +5778,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -5482,7 +5792,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>332.5</v>
+        <v>117.5</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -5506,7 +5816,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>NEW · REVIEW</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -5515,11 +5825,11 @@
         </is>
       </c>
       <c r="L31" s="4" t="n">
-        <v>72</v>
+        <v>30.3</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.9%) • sector strength 7/100 • regime </t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
     </row>
@@ -5531,145 +5841,193 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NEW · INVESTABLE</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>1895</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>NEW · REVIEW</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>NEW CANDIDATE · not a position · no auto-entry</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.1%) • outperforming Nifty • sector s</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>🟢 NEW · INVESTABLE</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="n">
+        <v>332</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>NEW · REVIEW</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>NEW CANDIDATE · not a position · no auto-entry</t>
         </is>
       </c>
-      <c r="L32" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low-risk Power holding (low vol) • below 200-dma (-6.5%) • sector strength 7/100 • regime </t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="L33" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.1%) • sector strength 15/100 • regime</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>MOMENTUM → R2 LIFECYCLE RECONCILIATION</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Where the rest went</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>1 · Declared universe</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>230</v>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2 · Actually evaluated</t>
+          <t>1 · Declared universe</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
         <v>230</v>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>unreadable=0 · insufficient history=0</t>
-        </is>
-      </c>
+      <c r="C38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3 · Momentum candidates</t>
+          <t>2 · Actually evaluated</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>225 evaluated tickers showed no momentum signal</t>
+          <t>unreadable=0 · insufficient history=0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>4 · In production universe</t>
+          <t>3 · Momentum candidates</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>5 candidate(s) dropped as outside the 50-name production universe</t>
+          <t>226 evaluated tickers showed no momentum signal</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>5 · ACCEPTED by ledger</t>
+          <t>4 · In production universe</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
@@ -5677,14 +6035,14 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>WATCH=0 · REJECTED=0 · NO_EVIDENCE=0</t>
+          <t>4 candidate(s) dropped as outside the 50-name production universe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>6 · Registry R2 NEW today</t>
+          <t>5 · ACCEPTED by ledger</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
@@ -5692,96 +6050,111 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>accepted momentum tickers not opened: none</t>
+          <t>WATCH=0 · REJECTED=0 · NO_EVIDENCE=0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
+          <t>6 · Registry R2 NEW today</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>accepted momentum tickers not opened: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>7 · R2 sheet ACTIVE</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B44" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C43" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>✅ No unexplained losses between momentum and R2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
+          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
+          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
+          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
+          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
+          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
+          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.491 · mean 0.349 · 0.0% of scored names sit at the maximum.</t>
+          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.309 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A46:M46"/>
+    <mergeCell ref="A36:M36"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A45:M45"/>
     <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="A50:M50"/>
     <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A54:M54"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A50:M50"/>
+    <mergeCell ref="A56:M56"/>
     <mergeCell ref="A53:M53"/>
-    <mergeCell ref="A54:M54"/>
     <mergeCell ref="A55:M55"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A49:M49"/>
@@ -5797,7 +6170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5819,14 +6192,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT · unified realized history · 90d · as of 2026-09-07</t>
+          <t>AEGIS INDIA · EXIT · unified realized history · 90d · as of 2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total 45 · R2 production 21 · R1 advisory 5 · administrative 19 · Momentum 0 (momentum never opens a position, so it can never produce an exit)</t>
+          <t>Total 46 · R2 production 21 · R1 advisory 5 · administrative 20 · Momentum 0 (momentum never opens a position, so it can never produce an exit)</t>
         </is>
       </c>
     </row>
@@ -5917,32 +6290,32 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>414.35</v>
+        <v>288.1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>414.35</v>
+        <v>288.1</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
@@ -5956,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>18.2</v>
+        <v>19.4</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
@@ -5965,7 +6338,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260907-a63a75</t>
+          <t>IND-R2-PETRONET-20260908-f20701</t>
         </is>
       </c>
     </row>
@@ -5977,7 +6350,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -5987,25 +6360,25 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>391.3</v>
+        <v>414.35</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>415.35</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>6.15</v>
+        <v>414.35</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -6016,95 +6389,93 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>17.1</v>
+        <v>18.2</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-RBLBANK-20260907-a63a75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>R1 · ADVISORY</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>177.09</v>
+        <v>391.3</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>177.09</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
+        <v>415.35</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>6.15</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.93</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>17.1</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>advisory</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-WIPRO-20260902-25d63c</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1 · ADVISORY</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -6121,33 +6492,35 @@
         <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2891.8</v>
+        <v>177.09</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2891.8</v>
+        <v>177.09</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
         </is>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>57</v>
+        <v>-2.42</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>advisory</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIENT-20260902-51452a</t>
+          <t>IND-R1-WIPRO-20260902-25d63c</t>
         </is>
       </c>
     </row>
@@ -6159,35 +6532,35 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2383.9</v>
+        <v>2891.8</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2160.2</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>-9.380000000000001</v>
+        <v>2891.8</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -6195,36 +6568,36 @@
         </is>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.32</v>
+        <v>2.01</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R2-ADANIENT-20260902-51452a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>R1 · ADVISORY</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -6241,95 +6614,95 @@
         <v>27</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>347.25</v>
+        <v>2383.9</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>326.5</v>
+        <v>2160.2</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-5.98</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-2.56</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>advisory</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-NTPC-20260804-b96a36</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1 · ADVISORY</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>398.8</v>
+        <v>347.25</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>398.8</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
+        <v>326.5</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>-5.98</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>52.9</v>
+        <v>1.68</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>advisory</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
+          <t>IND-R1-NTPC-20260804-b96a36</t>
         </is>
       </c>
     </row>
@@ -6341,35 +6714,35 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>415.15</v>
+        <v>398.8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>402.55</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>-3.04</v>
+        <v>398.8</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -6377,41 +6750,41 @@
         </is>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.18</v>
+        <v>1.53</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>14.3</v>
+        <v>52.9</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>R1 · ADVISORY</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -6420,38 +6793,36 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>289</v>
+        <v>415.15</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>268.15</v>
+        <v>402.55</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-7.21</v>
+        <v>-3.04</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.05</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>14.3</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>advisory</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ITC-20260805-3cdd2a</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
     </row>
@@ -6463,17 +6834,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -6482,16 +6853,16 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1955.3</v>
+        <v>289</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1912</v>
+        <v>268.15</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-2.21</v>
+        <v>-7.21</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -6499,7 +6870,7 @@
         </is>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.68</v>
+        <v>-1.73</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -6513,7 +6884,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
+          <t>IND-R1-ITC-20260805-3cdd2a</t>
         </is>
       </c>
     </row>
@@ -6525,35 +6896,35 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>283.4</v>
+        <v>1955.3</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>264.9</v>
+        <v>1912</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-6.53</v>
+        <v>-2.21</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -6561,7 +6932,7 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.42</v>
+        <v>-0.89</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -6575,67 +6946,69 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-POWERGRID-20260805-b39825</t>
+          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1 · ADVISORY</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>847.5</v>
+        <v>283.4</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>847.5</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0</v>
+        <v>264.9</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>-6.53</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.82</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>56.7</v>
+        <v>0.42</v>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>advisory</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARICO-20260826-1c5a1c</t>
+          <t>IND-R1-POWERGRID-20260805-b39825</t>
         </is>
       </c>
     </row>
@@ -6647,32 +7020,32 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1702.7</v>
+        <v>847.5</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1702.7</v>
+        <v>847.5</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -6683,10 +7056,10 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.14</v>
+        <v>-3.82</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>57.6</v>
+        <v>56.7</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -6695,7 +7068,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
+          <t>IND-R2-MARICO-20260826-1c5a1c</t>
         </is>
       </c>
     </row>
@@ -6707,32 +7080,32 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>244.55</v>
+        <v>1702.7</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>244.55</v>
+        <v>1702.7</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>0</v>
@@ -6743,10 +7116,10 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.07</v>
+        <v>3.14</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>10.1</v>
+        <v>57.6</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -6755,7 +7128,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260824-89850d</t>
+          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
         </is>
       </c>
     </row>
@@ -6767,7 +7140,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -6777,22 +7150,22 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>402.8</v>
+        <v>244.55</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>402.8</v>
+        <v>244.55</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -6803,10 +7176,10 @@
         </is>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5.39</v>
+        <v>-2.07</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>13.3</v>
+        <v>10.1</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -6815,7 +7188,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
+          <t>IND-R2-JIOFIN-20260824-89850d</t>
         </is>
       </c>
     </row>
@@ -6827,12 +7200,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -6849,10 +7222,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1114.2</v>
+        <v>402.8</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1114.2</v>
+        <v>402.8</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>0</v>
@@ -6863,10 +7236,10 @@
         </is>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.58</v>
+        <v>4.79</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -6875,7 +7248,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260821-142d93</t>
+          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
         </is>
       </c>
     </row>
@@ -6887,12 +7260,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -6909,10 +7282,10 @@
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>8693</v>
+        <v>1114.2</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>8693</v>
+        <v>1114.2</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>0</v>
@@ -6923,10 +7296,10 @@
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.49</v>
+        <v>-1.58</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>61.4</v>
+        <v>14.5</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -6935,7 +7308,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
+          <t>IND-R2-MGL-20260821-142d93</t>
         </is>
       </c>
     </row>
@@ -6947,46 +7320,46 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>174.9</v>
+        <v>8693</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>174.9</v>
+        <v>8693</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>12.52</v>
+        <v>-0.49</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>11.8</v>
+        <v>61.4</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -6995,7 +7368,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260820-80f37d</t>
+          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7380,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -7017,25 +7390,25 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>552.4</v>
+        <v>174.9</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>558</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1.01</v>
+        <v>174.9</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -7043,19 +7416,19 @@
         </is>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7.71</v>
+        <v>7.43</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>14.7</v>
+        <v>11.8</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-SAIL-20260820-80f37d</t>
         </is>
       </c>
     </row>
@@ -7067,17 +7440,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -7086,16 +7459,16 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>129.2</v>
+        <v>552.4</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>-3.72</v>
+        <v>558</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1.01</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -7103,10 +7476,10 @@
         </is>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.41</v>
+        <v>5.58</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>12.2</v>
+        <v>14.7</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
@@ -7115,7 +7488,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
     </row>
@@ -7127,35 +7500,35 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="F26" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5220</v>
+        <v>129.2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5220</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0</v>
+        <v>124.4</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-3.72</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -7163,19 +7536,19 @@
         </is>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4.66</v>
+        <v>-5.55</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>60</v>
+        <v>12.2</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
     </row>
@@ -7187,35 +7560,35 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1384</v>
+        <v>5220</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1327.6</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>-4.08</v>
+        <v>5220</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -7223,19 +7596,19 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.98</v>
+        <v>-4.66</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>56.7</v>
+        <v>60</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
         </is>
       </c>
     </row>
@@ -7247,12 +7620,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -7269,13 +7642,13 @@
         <v>12</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>377</v>
+        <v>1384</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>2.8</v>
+        <v>1327.6</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>-4.08</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -7283,10 +7656,10 @@
         </is>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.47</v>
+        <v>-2.98</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
@@ -7295,7 +7668,7 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
     </row>
@@ -7307,12 +7680,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -7322,20 +7695,20 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>11600</v>
+        <v>377</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>11828</v>
+        <v>387.55</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -7343,10 +7716,10 @@
         </is>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.94</v>
+        <v>-5.59</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
@@ -7355,7 +7728,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7740,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -7377,7 +7750,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -7386,16 +7759,16 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2439.4</v>
+        <v>11600</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2361</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>-3.21</v>
+        <v>11828</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1.97</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -7403,10 +7776,10 @@
         </is>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.41</v>
+        <v>0.16</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
@@ -7415,7 +7788,7 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
     </row>
@@ -7427,35 +7800,35 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3940</v>
+        <v>2439.4</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3940</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>0</v>
+        <v>2361</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>-3.21</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -7463,19 +7836,19 @@
         </is>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>-3.85</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
     </row>
@@ -7487,32 +7860,32 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1779.2</v>
+        <v>3940</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1779.2</v>
+        <v>3940</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>0</v>
@@ -7523,10 +7896,10 @@
         </is>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.75</v>
+        <v>-0.33</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
@@ -7535,7 +7908,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
+          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
         </is>
       </c>
     </row>
@@ -7547,35 +7920,35 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7454.5</v>
+        <v>1779.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>7095</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>-4.82</v>
+        <v>1779.2</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -7583,19 +7956,19 @@
         </is>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.34</v>
+        <v>-3.75</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>62.1</v>
+        <v>8.1</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
         </is>
       </c>
     </row>
@@ -7607,35 +7980,35 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F34" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>129</v>
+        <v>7454.5</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>0</v>
+        <v>7095</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-4.82</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -7643,19 +8016,19 @@
         </is>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-2.71</v>
+        <v>5.34</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.5</v>
+        <v>62.1</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260810-788da8</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
     </row>
@@ -7667,12 +8040,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -7689,10 +8062,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4924</v>
+        <v>129</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4924</v>
+        <v>129</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
@@ -7703,10 +8076,10 @@
         </is>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1.36</v>
+        <v>-3.88</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>60.1</v>
+        <v>6.5</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
@@ -7715,7 +8088,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
+          <t>IND-R2-CANBK-20260810-788da8</t>
         </is>
       </c>
     </row>
@@ -7727,12 +8100,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -7749,10 +8122,10 @@
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>181.14</v>
+        <v>4924</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>181.14</v>
+        <v>4924</v>
       </c>
       <c r="I36" s="4" t="n">
         <v>0</v>
@@ -7763,10 +8136,10 @@
         </is>
       </c>
       <c r="K36" s="4" t="n">
-        <v>3.36</v>
+        <v>-0.2</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>9.4</v>
+        <v>60.1</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
@@ -7775,7 +8148,7 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
+          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
         </is>
       </c>
     </row>
@@ -7787,35 +8160,35 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>6793.5</v>
+        <v>181.14</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>6774</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>-0.29</v>
+        <v>181.14</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -7823,19 +8196,19 @@
         </is>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-5.73</v>
+        <v>2.71</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
         </is>
       </c>
     </row>
@@ -7847,17 +8220,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -7866,16 +8239,16 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>471.2</v>
+        <v>6793.5</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>0.45</v>
+        <v>6774</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>-0.29</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -7883,10 +8256,10 @@
         </is>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-3.25</v>
+        <v>-5.73</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>60.7</v>
+        <v>8</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
@@ -7895,7 +8268,7 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
     </row>
@@ -7907,17 +8280,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -7926,16 +8299,16 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>845</v>
+        <v>471.2</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>889.5</v>
+        <v>473.3</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>5.27</v>
+        <v>0.45</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -7943,10 +8316,10 @@
         </is>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-1.1</v>
+        <v>-3.25</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>7.4</v>
+        <v>60.7</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
@@ -7955,7 +8328,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
     </row>
@@ -7967,12 +8340,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -7989,13 +8362,13 @@
         <v>2</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>450</v>
+        <v>845</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>442.8</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>-1.6</v>
+        <v>889.5</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>5.27</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -8003,10 +8376,10 @@
         </is>
       </c>
       <c r="K40" s="4" t="n">
-        <v>10.28</v>
+        <v>-1.1</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>10.3</v>
+        <v>7.4</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
@@ -8015,7 +8388,7 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8400,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -8049,13 +8422,13 @@
         <v>2</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1595</v>
+        <v>450</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1584.8</v>
+        <v>442.8</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>-0.64</v>
+        <v>-1.6</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -8063,10 +8436,10 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0.14</v>
+        <v>9.98</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>62.5</v>
+        <v>10.3</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
@@ -8075,7 +8448,7 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
     </row>
@@ -8087,12 +8460,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -8109,13 +8482,13 @@
         <v>2</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1327.7</v>
+        <v>1595</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1285</v>
+        <v>1584.8</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-3.22</v>
+        <v>-0.64</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -8123,10 +8496,10 @@
         </is>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-8.949999999999999</v>
+        <v>-2.2</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>64.8</v>
+        <v>62.5</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
@@ -8135,7 +8508,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8520,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -8162,20 +8535,20 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>2195</v>
+        <v>1327.7</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2182</v>
+        <v>1285</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>-0.59</v>
+        <v>-3.22</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -8183,10 +8556,10 @@
         </is>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-10.36</v>
+        <v>-9.17</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>59.7</v>
+        <v>64.8</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
@@ -8195,7 +8568,7 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
     </row>
@@ -8207,17 +8580,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -8226,16 +8599,16 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1363.6</v>
+        <v>2195</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1351.3</v>
+        <v>2182</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.9</v>
+        <v>-0.59</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -8243,10 +8616,10 @@
         </is>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-4.28</v>
+        <v>-10.4</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>7.8</v>
+        <v>59.7</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
@@ -8255,7 +8628,7 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8640,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -8289,13 +8662,13 @@
         <v>2</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>5470.5</v>
+        <v>1363.6</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>5651.5</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>3.31</v>
+        <v>1351.3</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>-0.9</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -8303,10 +8676,10 @@
         </is>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-6.22</v>
+        <v>-5.07</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
@@ -8315,7 +8688,7 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
     </row>
@@ -8327,17 +8700,17 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -8346,16 +8719,16 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1167.5</v>
+        <v>5470.5</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1177</v>
+        <v>5651.5</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.31</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -8363,10 +8736,10 @@
         </is>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-3.99</v>
+        <v>-6.75</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>11.7</v>
+        <v>10.6</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
@@ -8375,7 +8748,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
     </row>
@@ -8387,17 +8760,17 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -8406,16 +8779,16 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>268.5</v>
+        <v>1167.5</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>278.8</v>
+        <v>1177</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>3.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -8423,10 +8796,10 @@
         </is>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-2.4</v>
+        <v>-7.6</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
@@ -8435,7 +8808,7 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260804-563905</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
     </row>
@@ -8447,12 +8820,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -8462,40 +8835,40 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>425.05</v>
+        <v>268.5</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>425.05</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>0</v>
+        <v>278.8</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>3.84</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Outperformance exit</t>
         </is>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-6.51</v>
+        <v>-3.87</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>51.8</v>
+        <v>11.6</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BIOCON-20260804-954a24</t>
+          <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8880,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -8529,10 +8902,10 @@
         <v>0</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>939.95</v>
+        <v>425.05</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>939.95</v>
+        <v>425.05</v>
       </c>
       <c r="I49" s="4" t="n">
         <v>0</v>
@@ -8543,7 +8916,7 @@
         </is>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-3.72</v>
+        <v>-7.92</v>
       </c>
       <c r="L49" s="4" t="n">
         <v>51.8</v>
@@ -8555,7 +8928,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+          <t>IND-R2-BIOCON-20260804-954a24</t>
         </is>
       </c>
     </row>
@@ -8567,12 +8940,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -8589,10 +8962,10 @@
         <v>0</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>567.3</v>
+        <v>939.95</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>567.3</v>
+        <v>939.95</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
@@ -8603,192 +8976,252 @@
         </is>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-4.84</v>
+        <v>-3.72</v>
       </c>
       <c r="L50" s="4" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>administrative</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>567.3</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>567.3</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>-6.58</v>
+      </c>
+      <c r="L51" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>administrative</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>IND-R2-JSWENERGY-20260804-1210a0</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>MONTHLY SUMMARY · realized R2 production exits only · R1 advisory and administrative events excluded</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Exits</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Win Rate %</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Avg Realized P&amp;L %</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Best %</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Worst %</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>6.15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B57" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C57" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D57" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E57" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F57" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>5.27</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>-9.380000000000001</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>One unified exit history across R1 · R2 · Momentum · 90-day rolling.</t>
-        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>MONTHLY SUMMARY covers realized R2 production exits only · this is a 'realized 90d' scope, NOT a count of current holdings.</t>
+          <t>One unified exit history across R1 · R2 · Momentum · 90-day rolling.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Realized P&amp;L % · (Exit − Entry) / Entry · the trade's own result.</t>
+          <t>MONTHLY SUMMARY covers realized R2 production exits only · this is a 'realized 90d' scope, NOT a count of current holdings.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Return Since Exit % · price move from the exit price to today · positive means the stock kept rising after we sold (exit cost us) · negative means the exit protected capital.</t>
+          <t>Realized P&amp;L % · (Exit − Entry) / Entry · the trade's own result.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Relative Opportunity pp · rotation benefit vs the closed position · percentage points · this is NOT the trade's own P&amp;L.</t>
+          <t>Return Since Exit % · price move from the exit price to today · positive means the stock kept rising after we sold (exit cost us) · negative means the exit protected capital.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Classification · production (R2 real trade) · advisory (R1 · never counted in production P&amp;L) · administrative (same-day / zero-delta bookkeeping event · not a real trade).</t>
+          <t>Relative Opportunity pp · rotation benefit vs the closed position · percentage points · this is NOT the trade's own P&amp;L.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never silently zeroed.</t>
+          <t>Classification · production (R2 real trade) · advisory (R1 · never counted in production P&amp;L) · administrative (same-day / zero-delta bookkeeping event · not a real trade).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
+          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never silently zeroed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
           <t>Momentum contributes no exits by design · it is research-only and opens no positions.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A67:N67"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A61:N61"/>
-    <mergeCell ref="A53:N53"/>
     <mergeCell ref="A62:N62"/>
+    <mergeCell ref="A54:N54"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A59:N59"/>
     <mergeCell ref="A65:N65"/>
     <mergeCell ref="A60:N60"/>
     <mergeCell ref="A63:N63"/>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -4214,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4256,131 +4256,81 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>🔴 DATA FRESHNESS · 93 of 95 artifacts fresh · STALE 1 · MISSING 1 · 1 pipeline steps declare no artifact (unverifiable) · worst: usa/reports/macro_history.parquet (Nonetd) · usa/reports/news_sentiment_summary.json (10td)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>✅ No data blockers · every canonical source present and fresh.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Distance to Stop %</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>Lifecycle</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Why</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>🟡 WATCH</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>263.5</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>255.5857</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>297.98</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>R2 ACTIVE · held 35 d</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>approaching canonical stop</t>
         </is>
       </c>
     </row>
@@ -4392,33 +4342,33 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>🟢 NORMAL</t>
+          <t>🟡 WATCH</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>419.05</v>
+        <v>263.5</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-7.36</v>
+        <v>-7.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>403.5857</v>
+        <v>255.5857</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.69</v>
+        <v>3</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>477.49</v>
+        <v>297.98</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -4437,7 +4387,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>canonical dynamic stop intact</t>
+          <t>approaching canonical stop</t>
         </is>
       </c>
     </row>
@@ -4449,12 +4399,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -4463,19 +4413,19 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>669.45</v>
+        <v>419.05</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-5.58</v>
+        <v>-7.36</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>643.1072</v>
+        <v>403.5857</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.93</v>
+        <v>3.69</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>749.16</v>
+        <v>477.49</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -4506,12 +4456,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -4520,19 +4470,19 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10956</v>
+        <v>669.45</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-4.52</v>
+        <v>-5.58</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>10569.1429</v>
+        <v>643.1072</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.53</v>
+        <v>3.93</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11970.43</v>
+        <v>749.16</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -4541,7 +4491,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 34 d</t>
+          <t>R2 ACTIVE · held 35 d</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -4563,12 +4513,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -4577,19 +4527,19 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2698</v>
+        <v>10956</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-1.69</v>
+        <v>-4.52</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2556.9857</v>
+        <v>10569.1429</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.23</v>
+        <v>3.53</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2949.97</v>
+        <v>11970.43</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -4620,12 +4570,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -4634,19 +4584,19 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5540</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0.75</v>
+        <v>2698</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.69</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5265.5714</v>
+        <v>2556.9857</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.95</v>
+        <v>5.23</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5954.25</v>
+        <v>2949.97</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -4677,12 +4627,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -4691,19 +4641,19 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>115.6</v>
+        <v>5540</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1.98</v>
+        <v>0.75</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>111.9314</v>
+        <v>5265.5714</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.17</v>
+        <v>4.95</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>118.87</v>
+        <v>5954.25</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -4712,7 +4662,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 35 d</t>
+          <t>R2 ACTIVE · held 34 d</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -4734,12 +4684,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -4748,19 +4698,19 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>597.9</v>
+        <v>115.6</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>8.06</v>
+        <v>1.98</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>570.8357</v>
+        <v>111.9314</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.53</v>
+        <v>3.17</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>587.67</v>
+        <v>118.87</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -4769,11 +4719,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 33 d</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>34.1</v>
+          <t>R2 ACTIVE · held 35 d</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
@@ -4784,57 +4736,55 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>🔴 STOP BREACH</t>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2105</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>-12.66</v>
+        <v>597.9</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>8.06</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2314.8285</v>
+        <v>570.8357</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.53</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>587.67</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 34 d</t>
+          <t>R2 ACTIVE · held 33 d</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>40.6</v>
+        <v>34.1</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>R1 advisory stop breached · no auto-exit</t>
+          <t>canonical dynamic stop intact</t>
         </is>
       </c>
     </row>
@@ -4846,12 +4796,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -4860,16 +4810,16 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5042.5</v>
+        <v>2105</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-7.55</v>
+        <v>-12.66</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5283.7143</v>
+        <v>2314.8285</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.78</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -4883,13 +4833,11 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 35 d</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 34 d</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
@@ -4905,12 +4853,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -4919,16 +4867,16 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>476.05</v>
+        <v>5042.5</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-6.27</v>
+        <v>-7.55</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>493.3286</v>
+        <v>5283.7143</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.63</v>
+        <v>-4.78</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -4964,12 +4912,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -4978,16 +4926,16 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1973.4</v>
+        <v>476.05</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-4.43</v>
+        <v>-6.27</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1990.457</v>
+        <v>493.3286</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.86</v>
+        <v>-3.63</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -5001,7 +4949,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 27 d</t>
+          <t>R1 ADVISORY · held 35 d</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -5023,12 +4971,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -5037,16 +4985,16 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>365.7</v>
+        <v>1973.4</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-4.17</v>
+        <v>-4.43</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>369.75</v>
+        <v>1990.457</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.11</v>
+        <v>-0.86</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -5060,11 +5008,13 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 35 d</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>63</v>
+          <t>R1 ADVISORY · held 27 d</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -5080,12 +5030,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -5094,16 +5044,16 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1575</v>
+        <v>365.7</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-4.11</v>
+        <v>-4.17</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1594.6857</v>
+        <v>369.75</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.25</v>
+        <v>-1.11</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -5120,10 +5070,8 @@
           <t>R1 ADVISORY · held 35 d</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+      <c r="L19" s="4" t="n">
+        <v>63</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -5139,12 +5087,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -5153,16 +5101,16 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1005.9</v>
+        <v>1575</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-4.08</v>
+        <v>-4.11</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1011.5999</v>
+        <v>1594.6857</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.57</v>
+        <v>-1.25</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -5176,11 +5124,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 18 d</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>71</v>
+          <t>R1 ADVISORY · held 35 d</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -5196,12 +5146,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -5210,16 +5160,16 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>375.5</v>
+        <v>1005.9</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-2.51</v>
+        <v>-4.08</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>377.5071</v>
+        <v>1011.5999</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.53</v>
+        <v>-0.57</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -5233,11 +5183,11 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 11 d</t>
+          <t>R1 ADVISORY · held 18 d</t>
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -5253,30 +5203,30 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>🟡 WATCH</t>
+          <t>🔴 STOP BREACH</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1156.9</v>
+        <v>375.5</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-2.86</v>
+        <v>-2.51</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1149.2286</v>
+        <v>377.5071</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.66</v>
+        <v>-0.53</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -5285,22 +5235,20 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 28 d</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 11 d</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>62</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>R1 approaching advisory stop</t>
+          <t>R1 advisory stop breached · no auto-exit</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5260,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -5326,16 +5274,16 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>233.7</v>
+        <v>1156.9</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-2.4</v>
+        <v>-2.86</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>232.2186</v>
+        <v>1149.2286</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -5352,8 +5300,10 @@
           <t>R1 ADVISORY · held 28 d</t>
         </is>
       </c>
-      <c r="L23" s="4" t="n">
-        <v>68</v>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -5369,12 +5319,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -5383,16 +5333,16 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1385</v>
+        <v>233.7</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-2.02</v>
+        <v>-2.4</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1382.3857</v>
+        <v>232.2186</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.19</v>
+        <v>0.63</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -5406,13 +5356,11 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 11 d</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 28 d</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>68</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
@@ -5428,12 +5376,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -5442,16 +5390,16 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1427.5</v>
+        <v>1385</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-1.52</v>
+        <v>-2.02</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1412.0571</v>
+        <v>1382.3857</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.08</v>
+        <v>0.19</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -5465,11 +5413,13 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 35 d</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>83</v>
+          <t>R1 ADVISORY · held 11 d</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
@@ -5485,12 +5435,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -5499,16 +5449,16 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>185.61</v>
+        <v>1427.5</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.99</v>
+        <v>-1.52</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>181.8114</v>
+        <v>1412.0571</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.05</v>
+        <v>1.08</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -5522,11 +5472,11 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 11 d</t>
+          <t>R1 ADVISORY · held 35 d</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
@@ -5542,12 +5492,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -5556,16 +5506,16 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>418.85</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>0.3</v>
+        <v>185.61</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-0.99</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>407.3714</v>
+        <v>181.8114</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -5579,11 +5529,11 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 34 d</t>
+          <t>R1 ADVISORY · held 11 d</t>
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>33.3</v>
+        <v>65</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
@@ -5599,30 +5549,30 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>🟢 NORMAL</t>
+          <t>🟡 WATCH</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>404</v>
+        <v>418.85</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3.63</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>378.3286</v>
+        <v>407.3714</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.35</v>
+        <v>2.74</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -5631,20 +5581,20 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 35 d</t>
+          <t>R1 ADVISORY · held 34 d</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>65</v>
+        <v>33.3</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>R1 advisory · within suggested stop</t>
+          <t>R1 approaching advisory stop</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5606,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -5670,16 +5620,16 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>422.1</v>
+        <v>404</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>6.32</v>
+        <v>3.63</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>386.4571</v>
+        <v>378.3286</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.44</v>
+        <v>6.35</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -5696,10 +5646,8 @@
           <t>R1 ADVISORY · held 35 d</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+      <c r="L29" s="4" t="n">
+        <v>65</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
@@ -5715,58 +5663,54 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>186.04</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
+        <v>422.1</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>386.4571</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>30.3</v>
+          <t>R1 ADVISORY · held 35 d</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>engine verdict NEW_POSITION</t>
+          <t>R1 advisory · within suggested stop</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5722,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -5792,7 +5736,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>117.5</v>
+        <v>186.04</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -5816,7 +5760,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>NEW · BUY</t>
+          <t>NEW · STRONG BUY</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -5841,12 +5785,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -5855,7 +5799,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1895</v>
+        <v>117.5</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
@@ -5879,7 +5823,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>NEW · REVIEW</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -5888,11 +5832,11 @@
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>88</v>
+        <v>30.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.1%) • outperforming Nifty • sector s</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
     </row>
@@ -5904,145 +5848,193 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NEW · INVESTABLE</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1895</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>NEW · REVIEW</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>NEW CANDIDATE · not a position · no auto-entry</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.1%) • outperforming Nifty • sector s</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>NTPC</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>🟢 NEW · INVESTABLE</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E34" s="4" t="n">
         <v>332</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>NEW · REVIEW</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>NEW CANDIDATE · not a position · no auto-entry</t>
         </is>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="L34" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>Low-risk Power holding (low vol) • below 200-dma (-7.1%) • sector strength 15/100 • regime</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>MOMENTUM → R2 LIFECYCLE RECONCILIATION</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Where the rest went</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>1 · Declared universe</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>230</v>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2 · Actually evaluated</t>
+          <t>1 · Declared universe</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
         <v>230</v>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>unreadable=0 · insufficient history=0</t>
-        </is>
-      </c>
+      <c r="C39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3 · Momentum candidates</t>
+          <t>2 · Actually evaluated</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>4</v>
+        <v>230</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>226 evaluated tickers showed no momentum signal</t>
+          <t>unreadable=0 · insufficient history=0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>4 · In production universe</t>
+          <t>3 · Momentum candidates</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>4 candidate(s) dropped as outside the 50-name production universe</t>
+          <t>226 evaluated tickers showed no momentum signal</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>5 · ACCEPTED by ledger</t>
+          <t>4 · In production universe</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
@@ -6050,14 +6042,14 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>WATCH=0 · REJECTED=0 · NO_EVIDENCE=0</t>
+          <t>4 candidate(s) dropped as outside the 50-name production universe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>6 · Registry R2 NEW today</t>
+          <t>5 · ACCEPTED by ledger</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
@@ -6065,100 +6057,116 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>accepted momentum tickers not opened: none</t>
+          <t>WATCH=0 · REJECTED=0 · NO_EVIDENCE=0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t>6 · Registry R2 NEW today</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>accepted momentum tickers not opened: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
           <t>7 · R2 sheet ACTIVE</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B45" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C44" s="4" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>✅ No unexplained losses between momentum and R2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
+          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
+          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
+          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
+          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
+          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
+          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
+          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
           <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.309 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A46:M46"/>
-    <mergeCell ref="A36:M36"/>
+  <mergeCells count="15">
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A54:M54"/>
     <mergeCell ref="A50:M50"/>
     <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="A56:M56"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A56:M56"/>
     <mergeCell ref="A53:M53"/>
     <mergeCell ref="A55:M55"/>
+    <mergeCell ref="A57:M57"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A49:M49"/>
+    <mergeCell ref="A51:M51"/>
     <mergeCell ref="A52:M52"/>
+    <mergeCell ref="A47:M47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -633,16 +633,16 @@
         <v>2410</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2105</v>
+        <v>2106.2</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-12.66</v>
+        <v>-12.61</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>2314.8285</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-9.970000000000001</v>
+        <v>-9.91</v>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
@@ -701,16 +701,16 @@
         <v>5454.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5042.5</v>
+        <v>5027</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-7.55</v>
+        <v>-7.84</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>5283.7143</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.78</v>
+        <v>-5.11</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
@@ -771,16 +771,16 @@
         <v>507.9</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>476.05</v>
+        <v>473</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-6.27</v>
+        <v>-6.87</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>493.3286</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.63</v>
+        <v>-4.3</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -841,16 +841,16 @@
         <v>2064.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1973.4</v>
+        <v>1964.3</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-4.43</v>
+        <v>-4.87</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>1990.457</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.86</v>
+        <v>-1.33</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -911,16 +911,16 @@
         <v>381.6</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>365.7</v>
+        <v>363.5</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-4.17</v>
+        <v>-4.74</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>369.75</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.11</v>
+        <v>-1.72</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -964,31 +964,31 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1642.5</v>
+        <v>1048.7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1575</v>
+        <v>1004.2</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-4.11</v>
+        <v>-4.24</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1594.6857</v>
+        <v>1011.5999</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.25</v>
+        <v>-0.74</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -1000,14 +1000,12 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+      <c r="M11" s="4" t="n">
+        <v>71</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>NOT CAPTURED</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1017,14 +1015,14 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
+          <t>IND-R1-SBIN-20260821-b637f4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1034,31 +1032,31 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1048.7</v>
+        <v>1642.5</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1005.9</v>
+        <v>1580.8</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-4.08</v>
+        <v>-3.76</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1011.5999</v>
+        <v>1594.6857</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.57</v>
+        <v>-0.88</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -1070,12 +1068,14 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>71</v>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-SBIN-20260821-b637f4</t>
+          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>385.15</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>375.5</v>
+        <v>374.1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-2.51</v>
+        <v>-2.87</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>377.5071</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.53</v>
+        <v>-0.91</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1185,16 +1185,16 @@
         <v>1191</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1156.9</v>
+        <v>1151.9</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-2.86</v>
+        <v>-3.28</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>1149.2286</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.66</v>
+        <v>0.23</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1255,16 +1255,16 @@
         <v>239.45</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>233.7</v>
+        <v>233.47</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>232.2186</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1308,31 +1308,31 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1413.5</v>
+        <v>1449.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1385</v>
+        <v>1416.3</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-2.02</v>
+        <v>-2.29</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1382.3857</v>
+        <v>1412.0571</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1344,14 +1344,12 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+      <c r="M16" s="4" t="n">
+        <v>83</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>NOT CAPTURED</t>
+          <t>r1_daily_picks:Rec Confidence %</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1361,14 +1359,14 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1378,31 +1376,31 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1449.5</v>
+        <v>1413.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1427.5</v>
+        <v>1390</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-1.52</v>
+        <v>-1.66</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1412.0571</v>
+        <v>1382.3857</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1414,12 +1412,14 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="M17" s="4" t="n">
-        <v>83</v>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>r1_daily_picks:Rec Confidence %</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
         <v>187.46</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>185.61</v>
+        <v>185.6</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>-0.99</v>
@@ -1470,7 +1470,7 @@
         <v>181.8114</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
         <v>417.6</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>418.85</v>
+        <v>421.2</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.3</v>
+        <v>0.86</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>407.3714</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>🟡 WATCH</t>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M19" s="4" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>R1 approaching advisory stop</t>
+          <t>R1 advisory · within suggested stop</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -1597,16 +1597,16 @@
         <v>389.85</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>404</v>
+        <v>410.05</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3.63</v>
+        <v>5.18</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>378.3286</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>6.35</v>
+        <v>7.74</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>397</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>422.1</v>
+        <v>421.75</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>6.32</v>
+        <v>6.23</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>386.4571</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>8.44</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>597.9</v>
+        <v>591.25</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>597.9</v>
+        <v>591.25</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1813,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>186.04</v>
+        <v>117.05</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>186.04</v>
+        <v>117.05</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1887,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>117.5</v>
+        <v>233.86</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>117.5</v>
+        <v>233.86</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1427.5</v>
+        <v>1416.3</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1427.5</v>
+        <v>1416.3</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.2%) • outperforming Nifty • sect</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.4%) • outperforming Nifty • sect</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -2035,10 +2035,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1895</v>
+        <v>1883</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1895</v>
+        <v>1883</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.1%) • outperforming Nifty • sector s</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+4.4%) • outperforming Nifty • sector s</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -2109,10 +2109,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>332</v>
+        <v>331.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>332</v>
+        <v>331.5</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.1%) • sector strength 15/100 • regime</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.2%) • sector strength 23/100 • regime</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -2183,10 +2183,10 @@
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1005.9</v>
+        <v>1004.2</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1005.9</v>
+        <v>1004.2</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.2%) • sector strength 77/100 • r</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.4%) • sector strength 77/100 • r</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>418.85</v>
+        <v>410.05</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>418.85</v>
+        <v>410.05</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.3%) • sector strength 46/100 • regime</t>
+          <t xml:space="preserve">Low-risk Industrials holding (low vol) • below 200-dma (-2.1%) • sector strength 38/100 • </t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2331,10 +2331,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>404</v>
+        <v>233.47</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>404</v>
+        <v>233.47</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="M32" s="4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-risk Industrials holding (low vol) • below 200-dma (-3.6%) • sector strength 38/100 • </t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.3%) • sector strength 69/100 • regim</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2405,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>233.7</v>
+        <v>421.2</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>233.7</v>
+        <v>421.2</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.2%) • sector strength 62/100 • regim</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-1.8%) • sector strength 54/100 • regime</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -2479,10 +2479,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>185.61</v>
+        <v>185.6</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>185.61</v>
+        <v>185.6</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.5%) • sector strength 46/100 • regime</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.6%) • sector strength 54/100 • regime</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.309 · 0.0% of scored names sit at the maximum.</t>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.305 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
@@ -2783,13 +2783,13 @@
         <v>284.85</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>263.5</v>
+        <v>263.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-7.5</v>
+        <v>-7.57</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>255.5857</v>
+        <v>255.8714</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -2797,16 +2797,16 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>297.98</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.08</v>
+        <v>13.17</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.36</v>
+        <v>4.67</v>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
@@ -2872,13 +2872,13 @@
         <v>452.35</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>419.05</v>
+        <v>419.35</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-7.36</v>
+        <v>-7.3</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>403.5857</v>
+        <v>404.55</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -2886,16 +2886,16 @@
         </is>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.69</v>
+        <v>3.53</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>477.49</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>13.94</v>
+        <v>13.86</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.78</v>
+        <v>3.93</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>709</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>669.45</v>
+        <v>665.7</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-5.58</v>
+        <v>-6.11</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>643.1072</v>
+        <v>639.9857</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>749.16</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>11.91</v>
+        <v>12.54</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         <v>11475</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>10956</v>
+        <v>11005</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-4.52</v>
+        <v>-4.1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10569.1429</v>
+        <v>10630.4286</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>11970.43</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>9.26</v>
+        <v>8.77</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -3139,13 +3139,13 @@
         <v>2744.3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2698</v>
+        <v>2654.2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-1.69</v>
+        <v>-3.28</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2556.9857</v>
+        <v>2542.2</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -3153,16 +3153,16 @@
         </is>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.23</v>
+        <v>4.22</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>2949.97</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>9.34</v>
+        <v>11.14</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.79</v>
+        <v>2.64</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -3228,13 +3228,13 @@
         <v>5499</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5540</v>
+        <v>5519.5</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.75</v>
+        <v>0.37</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5265.5714</v>
+        <v>5251.9286</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -3242,16 +3242,16 @@
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>5954.25</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.48</v>
+        <v>7.88</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -3317,13 +3317,13 @@
         <v>113.36</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>115.6</v>
+        <v>116.19</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>111.9314</v>
+        <v>112.5514</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -3331,16 +3331,16 @@
         </is>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="L12" s="4" t="n">
         <v>118.87</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.83</v>
+        <v>2.31</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -3406,13 +3406,13 @@
         <v>553.3</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>597.9</v>
+        <v>591.25</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>8.06</v>
+        <v>6.86</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>570.8357</v>
+        <v>565.6214</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -3420,13 +3420,13 @@
         </is>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.53</v>
+        <v>4.33</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>587.67</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.71</v>
+        <v>-0.61</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.309 · 0.0% of scored names sit at the maximum.</t>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.305 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -3910,24 +3910,24 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CANDIDATES FOUND BUT OUTSIDE THE PRODUCTION UNIVERSE · 4 · real momentum · not R2-tradable · shown so a zero above is never mistaken for a quiet market</t>
+          <t>CANDIDATES FOUND BUT OUTSIDE THE PRODUCTION UNIVERSE · 3 · real momentum · not R2-tradable · shown so a zero above is never mistaken for a quiet market</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>QUICK_RISE</t>
+          <t>SUSTAINED_DOWN</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -3936,26 +3936,26 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.53</v>
+        <v>-0.51</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.9</v>
+        <v>-2.56</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.380000000000001</v>
+        <v>-5.25</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>8.880000000000001</v>
+        <v>-16.99</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>71.3</v>
+        <v>18.6</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.73</v>
+        <v>0.05</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>MOMENTUM_WATCH</t>
+          <t>AVOID</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>unknown quality · watch but don't act blind</t>
+          <t>unknown quality + falling · not a value play</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3977,17 +3977,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>QUICK_RISE</t>
+          <t>QUICK_FALL</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3996,26 +3996,26 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.77</v>
+        <v>-5.02</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.47</v>
+        <v>-6.2</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.65</v>
+        <v>-6.47</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.44</v>
+        <v>-5.55</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>61.9</v>
+        <v>28.1</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.65</v>
+        <v>0.16</v>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>MOMENTUM_WATCH</t>
+          <t>AVOID</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>unknown quality · watch but don't act blind</t>
+          <t>unknown quality + falling · not a value play</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -4037,17 +4037,17 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>QUICK_RISE</t>
+          <t>SUSTAINED_DOWN</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -4056,26 +4056,26 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.83</v>
+        <v>0.66</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.48</v>
+        <v>-11.11</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.92</v>
+        <v>-11.46</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.67</v>
+        <v>-16.12</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>55.2</v>
+        <v>17.9</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.32</v>
+        <v>0.39</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>MOMENTUM_WATCH</t>
+          <t>AVOID</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>unknown quality · watch but don't act blind</t>
+          <t>unknown quality + falling · not a value play</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -4094,96 +4094,36 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>KEI</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>SUSTAINED_DOWN</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>-9.01</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>-14.07</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>-16.89</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>AVOID</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>NOT CLASSIFIED</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>unknown quality + falling · not a value play</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>'Declared universe' is NOT 'scanned' · only ACTUALLY EVALUATED counts tickers that were genuinely scored.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>'Declared universe' is NOT 'scanned' · only ACTUALLY EVALUATED counts tickers that were genuinely scored.</t>
+          <t>Thresholds are UNCHANGED production values and are never lowered to manufacture candidates: {"1d_rise_pct": 4.0, "3d_rise_pct": 8.0, "5d_rise_pct": 12.0, "1d_fall_pct": -4.0, "3d_fall_pct": -8.0, "5d_fall_pct": -12.0, "volume_confirm_multiplier": 1.5, "rsi_overbought": 70, "rsi_oversold": 30, "vol_adjust_cap": 2.0}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Thresholds are UNCHANGED production values and are never lowered to manufacture candidates: {"1d_rise_pct": 4.0, "3d_rise_pct": 8.0, "5d_rise_pct": 12.0, "1d_fall_pct": -4.0, "3d_fall_pct": -8.0, "5d_fall_pct": -12.0, "volume_confirm_multiplier": 1.5, "rsi_overbought": 70, "rsi_oversold": 30, "vol_adjust_cap": 2.0}</t>
+          <t>Momentum never opens a position · production_impact is null by design.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Momentum never opens a position · production_impact is null by design.</t>
+          <t>A candidate reaches R2 only through R2 eligibility · see the reconciliation block on DAILY RECOMMENDATION.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>A candidate reaches R2 only through R2 eligibility · see the reconciliation block on DAILY RECOMMENDATION.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>STALE means the producer's as-of date is older than this report's as-of date · the rows are not today's market.</t>
         </is>
@@ -4198,7 +4138,7 @@
     <mergeCell ref="A21:N21"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A37:N37"/>
-    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A33:N33"/>
     <mergeCell ref="A5:N5"/>
     <mergeCell ref="A23:N23"/>
     <mergeCell ref="A36:N36"/>
@@ -4356,16 +4296,16 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>263.5</v>
+        <v>263.3</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-7.5</v>
+        <v>-7.57</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>255.5857</v>
+        <v>255.8714</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>297.98</v>
@@ -4413,16 +4353,16 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>419.05</v>
+        <v>419.35</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-7.36</v>
+        <v>-7.3</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>403.5857</v>
+        <v>404.55</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.69</v>
+        <v>3.53</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>477.49</v>
@@ -4470,16 +4410,16 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>669.45</v>
+        <v>665.7</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-5.58</v>
+        <v>-6.11</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>643.1072</v>
+        <v>639.9857</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>749.16</v>
@@ -4527,16 +4467,16 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10956</v>
+        <v>11005</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-4.52</v>
+        <v>-4.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10569.1429</v>
+        <v>10630.4286</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>11970.43</v>
@@ -4584,16 +4524,16 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2698</v>
+        <v>2654.2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-1.69</v>
+        <v>-3.28</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2556.9857</v>
+        <v>2542.2</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.23</v>
+        <v>4.22</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>2949.97</v>
@@ -4641,16 +4581,16 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5540</v>
+        <v>5519.5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.75</v>
+        <v>0.37</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5265.5714</v>
+        <v>5251.9286</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>5954.25</v>
@@ -4698,16 +4638,16 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>115.6</v>
+        <v>116.19</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>111.9314</v>
+        <v>112.5514</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>118.87</v>
@@ -4755,16 +4695,16 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>597.9</v>
+        <v>591.25</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>8.06</v>
+        <v>6.86</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>570.8357</v>
+        <v>565.6214</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.53</v>
+        <v>4.33</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>587.67</v>
@@ -4810,16 +4750,16 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2105</v>
+        <v>2106.2</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-12.66</v>
+        <v>-12.61</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>2314.8285</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-9.970000000000001</v>
+        <v>-9.91</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -4867,16 +4807,16 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5042.5</v>
+        <v>5027</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-7.55</v>
+        <v>-7.84</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>5283.7143</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.78</v>
+        <v>-5.11</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -4926,16 +4866,16 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>476.05</v>
+        <v>473</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-6.27</v>
+        <v>-6.87</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>493.3286</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.63</v>
+        <v>-4.3</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -4985,16 +4925,16 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1973.4</v>
+        <v>1964.3</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-4.43</v>
+        <v>-4.87</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>1990.457</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.86</v>
+        <v>-1.33</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -5044,16 +4984,16 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>365.7</v>
+        <v>363.5</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-4.17</v>
+        <v>-4.74</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>369.75</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.11</v>
+        <v>-1.72</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -5087,12 +5027,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -5101,16 +5041,16 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1575</v>
+        <v>1004.2</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-4.11</v>
+        <v>-4.24</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1594.6857</v>
+        <v>1011.5999</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.25</v>
+        <v>-0.74</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -5124,13 +5064,11 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 35 d</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 18 d</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>71</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -5146,12 +5084,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -5160,16 +5098,16 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1005.9</v>
+        <v>1580.8</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-4.08</v>
+        <v>-3.76</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1011.5999</v>
+        <v>1594.6857</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.57</v>
+        <v>-0.88</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -5183,11 +5121,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 18 d</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>71</v>
+          <t>R1 ADVISORY · held 35 d</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -5217,16 +5157,16 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>375.5</v>
+        <v>374.1</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-2.51</v>
+        <v>-2.87</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>377.5071</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.53</v>
+        <v>-0.91</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -5274,16 +5214,16 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1156.9</v>
+        <v>1151.9</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-2.86</v>
+        <v>-3.28</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>1149.2286</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.66</v>
+        <v>0.23</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -5333,16 +5273,16 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>233.7</v>
+        <v>233.47</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>232.2186</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -5376,12 +5316,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -5390,16 +5330,16 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1385</v>
+        <v>1416.3</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-2.02</v>
+        <v>-2.29</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1382.3857</v>
+        <v>1412.0571</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -5413,13 +5353,11 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 11 d</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 35 d</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>83</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
@@ -5435,12 +5373,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -5449,16 +5387,16 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1427.5</v>
+        <v>1390</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-1.52</v>
+        <v>-1.66</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1412.0571</v>
+        <v>1382.3857</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -5472,11 +5410,13 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 35 d</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>83</v>
+          <t>R1 ADVISORY · held 11 d</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
@@ -5506,7 +5446,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>185.61</v>
+        <v>185.6</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>-0.99</v>
@@ -5515,7 +5455,7 @@
         <v>181.8114</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -5559,20 +5499,20 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>🟡 WATCH</t>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>418.85</v>
+        <v>421.2</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.3</v>
+        <v>0.86</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>407.3714</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -5581,7 +5521,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -5594,7 +5534,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>R1 approaching advisory stop</t>
+          <t>R1 advisory · within suggested stop</t>
         </is>
       </c>
     </row>
@@ -5620,16 +5560,16 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>404</v>
+        <v>410.05</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3.63</v>
+        <v>5.18</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>378.3286</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.35</v>
+        <v>7.74</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -5647,7 +5587,7 @@
         </is>
       </c>
       <c r="L29" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
@@ -5677,16 +5617,16 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>422.1</v>
+        <v>421.75</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>6.32</v>
+        <v>6.23</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>386.4571</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>8.44</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
@@ -5722,7 +5662,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -5736,7 +5676,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>186.04</v>
+        <v>117.05</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -5785,7 +5725,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -5799,7 +5739,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>117.5</v>
+        <v>233.86</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
@@ -5862,7 +5802,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1895</v>
+        <v>1883</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
@@ -5899,7 +5839,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.1%) • outperforming Nifty • sector s</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+4.4%) • outperforming Nifty • sector s</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5865,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>332</v>
+        <v>331.5</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
@@ -5962,7 +5902,7 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.1%) • sector strength 15/100 • regime</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.2%) • sector strength 23/100 • regime</t>
         </is>
       </c>
     </row>
@@ -6023,11 +5963,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>226 evaluated tickers showed no momentum signal</t>
+          <t>227 evaluated tickers showed no momentum signal</t>
         </is>
       </c>
     </row>
@@ -6042,7 +5982,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>4 candidate(s) dropped as outside the 50-name production universe</t>
+          <t>3 candidate(s) dropped as outside the 50-name production universe</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6086,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.309 · 0.0% of scored names sit at the maximum.</t>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.198–0.436 · mean 0.305 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6207,7 +6147,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total 46 · R2 production 21 · R1 advisory 5 · administrative 20 · Momentum 0 (momentum never opens a position, so it can never produce an exit)</t>
+          <t>Total 47 · R2 production 21 · R1 advisory 5 · administrative 21 · Momentum 0 (momentum never opens a position, so it can never produce an exit)</t>
         </is>
       </c>
     </row>
@@ -6320,10 +6260,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>288.1</v>
+        <v>289</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>288.1</v>
+        <v>289</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
@@ -6358,32 +6298,32 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>414.35</v>
+        <v>454.85</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>414.35</v>
+        <v>454.85</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>0</v>
@@ -6397,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>18.2</v>
+        <v>15.5</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
@@ -6406,7 +6346,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260907-a63a75</t>
+          <t>IND-R2-SUNTV-20260908-c6e7dc</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6358,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -6428,25 +6368,25 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>391.3</v>
+        <v>414.35</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>415.35</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>6.15</v>
+        <v>414.35</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -6454,98 +6394,96 @@
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.93</v>
+        <v>0.45</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>17.1</v>
+        <v>18.2</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-RBLBANK-20260907-a63a75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>R1 · ADVISORY</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>177.09</v>
+        <v>391.3</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>177.09</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>415.35</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>6.15</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.13</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>17.1</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>advisory</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-WIPRO-20260902-25d63c</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1 · ADVISORY</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -6562,33 +6500,35 @@
         <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2891.8</v>
+        <v>177.09</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2891.8</v>
+        <v>177.09</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
         </is>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>57</v>
+        <v>-2.93</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>advisory</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIENT-20260902-51452a</t>
+          <t>IND-R1-WIPRO-20260902-25d63c</t>
         </is>
       </c>
     </row>
@@ -6600,35 +6540,35 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2383.9</v>
+        <v>2891.8</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2160.2</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>-9.380000000000001</v>
+        <v>2891.8</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -6636,36 +6576,36 @@
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.56</v>
+        <v>1.46</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R2-ADANIENT-20260902-51452a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>R1 · ADVISORY</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -6682,95 +6622,95 @@
         <v>27</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>347.25</v>
+        <v>2383.9</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>326.5</v>
+        <v>2160.2</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-5.98</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-2.5</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>advisory</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-NTPC-20260804-b96a36</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1 · ADVISORY</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>398.8</v>
+        <v>347.25</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>398.8</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>326.5</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>-5.98</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="K13" s="4" t="n">
         <v>1.53</v>
       </c>
-      <c r="L13" s="4" t="n">
-        <v>52.9</v>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>advisory</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
+          <t>IND-R1-NTPC-20260804-b96a36</t>
         </is>
       </c>
     </row>
@@ -6782,35 +6722,35 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>415.15</v>
+        <v>398.8</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>402.55</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>-3.04</v>
+        <v>398.8</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -6818,41 +6758,41 @@
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.05</v>
+        <v>-0.16</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>14.3</v>
+        <v>52.9</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>R1 · ADVISORY</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -6861,38 +6801,36 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>289</v>
+        <v>415.15</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>268.15</v>
+        <v>402.55</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-7.21</v>
+        <v>-3.04</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.63</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>14.3</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>advisory</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ITC-20260805-3cdd2a</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6842,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -6923,16 +6861,16 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1955.3</v>
+        <v>289</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1912</v>
+        <v>268.15</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-2.21</v>
+        <v>-7.21</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -6940,7 +6878,7 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.89</v>
+        <v>-1.81</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -6954,7 +6892,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
+          <t>IND-R1-ITC-20260805-3cdd2a</t>
         </is>
       </c>
     </row>
@@ -6966,35 +6904,35 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>283.4</v>
+        <v>1955.3</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>264.9</v>
+        <v>1912</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-6.53</v>
+        <v>-2.21</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -7002,7 +6940,7 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.42</v>
+        <v>-1.52</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -7016,67 +6954,69 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-POWERGRID-20260805-b39825</t>
+          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1 · ADVISORY</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>847.5</v>
+        <v>283.4</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>847.5</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>264.9</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-6.53</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.82</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>56.7</v>
+        <v>0.17</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>advisory</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARICO-20260826-1c5a1c</t>
+          <t>IND-R1-POWERGRID-20260805-b39825</t>
         </is>
       </c>
     </row>
@@ -7088,32 +7028,32 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1702.7</v>
+        <v>847.5</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1702.7</v>
+        <v>847.5</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>0</v>
@@ -7124,10 +7064,10 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.14</v>
+        <v>-5.26</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>57.6</v>
+        <v>56.7</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -7136,7 +7076,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
+          <t>IND-R2-MARICO-20260826-1c5a1c</t>
         </is>
       </c>
     </row>
@@ -7148,32 +7088,32 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>244.55</v>
+        <v>1702.7</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>244.55</v>
+        <v>1702.7</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -7184,10 +7124,10 @@
         </is>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.07</v>
+        <v>1.39</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>10.1</v>
+        <v>57.6</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -7196,7 +7136,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260824-89850d</t>
+          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7148,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -7218,22 +7158,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>402.8</v>
+        <v>244.55</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>402.8</v>
+        <v>244.55</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>0</v>
@@ -7244,10 +7184,10 @@
         </is>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.79</v>
+        <v>-4.37</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>13.3</v>
+        <v>10.1</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -7256,7 +7196,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
+          <t>IND-R2-JIOFIN-20260824-89850d</t>
         </is>
       </c>
     </row>
@@ -7268,12 +7208,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -7290,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1114.2</v>
+        <v>402.8</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1114.2</v>
+        <v>402.8</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>0</v>
@@ -7304,10 +7244,10 @@
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.58</v>
+        <v>4.7</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -7316,7 +7256,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260821-142d93</t>
+          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7268,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -7350,10 +7290,10 @@
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>8693</v>
+        <v>1114.2</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>8693</v>
+        <v>1114.2</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>0</v>
@@ -7364,10 +7304,10 @@
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.49</v>
+        <v>-1.46</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>61.4</v>
+        <v>14.5</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -7376,7 +7316,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
+          <t>IND-R2-MGL-20260821-142d93</t>
         </is>
       </c>
     </row>
@@ -7388,46 +7328,46 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>174.9</v>
+        <v>8693</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>174.9</v>
+        <v>8693</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7.43</v>
+        <v>1.05</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>11.8</v>
+        <v>61.4</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
@@ -7436,7 +7376,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260820-80f37d</t>
+          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7388,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -7458,25 +7398,25 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>552.4</v>
+        <v>174.9</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>558</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1.01</v>
+        <v>174.9</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -7484,19 +7424,19 @@
         </is>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.58</v>
+        <v>8.49</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>14.7</v>
+        <v>11.8</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-SAIL-20260820-80f37d</t>
         </is>
       </c>
     </row>
@@ -7508,17 +7448,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -7527,16 +7467,16 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>129.2</v>
+        <v>552.4</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>-3.72</v>
+        <v>558</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1.01</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -7544,10 +7484,10 @@
         </is>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-5.55</v>
+        <v>7.82</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>12.2</v>
+        <v>14.7</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
@@ -7556,7 +7496,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
     </row>
@@ -7568,35 +7508,35 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="F27" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5220</v>
+        <v>129.2</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5220</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>0</v>
+        <v>124.4</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>-3.72</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -7604,19 +7544,19 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-4.66</v>
+        <v>-5.91</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>60</v>
+        <v>12.2</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
     </row>
@@ -7628,35 +7568,35 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1384</v>
+        <v>5220</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1327.6</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>-4.08</v>
+        <v>5220</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -7664,19 +7604,19 @@
         </is>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.98</v>
+        <v>-4.9</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>56.7</v>
+        <v>60</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
         </is>
       </c>
     </row>
@@ -7688,12 +7628,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -7710,13 +7650,13 @@
         <v>12</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>377</v>
+        <v>1384</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>2.8</v>
+        <v>1327.6</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>-4.08</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -7724,10 +7664,10 @@
         </is>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-5.59</v>
+        <v>-3.51</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
@@ -7736,7 +7676,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
     </row>
@@ -7748,12 +7688,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -7763,20 +7703,20 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>11600</v>
+        <v>377</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11828</v>
+        <v>387.55</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -7784,10 +7724,10 @@
         </is>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.16</v>
+        <v>-2.92</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
@@ -7796,7 +7736,7 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7748,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -7818,7 +7758,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -7827,16 +7767,16 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2439.4</v>
+        <v>11600</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2361</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>-3.21</v>
+        <v>11828</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1.97</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -7844,10 +7784,10 @@
         </is>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.85</v>
+        <v>-0.51</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
@@ -7856,7 +7796,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
     </row>
@@ -7868,35 +7808,35 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
       <c r="F32" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3940</v>
+        <v>2439.4</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3940</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>0</v>
+        <v>2361</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>-3.21</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -7904,19 +7844,19 @@
         </is>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.33</v>
+        <v>-4.18</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
     </row>
@@ -7928,32 +7868,32 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1779.2</v>
+        <v>3940</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1779.2</v>
+        <v>3940</v>
       </c>
       <c r="I33" s="4" t="n">
         <v>0</v>
@@ -7964,10 +7904,10 @@
         </is>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.75</v>
+        <v>0.12</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -7976,7 +7916,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
+          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
         </is>
       </c>
     </row>
@@ -7988,35 +7928,35 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7454.5</v>
+        <v>1779.2</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7095</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>-4.82</v>
+        <v>1779.2</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -8024,19 +7964,19 @@
         </is>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.34</v>
+        <v>-8.58</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>62.1</v>
+        <v>8.1</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
         </is>
       </c>
     </row>
@@ -8048,35 +7988,35 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F35" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>129</v>
+        <v>7454.5</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>0</v>
+        <v>7095</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>-4.82</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -8084,19 +8024,19 @@
         </is>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-3.88</v>
+        <v>3.13</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>6.5</v>
+        <v>62.1</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260810-788da8</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
     </row>
@@ -8108,12 +8048,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -8130,10 +8070,10 @@
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>4924</v>
+        <v>129</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>4924</v>
+        <v>129</v>
       </c>
       <c r="I36" s="4" t="n">
         <v>0</v>
@@ -8144,10 +8084,10 @@
         </is>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-0.2</v>
+        <v>-3.4</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>60.1</v>
+        <v>6.5</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
@@ -8156,7 +8096,7 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
+          <t>IND-R2-CANBK-20260810-788da8</t>
         </is>
       </c>
     </row>
@@ -8168,12 +8108,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -8190,10 +8130,10 @@
         <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>181.14</v>
+        <v>4924</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>181.14</v>
+        <v>4924</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>0</v>
@@ -8204,10 +8144,10 @@
         </is>
       </c>
       <c r="K37" s="4" t="n">
-        <v>2.71</v>
+        <v>-0.28</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>9.4</v>
+        <v>60.1</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
@@ -8216,7 +8156,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
+          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
         </is>
       </c>
     </row>
@@ -8228,35 +8168,35 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>6793.5</v>
+        <v>181.14</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>6774</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>-0.29</v>
+        <v>181.14</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -8264,19 +8204,19 @@
         </is>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-5.73</v>
+        <v>1.66</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
         </is>
       </c>
     </row>
@@ -8288,17 +8228,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -8307,16 +8247,16 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>471.2</v>
+        <v>6793.5</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>0.45</v>
+        <v>6774</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>-0.29</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -8324,10 +8264,10 @@
         </is>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-3.25</v>
+        <v>-6.76</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>60.7</v>
+        <v>8</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
@@ -8336,7 +8276,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
     </row>
@@ -8348,17 +8288,17 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -8367,16 +8307,16 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>845</v>
+        <v>471.2</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>889.5</v>
+        <v>473.3</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>5.27</v>
+        <v>0.45</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -8384,10 +8324,10 @@
         </is>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-1.1</v>
+        <v>-4.29</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>7.4</v>
+        <v>60.7</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
@@ -8396,7 +8336,7 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8348,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -8430,13 +8370,13 @@
         <v>2</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>450</v>
+        <v>845</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>442.8</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>-1.6</v>
+        <v>889.5</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>5.27</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -8444,10 +8384,10 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>9.98</v>
+        <v>-2.48</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>10.3</v>
+        <v>7.4</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
@@ -8456,7 +8396,7 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8408,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -8490,13 +8430,13 @@
         <v>2</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1595</v>
+        <v>450</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1584.8</v>
+        <v>442.8</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-0.64</v>
+        <v>-1.6</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -8504,10 +8444,10 @@
         </is>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-2.2</v>
+        <v>10.09</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>62.5</v>
+        <v>10.3</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
@@ -8516,7 +8456,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
     </row>
@@ -8528,12 +8468,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -8550,13 +8490,13 @@
         <v>2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1327.7</v>
+        <v>1595</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1285</v>
+        <v>1584.8</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>-3.22</v>
+        <v>-0.64</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -8564,10 +8504,10 @@
         </is>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-9.17</v>
+        <v>-2.62</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>64.8</v>
+        <v>62.5</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
@@ -8576,7 +8516,7 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8528,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -8603,20 +8543,20 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>2195</v>
+        <v>1327.7</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2182</v>
+        <v>1285</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.59</v>
+        <v>-3.22</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -8624,10 +8564,10 @@
         </is>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-10.4</v>
+        <v>-10.04</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>59.7</v>
+        <v>64.8</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
@@ -8636,7 +8576,7 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
     </row>
@@ -8648,17 +8588,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -8667,16 +8607,16 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1363.6</v>
+        <v>2195</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1351.3</v>
+        <v>2182</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>-0.9</v>
+        <v>-0.59</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -8684,10 +8624,10 @@
         </is>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-5.07</v>
+        <v>-11.46</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>7.8</v>
+        <v>59.7</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
@@ -8696,7 +8636,7 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
     </row>
@@ -8708,12 +8648,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -8730,13 +8670,13 @@
         <v>2</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>5470.5</v>
+        <v>1363.6</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>5651.5</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>3.31</v>
+        <v>1351.3</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>-0.9</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -8744,10 +8684,10 @@
         </is>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-6.75</v>
+        <v>-5.31</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
@@ -8756,7 +8696,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
     </row>
@@ -8768,17 +8708,17 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -8787,16 +8727,16 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1167.5</v>
+        <v>5470.5</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1177</v>
+        <v>5651.5</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.31</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -8804,10 +8744,10 @@
         </is>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-7.6</v>
+        <v>-5.71</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>11.7</v>
+        <v>10.6</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
@@ -8816,7 +8756,7 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
     </row>
@@ -8828,17 +8768,17 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -8847,16 +8787,16 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>268.5</v>
+        <v>1167.5</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>278.8</v>
+        <v>1177</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>3.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -8864,10 +8804,10 @@
         </is>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-3.87</v>
+        <v>-7.76</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
@@ -8876,7 +8816,7 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260804-563905</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
     </row>
@@ -8888,12 +8828,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -8903,40 +8843,40 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>425.05</v>
+        <v>268.5</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>425.05</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>0</v>
+        <v>278.8</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>3.84</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Outperformance exit</t>
         </is>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-7.92</v>
+        <v>-2.3</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>51.8</v>
+        <v>11.6</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>administrative</t>
+          <t>production</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BIOCON-20260804-954a24</t>
+          <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8888,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -8970,10 +8910,10 @@
         <v>0</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>939.95</v>
+        <v>425.05</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>939.95</v>
+        <v>425.05</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
@@ -8984,7 +8924,7 @@
         </is>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-3.72</v>
+        <v>-6.87</v>
       </c>
       <c r="L50" s="4" t="n">
         <v>51.8</v>
@@ -8996,7 +8936,7 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+          <t>IND-R2-BIOCON-20260804-954a24</t>
         </is>
       </c>
     </row>
@@ -9008,12 +8948,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -9030,10 +8970,10 @@
         <v>0</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>567.3</v>
+        <v>939.95</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>567.3</v>
+        <v>939.95</v>
       </c>
       <c r="I51" s="4" t="n">
         <v>0</v>
@@ -9044,178 +8984,238 @@
         </is>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-6.58</v>
+        <v>-3.57</v>
       </c>
       <c r="L51" s="4" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>administrative</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>567.3</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>567.3</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>-7.09</v>
+      </c>
+      <c r="L52" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>administrative</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>IND-R2-JSWENERGY-20260804-1210a0</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>MONTHLY SUMMARY · realized R2 production exits only · R1 advisory and administrative events excluded</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Exits</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Win Rate %</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>Avg Realized P&amp;L %</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>Best %</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Worst %</t>
         </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>6.15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B58" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="C58" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D58" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E58" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="F58" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>5.27</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>-9.380000000000001</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>One unified exit history across R1 · R2 · Momentum · 90-day rolling.</t>
-        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>MONTHLY SUMMARY covers realized R2 production exits only · this is a 'realized 90d' scope, NOT a count of current holdings.</t>
+          <t>One unified exit history across R1 · R2 · Momentum · 90-day rolling.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Realized P&amp;L % · (Exit − Entry) / Entry · the trade's own result.</t>
+          <t>MONTHLY SUMMARY covers realized R2 production exits only · this is a 'realized 90d' scope, NOT a count of current holdings.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Return Since Exit % · price move from the exit price to today · positive means the stock kept rising after we sold (exit cost us) · negative means the exit protected capital.</t>
+          <t>Realized P&amp;L % · (Exit − Entry) / Entry · the trade's own result.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Relative Opportunity pp · rotation benefit vs the closed position · percentage points · this is NOT the trade's own P&amp;L.</t>
+          <t>Return Since Exit % · price move from the exit price to today · positive means the stock kept rising after we sold (exit cost us) · negative means the exit protected capital.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Classification · production (R2 real trade) · advisory (R1 · never counted in production P&amp;L) · administrative (same-day / zero-delta bookkeeping event · not a real trade).</t>
+          <t>Relative Opportunity pp · rotation benefit vs the closed position · percentage points · this is NOT the trade's own P&amp;L.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never silently zeroed.</t>
+          <t>Classification · production (R2 real trade) · advisory (R1 · never counted in production P&amp;L) · administrative (same-day / zero-delta bookkeeping event · not a real trade).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never silently zeroed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>Momentum contributes no exits by design · it is research-only and opens no positions.</t>
         </is>
@@ -9226,12 +9226,12 @@
     <mergeCell ref="A67:N67"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A61:N61"/>
+    <mergeCell ref="A55:N55"/>
     <mergeCell ref="A62:N62"/>
-    <mergeCell ref="A54:N54"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A64:N64"/>
     <mergeCell ref="A65:N65"/>
-    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="A68:N68"/>
     <mergeCell ref="A63:N63"/>
     <mergeCell ref="A66:N66"/>
     <mergeCell ref="A1:N1"/>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -527,220 +527,91 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>🔎 WHY NEW=0 · 228 scored · 16 already in CURRENT · biggest blocker: model disagreement (198) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Stop State</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Dist to Stop %</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Max Loss if Stop %</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>GNFC</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE+</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>553.3</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>591.25</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>570.8357</v>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>587.67</v>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-GNFC-20260806-03d0a7</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE+</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>452.35</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>419.35</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>403.5857</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>-10.78</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>477.49</v>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -752,12 +623,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -767,17 +638,17 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>397</v>
+        <v>553.3</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>421.75</v>
+        <v>591.25</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>6.23</v>
+        <v>6.86</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -785,7 +656,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>386.4571</v>
+        <v>570.8357</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -793,22 +664,22 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.369999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.66</v>
+        <v>3.17</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>412.81</v>
+        <v>587.67</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -820,12 +691,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -839,13 +710,13 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>389.85</v>
+        <v>452.35</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>410.05</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>5.18</v>
+        <v>419.35</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-7.3</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -853,7 +724,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>378.3286</v>
+        <v>403.5857</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -861,22 +732,22 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.74</v>
+        <v>3.76</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.96</v>
+        <v>-10.78</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>407.13</v>
+        <v>477.49</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -888,7 +759,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -903,17 +774,17 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>417.6</v>
+        <v>397</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>421.2</v>
+        <v>421.75</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.86</v>
+        <v>6.23</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -921,7 +792,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>407.3714</v>
+        <v>386.4571</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -929,17 +800,17 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.28</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.45</v>
+        <v>-2.66</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>432.94</v>
+        <v>412.81</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -956,7 +827,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -971,17 +842,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>187.46</v>
+        <v>389.85</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>185.6</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>-0.99</v>
+        <v>410.05</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>5.18</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -989,7 +860,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>181.8114</v>
+        <v>378.3286</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -997,17 +868,17 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.04</v>
+        <v>7.74</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.01</v>
+        <v>-2.96</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>195.93</v>
+        <v>407.13</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1024,7 +895,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1039,17 +910,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1413.5</v>
+        <v>417.6</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1390</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>-1.66</v>
+        <v>421.2</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.86</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -1057,7 +928,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1382.3857</v>
+        <v>407.3714</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -1065,17 +936,17 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.55</v>
+        <v>3.28</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.2</v>
+        <v>-2.45</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1460.17</v>
+        <v>432.94</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -1092,7 +963,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1107,17 +978,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1449.5</v>
+        <v>187.46</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1416.3</v>
+        <v>185.6</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-2.29</v>
+        <v>-0.99</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1125,7 +996,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1412.0571</v>
+        <v>181.8114</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1133,17 +1004,17 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3</v>
+        <v>2.04</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.58</v>
+        <v>-3.01</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1505.66</v>
+        <v>195.93</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1160,7 +1031,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1175,17 +1046,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>239.45</v>
+        <v>1413.5</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>233.47</v>
+        <v>1390</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-2.5</v>
+        <v>-1.66</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1193,7 +1064,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>232.2186</v>
+        <v>1382.3857</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1201,17 +1072,17 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.02</v>
+        <v>-2.2</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>250.3</v>
+        <v>1460.17</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -1228,7 +1099,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1243,17 +1114,17 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1191</v>
+        <v>1449.5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1151.9</v>
+        <v>1416.3</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-3.28</v>
+        <v>-2.29</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1261,7 +1132,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1149.2286</v>
+        <v>1412.0571</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1269,17 +1140,17 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.51</v>
+        <v>-2.58</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1253.66</v>
+        <v>1505.66</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -1296,32 +1167,32 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>113.36</v>
+        <v>239.45</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>116.19</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>2.5</v>
+        <v>233.47</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-2.5</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1329,7 +1200,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>111.9314</v>
+        <v>232.2186</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1337,22 +1208,22 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.67</v>
+        <v>0.54</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.26</v>
+        <v>-3.02</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>118.87</v>
+        <v>250.3</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1364,32 +1235,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5499</v>
+        <v>1191</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5519.5</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>0.37</v>
+        <v>1151.9</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-3.28</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1397,7 +1268,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5265.5714</v>
+        <v>1149.2286</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1405,22 +1276,22 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.6</v>
+        <v>0.23</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.24</v>
+        <v>-3.51</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5954.25</v>
+        <v>1253.66</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1303,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1447,17 +1318,17 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2744.3</v>
+        <v>113.36</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2654.2</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>-3.28</v>
+        <v>116.19</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1465,7 +1336,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2556.9857</v>
+        <v>111.9314</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1473,22 +1344,22 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.83</v>
+        <v>-1.26</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2949.97</v>
+        <v>118.87</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1371,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1519,13 +1390,13 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>11475</v>
+        <v>5499</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>11005</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>-4.1</v>
+        <v>5519.5</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.37</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1533,7 +1404,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>10569.1429</v>
+        <v>5265.5714</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1541,17 +1412,17 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.89</v>
+        <v>-4.24</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>11970.43</v>
+        <v>5954.25</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -1568,7 +1439,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1583,17 +1454,17 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>709</v>
+        <v>2744.3</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>665.7</v>
+        <v>2654.2</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-6.11</v>
+        <v>-3.28</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1601,7 +1472,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>643.1072</v>
+        <v>2556.9857</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1609,22 +1480,22 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.39</v>
+        <v>3.66</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-9.289999999999999</v>
+        <v>-6.83</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>749.16</v>
+        <v>2949.97</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1636,143 +1507,288 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>11005</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>10569.1429</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>11970.43</v>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>709</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>643.1072</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>749.16</v>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F23" s="4" t="n">
         <v>284.85</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>263.3</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H23" s="6" t="n">
         <v>-7.57</v>
       </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="n">
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
         <v>255.5857</v>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L23" s="4" t="n">
         <v>2.93</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="M23" s="4" t="n">
         <v>-10.27</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <v>297.98</v>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
           <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
+    <mergeCell ref="A5:P5"/>
     <mergeCell ref="A28:P28"/>
     <mergeCell ref="A32:P32"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A27:P27"/>
     <mergeCell ref="A31:P31"/>
+    <mergeCell ref="A34:P34"/>
+    <mergeCell ref="A35:P35"/>
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A30:P30"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A26:P26"/>
     <mergeCell ref="A29:P29"/>
-    <mergeCell ref="A25:P25"/>
-    <mergeCell ref="A24:P24"/>
+    <mergeCell ref="A33:P33"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,14 +508,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>16 investable · NEW 0 · ACTIVE+ 10 · ACTIVE 6   ·   R2 8 · MOMENTUM 0 · R1 8 (advisory)</t>
+          <t>18 investable · NEW 2 · ACTIVE+ 10 · ACTIVE 6   ·   R2 10 · MOMENTUM 0 · R1 8 (advisory)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 16 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.36% from entry, worst single -10.78%</t>
+          <t>🛡 DOWNSIDE · 18 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.25% from entry, worst single -10.57%</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 228 scored · 16 already in CURRENT · biggest blocker: model disagreement (198) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -633,22 +633,22 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>553.3</v>
+        <v>117.05</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>591.25</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>6.86</v>
+        <v>117.05</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>570.8357</v>
+        <v>113.8</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.17</v>
+        <v>-2.78</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>587.67</v>
+        <v>121.93</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20260806-03d0a7</t>
+          <t>IND-R2-IEX-20260908-d0ae28</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -701,22 +701,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>452.35</v>
+        <v>233.86</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>419.35</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>-7.3</v>
+        <v>233.86</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>403.5857</v>
+        <v>226.5271</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -732,22 +732,22 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.76</v>
+        <v>3.14</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-10.78</v>
+        <v>-3.14</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>477.49</v>
+        <v>244.86</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>397</v>
+        <v>553.3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>421.75</v>
+        <v>591.25</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6.23</v>
+        <v>6.86</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>386.4571</v>
+        <v>565.6214</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>8.369999999999999</v>
+        <v>4.33</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.66</v>
+        <v>2.23</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>412.81</v>
+        <v>587.67</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>389.85</v>
+        <v>452.35</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>410.05</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>5.18</v>
+        <v>419.35</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-7.3</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>378.3286</v>
+        <v>404.55</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.74</v>
+        <v>3.53</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.96</v>
+        <v>-10.57</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>407.13</v>
+        <v>477.49</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>417.6</v>
+        <v>397</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>421.2</v>
+        <v>421.75</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.86</v>
+        <v>6.23</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>407.3714</v>
+        <v>386.4571</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -936,17 +936,17 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.28</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.45</v>
+        <v>-2.66</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>432.94</v>
+        <v>412.81</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -978,17 +978,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>187.46</v>
+        <v>389.85</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>185.6</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>-0.99</v>
+        <v>410.05</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>5.18</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>181.8114</v>
+        <v>378.3286</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1004,17 +1004,17 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.04</v>
+        <v>7.74</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.01</v>
+        <v>-2.96</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>195.93</v>
+        <v>407.13</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1413.5</v>
+        <v>417.6</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1390</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>-1.66</v>
+        <v>421.2</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.86</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1382.3857</v>
+        <v>407.3714</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1072,17 +1072,17 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.55</v>
+        <v>3.28</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.2</v>
+        <v>-2.45</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1460.17</v>
+        <v>432.94</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1449.5</v>
+        <v>187.46</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1416.3</v>
+        <v>185.6</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-2.29</v>
+        <v>-0.99</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1412.0571</v>
+        <v>181.8114</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1140,17 +1140,17 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3</v>
+        <v>2.04</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.58</v>
+        <v>-3.01</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1505.66</v>
+        <v>195.93</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>239.45</v>
+        <v>1413.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>233.47</v>
+        <v>1390</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-2.5</v>
+        <v>-1.66</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>232.2186</v>
+        <v>1382.3857</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1208,17 +1208,17 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.02</v>
+        <v>-2.2</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>250.3</v>
+        <v>1460.17</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1191</v>
+        <v>1449.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1151.9</v>
+        <v>1416.3</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-3.28</v>
+        <v>-2.29</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1149.2286</v>
+        <v>1412.0571</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1276,17 +1276,17 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.51</v>
+        <v>-2.58</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1253.66</v>
+        <v>1505.66</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -1303,32 +1303,32 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>113.36</v>
+        <v>239.45</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>116.19</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>2.5</v>
+        <v>233.47</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-2.5</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>111.9314</v>
+        <v>232.2186</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1344,22 +1344,22 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.67</v>
+        <v>0.54</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.26</v>
+        <v>-3.02</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>118.87</v>
+        <v>250.3</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1371,32 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5499</v>
+        <v>1191</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5519.5</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0.37</v>
+        <v>1151.9</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-3.28</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>5265.5714</v>
+        <v>1149.2286</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1412,22 +1412,22 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.6</v>
+        <v>0.23</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.24</v>
+        <v>-3.51</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>5954.25</v>
+        <v>1253.66</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2744.3</v>
+        <v>113.36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2654.2</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>-3.28</v>
+        <v>116.19</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2556.9857</v>
+        <v>112.5514</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1480,22 +1480,22 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.66</v>
+        <v>3.13</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.83</v>
+        <v>-0.71</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2949.97</v>
+        <v>118.87</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>11475</v>
+        <v>5499</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>11005</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>-4.1</v>
+        <v>5519.5</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.37</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>10569.1429</v>
+        <v>5251.9286</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1548,17 +1548,17 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.96</v>
+        <v>4.85</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.89</v>
+        <v>-4.49</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>11970.43</v>
+        <v>5954.25</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>709</v>
+        <v>2744.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>665.7</v>
+        <v>2654.2</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-6.11</v>
+        <v>-3.28</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>643.1072</v>
+        <v>2542.2</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -1616,22 +1616,22 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.39</v>
+        <v>4.22</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-9.289999999999999</v>
+        <v>-7.36</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>749.16</v>
+        <v>2949.97</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1643,131 +1643,267 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>11005</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>10630.4286</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>11970.43</v>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>709</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>639.9857</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>-9.73</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>749.16</v>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F25" s="4" t="n">
         <v>284.85</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>263.3</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H25" s="6" t="n">
         <v>-7.57</v>
       </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>255.5857</v>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>255.8714</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L23" s="4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>-10.27</v>
-      </c>
-      <c r="N23" s="4" t="n">
+      <c r="L25" s="4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>-10.17</v>
+      </c>
+      <c r="N25" s="4" t="n">
         <v>297.98</v>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -1778,15 +1914,15 @@
     <mergeCell ref="A5:P5"/>
     <mergeCell ref="A28:P28"/>
     <mergeCell ref="A32:P32"/>
+    <mergeCell ref="A36:P36"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A27:P27"/>
+    <mergeCell ref="A37:P37"/>
     <mergeCell ref="A31:P31"/>
     <mergeCell ref="A34:P34"/>
     <mergeCell ref="A35:P35"/>
     <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A3:P3"/>
     <mergeCell ref="A30:P30"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A26:P26"/>
     <mergeCell ref="A29:P29"/>
     <mergeCell ref="A33:P33"/>
     <mergeCell ref="A2:P2"/>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -1937,23 +1937,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1990,60 +1991,65 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Realized P&amp;L %</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Holding Days</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Entry Confidence %</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Exit Trigger</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2062,52 +2068,57 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>381.6</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>363.5</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>-4.74</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="J5" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 369.75 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>IND-R1-TATAPOWER-20260804-29907f</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -2126,52 +2137,57 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>454.85</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>454.85</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>454.85</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+15.5pp)</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>IND-R2-SUNTV-20260908-c6e7dc</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -2190,52 +2206,57 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>1048.7</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>1004.2</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>-4.24</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 1011.5999 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>IND-R1-SBIN-20260821-b637f4</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -2254,52 +2275,57 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>1642.5</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>1580.8</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>-3.76</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="J8" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 1594.6857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -2318,52 +2344,57 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>289</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>289</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+19.4pp)</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>IND-R2-PETRONET-20260908-f20701</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -2382,52 +2413,57 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>2410</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>2106.2</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="6" t="n">
         <v>-12.61</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 2314.8285 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>IND-R1-LUPIN-20260805-71abab</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -2446,52 +2482,57 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>507.9</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>473</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>-6.87</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 493.3286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>IND-R1-IRCTC-20260804-afbb8f</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -2510,52 +2551,57 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>2064.9</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>1964.3</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="6" t="n">
         <v>-4.87</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 1990.457 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -2574,52 +2620,57 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>385.15</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>374.1</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="6" t="n">
         <v>-2.87</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 377.5071 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>IND-R1-DABUR-20260828-be7819</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -2638,52 +2689,57 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>5454.5</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>5027</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="6" t="n">
         <v>-7.84</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="J14" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 5283.7143 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>IND-R1-BRITANNIA-20260804-3de31c</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -2702,52 +2758,57 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>414.35</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>414.35</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>414.35</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+18.2pp)</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>IND-R2-RBLBANK-20260907-a63a75</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -2766,52 +2827,57 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>391.3</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>415.35</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>6.15</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="J16" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+17.1pp)</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -2830,52 +2896,57 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>177.09</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>177.09</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0</v>
+        <v>177.09</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
           <t>Retired-runner cleanup · producer guard added 2026-09-02 · t</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>IND-R1-WIPRO-20260902-25d63c</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>registry:advisory</t>
         </is>
@@ -2894,52 +2965,57 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>2891.8</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>2891.8</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0</v>
+        <v>2891.8</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+57.0pp)</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ADANIENT-20260902-51452a</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -2958,52 +3034,57 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>347.25</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>326.5</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="6" t="n">
         <v>-5.98</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="J19" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Historical reconciliation</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
           <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>IND-R1-NTPC-20260804-b96a36</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>registry:advisory</t>
         </is>
@@ -3022,52 +3103,57 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>2383.9</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>2160.2</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="6" t="n">
         <v>-9.380000000000001</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="J20" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+13.0pp)</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -3086,52 +3172,57 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>398.8</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>398.8</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0</v>
+        <v>398.8</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+52.9pp)</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ABCAPITAL-20260831-d36452</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -3150,52 +3241,57 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>1955.3</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>1912</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="6" t="n">
         <v>-2.21</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="J22" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Historical reconciliation</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
           <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>registry:advisory</t>
         </is>
@@ -3214,52 +3310,57 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>268.15</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>-7.21</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="J23" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Historical reconciliation</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
           <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>IND-R1-ITC-20260805-3cdd2a</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>registry:advisory</t>
         </is>
@@ -3278,52 +3379,57 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>415.15</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>402.55</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>-3.04</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="J24" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+14.3pp)</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -3342,52 +3448,57 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>283.4</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>264.9</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="6" t="n">
         <v>-6.53</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="J25" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Historical reconciliation</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
           <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>IND-R1-POWERGRID-20260805-b39825</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>registry:advisory</t>
         </is>
@@ -3406,52 +3517,57 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>847.5</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>847.5</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0</v>
+        <v>847.5</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+56.7pp)</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>IND-R2-MARICO-20260826-1c5a1c</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -3470,52 +3586,57 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>1702.7</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>1702.7</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0</v>
+        <v>1702.7</v>
       </c>
       <c r="I27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+57.6pp)</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>IND-R2-TATACOMM-20260825-e3fb82</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -3534,52 +3655,57 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>244.55</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>244.55</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0</v>
+        <v>244.55</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+10.1pp)</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>IND-R2-JIOFIN-20260824-89850d</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -3598,52 +3724,57 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>1114.2</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>1114.2</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0</v>
+        <v>1114.2</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+14.5pp)</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>IND-R2-MGL-20260821-142d93</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -3662,52 +3793,57 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>402.8</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>402.8</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0</v>
+        <v>402.8</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+13.3pp)</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -3726,52 +3862,57 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>8693</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>8693</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0</v>
+        <v>8693</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+61.4pp)</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -3790,52 +3931,57 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>174.9</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>174.9</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
+        <v>174.9</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +11.8pp alpha</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>IND-R2-SAIL-20260820-80f37d</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -3854,52 +4000,57 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>5220</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>5220</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0</v>
+        <v>5220</v>
       </c>
       <c r="I33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +60.0pp alpha</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>IND-R2-INDIGO-20260818-ebf1a4</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -3918,52 +4069,57 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>129.2</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>124.4</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="6" t="n">
         <v>-3.72</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="J34" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +12.2pp alpha</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -3982,52 +4138,57 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>552.4</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>558</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="I35" s="5" t="n">
         <v>1.01</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="J35" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +14.7pp alpha</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4046,52 +4207,57 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>377</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>387.55</v>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="I36" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="J36" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +9.8pp alpha</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4110,52 +4276,57 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>1384</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>1327.6</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="6" t="n">
         <v>-4.08</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="J37" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +56.7pp alpha</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4174,52 +4345,57 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>2439.4</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>2361</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="6" t="n">
         <v>-3.21</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="J38" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +6.7pp alpha</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4238,52 +4414,57 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>3940</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>3940</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0</v>
+        <v>3940</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +7.5pp alpha</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -4302,52 +4483,57 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>11600</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>11828</v>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="I40" s="5" t="n">
         <v>1.97</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="J40" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +6.6pp alpha</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4366,52 +4552,57 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>1779.2</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>1779.2</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0</v>
+        <v>1779.2</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +8.1pp alpha</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -4430,52 +4621,57 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>181.14</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>181.14</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0</v>
+        <v>181.14</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
           <t>→ TCS.NS · +9.4pp alpha</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -4494,52 +4690,57 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>4924</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>4924</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0</v>
+        <v>4924</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
           <t>→ TCS.NS · +60.1pp alpha</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>IND-R2-TORNTPHARM-20260810-23303f</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -4558,52 +4759,57 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>129</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>129</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
           <t>→ TCS.NS · +6.5pp alpha</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>IND-R2-CANBK-20260810-788da8</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -4622,52 +4828,57 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>7454.5</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>7095</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="6" t="n">
         <v>-4.82</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="J45" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
           <t>→ TCS.NS · +62.1pp alpha</t>
         </is>
       </c>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4686,52 +4897,57 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>1327.7</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>1285</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="I46" s="6" t="n">
         <v>-3.22</v>
       </c>
-      <c r="I46" s="4" t="n">
+      <c r="J46" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +64.8pp alpha</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4750,52 +4966,57 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>1595</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>1584.8</v>
       </c>
-      <c r="H47" s="6" t="n">
+      <c r="I47" s="6" t="n">
         <v>-0.64</v>
       </c>
-      <c r="I47" s="4" t="n">
+      <c r="J47" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +62.5pp alpha</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4814,52 +5035,57 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>442.8</v>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="I48" s="6" t="n">
         <v>-1.6</v>
       </c>
-      <c r="I48" s="4" t="n">
+      <c r="J48" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +10.3pp alpha</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4878,52 +5104,57 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>845</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>889.5</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="I49" s="5" t="n">
         <v>5.27</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="J49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +7.4pp alpha</t>
         </is>
       </c>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="N49" s="4" t="inlineStr">
         <is>
           <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr">
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -4942,52 +5173,57 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>471.2</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>473.3</v>
       </c>
-      <c r="H50" s="5" t="n">
+      <c r="I50" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="I50" s="4" t="n">
+      <c r="J50" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +60.7pp alpha</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="N50" s="4" t="inlineStr">
         <is>
           <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -5006,52 +5242,57 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>6793.5</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>6774</v>
       </c>
-      <c r="H51" s="6" t="n">
+      <c r="I51" s="6" t="n">
         <v>-0.29</v>
       </c>
-      <c r="I51" s="4" t="n">
+      <c r="J51" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +8.0pp alpha</t>
         </is>
       </c>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -5070,52 +5311,57 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>268.5</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>278.8</v>
       </c>
-      <c r="H52" s="5" t="n">
+      <c r="I52" s="5" t="n">
         <v>3.84</v>
       </c>
-      <c r="I52" s="4" t="n">
+      <c r="J52" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +11.6pp alpha</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -5134,52 +5380,57 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>1167.5</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>1177</v>
       </c>
-      <c r="H53" s="5" t="n">
+      <c r="I53" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="I53" s="4" t="n">
+      <c r="J53" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +11.7pp alpha</t>
         </is>
       </c>
-      <c r="M53" s="4" t="inlineStr">
+      <c r="N53" s="4" t="inlineStr">
         <is>
           <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr">
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -5198,52 +5449,57 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>5470.5</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>5651.5</v>
       </c>
-      <c r="H54" s="5" t="n">
+      <c r="I54" s="5" t="n">
         <v>3.31</v>
       </c>
-      <c r="I54" s="4" t="n">
+      <c r="J54" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +10.6pp alpha</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="N54" s="4" t="inlineStr">
         <is>
           <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -5262,52 +5518,57 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>1363.6</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>1351.3</v>
       </c>
-      <c r="H55" s="6" t="n">
+      <c r="I55" s="6" t="n">
         <v>-0.9</v>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="J55" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +7.8pp alpha</t>
         </is>
       </c>
-      <c r="M55" s="4" t="inlineStr">
+      <c r="N55" s="4" t="inlineStr">
         <is>
           <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
-      <c r="N55" s="4" t="inlineStr">
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -5326,52 +5587,57 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>2195</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <v>2182</v>
       </c>
-      <c r="H56" s="6" t="n">
+      <c r="I56" s="6" t="n">
         <v>-0.59</v>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="J56" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
           <t>→ GNFC.NS · +59.7pp alpha</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="N56" s="4" t="inlineStr">
         <is>
           <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -5390,52 +5656,57 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>567.3</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>567.3</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>0</v>
+        <v>567.3</v>
       </c>
       <c r="I57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
           <t>Rotation → LUPIN.NS (+52.0pp)</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="N57" s="4" t="inlineStr">
         <is>
           <t>IND-R2-JSWENERGY-20260804-1210a0</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -5454,52 +5725,57 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>939.95</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>939.95</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>0</v>
+        <v>939.95</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
           <t>Rotation → LUPIN.NS (+51.8pp)</t>
         </is>
       </c>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="N58" s="4" t="inlineStr">
         <is>
           <t>IND-R2-FORTIS-20260804-6a4e4f</t>
         </is>
       </c>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -5518,52 +5794,57 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>425.05</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>425.05</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>0</v>
+        <v>425.05</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
           <t>Rotation → LUPIN.NS (+51.8pp)</t>
         </is>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="N59" s="4" t="inlineStr">
         <is>
           <t>IND-R2-BIOCON-20260804-954a24</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="O59" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -5611,17 +5892,25 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Sector · the company's CURRENT classification from the canonical sector cache, not its sector as of the exit date. No point-in-time sector history exists, so this column describes the company today and must not be read as evidence about what the sector was when the trade was live. NOT_AVAILABLE means the canonical source has no entry · it is never guessed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A67:N67"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A62:N62"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A65:N65"/>
-    <mergeCell ref="A63:N63"/>
-    <mergeCell ref="A66:N66"/>
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="10">
+    <mergeCell ref="A65:O65"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A63:O63"/>
+    <mergeCell ref="A64:O64"/>
+    <mergeCell ref="A68:O68"/>
+    <mergeCell ref="A66:O66"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A67:O67"/>
+    <mergeCell ref="A62:O62"/>
+    <mergeCell ref="A3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,17 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -533,6 +544,13 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>🤖 R3 = RESEARCH / SHADOW INTELLIGENCE · DOES NOT CHANGE R2 ACTION · 10 candidate(s) evaluated · every specialist is currently unvalidated, so every decision is ABSTAIN and every probability is withheld rather than guessed</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -614,6 +632,61 @@
           <t>Reason</t>
         </is>
       </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Decision</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Evidence</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Risk</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Fundamental</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Statistical</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Temporal</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Sector</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Uncertainty</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Reason</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>R3 As-of</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Model</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -682,6 +755,61 @@
           <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -750,6 +878,61 @@
           <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -818,6 +1001,61 @@
           <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -886,6 +1124,61 @@
           <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -954,6 +1247,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1022,6 +1370,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1090,6 +1493,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1158,6 +1616,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1226,6 +1739,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1294,6 +1862,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1362,6 +1985,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1430,6 +2108,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1498,6 +2231,61 @@
           <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X20" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y20" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA20" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1566,6 +2354,61 @@
           <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X21" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y21" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA21" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1634,6 +2477,61 @@
           <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X22" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y22" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA22" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1702,6 +2600,61 @@
           <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y23" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA23" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1770,6 +2723,61 @@
           <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X24" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y24" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA24" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1838,94 +2846,198 @@
           <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X25" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y25" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA25" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>R3 columns are RESEARCH / SHADOW INTELLIGENCE. They describe an R2 candidate and never change one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>R3 Decision · TAKE / AVOID / ABSTAIN. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate. ABSTAIN is R3 stating that it does not know · it is not a neutral default and not a placeholder.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>R3 probabilities are deliberately absent rather than zero. An unvalidated model reporting 0.5 is indistinguishable, months later, from a validated one reporting 0.5.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>R3 specialist states · NOT_VALIDATED (branch resolved, no usable model) · INSUFFICIENT_SUBSTRATE (data cannot support the claim) · NOT_AVAILABLE_AT_ASOF (input did not exist on this date) · BLOCKED (no substrate at all) · DESCRIPTIVE_ONLY (real information, not predictive).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>NOT_APPLICABLE on an R1 row is correct · R3 evaluates R2 candidates only, and R1 is retired advisory.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>R3 can only ever become actionable through explicit authorisation after out-of-sample and incremental-value evidence. It cannot promote itself.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A5:P5"/>
-    <mergeCell ref="A28:P28"/>
-    <mergeCell ref="A32:P32"/>
-    <mergeCell ref="A36:P36"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A31:P31"/>
-    <mergeCell ref="A34:P34"/>
-    <mergeCell ref="A35:P35"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A30:P30"/>
-    <mergeCell ref="A29:P29"/>
-    <mergeCell ref="A33:P33"/>
-    <mergeCell ref="A2:P2"/>
+  <mergeCells count="22">
+    <mergeCell ref="A6:AA6"/>
+    <mergeCell ref="A41:AA41"/>
+    <mergeCell ref="A37:AA37"/>
+    <mergeCell ref="A3:AA3"/>
+    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="A42:AA42"/>
+    <mergeCell ref="A33:AA33"/>
+    <mergeCell ref="A5:AA5"/>
+    <mergeCell ref="A32:AA32"/>
+    <mergeCell ref="A35:AA35"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="A29:AA29"/>
+    <mergeCell ref="A43:AA43"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="A28:AA28"/>
+    <mergeCell ref="A31:AA31"/>
+    <mergeCell ref="A34:AA34"/>
+    <mergeCell ref="A40:AA40"/>
+    <mergeCell ref="A30:AA30"/>
+    <mergeCell ref="A39:AA39"/>
+    <mergeCell ref="A36:AA36"/>
+    <mergeCell ref="A1:AA1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -533,7 +533,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 8 position(s) left CURRENT on a STOP BREACH (R1 8 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>⚠ lifecycle dataset is dated 2026-09-08, not this report's as-of · rerun the pipeline</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 = RESEARCH / SHADOW INTELLIGENCE · DOES NOT CHANGE R2 ACTION · 10 candidate(s) evaluated · every specialist is currently unvalidated, so every decision is ABSTAIN and every probability is withheld rather than guessed</t>
+          <t>🤖 R3 = RESEARCH / SHADOW INTELLIGENCE · DOES NOT CHANGE R2 ACTION · 0 candidate(s) evaluated · every specialist is currently unvalidated, so every decision is ABSTAIN and every probability is withheld rather than guessed</t>
         </is>
       </c>
     </row>
@@ -757,57 +757,57 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -880,57 +880,57 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1003,57 +1003,57 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA10" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1126,57 +1126,57 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y11" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA11" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2233,57 +2233,57 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X20" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA20" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2356,57 +2356,57 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X21" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y21" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA21" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2479,57 +2479,57 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X22" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA22" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2602,57 +2602,57 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U23" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X23" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y23" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA23" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2725,57 +2725,57 @@
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA24" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2848,57 +2848,57 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T25" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U25" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X25" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y25" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA25" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -496,58 +496,48 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="34" customWidth="1" min="24" max="24"/>
-    <col width="60" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · 2026-09-08</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · 2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>18 investable · NEW 2 · ACTIVE+ 10 · ACTIVE 6   ·   R2 10 · MOMENTUM 0 · R1 8 (advisory)</t>
+          <t>48 investable · NEW 33 · ACTIVE+ 9 · ACTIVE 6   ·   R2 43 · MOMENTUM 0 · R1 5 (advisory)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 18 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.25% from entry, worst single -10.57%</t>
+          <t>🛡 DOWNSIDE · 48 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.30% from entry, worst single -11.32%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>⚠ lifecycle dataset is dated 2026-09-08, not this report's as-of · rerun the pipeline</t>
+          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=33 · 228 scored · 47 already in CURRENT · biggest blocker: model disagreement (171) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 = RESEARCH / SHADOW INTELLIGENCE · DOES NOT CHANGE R2 ACTION · 0 candidate(s) evaluated · every specialist is currently unvalidated, so every decision is ABSTAIN and every probability is withheld rather than guessed</t>
+          <t>🤖 R3 SHADOW INTELLIGENCE — RESEARCH ONLY. R3 reviews R2 candidates but does NOT change R2 Action, Confidence, Stop or Position. ABSTAIN means R3 has no validated opinion yet — it is NOT Hold, Buy, Avoid, or a 50/50 probability. A future AVOID is a research annotation and never implies an R2 EXIT. R3 can become actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 43 candidate(s) evaluated today.</t>
         </is>
       </c>
     </row>
@@ -634,57 +624,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>R3 Decision</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Evidence</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Risk</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Fundamental</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Statistical</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Temporal</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Sector</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Uncertainty</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Reason</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>R3 As-of</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Model</t>
+          <t>R3 SHADOW</t>
         </is>
       </c>
     </row>
@@ -696,7 +636,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -711,25 +651,23 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>117.05</v>
+        <v>25455</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>117.05</v>
+        <v>25455</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I8" s="4" t="n">
+        <v>31.3</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>113.8</v>
+        <v>24667.8571</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -737,77 +675,27 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.78</v>
+        <v>-3.09</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>121.93</v>
+        <v>26635.71</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260908-d0ae28</t>
+          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -819,7 +707,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -834,25 +722,23 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>233.86</v>
+        <v>5163.5</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>233.86</v>
+        <v>5163.5</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I9" s="4" t="n">
+        <v>31.3</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>226.5271</v>
+        <v>5015.7143</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -860,17 +746,17 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.14</v>
+        <v>-2.86</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>244.86</v>
+        <v>5385.18</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
+          <t>IND-R2-ALKEM-20260909-517913</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -880,57 +766,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -942,7 +778,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -952,30 +788,28 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>553.3</v>
+        <v>292.9</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>591.25</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>292.9</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>34.3</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>565.6214</v>
+        <v>277.55</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -983,77 +817,27 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.33</v>
+        <v>5.24</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.23</v>
+        <v>-5.24</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>587.67</v>
+        <v>315.92</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20260806-03d0a7</t>
+          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -1065,7 +849,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1075,30 +859,28 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>452.35</v>
+        <v>6291</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>419.35</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6291</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>404.55</v>
+        <v>6059.4286</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -1106,77 +888,27 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-10.57</v>
+        <v>-3.68</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>477.49</v>
+        <v>6638.36</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+          <t>IND-R2-ATUL-20260909-2f64b0</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -1188,40 +920,38 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>397</v>
+        <v>1244.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>421.75</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1244.4</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>32.9</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>386.4571</v>
+        <v>1211.2286</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -1229,77 +959,27 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.369999999999999</v>
+        <v>2.67</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.66</v>
+        <v>-2.67</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>412.81</v>
+        <v>1294.16</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-AXISBANK-20260909-3abb74</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -1311,40 +991,38 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>389.85</v>
+        <v>172.76</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>410.05</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>172.76</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>30.1</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>378.3286</v>
+        <v>164.7914</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1352,77 +1030,27 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7.74</v>
+        <v>4.61</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.96</v>
+        <v>-4.61</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>407.13</v>
+        <v>184.71</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -1439,35 +1067,33 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>417.6</v>
+        <v>434.2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>421.2</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>434.2</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>407.3714</v>
+        <v>419.5786</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1475,77 +1101,27 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.45</v>
+        <v>-3.37</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>432.94</v>
+        <v>456.13</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R2-COALINDIA-20260909-3c298a</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -1557,40 +1133,38 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>187.46</v>
+        <v>370</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>185.6</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>370</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>31.2</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>181.8114</v>
+        <v>351.5286</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1598,77 +1172,27 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.04</v>
+        <v>4.99</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.01</v>
+        <v>-4.99</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>195.93</v>
+        <v>397.71</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -1680,40 +1204,38 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1413.5</v>
+        <v>2410.1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1390</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2410.1</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1382.3857</v>
+        <v>2296.8716</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1721,77 +1243,27 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.55</v>
+        <v>4.7</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.2</v>
+        <v>-4.7</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1460.17</v>
+        <v>2579.94</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R2-GLENMARK-20260909-ef0373</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -1803,40 +1275,38 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1449.5</v>
+        <v>694.35</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1416.3</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>694.35</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>34.8</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1412.0571</v>
+        <v>671.25</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1844,77 +1314,27 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.3</v>
+        <v>3.33</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.58</v>
+        <v>-3.33</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1505.66</v>
+        <v>729</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -1926,40 +1346,38 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>239.45</v>
+        <v>1952</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>233.47</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1952</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>31.2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>232.2186</v>
+        <v>1906.3286</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1967,77 +1385,27 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.54</v>
+        <v>2.34</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.02</v>
+        <v>-2.34</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>250.3</v>
+        <v>2020.51</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -2049,40 +1417,38 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1191</v>
+        <v>154.28</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1151.9</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>-3.28</v>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>154.28</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1149.2286</v>
+        <v>148.0157</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -2090,77 +1456,27 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.23</v>
+        <v>4.06</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.51</v>
+        <v>-4.06</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1253.66</v>
+        <v>163.68</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
+          <t>IND-R2-IGL-20260909-938c43</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -2172,7 +1488,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2182,30 +1498,28 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>113.36</v>
+        <v>860.45</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>116.19</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>860.45</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>35</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>112.5514</v>
+        <v>831.6070999999999</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -2213,77 +1527,27 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.13</v>
+        <v>3.35</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.71</v>
+        <v>-3.35</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>118.87</v>
+        <v>903.71</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-INDIANB-20260909-3ab469</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -2295,7 +1559,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2305,30 +1569,28 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5499</v>
+        <v>1038.3</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5519.5</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1038.3</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>38.3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5251.9286</v>
+        <v>983.3143</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -2336,77 +1598,27 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.85</v>
+        <v>5.3</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.49</v>
+        <v>-5.3</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5954.25</v>
+        <v>1120.78</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -2418,7 +1630,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2428,30 +1640,28 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2744.3</v>
+        <v>1949</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2654.2</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>-3.28</v>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1949</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2542.2</v>
+        <v>1878.6</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -2459,77 +1669,27 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.22</v>
+        <v>3.61</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-7.36</v>
+        <v>-3.61</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2949.97</v>
+        <v>2054.6</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y22" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -2541,7 +1701,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2551,30 +1711,28 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>11475</v>
+        <v>19.11</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>11005</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>19.11</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>10630.4286</v>
+        <v>18.3757</v>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
@@ -2582,77 +1740,27 @@
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.36</v>
+        <v>-3.84</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>11970.43</v>
+        <v>20.21</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+          <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y23" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -2664,7 +1772,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2674,30 +1782,28 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>709</v>
+        <v>470.4</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>665.7</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>-6.11</v>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>470.4</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>28.4</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>639.9857</v>
+        <v>459.6357</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
@@ -2705,77 +1811,27 @@
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.86</v>
+        <v>2.29</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-9.73</v>
+        <v>-2.29</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>749.16</v>
+        <v>486.55</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+          <t>IND-R2-IRCTC-20260909-add681</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y24" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ABSTAIN · R3 not yet validated</t>
         </is>
       </c>
     </row>
@@ -2787,257 +1843,2357 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>12603</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>12603</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>12160.1429</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>13267.29</v>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-MARUTI-20260909-c59a94</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>3365.2</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>3365.2</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>3203.1143</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>3608.33</v>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>3134.7</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>3134.7</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>3019.7429</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>3307.14</v>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-MM-20260909-3a8a06</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2825</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>2825</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>2663.5858</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>3067.12</v>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>818.3</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>818.3</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>785.8786</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>866.9299999999999</v>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>366.9428</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>412.84</v>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1260</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>1201.0857</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>1348.37</v>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-NAUKRI-20260909-930931</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>273.3</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>273.3</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>262.5714</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>289.39</v>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>11644</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>11644</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>11094.7143</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>12467.93</v>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-OFSS-20260909-1e09a0</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>479.7</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>530.45</v>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-OIL-20260909-82436d</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>339.55</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>339.55</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>330.1714</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>353.62</v>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-PATANJALI-20260909-508e75</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>306.4143</v>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>329.25</v>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-RECLTD-20260909-84e6d1</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>187.94</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>187.94</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>178.5243</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>206.77</v>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1007.2</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1007.2</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>978.6572</v>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>1050.01</v>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-SBIN-20260909-a73231</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>2197.4</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>2197.4</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>2101.4713</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>2341.29</v>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-TCS-20260909-fb0a7f</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>260.9143</v>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>-5.12</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>296.13</v>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-VEDL-20260909-bbba1f</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>563.35</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>534.9285</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>587.67</v>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>117.05</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>117.14</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>114.0186</v>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>121.93</v>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-IEX-20260908-d0ae28</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>233.86</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>231.86</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>224.7686</v>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>244.86</v>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>452.35</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>415.8</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>-8.08</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>401.1571</v>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>-11.32</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>477.49</v>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>408.9</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>378.3286</v>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>N/A · R3 evaluates R2 candidates only</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>397</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>414.45</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>386.4571</v>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>412.81</v>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>N/A · R3 evaluates R2 candidates only</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>434.2</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>407.3714</v>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>432.94</v>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>N/A · R3 evaluates R2 candidates only</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>187.46</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>181.8114</v>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>195.93</v>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>N/A · R3 evaluates R2 candidates only</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>239.45</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>236.91</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>232.2186</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>250.3</v>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>N/A · R3 evaluates R2 candidates only</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>112.9343</v>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>118.87</v>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>5499</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>5442.5</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>5176.5</v>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>5954.25</v>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>2646.4</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>2533.3999</v>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>-7.69</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>2949.97</v>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="inlineStr">
+        <is>
+          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>11054</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>10682.7143</v>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>11970.43</v>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>709</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>663.3</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>642.3928</v>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>749.16</v>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+        </is>
+      </c>
+      <c r="P54" s="4" t="inlineStr">
+        <is>
+          <t>ROTATED_SAMEDAY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F55" s="4" t="n">
         <v>284.85</v>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>-7.57</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="G55" s="4" t="n">
+        <v>260.75</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>255.8714</v>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="J55" s="4" t="n">
+        <v>253.7214</v>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L25" s="4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>-10.17</v>
-      </c>
-      <c r="N25" s="4" t="n">
+      <c r="L55" s="4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>-10.93</v>
+      </c>
+      <c r="N55" s="4" t="n">
         <v>297.98</v>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y25" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>R3 columns are RESEARCH / SHADOW INTELLIGENCE. They describe an R2 candidate and never change one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>R3 Decision · TAKE / AVOID / ABSTAIN. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate. ABSTAIN is R3 stating that it does not know · it is not a neutral default and not a placeholder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>R3 probabilities are deliberately absent rather than zero. An unvalidated model reporting 0.5 is indistinguishable, months later, from a validated one reporting 0.5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>R3 specialist states · NOT_VALIDATED (branch resolved, no usable model) · INSUFFICIENT_SUBSTRATE (data cannot support the claim) · NOT_AVAILABLE_AT_ASOF (input did not exist on this date) · BLOCKED (no substrate at all) · DESCRIPTIVE_ONLY (real information, not predictive).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE on an R1 row is correct · R3 evaluates R2 candidates only, and R1 is retired advisory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>R3 can only ever become actionable through explicit authorisation after out-of-sample and incremental-value evidence. It cannot promote itself.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="P55" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN · R3 not yet validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A6:AA6"/>
-    <mergeCell ref="A41:AA41"/>
-    <mergeCell ref="A37:AA37"/>
-    <mergeCell ref="A3:AA3"/>
-    <mergeCell ref="A2:AA2"/>
-    <mergeCell ref="A42:AA42"/>
-    <mergeCell ref="A33:AA33"/>
-    <mergeCell ref="A5:AA5"/>
-    <mergeCell ref="A32:AA32"/>
-    <mergeCell ref="A35:AA35"/>
-    <mergeCell ref="A4:AA4"/>
-    <mergeCell ref="A29:AA29"/>
-    <mergeCell ref="A43:AA43"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="A28:AA28"/>
-    <mergeCell ref="A31:AA31"/>
-    <mergeCell ref="A34:AA34"/>
-    <mergeCell ref="A40:AA40"/>
-    <mergeCell ref="A30:AA30"/>
-    <mergeCell ref="A39:AA39"/>
-    <mergeCell ref="A36:AA36"/>
-    <mergeCell ref="A1:AA1"/>
+  <mergeCells count="21">
+    <mergeCell ref="A58:Q58"/>
+    <mergeCell ref="A67:Q67"/>
+    <mergeCell ref="A59:Q59"/>
+    <mergeCell ref="A64:Q64"/>
+    <mergeCell ref="A60:Q60"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A70:Q70"/>
+    <mergeCell ref="A69:Q69"/>
+    <mergeCell ref="A65:Q65"/>
+    <mergeCell ref="A66:Q66"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A71:Q71"/>
+    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A62:Q62"/>
+    <mergeCell ref="A72:Q72"/>
+    <mergeCell ref="A68:Q68"/>
+    <mergeCell ref="A63:Q63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3049,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3072,21 +4228,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · every closed position · 2026-09-08</t>
+          <t>AEGIS INDIA · EXIT HISTORY · every closed position · 2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>55 exits · R1 13 · R2 42   ·   R1 rows are ADVISORY and are excluded from production P&amp;L</t>
+          <t>58 exits · R1 16 · R2 42   ·   R1 rows are ADVISORY and are excluded from production P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🔴 8 of these are STOP-BREACH exits · the stop was passed and the position left CURRENT, but it is NOT sold · price and P&amp;L are today's MARK · avg -5.97% · worst -12.61%</t>
+          <t>🔴 11 of these are STOP-BREACH exits · the stop was passed and the position left CURRENT, but it is NOT sold · price and P&amp;L are today's MARK · avg -5.49% · worst -13.11%</t>
         </is>
       </c>
     </row>
@@ -3170,17 +4326,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3195,20 +4351,20 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>381.6</v>
+        <v>1191</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>363.5</v>
+        <v>1129.5</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-4.74</v>
+        <v>-5.16</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
@@ -3222,12 +4378,12 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 369.75 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1149.2286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATAPOWER-20260804-29907f</t>
+          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -3239,17 +4395,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3259,29 +4415,29 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>454.85</v>
+        <v>1449.5</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>454.85</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
+        <v>1391.1</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-4.03</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -3291,34 +4447,34 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+15.5pp)</t>
+          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260908-c6e7dc</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -3333,20 +4489,20 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1048.7</v>
+        <v>1413.5</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1004.2</v>
+        <v>1373.6</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-4.24</v>
+        <v>-2.82</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
@@ -3360,12 +4516,12 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1011.5999 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-SBIN-20260821-b637f4</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -3382,12 +4538,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -3406,13 +4562,13 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1642.5</v>
+        <v>381.6</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1580.8</v>
+        <v>369.35</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-3.76</v>
+        <v>-3.21</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>35</v>
@@ -3429,12 +4585,12 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1594.6857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 369.75 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
+          <t>IND-R1-TATAPOWER-20260804-29907f</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -3451,12 +4607,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -3475,10 +4631,10 @@
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>289</v>
+        <v>454.85</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>289</v>
+        <v>454.85</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>0</v>
@@ -3498,12 +4654,12 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+19.4pp)</t>
+          <t>Rotation → GNFC.NS (+15.5pp)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260908-f20701</t>
+          <t>IND-R2-SUNTV-20260908-c6e7dc</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -3520,12 +4676,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -3540,20 +4696,20 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2410</v>
+        <v>1048.7</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2106.2</v>
+        <v>1007.2</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-12.61</v>
+        <v>-3.96</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -3567,12 +4723,12 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 2314.8285 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1011.5999 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-LUPIN-20260805-71abab</t>
+          <t>IND-R1-SBIN-20260821-b637f4</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -3589,12 +4745,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3613,13 +4769,13 @@
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>507.9</v>
+        <v>1642.5</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>473</v>
+        <v>1577.1</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-6.87</v>
+        <v>-3.98</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>35</v>
@@ -3636,12 +4792,12 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 493.3286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1594.6857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-IRCTC-20260804-afbb8f</t>
+          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -3658,12 +4814,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -3673,29 +4829,29 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2064.9</v>
+        <v>289</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1964.3</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>-4.87</v>
+        <v>289</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -3705,17 +4861,17 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1990.457 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>Rotation → GNFC.NS (+19.4pp)</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
+          <t>IND-R2-PETRONET-20260908-f20701</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -3727,12 +4883,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3747,20 +4903,20 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>385.15</v>
+        <v>2410</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>374.1</v>
+        <v>2094</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-2.87</v>
+        <v>-13.11</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -3774,12 +4930,12 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 377.5071 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 2314.8285 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-DABUR-20260828-be7819</t>
+          <t>IND-R1-LUPIN-20260805-71abab</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -3796,12 +4952,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -3820,13 +4976,13 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5454.5</v>
+        <v>507.9</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5027</v>
+        <v>470.4</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-7.84</v>
+        <v>-7.38</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>35</v>
@@ -3843,12 +4999,12 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 5283.7143 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 493.3286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BRITANNIA-20260804-3de31c</t>
+          <t>IND-R1-IRCTC-20260804-afbb8f</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -3860,17 +5016,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -3880,29 +5036,29 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>414.35</v>
+        <v>2064.9</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>414.35</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0</v>
+        <v>1952</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-5.47</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -3912,34 +5068,34 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+18.2pp)</t>
+          <t>STOP BREACHED - stop 1990.457 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260907-a63a75</t>
+          <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3949,29 +5105,29 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>391.3</v>
+        <v>385.15</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>415.35</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>6.15</v>
+        <v>369.85</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-3.97</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -3981,34 +5137,34 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+17.1pp)</t>
+          <t>STOP BREACHED - stop 377.5071 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R1-DABUR-20260828-be7819</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -4023,24 +5179,24 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>177.09</v>
+        <v>5454.5</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>177.09</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0</v>
+        <v>5054.5</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-7.33</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -4050,34 +5206,34 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Retired-runner cleanup · producer guard added 2026-09-02 · t</t>
+          <t>STOP BREACHED - stop 5283.7143 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-WIPRO-20260902-25d63c</t>
+          <t>IND-R1-BRITANNIA-20260804-3de31c</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -4092,14 +5248,14 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2891.8</v>
+        <v>414.35</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2891.8</v>
+        <v>414.35</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -4119,12 +5275,12 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.0pp)</t>
+          <t>Rotation → GNFC.NS (+18.2pp)</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIENT-20260902-51452a</t>
+          <t>IND-R2-RBLBANK-20260907-a63a75</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -4136,17 +5292,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -4156,29 +5312,29 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>347.25</v>
+        <v>391.3</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>326.5</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>-5.98</v>
+        <v>415.35</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>6.15</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -4188,34 +5344,34 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
+          <t>Rotation → GNFC.NS (+17.1pp)</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-NTPC-20260804-b96a36</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -4225,29 +5381,29 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2383.9</v>
+        <v>177.09</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2160.2</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>-9.380000000000001</v>
+        <v>177.09</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -4257,34 +5413,34 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.0pp)</t>
+          <t>Retired-runner cleanup · producer guard added 2026-09-02 · t</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R1-WIPRO-20260902-25d63c</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -4299,14 +5455,14 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>398.8</v>
+        <v>2891.8</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>398.8</v>
+        <v>2891.8</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>0</v>
@@ -4326,12 +5482,12 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+52.9pp)</t>
+          <t>Rotation → GNFC.NS (+57.0pp)</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
+          <t>IND-R2-ADANIENT-20260902-51452a</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -4343,17 +5499,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -4372,16 +5528,16 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1955.3</v>
+        <v>347.25</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1912</v>
+        <v>326.5</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-2.21</v>
+        <v>-5.98</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -4400,7 +5556,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
+          <t>IND-R1-NTPC-20260804-b96a36</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -4412,17 +5568,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -4432,29 +5588,29 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>289</v>
+        <v>2383.9</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>268.15</v>
+        <v>2160.2</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-7.21</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -4464,34 +5620,34 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
+          <t>Rotation → GNFC.NS (+13.0pp)</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ITC-20260805-3cdd2a</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -4506,20 +5662,20 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>415.15</v>
+        <v>398.8</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>402.55</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>-3.04</v>
+        <v>398.8</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
@@ -4533,34 +5689,34 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.3pp)</t>
+          <t>Rotation → GNFC.NS (+52.9pp)</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -4575,20 +5731,20 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>283.4</v>
+        <v>1955.3</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>264.9</v>
+        <v>1912</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-6.53</v>
+        <v>-2.21</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -4607,7 +5763,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-POWERGRID-20260805-b39825</t>
+          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -4619,12 +5775,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -4639,29 +5795,29 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>847.5</v>
+        <v>289</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>847.5</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0</v>
+        <v>268.15</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>-7.21</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -4671,34 +5827,34 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+56.7pp)</t>
+          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARICO-20260826-1c5a1c</t>
+          <t>IND-R1-ITC-20260805-3cdd2a</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -4713,20 +5869,20 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1702.7</v>
+        <v>415.15</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1702.7</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>0</v>
+        <v>402.55</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>-3.04</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
@@ -4740,34 +5896,34 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.6pp)</t>
+          <t>Rotation → GNFC.NS (+14.3pp)</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -4777,29 +5933,29 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>244.55</v>
+        <v>283.4</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>244.55</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>0</v>
+        <v>264.9</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>-6.53</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -4809,34 +5965,34 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+10.1pp)</t>
+          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260824-89850d</t>
+          <t>IND-R1-POWERGRID-20260805-b39825</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -4851,14 +6007,14 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1114.2</v>
+        <v>847.5</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1114.2</v>
+        <v>847.5</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
@@ -4878,12 +6034,12 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.5pp)</t>
+          <t>Rotation → GNFC.NS (+56.7pp)</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260821-142d93</t>
+          <t>IND-R2-MARICO-20260826-1c5a1c</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -4895,17 +6051,17 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -4920,14 +6076,14 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>402.8</v>
+        <v>1702.7</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>402.8</v>
+        <v>1702.7</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>0</v>
@@ -4947,12 +6103,12 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.3pp)</t>
+          <t>Rotation → GNFC.NS (+57.6pp)</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
+          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -4964,17 +6120,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -4989,14 +6145,14 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8693</v>
+        <v>244.55</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8693</v>
+        <v>244.55</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>0</v>
@@ -5016,12 +6172,12 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+61.4pp)</t>
+          <t>Rotation → GNFC.NS (+10.1pp)</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
+          <t>IND-R2-JIOFIN-20260824-89850d</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -5033,17 +6189,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -5058,14 +6214,14 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>174.9</v>
+        <v>1114.2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>174.9</v>
+        <v>1114.2</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>0</v>
@@ -5075,7 +6231,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -5085,12 +6241,12 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.8pp alpha</t>
+          <t>Rotation → GNFC.NS (+14.5pp)</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260820-80f37d</t>
+          <t>IND-R2-MGL-20260821-142d93</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -5102,17 +6258,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -5127,14 +6283,14 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5220</v>
+        <v>402.8</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5220</v>
+        <v>402.8</v>
       </c>
       <c r="I33" s="4" t="n">
         <v>0</v>
@@ -5144,7 +6300,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -5154,12 +6310,12 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.0pp alpha</t>
+          <t>Rotation → GNFC.NS (+13.3pp)</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
+          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -5171,17 +6327,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -5196,24 +6352,24 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>129.2</v>
+        <v>8693</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>-3.72</v>
+        <v>8693</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -5223,29 +6379,29 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +12.2pp alpha</t>
+          <t>Rotation → GNFC.NS (+61.4pp)</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -5265,20 +6421,20 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>552.4</v>
+        <v>174.9</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>558</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>1.01</v>
+        <v>174.9</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -5292,34 +6448,34 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +14.7pp alpha</t>
+          <t>→ GNFC.NS · +11.8pp alpha</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-SAIL-20260820-80f37d</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -5334,20 +6490,20 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>377</v>
+        <v>5220</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>2.8</v>
+        <v>5220</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
@@ -5361,34 +6517,34 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +9.8pp alpha</t>
+          <t>→ GNFC.NS · +60.0pp alpha</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -5407,16 +6563,16 @@
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1384</v>
+        <v>129.2</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1327.6</v>
+        <v>124.4</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-4.08</v>
+        <v>-3.72</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
@@ -5430,12 +6586,12 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +56.7pp alpha</t>
+          <t>→ GNFC.NS · +12.2pp alpha</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -5447,17 +6603,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -5476,16 +6632,16 @@
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>2439.4</v>
+        <v>552.4</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2361</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>-3.21</v>
+        <v>558</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>1.01</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
@@ -5499,12 +6655,12 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.7pp alpha</t>
+          <t>→ GNFC.NS · +14.7pp alpha</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -5516,17 +6672,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -5541,20 +6697,20 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>3940</v>
+        <v>377</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>3940</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>0</v>
+        <v>387.55</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>2.8</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
@@ -5568,34 +6724,34 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.5pp alpha</t>
+          <t>→ GNFC.NS · +9.8pp alpha</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -5614,16 +6770,16 @@
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>11600</v>
+        <v>1384</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>11828</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>1.97</v>
+        <v>1327.6</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>-4.08</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
@@ -5637,12 +6793,12 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.6pp alpha</t>
+          <t>→ GNFC.NS · +56.7pp alpha</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -5654,17 +6810,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -5679,20 +6835,20 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1779.2</v>
+        <v>2439.4</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1779.2</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>0</v>
+        <v>2361</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>-3.21</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
@@ -5706,34 +6862,34 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.1pp alpha</t>
+          <t>→ GNFC.NS · +6.7pp alpha</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -5748,14 +6904,14 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>181.14</v>
+        <v>3940</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>181.14</v>
+        <v>3940</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>0</v>
@@ -5775,12 +6931,12 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +9.4pp alpha</t>
+          <t>→ GNFC.NS · +7.5pp alpha</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
+          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -5792,17 +6948,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -5817,20 +6973,20 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>4924</v>
+        <v>11600</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>4924</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>0</v>
+        <v>11828</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>1.97</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
@@ -5844,34 +7000,34 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +60.1pp alpha</t>
+          <t>→ GNFC.NS · +6.6pp alpha</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -5886,14 +7042,14 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>129</v>
+        <v>1779.2</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>129</v>
+        <v>1779.2</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>0</v>
@@ -5913,12 +7069,12 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +6.5pp alpha</t>
+          <t>→ GNFC.NS · +8.1pp alpha</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260810-788da8</t>
+          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -5935,12 +7091,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -5955,20 +7111,20 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>7454.5</v>
+        <v>181.14</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>7095</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>-4.82</v>
+        <v>181.14</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
@@ -5982,34 +7138,34 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +62.1pp alpha</t>
+          <t>→ TCS.NS · +9.4pp alpha</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -6024,20 +7180,20 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1327.7</v>
+        <v>4924</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1285</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>-3.22</v>
+        <v>4924</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
@@ -6051,34 +7207,34 @@
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +64.8pp alpha</t>
+          <t>→ TCS.NS · +60.1pp alpha</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
+          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -6093,20 +7249,20 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1595</v>
+        <v>129</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1584.8</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>-0.64</v>
+        <v>129</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
@@ -6120,34 +7276,34 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +62.5pp alpha</t>
+          <t>→ TCS.NS · +6.5pp alpha</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
+          <t>IND-R2-CANBK-20260810-788da8</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -6162,20 +7318,20 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>450</v>
+        <v>7454.5</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>442.8</v>
+        <v>7095</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-1.6</v>
+        <v>-4.82</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
@@ -6189,12 +7345,12 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.3pp alpha</t>
+          <t>→ TCS.NS · +62.1pp alpha</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -6211,12 +7367,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -6235,13 +7391,13 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>845</v>
+        <v>1327.7</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>889.5</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>5.27</v>
+        <v>1285</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>-3.22</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>2</v>
@@ -6258,12 +7414,12 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.4pp alpha</t>
+          <t>→ GNFC.NS · +64.8pp alpha</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -6280,12 +7436,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -6300,20 +7456,20 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>471.2</v>
+        <v>1595</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>0.45</v>
+        <v>1584.8</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>-0.64</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
@@ -6327,12 +7483,12 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.7pp alpha</t>
+          <t>→ GNFC.NS · +62.5pp alpha</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -6349,12 +7505,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -6373,13 +7529,13 @@
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>6793.5</v>
+        <v>450</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>6774</v>
+        <v>442.8</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.29</v>
+        <v>-1.6</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>2</v>
@@ -6396,12 +7552,12 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.0pp alpha</t>
+          <t>→ GNFC.NS · +10.3pp alpha</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -6413,17 +7569,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -6438,17 +7594,17 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>268.5</v>
+        <v>845</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>278.8</v>
+        <v>889.5</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>3.84</v>
+        <v>5.27</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>2</v>
@@ -6465,12 +7621,12 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.6pp alpha</t>
+          <t>→ GNFC.NS · +7.4pp alpha</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260804-563905</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -6482,42 +7638,42 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="G53" s="4" t="n">
-        <v>1167.5</v>
+        <v>471.2</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1177</v>
+        <v>473.3</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>1</v>
@@ -6534,12 +7690,12 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.7pp alpha</t>
+          <t>→ GNFC.NS · +60.7pp alpha</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -6551,17 +7707,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -6576,17 +7732,17 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>5470.5</v>
+        <v>6793.5</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>5651.5</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>3.31</v>
+        <v>6774</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>2</v>
@@ -6603,12 +7759,12 @@
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.6pp alpha</t>
+          <t>→ GNFC.NS · +8.0pp alpha</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -6625,12 +7781,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -6649,13 +7805,13 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1363.6</v>
+        <v>268.5</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1351.3</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>-0.9</v>
+        <v>278.8</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>3.84</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>2</v>
@@ -6672,12 +7828,12 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.8pp alpha</t>
+          <t>→ GNFC.NS · +11.6pp alpha</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
+          <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -6694,12 +7850,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -6718,13 +7874,13 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>2195</v>
+        <v>1167.5</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>-0.59</v>
+        <v>1177</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>1</v>
@@ -6741,12 +7897,12 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +59.7pp alpha</t>
+          <t>→ GNFC.NS · +11.7pp alpha</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -6758,49 +7914,49 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="G57" s="4" t="n">
-        <v>567.3</v>
+        <v>5470.5</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>567.3</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>0</v>
+        <v>5651.5</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>3.31</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Outperformance exit</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -6810,66 +7966,66 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+52.0pp)</t>
+          <t>→ GNFC.NS · +10.6pp alpha</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWENERGY-20260804-1210a0</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>FORTIS</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="G58" s="4" t="n">
-        <v>939.95</v>
+        <v>1363.6</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>939.95</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>0</v>
+        <v>1351.3</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>-0.9</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Outperformance exit</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -6879,149 +8035,356 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+          <t>→ GNFC.NS · +7.8pp alpha</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>2195</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>2182</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +59.7pp alpha</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>registry:production</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>567.3</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>567.3</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → LUPIN.NS (+52.0pp)</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-JSWENERGY-20260804-1210a0</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>registry:administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>939.95</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>939.95</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>registry:administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>BIOCON</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>425.05</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>425.05</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="I62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="4" t="n">
+      <c r="J62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>Rotation → LUPIN.NS (+51.8pp)</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>IND-R2-BIOCON-20260804-954a24</t>
         </is>
       </c>
-      <c r="O59" s="4" t="inlineStr">
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>Permanent record of every closed R1 / R2 / Momentum position, rendered from the canonical lifecycle dataset.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>Realized P&amp;L % · (Exit − Entry) / Entry · the trade's own result.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Source · registry:production (a real R2 trade) · registry:advisory (R1 · never counted in production P&amp;L) · registry:administrative (same-day or zero-delta bookkeeping · not a real trade) · lifecycle:stop-breach (price passed the stop · the row left CURRENT and is recorded here).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach rows are MARKS, not fills. The position is still open in its engine, Exit Price is the latest close, and Realized P&amp;L % is the live unrealized figure. They carry their own source precisely so they are never counted in the realized win-rate or average return alongside trades that actually closed.</t>
+          <t>Permanent record of every closed R1 / R2 / Momentum position, rendered from the canonical lifecycle dataset.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Exit Date on a breach row is the day the breach was FIRST observed, not today, and it never moves. A position that later recovers above its stop stays here · recovering does not undo having passed the stop.</t>
+          <t>Realized P&amp;L % · (Exit − Entry) / Entry · the trade's own result.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never backfilled from today's state.</t>
+          <t>Source · registry:production (a real R2 trade) · registry:advisory (R1 · never counted in production P&amp;L) · registry:administrative (same-day or zero-delta bookkeeping · not a real trade) · lifecycle:stop-breach (price passed the stop · the row left CURRENT and is recorded here).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
+          <t>lifecycle:stop-breach rows are MARKS, not fills. The position is still open in its engine, Exit Price is the latest close, and Realized P&amp;L % is the live unrealized figure. They carry their own source precisely so they are never counted in the realized win-rate or average return alongside trades that actually closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Exit Date on a breach row is the day the breach was FIRST observed, not today, and it never moves. A position that later recovers above its stop stays here · recovering does not undo having passed the stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never backfilled from today's state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
           <t>Sector · the company's CURRENT classification from the canonical sector cache, not its sector as of the exit date. No point-in-time sector history exists, so this column describes the company today and must not be read as evidence about what the sector was when the trade was live. NOT_AVAILABLE means the canonical source has no entry · it is never guessed.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A69:O69"/>
     <mergeCell ref="A65:O65"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A63:O63"/>
-    <mergeCell ref="A64:O64"/>
     <mergeCell ref="A68:O68"/>
     <mergeCell ref="A66:O66"/>
+    <mergeCell ref="A71:O71"/>
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A70:O70"/>
     <mergeCell ref="A67:O67"/>
-    <mergeCell ref="A62:O62"/>
     <mergeCell ref="A3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -502,14 +502,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · 2026-09-09</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · 2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>48 investable · NEW 33 · ACTIVE+ 9 · ACTIVE 6   ·   R2 43 · MOMENTUM 0 · R1 5 (advisory)</t>
+          <t>48 investable · NEW 0 · ACTIVE+ 42 · ACTIVE 6   ·   R2 43 · MOMENTUM 0 · R1 5 (advisory)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=33 · 228 scored · 47 already in CURRENT · biggest blocker: model disagreement (171) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 228 scored · 47 already in CURRENT · biggest blocker: model disagreement (171) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -646,28 +646,30 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>25455</v>
+        <v>553.3</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>25455</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>31.3</v>
+        <v>563.35</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>24667.8571</v>
+        <v>534.9285</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -675,22 +677,22 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.09</v>
+        <v>5.05</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.09</v>
+        <v>-3.32</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>26635.71</v>
+        <v>587.67</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -707,7 +709,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -717,28 +719,30 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5163.5</v>
+        <v>117.05</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5163.5</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>31.3</v>
+        <v>117.14</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5015.7143</v>
+        <v>114.0186</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -746,22 +750,22 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.86</v>
+        <v>-2.59</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5385.18</v>
+        <v>121.93</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ALKEM-20260909-517913</t>
+          <t>IND-R2-IEX-20260908-d0ae28</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -778,7 +782,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -788,7 +792,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -797,19 +801,19 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>292.9</v>
+        <v>25455</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>292.9</v>
+        <v>25455</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>34.3</v>
+        <v>31.3</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>277.55</v>
+        <v>24667.8571</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -817,22 +821,22 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.24</v>
+        <v>3.09</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.24</v>
+        <v>-3.09</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>315.92</v>
+        <v>26635.71</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
+          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -849,7 +853,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -859,7 +863,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -868,19 +872,19 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6291</v>
+        <v>5163.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6291</v>
+        <v>5163.5</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>33.3</v>
+        <v>31.3</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6059.4286</v>
+        <v>5015.7143</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -888,22 +892,22 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.68</v>
+        <v>2.86</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.68</v>
+        <v>-2.86</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6638.36</v>
+        <v>5385.18</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260909-2f64b0</t>
+          <t>IND-R2-ALKEM-20260909-517913</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -920,7 +924,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -930,7 +934,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -939,19 +943,19 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1244.4</v>
+        <v>292.9</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1244.4</v>
+        <v>292.9</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>32.9</v>
+        <v>34.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1211.2286</v>
+        <v>277.55</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -959,22 +963,22 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.67</v>
+        <v>5.24</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.67</v>
+        <v>-5.24</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1294.16</v>
+        <v>315.92</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20260909-3abb74</t>
+          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -991,7 +995,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1001,7 +1005,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1010,19 +1014,19 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>172.76</v>
+        <v>6291</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>172.76</v>
+        <v>6291</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>30.1</v>
+        <v>33.3</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>164.7914</v>
+        <v>6059.4286</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1030,22 +1034,22 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.61</v>
+        <v>3.68</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.61</v>
+        <v>-3.68</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>184.71</v>
+        <v>6638.36</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
+          <t>IND-R2-ATUL-20260909-2f64b0</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -1062,7 +1066,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1081,19 +1085,19 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>434.2</v>
+        <v>1244.4</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>434.2</v>
+        <v>1244.4</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>33.3</v>
+        <v>32.9</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>419.5786</v>
+        <v>1211.2286</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1101,22 +1105,22 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.37</v>
+        <v>2.67</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.37</v>
+        <v>-2.67</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>456.13</v>
+        <v>1294.16</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260909-3c298a</t>
+          <t>IND-R2-AXISBANK-20260909-3abb74</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
@@ -1133,7 +1137,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1143,7 +1147,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1152,19 +1156,19 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>370</v>
+        <v>172.76</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>370</v>
+        <v>172.76</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>351.5286</v>
+        <v>164.7914</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1172,22 +1176,22 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.99</v>
+        <v>4.61</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.99</v>
+        <v>-4.61</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>397.71</v>
+        <v>184.71</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -1204,7 +1208,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1214,7 +1218,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1223,19 +1227,19 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2410.1</v>
+        <v>434.2</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2410.1</v>
+        <v>434.2</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>40.6</v>
+        <v>33.3</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2296.8716</v>
+        <v>419.5786</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1243,22 +1247,22 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.7</v>
+        <v>3.37</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.7</v>
+        <v>-3.37</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2579.94</v>
+        <v>456.13</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20260909-ef0373</t>
+          <t>IND-R2-COALINDIA-20260909-3c298a</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
@@ -1275,7 +1279,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1294,19 +1298,19 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>694.35</v>
+        <v>370</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>694.35</v>
+        <v>370</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>34.8</v>
+        <v>31.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>671.25</v>
+        <v>351.5286</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1314,22 +1318,22 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.33</v>
+        <v>4.99</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.33</v>
+        <v>-4.99</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>729</v>
+        <v>397.71</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
+          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -1346,7 +1350,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1356,7 +1360,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1365,19 +1369,19 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1952</v>
+        <v>2410.1</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1952</v>
+        <v>2410.1</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>31.2</v>
+        <v>40.6</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1906.3286</v>
+        <v>2296.8716</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1385,22 +1389,22 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.34</v>
+        <v>4.7</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.34</v>
+        <v>-4.7</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2020.51</v>
+        <v>2579.94</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
+          <t>IND-R2-GLENMARK-20260909-ef0373</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
@@ -1417,7 +1421,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1427,7 +1431,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1436,19 +1440,19 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>154.28</v>
+        <v>694.35</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>154.28</v>
+        <v>694.35</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>33.3</v>
+        <v>34.8</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>148.0157</v>
+        <v>671.25</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1456,22 +1460,22 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.06</v>
+        <v>3.33</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.06</v>
+        <v>-3.33</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>163.68</v>
+        <v>729</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20260909-938c43</t>
+          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -1488,7 +1492,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1498,7 +1502,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1507,19 +1511,19 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>860.45</v>
+        <v>1952</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>860.45</v>
+        <v>1952</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>35</v>
+        <v>31.2</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>831.6070999999999</v>
+        <v>1906.3286</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1527,22 +1531,22 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.35</v>
+        <v>-2.34</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>903.71</v>
+        <v>2020.51</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260909-3ab469</t>
+          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
@@ -1559,7 +1563,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1569,7 +1573,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1578,19 +1582,19 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1038.3</v>
+        <v>154.28</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1038.3</v>
+        <v>154.28</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>38.3</v>
+        <v>33.3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>983.3143</v>
+        <v>148.0157</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1598,22 +1602,22 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>5.3</v>
+        <v>4.06</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.3</v>
+        <v>-4.06</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1120.78</v>
+        <v>163.68</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260909-f2b7ad</t>
+          <t>IND-R2-IGL-20260909-938c43</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
@@ -1630,7 +1634,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1640,7 +1644,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1649,19 +1653,19 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1949</v>
+        <v>860.45</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1949</v>
+        <v>860.45</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>40.6</v>
+        <v>35</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1878.6</v>
+        <v>831.6070999999999</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -1669,22 +1673,22 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.61</v>
+        <v>-3.35</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2054.6</v>
+        <v>903.71</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-INDIANB-20260909-3ab469</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
@@ -1701,7 +1705,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1711,7 +1715,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1720,19 +1724,19 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>19.11</v>
+        <v>1038.3</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>19.11</v>
+        <v>1038.3</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>33.3</v>
+        <v>38.3</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>18.3757</v>
+        <v>983.3143</v>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
@@ -1740,22 +1744,22 @@
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.84</v>
+        <v>5.3</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.84</v>
+        <v>-5.3</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>20.21</v>
+        <v>1120.78</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260909-153c95</t>
+          <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q23" s="4" t="inlineStr">
@@ -1772,7 +1776,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1782,7 +1786,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1791,19 +1795,19 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>470.4</v>
+        <v>1949</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>470.4</v>
+        <v>1949</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>28.4</v>
+        <v>40.6</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>459.6357</v>
+        <v>1878.6</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
@@ -1811,22 +1815,22 @@
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.29</v>
+        <v>3.61</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.29</v>
+        <v>-3.61</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>486.55</v>
+        <v>2054.6</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRCTC-20260909-add681</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr">
@@ -1843,7 +1847,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1853,7 +1857,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1862,19 +1866,19 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>12603</v>
+        <v>19.11</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>12603</v>
+        <v>19.11</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>12160.1429</v>
+        <v>18.3757</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -1882,22 +1886,22 @@
         </is>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.51</v>
+        <v>3.84</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.51</v>
+        <v>-3.84</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>13267.29</v>
+        <v>20.21</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20260909-c59a94</t>
+          <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
@@ -1914,7 +1918,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1924,7 +1928,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1933,19 +1937,19 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3365.2</v>
+        <v>470.4</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3365.2</v>
+        <v>470.4</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>40.4</v>
+        <v>28.4</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3203.1143</v>
+        <v>459.6357</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
@@ -1953,22 +1957,22 @@
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.82</v>
+        <v>2.29</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.82</v>
+        <v>-2.29</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3608.33</v>
+        <v>486.55</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MCX-20260909-1bc45f</t>
+          <t>IND-R2-IRCTC-20260909-add681</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr">
@@ -1985,7 +1989,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1995,7 +1999,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2004,19 +2008,19 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3134.7</v>
+        <v>12603</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3134.7</v>
+        <v>12603</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11.2</v>
+        <v>31.3</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3019.7429</v>
+        <v>12160.1429</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
@@ -2024,22 +2028,22 @@
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.67</v>
+        <v>3.51</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.67</v>
+        <v>-3.51</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3307.14</v>
+        <v>13267.29</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20260909-3a8a06</t>
+          <t>IND-R2-MARUTI-20260909-c59a94</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q27" s="4" t="inlineStr">
@@ -2056,7 +2060,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2066,7 +2070,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2075,19 +2079,19 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2825</v>
+        <v>3365.2</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2825</v>
+        <v>3365.2</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>36.1</v>
+        <v>40.4</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2663.5858</v>
+        <v>3203.1143</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
@@ -2095,22 +2099,22 @@
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.71</v>
+        <v>4.82</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.71</v>
+        <v>-4.82</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3067.12</v>
+        <v>3608.33</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr">
@@ -2127,7 +2131,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2137,7 +2141,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2146,19 +2150,19 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>818.3</v>
+        <v>3134.7</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>818.3</v>
+        <v>3134.7</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>31.2</v>
+        <v>11.2</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>785.8786</v>
+        <v>3019.7429</v>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
@@ -2166,22 +2170,22 @@
         </is>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.96</v>
+        <v>3.67</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.96</v>
+        <v>-3.67</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>866.9299999999999</v>
+        <v>3307.14</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+          <t>IND-R2-MM-20260909-3a8a06</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q29" s="4" t="inlineStr">
@@ -2198,7 +2202,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2208,7 +2212,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2217,19 +2221,19 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>385.3</v>
+        <v>2825</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>385.3</v>
+        <v>2825</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>40.6</v>
+        <v>36.1</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>366.9428</v>
+        <v>2663.5858</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2237,22 +2241,22 @@
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.76</v>
+        <v>5.71</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.76</v>
+        <v>-5.71</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>412.84</v>
+        <v>3067.12</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
@@ -2269,7 +2273,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2279,7 +2283,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2288,19 +2292,19 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1260</v>
+        <v>818.3</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1260</v>
+        <v>818.3</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1201.0857</v>
+        <v>785.8786</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2308,22 +2312,22 @@
         </is>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.68</v>
+        <v>3.96</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.68</v>
+        <v>-3.96</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1348.37</v>
+        <v>866.9299999999999</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NAUKRI-20260909-930931</t>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
@@ -2340,7 +2344,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2350,7 +2354,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2359,19 +2363,19 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>273.3</v>
+        <v>385.3</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>273.3</v>
+        <v>385.3</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>28.4</v>
+        <v>40.6</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>262.5714</v>
+        <v>366.9428</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2379,22 +2383,22 @@
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.93</v>
+        <v>4.76</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.93</v>
+        <v>-4.76</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>289.39</v>
+        <v>412.84</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr">
@@ -2411,7 +2415,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2421,7 +2425,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2430,19 +2434,19 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11644</v>
+        <v>1260</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11644</v>
+        <v>1260</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>43.6</v>
+        <v>33.3</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11094.7143</v>
+        <v>1201.0857</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2450,22 +2454,22 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.72</v>
+        <v>-4.68</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12467.93</v>
+        <v>1348.37</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260909-1e09a0</t>
+          <t>IND-R2-NAUKRI-20260909-930931</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q33" s="4" t="inlineStr">
@@ -2482,7 +2486,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2492,7 +2496,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -2501,19 +2505,19 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>500</v>
+        <v>273.3</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>500</v>
+        <v>273.3</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>35.4</v>
+        <v>28.4</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>479.7</v>
+        <v>262.5714</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
@@ -2521,22 +2525,22 @@
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.06</v>
+        <v>3.93</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-4.06</v>
+        <v>-3.93</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>530.45</v>
+        <v>289.39</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260909-82436d</t>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q34" s="4" t="inlineStr">
@@ -2553,7 +2557,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2563,7 +2567,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -2572,19 +2576,19 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>339.55</v>
+        <v>11644</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>339.55</v>
+        <v>11644</v>
       </c>
       <c r="H35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>32.3</v>
+        <v>43.6</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>330.1714</v>
+        <v>11094.7143</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2592,22 +2596,22 @@
         </is>
       </c>
       <c r="L35" s="4" t="n">
-        <v>2.76</v>
+        <v>4.72</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-2.76</v>
+        <v>-4.72</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>353.62</v>
+        <v>12467.93</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20260909-508e75</t>
+          <t>IND-R2-OFSS-20260909-1e09a0</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
@@ -2624,7 +2628,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2634,7 +2638,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -2643,19 +2647,19 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>315.55</v>
+        <v>500</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>315.55</v>
+        <v>500</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>31.2</v>
+        <v>35.4</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>306.4143</v>
+        <v>479.7</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
@@ -2663,22 +2667,22 @@
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>2.9</v>
+        <v>4.06</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>-2.9</v>
+        <v>-4.06</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>329.25</v>
+        <v>530.45</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RECLTD-20260909-84e6d1</t>
+          <t>IND-R2-OIL-20260909-82436d</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q36" s="4" t="inlineStr">
@@ -2695,7 +2699,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2705,7 +2709,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -2714,19 +2718,19 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>187.94</v>
+        <v>339.55</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>187.94</v>
+        <v>339.55</v>
       </c>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>40.6</v>
+        <v>32.3</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>178.5243</v>
+        <v>330.1714</v>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
@@ -2734,22 +2738,22 @@
         </is>
       </c>
       <c r="L37" s="4" t="n">
-        <v>5.01</v>
+        <v>2.76</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>-5.01</v>
+        <v>-2.76</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>206.77</v>
+        <v>353.62</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260909-29ffd5</t>
+          <t>IND-R2-PATANJALI-20260909-508e75</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -2766,7 +2770,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2776,7 +2780,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -2785,19 +2789,19 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1007.2</v>
+        <v>315.55</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1007.2</v>
+        <v>315.55</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>35</v>
+        <v>31.2</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>978.6572</v>
+        <v>306.4143</v>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
@@ -2805,22 +2809,22 @@
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.83</v>
+        <v>-2.9</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>1050.01</v>
+        <v>329.25</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20260909-a73231</t>
+          <t>IND-R2-RECLTD-20260909-84e6d1</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q38" s="4" t="inlineStr">
@@ -2837,7 +2841,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2847,7 +2851,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2856,19 +2860,19 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2197.4</v>
+        <v>187.94</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>2197.4</v>
+        <v>187.94</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>37.1</v>
+        <v>40.6</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>2101.4713</v>
+        <v>178.5243</v>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
@@ -2876,22 +2880,22 @@
         </is>
       </c>
       <c r="L39" s="4" t="n">
-        <v>4.37</v>
+        <v>5.01</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-4.37</v>
+        <v>-5.01</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>2341.29</v>
+        <v>206.77</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260909-fb0a7f</t>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q39" s="4" t="inlineStr">
@@ -2908,7 +2912,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2918,7 +2922,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -2927,19 +2931,19 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>275</v>
+        <v>1007.2</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>275</v>
+        <v>1007.2</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>260.9143</v>
+        <v>978.6572</v>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
@@ -2947,22 +2951,22 @@
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>5.12</v>
+        <v>2.83</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-5.12</v>
+        <v>-2.83</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>296.13</v>
+        <v>1050.01</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260909-bbba1f</t>
+          <t>IND-R2-SBIN-20260909-a73231</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q40" s="4" t="inlineStr">
@@ -2979,7 +2983,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2994,25 +2998,23 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>553.3</v>
+        <v>2197.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>563.35</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2197.4</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>37.1</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>534.9285</v>
+        <v>2101.4713</v>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
@@ -3020,22 +3022,22 @@
         </is>
       </c>
       <c r="L41" s="4" t="n">
-        <v>5.05</v>
+        <v>4.37</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-3.32</v>
+        <v>-4.37</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>587.67</v>
+        <v>2341.29</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20260806-03d0a7</t>
+          <t>IND-R2-TCS-20260909-fb0a7f</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -3052,7 +3054,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3067,25 +3069,23 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>117.05</v>
+        <v>275</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>117.14</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>275</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>35.4</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>114.0186</v>
+        <v>260.9143</v>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
@@ -3093,17 +3093,17 @@
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>2.66</v>
+        <v>5.12</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-2.59</v>
+        <v>-5.12</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>121.93</v>
+        <v>296.13</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260908-d0ae28</t>
+          <t>IND-R2-VEDL-20260909-bbba1f</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q43" s="4" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q44" s="4" t="inlineStr">
@@ -3317,8 +3317,10 @@
       <c r="M45" s="4" t="n">
         <v>-2.96</v>
       </c>
-      <c r="N45" s="4" t="n">
-        <v>407.13</v>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
@@ -3390,8 +3392,10 @@
       <c r="M46" s="4" t="n">
         <v>-2.66</v>
       </c>
-      <c r="N46" s="4" t="n">
-        <v>412.81</v>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
@@ -3463,8 +3467,10 @@
       <c r="M47" s="4" t="n">
         <v>-2.45</v>
       </c>
-      <c r="N47" s="4" t="n">
-        <v>432.94</v>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
@@ -3692,7 +3698,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q50" s="4" t="inlineStr">
@@ -3765,7 +3771,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q51" s="4" t="inlineStr">
@@ -3838,7 +3844,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>ROTATED_SAMEDAY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q52" s="4" t="inlineStr">
@@ -3911,7 +3917,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q53" s="4" t="inlineStr">
@@ -3984,7 +3990,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>ROTATED_SAMEDAY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q54" s="4" t="inlineStr">
@@ -4057,7 +4063,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
       <c r="Q55" s="4" t="inlineStr">
@@ -4069,113 +4075,128 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="23">
     <mergeCell ref="A58:Q58"/>
     <mergeCell ref="A67:Q67"/>
     <mergeCell ref="A59:Q59"/>
+    <mergeCell ref="A73:Q73"/>
     <mergeCell ref="A64:Q64"/>
     <mergeCell ref="A60:Q60"/>
     <mergeCell ref="A1:Q1"/>
@@ -4185,6 +4206,7 @@
     <mergeCell ref="A69:Q69"/>
     <mergeCell ref="A65:Q65"/>
     <mergeCell ref="A66:Q66"/>
+    <mergeCell ref="A74:Q74"/>
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A71:Q71"/>
@@ -4228,7 +4250,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · every closed position · 2026-09-09</t>
+          <t>AEGIS INDIA · EXIT HISTORY · every closed position · 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4348,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4364,7 +4386,7 @@
         <v>-5.16</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
@@ -4395,7 +4417,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -4433,7 +4455,7 @@
         <v>-4.03</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
@@ -4464,7 +4486,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -4502,7 +4524,7 @@
         <v>-2.82</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,39 +477,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · 2026-09-10</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-11 · prices = 2026-09-09 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>48 investable · NEW 0 · ACTIVE+ 42 · ACTIVE 6   ·   R2 43 · MOMENTUM 0 · R1 5 (advisory)</t>
+          <t>48 investable · NEW 0 · ACTIVE+ 42 · ACTIVE 6   ·   R2 43 · MOMENTUM 0 · R1 5 (advisory)   ·   33 row(s) read 0.00%: admitted at the 2026-09-09 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
@@ -530,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 228 scored · 47 already in CURRENT · biggest blocker: model disagreement (171) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 228 scored · 47 already in CURRENT · biggest blocker: model disagreement (170) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW INTELLIGENCE — RESEARCH ONLY. R3 reviews R2 candidates but does NOT change R2 Action, Confidence, Stop or Position. ABSTAIN means R3 has no validated opinion yet — it is NOT Hold, Buy, Avoid, or a 50/50 probability. A future AVOID is a research annotation and never implies an R2 EXIT. R3 can become actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 43 candidate(s) evaluated today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 43 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -564,67 +570,97 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
+          <t>R3 SHADOW</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Admission Status</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Current Price</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Last Price</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Market Data As-of</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Current Market Cap</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Market Cap As-of</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>Stop State</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Dist to Stop %</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>Stop Distance %</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>Max Loss if Stop %</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t>Reason</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>R3 SHADOW</t>
         </is>
       </c>
     </row>
@@ -651,53 +687,83 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-06</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>553.3</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>563.35</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>1.82</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>534.9285</v>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>5.05</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="T8" s="4" t="n">
         <v>-3.32</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="U8" s="4" t="n">
         <v>587.67</v>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>IND-R2-GNFC-20260806-03d0a7</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -724,53 +790,83 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-08</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>117.05</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>117.14</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>114.0186</v>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>2.66</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="T9" s="4" t="n">
         <v>-2.59</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>121.93</v>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>IND-R2-IEX-20260908-d0ae28</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -797,51 +893,81 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>25455</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>25455</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>24667.8571</v>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>3.09</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="T10" s="4" t="n">
         <v>-3.09</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>26635.71</v>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -868,51 +994,81 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>5163.5</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>5163.5</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>5015.7143</v>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>-2.86</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>5385.18</v>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ALKEM-20260909-517913</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -939,51 +1095,81 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>292.9</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>292.9</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>34.3</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>277.55</v>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>5.24</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="T12" s="4" t="n">
         <v>-5.24</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>315.92</v>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ANGELONE-20260909-43aaa1</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1010,51 +1196,81 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>6291</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>6291</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="L13" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="n">
         <v>6059.4286</v>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>3.68</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="T13" s="4" t="n">
         <v>-3.68</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>6638.36</v>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ATUL-20260909-2f64b0</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1081,51 +1297,81 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>1244.4</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>1244.4</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="L14" s="4" t="n">
         <v>32.9</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>1211.2286</v>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>2.67</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="T14" s="4" t="n">
         <v>-2.67</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>1294.16</v>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="V14" s="4" t="inlineStr">
         <is>
           <t>IND-R2-AXISBANK-20260909-3abb74</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1152,51 +1398,81 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>172.76</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>172.76</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="L15" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="n">
         <v>164.7914</v>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="S15" s="4" t="n">
         <v>4.61</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="T15" s="4" t="n">
         <v>-4.61</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>184.71</v>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1223,51 +1499,81 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>434.2</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>434.2</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="L16" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="n">
         <v>419.5786</v>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="S16" s="4" t="n">
         <v>3.37</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="T16" s="4" t="n">
         <v>-3.37</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="U16" s="4" t="n">
         <v>456.13</v>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="V16" s="4" t="inlineStr">
         <is>
           <t>IND-R2-COALINDIA-20260909-3c298a</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1294,51 +1600,81 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>370</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>370</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="L17" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>351.5286</v>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="S17" s="4" t="n">
         <v>4.99</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="T17" s="4" t="n">
         <v>-4.99</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>397.71</v>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>IND-R2-EMAMILTD-20260909-0f7729</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1365,51 +1701,81 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>2410.1</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="I18" s="4" t="n">
         <v>2410.1</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="L18" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>2296.8716</v>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="S18" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="T18" s="4" t="n">
         <v>-4.7</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>2579.94</v>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="V18" s="4" t="inlineStr">
         <is>
           <t>IND-R2-GLENMARK-20260909-ef0373</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1436,51 +1802,81 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>694.35</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>694.35</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="L19" s="4" t="n">
         <v>34.8</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>671.25</v>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="S19" s="4" t="n">
         <v>3.33</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="T19" s="4" t="n">
         <v>-3.33</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>729</v>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1507,51 +1903,81 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>1952</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="I20" s="4" t="n">
         <v>1952</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="L20" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>1906.3286</v>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="S20" s="4" t="n">
         <v>2.34</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="T20" s="4" t="n">
         <v>-2.34</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>2020.51</v>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1578,51 +2004,81 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>154.28</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="I21" s="4" t="n">
         <v>154.28</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="L21" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>148.0157</v>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="S21" s="4" t="n">
         <v>4.06</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="T21" s="4" t="n">
         <v>-4.06</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>163.68</v>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>IND-R2-IGL-20260909-938c43</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1649,51 +2105,81 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>860.45</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="I22" s="4" t="n">
         <v>860.45</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="L22" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>831.6070999999999</v>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="S22" s="4" t="n">
         <v>3.35</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="T22" s="4" t="n">
         <v>-3.35</v>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>903.71</v>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="V22" s="4" t="inlineStr">
         <is>
           <t>IND-R2-INDIANB-20260909-3ab469</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W22" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1720,51 +2206,81 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>1038.3</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="I23" s="4" t="n">
         <v>1038.3</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="L23" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="n">
         <v>983.3143</v>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="R23" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="S23" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="T23" s="4" t="n">
         <v>-5.3</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>1120.78</v>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="V23" s="4" t="inlineStr">
         <is>
           <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1791,51 +2307,81 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>1949</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="I24" s="4" t="n">
         <v>1949</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="L24" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="n">
         <v>1878.6</v>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="R24" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="S24" s="4" t="n">
         <v>3.61</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="T24" s="4" t="n">
         <v>-3.61</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>2054.6</v>
       </c>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="V24" s="4" t="inlineStr">
         <is>
           <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1862,51 +2408,81 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>19.11</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="I25" s="4" t="n">
         <v>19.11</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="L25" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="n">
         <v>18.3757</v>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="R25" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="S25" s="4" t="n">
         <v>3.84</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="T25" s="4" t="n">
         <v>-3.84</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>20.21</v>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="V25" s="4" t="inlineStr">
         <is>
           <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W25" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1933,51 +2509,81 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>470.4</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="I26" s="4" t="n">
         <v>470.4</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="L26" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="n">
         <v>459.6357</v>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="R26" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="S26" s="4" t="n">
         <v>2.29</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="T26" s="4" t="n">
         <v>-2.29</v>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>486.55</v>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="V26" s="4" t="inlineStr">
         <is>
           <t>IND-R2-IRCTC-20260909-add681</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2004,51 +2610,81 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>12603</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="I27" s="4" t="n">
         <v>12603</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="L27" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="n">
         <v>12160.1429</v>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="R27" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="S27" s="4" t="n">
         <v>3.51</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="T27" s="4" t="n">
         <v>-3.51</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>13267.29</v>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>IND-R2-MARUTI-20260909-c59a94</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2075,51 +2711,81 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>3365.2</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="I28" s="4" t="n">
         <v>3365.2</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="L28" s="4" t="n">
         <v>40.4</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="n">
         <v>3203.1143</v>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="R28" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="S28" s="4" t="n">
         <v>4.82</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="T28" s="4" t="n">
         <v>-4.82</v>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="U28" s="4" t="n">
         <v>3608.33</v>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="V28" s="4" t="inlineStr">
         <is>
           <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2146,51 +2812,81 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>3134.7</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="I29" s="4" t="n">
         <v>3134.7</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="L29" s="4" t="n">
         <v>11.2</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="n">
         <v>3019.7429</v>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="R29" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="S29" s="4" t="n">
         <v>3.67</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="T29" s="4" t="n">
         <v>-3.67</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>3307.14</v>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="V29" s="4" t="inlineStr">
         <is>
           <t>IND-R2-MM-20260909-3a8a06</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2217,51 +2913,81 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>2825</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="I30" s="4" t="n">
         <v>2825</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="L30" s="4" t="n">
         <v>36.1</v>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="n">
         <v>2663.5858</v>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="R30" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="S30" s="4" t="n">
         <v>5.71</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="T30" s="4" t="n">
         <v>-5.71</v>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="U30" s="4" t="n">
         <v>3067.12</v>
       </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="V30" s="4" t="inlineStr">
         <is>
           <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2288,51 +3014,81 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>818.3</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="I31" s="4" t="n">
         <v>818.3</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="L31" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="n">
         <v>785.8786</v>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="R31" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="S31" s="4" t="n">
         <v>3.96</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="T31" s="4" t="n">
         <v>-3.96</v>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="U31" s="4" t="n">
         <v>866.9299999999999</v>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="V31" s="4" t="inlineStr">
         <is>
           <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2359,51 +3115,81 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>385.3</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="I32" s="4" t="n">
         <v>385.3</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="L32" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="n">
         <v>366.9428</v>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="R32" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="S32" s="4" t="n">
         <v>4.76</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="T32" s="4" t="n">
         <v>-4.76</v>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="U32" s="4" t="n">
         <v>412.84</v>
       </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="V32" s="4" t="inlineStr">
         <is>
           <t>IND-R2-NATIONALUM-20260909-36e82f</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2430,51 +3216,81 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>1260</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="I33" s="4" t="n">
         <v>1260</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="L33" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="n">
         <v>1201.0857</v>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="R33" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="S33" s="4" t="n">
         <v>4.68</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="T33" s="4" t="n">
         <v>-4.68</v>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>1348.37</v>
       </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="V33" s="4" t="inlineStr">
         <is>
           <t>IND-R2-NAUKRI-20260909-930931</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2501,51 +3317,81 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>273.3</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="I34" s="4" t="n">
         <v>273.3</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="L34" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="n">
         <v>262.5714</v>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="S34" s="4" t="n">
         <v>3.93</v>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="T34" s="4" t="n">
         <v>-3.93</v>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="U34" s="4" t="n">
         <v>289.39</v>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="V34" s="4" t="inlineStr">
         <is>
           <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2572,51 +3418,81 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>11644</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="I35" s="4" t="n">
         <v>11644</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="L35" s="4" t="n">
         <v>43.6</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="n">
         <v>11094.7143</v>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="R35" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="S35" s="4" t="n">
         <v>4.72</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="T35" s="4" t="n">
         <v>-4.72</v>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="U35" s="4" t="n">
         <v>12467.93</v>
       </c>
-      <c r="O35" s="4" t="inlineStr">
+      <c r="V35" s="4" t="inlineStr">
         <is>
           <t>IND-R2-OFSS-20260909-1e09a0</t>
         </is>
       </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2643,51 +3519,81 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="I36" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="L36" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="n">
         <v>479.7</v>
       </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="R36" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="S36" s="4" t="n">
         <v>4.06</v>
       </c>
-      <c r="M36" s="4" t="n">
+      <c r="T36" s="4" t="n">
         <v>-4.06</v>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="U36" s="4" t="n">
         <v>530.45</v>
       </c>
-      <c r="O36" s="4" t="inlineStr">
+      <c r="V36" s="4" t="inlineStr">
         <is>
           <t>IND-R2-OIL-20260909-82436d</t>
         </is>
       </c>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W36" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2714,51 +3620,81 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>339.55</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="I37" s="4" t="n">
         <v>339.55</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="L37" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="n">
         <v>330.1714</v>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="R37" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="S37" s="4" t="n">
         <v>2.76</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="T37" s="4" t="n">
         <v>-2.76</v>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="U37" s="4" t="n">
         <v>353.62</v>
       </c>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="V37" s="4" t="inlineStr">
         <is>
           <t>IND-R2-PATANJALI-20260909-508e75</t>
         </is>
       </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W37" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2785,51 +3721,81 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>315.55</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>315.55</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="L38" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="n">
         <v>306.4143</v>
       </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="R38" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="S38" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="M38" s="4" t="n">
+      <c r="T38" s="4" t="n">
         <v>-2.9</v>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="U38" s="4" t="n">
         <v>329.25</v>
       </c>
-      <c r="O38" s="4" t="inlineStr">
+      <c r="V38" s="4" t="inlineStr">
         <is>
           <t>IND-R2-RECLTD-20260909-84e6d1</t>
         </is>
       </c>
-      <c r="P38" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2856,51 +3822,81 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>187.94</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="I39" s="4" t="n">
         <v>187.94</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="L39" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="n">
         <v>178.5243</v>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="R39" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="S39" s="4" t="n">
         <v>5.01</v>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="T39" s="4" t="n">
         <v>-5.01</v>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="U39" s="4" t="n">
         <v>206.77</v>
       </c>
-      <c r="O39" s="4" t="inlineStr">
+      <c r="V39" s="4" t="inlineStr">
         <is>
           <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2927,51 +3923,81 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>1007.2</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="I40" s="4" t="n">
         <v>1007.2</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="L40" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="n">
         <v>978.6572</v>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="R40" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="S40" s="4" t="n">
         <v>2.83</v>
       </c>
-      <c r="M40" s="4" t="n">
+      <c r="T40" s="4" t="n">
         <v>-2.83</v>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="U40" s="4" t="n">
         <v>1050.01</v>
       </c>
-      <c r="O40" s="4" t="inlineStr">
+      <c r="V40" s="4" t="inlineStr">
         <is>
           <t>IND-R2-SBIN-20260909-a73231</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2998,51 +4024,81 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>2197.4</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="I41" s="4" t="n">
         <v>2197.4</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="L41" s="4" t="n">
         <v>37.1</v>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="n">
         <v>2101.4713</v>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="R41" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="S41" s="4" t="n">
         <v>4.37</v>
       </c>
-      <c r="M41" s="4" t="n">
+      <c r="T41" s="4" t="n">
         <v>-4.37</v>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="U41" s="4" t="n">
         <v>2341.29</v>
       </c>
-      <c r="O41" s="4" t="inlineStr">
+      <c r="V41" s="4" t="inlineStr">
         <is>
           <t>IND-R2-TCS-20260909-fb0a7f</t>
         </is>
       </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3069,51 +4125,81 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>275</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="I42" s="4" t="n">
         <v>275</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="L42" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="n">
         <v>260.9143</v>
       </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="R42" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="S42" s="4" t="n">
         <v>5.12</v>
       </c>
-      <c r="M42" s="4" t="n">
+      <c r="T42" s="4" t="n">
         <v>-5.12</v>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="U42" s="4" t="n">
         <v>296.13</v>
       </c>
-      <c r="O42" s="4" t="inlineStr">
+      <c r="V42" s="4" t="inlineStr">
         <is>
           <t>IND-R2-VEDL-20260909-bbba1f</t>
         </is>
       </c>
-      <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q42" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W42" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3140,53 +4226,83 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-08</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>233.86</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="I43" s="4" t="n">
         <v>231.86</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="n">
         <v>-0.86</v>
       </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n">
         <v>224.7686</v>
       </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="R43" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="S43" s="4" t="n">
         <v>3.06</v>
       </c>
-      <c r="M43" s="4" t="n">
+      <c r="T43" s="4" t="n">
         <v>-3.89</v>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="U43" s="4" t="n">
         <v>244.86</v>
       </c>
-      <c r="O43" s="4" t="inlineStr">
+      <c r="V43" s="4" t="inlineStr">
         <is>
           <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
         </is>
       </c>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3213,53 +4329,83 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>452.35</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="I44" s="4" t="n">
         <v>415.8</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="n">
         <v>-8.08</v>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="n">
         <v>401.1571</v>
       </c>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="R44" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="S44" s="4" t="n">
         <v>3.52</v>
       </c>
-      <c r="M44" s="4" t="n">
+      <c r="T44" s="4" t="n">
         <v>-11.32</v>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="U44" s="4" t="n">
         <v>477.49</v>
       </c>
-      <c r="O44" s="4" t="inlineStr">
+      <c r="V44" s="4" t="inlineStr">
         <is>
           <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
         </is>
       </c>
-      <c r="P44" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3286,55 +4432,85 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>389.85</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="I45" s="4" t="n">
         <v>408.9</v>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
         <v>4.89</v>
       </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="n">
         <v>378.3286</v>
       </c>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="R45" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="S45" s="4" t="n">
         <v>7.48</v>
       </c>
-      <c r="M45" s="4" t="n">
+      <c r="T45" s="4" t="n">
         <v>-2.96</v>
       </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="U45" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O45" s="4" t="inlineStr">
+      <c r="V45" s="4" t="inlineStr">
         <is>
           <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
-      <c r="P45" s="4" t="inlineStr">
+      <c r="W45" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-      <c r="Q45" s="4" t="inlineStr">
-        <is>
-          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3361,55 +4537,85 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>397</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="I46" s="4" t="n">
         <v>414.45</v>
       </c>
-      <c r="H46" s="5" t="n">
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
         <v>4.4</v>
       </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J46" s="4" t="n">
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="n">
         <v>386.4571</v>
       </c>
-      <c r="K46" s="4" t="inlineStr">
+      <c r="R46" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="S46" s="4" t="n">
         <v>6.75</v>
       </c>
-      <c r="M46" s="4" t="n">
+      <c r="T46" s="4" t="n">
         <v>-2.66</v>
       </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="U46" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O46" s="4" t="inlineStr">
+      <c r="V46" s="4" t="inlineStr">
         <is>
           <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="W46" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="inlineStr">
-        <is>
-          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3436,55 +4642,85 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>417.6</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="I47" s="4" t="n">
         <v>434.2</v>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
         <v>3.98</v>
       </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J47" s="4" t="n">
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="n">
         <v>407.3714</v>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="R47" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="S47" s="4" t="n">
         <v>6.18</v>
       </c>
-      <c r="M47" s="4" t="n">
+      <c r="T47" s="4" t="n">
         <v>-2.45</v>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="U47" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O47" s="4" t="inlineStr">
+      <c r="V47" s="4" t="inlineStr">
         <is>
           <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
-      <c r="P47" s="4" t="inlineStr">
+      <c r="W47" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3511,53 +4747,83 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-28</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>187.46</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="I48" s="4" t="n">
         <v>188</v>
       </c>
-      <c r="H48" s="5" t="n">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
         <v>0.29</v>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n">
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="n">
         <v>181.8114</v>
       </c>
-      <c r="K48" s="4" t="inlineStr">
+      <c r="R48" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L48" s="4" t="n">
+      <c r="S48" s="4" t="n">
         <v>3.29</v>
       </c>
-      <c r="M48" s="4" t="n">
+      <c r="T48" s="4" t="n">
         <v>-3.01</v>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="U48" s="4" t="n">
         <v>195.93</v>
       </c>
-      <c r="O48" s="4" t="inlineStr">
+      <c r="V48" s="4" t="inlineStr">
         <is>
           <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
-      <c r="P48" s="4" t="inlineStr">
+      <c r="W48" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="inlineStr">
-        <is>
-          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3584,53 +4850,83 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-11</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>239.45</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="I49" s="4" t="n">
         <v>236.91</v>
       </c>
-      <c r="H49" s="6" t="n">
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="n">
         <v>-1.06</v>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n">
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="n">
         <v>232.2186</v>
       </c>
-      <c r="K49" s="4" t="inlineStr">
+      <c r="R49" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="S49" s="4" t="n">
         <v>1.98</v>
       </c>
-      <c r="M49" s="4" t="n">
+      <c r="T49" s="4" t="n">
         <v>-3.02</v>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="U49" s="4" t="n">
         <v>250.3</v>
       </c>
-      <c r="O49" s="4" t="inlineStr">
+      <c r="V49" s="4" t="inlineStr">
         <is>
           <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
-      <c r="P49" s="4" t="inlineStr">
+      <c r="W49" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-      <c r="Q49" s="4" t="inlineStr">
-        <is>
-          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3657,53 +4953,83 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>113.36</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="I50" s="4" t="n">
         <v>116.55</v>
       </c>
-      <c r="H50" s="5" t="n">
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
         <v>2.81</v>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n">
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="n">
         <v>112.9343</v>
       </c>
-      <c r="K50" s="4" t="inlineStr">
+      <c r="R50" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L50" s="4" t="n">
+      <c r="S50" s="4" t="n">
         <v>3.1</v>
       </c>
-      <c r="M50" s="4" t="n">
+      <c r="T50" s="4" t="n">
         <v>-0.38</v>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="U50" s="4" t="n">
         <v>118.87</v>
       </c>
-      <c r="O50" s="4" t="inlineStr">
+      <c r="V50" s="4" t="inlineStr">
         <is>
           <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
-      <c r="P50" s="4" t="inlineStr">
-        <is>
-          <t>HOLD · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W50" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3730,53 +5056,83 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>5499</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="I51" s="4" t="n">
         <v>5442.5</v>
       </c>
-      <c r="H51" s="6" t="n">
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="n">
         <v>-1.03</v>
       </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="n">
         <v>5176.5</v>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="R51" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="S51" s="4" t="n">
         <v>4.89</v>
       </c>
-      <c r="M51" s="4" t="n">
+      <c r="T51" s="4" t="n">
         <v>-5.86</v>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="U51" s="4" t="n">
         <v>5954.25</v>
       </c>
-      <c r="O51" s="4" t="inlineStr">
+      <c r="V51" s="4" t="inlineStr">
         <is>
           <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
-      <c r="P51" s="4" t="inlineStr">
-        <is>
-          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q51" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W51" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3803,53 +5159,83 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>2744.3</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="I52" s="4" t="n">
         <v>2646.4</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="n">
         <v>-3.57</v>
       </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J52" s="4" t="n">
+      <c r="P52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="n">
         <v>2533.3999</v>
       </c>
-      <c r="K52" s="4" t="inlineStr">
+      <c r="R52" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="S52" s="4" t="n">
         <v>4.27</v>
       </c>
-      <c r="M52" s="4" t="n">
+      <c r="T52" s="4" t="n">
         <v>-7.69</v>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="U52" s="4" t="n">
         <v>2949.97</v>
       </c>
-      <c r="O52" s="4" t="inlineStr">
+      <c r="V52" s="4" t="inlineStr">
         <is>
           <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
-      <c r="P52" s="4" t="inlineStr">
-        <is>
-          <t>ROTATED_SAMEDAY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W52" s="4" t="inlineStr">
+        <is>
+          <t>ROTATED_SAMEDAY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3876,53 +5262,83 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>11475</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="I53" s="4" t="n">
         <v>11054</v>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="n">
         <v>-3.67</v>
       </c>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J53" s="4" t="n">
+      <c r="P53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="n">
         <v>10682.7143</v>
       </c>
-      <c r="K53" s="4" t="inlineStr">
+      <c r="R53" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L53" s="4" t="n">
+      <c r="S53" s="4" t="n">
         <v>3.36</v>
       </c>
-      <c r="M53" s="4" t="n">
+      <c r="T53" s="4" t="n">
         <v>-6.9</v>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="U53" s="4" t="n">
         <v>11970.43</v>
       </c>
-      <c r="O53" s="4" t="inlineStr">
+      <c r="V53" s="4" t="inlineStr">
         <is>
           <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
         </is>
       </c>
-      <c r="P53" s="4" t="inlineStr">
-        <is>
-          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W53" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3949,53 +5365,83 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>709</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="I54" s="4" t="n">
         <v>663.3</v>
       </c>
-      <c r="H54" s="6" t="n">
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="n">
         <v>-6.45</v>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J54" s="4" t="n">
+      <c r="P54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="n">
         <v>642.3928</v>
       </c>
-      <c r="K54" s="4" t="inlineStr">
+      <c r="R54" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="S54" s="4" t="n">
         <v>3.15</v>
       </c>
-      <c r="M54" s="4" t="n">
+      <c r="T54" s="4" t="n">
         <v>-9.390000000000001</v>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="U54" s="4" t="n">
         <v>749.16</v>
       </c>
-      <c r="O54" s="4" t="inlineStr">
+      <c r="V54" s="4" t="inlineStr">
         <is>
           <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
         </is>
       </c>
-      <c r="P54" s="4" t="inlineStr">
-        <is>
-          <t>ROTATED_SAMEDAY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W54" s="4" t="inlineStr">
+        <is>
+          <t>ROTATED_SAMEDAY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4022,53 +5468,83 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>284.85</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="I55" s="4" t="n">
         <v>260.75</v>
       </c>
-      <c r="H55" s="6" t="n">
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="n">
         <v>-8.460000000000001</v>
       </c>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n">
+      <c r="P55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="n">
         <v>253.7214</v>
       </c>
-      <c r="K55" s="4" t="inlineStr">
+      <c r="R55" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="S55" s="4" t="n">
         <v>2.7</v>
       </c>
-      <c r="M55" s="4" t="n">
+      <c r="T55" s="4" t="n">
         <v>-10.93</v>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="U55" s="4" t="n">
         <v>297.98</v>
       </c>
-      <c r="O55" s="4" t="inlineStr">
+      <c r="V55" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
-      <c r="P55" s="4" t="inlineStr">
-        <is>
-          <t>HOLD · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="inlineStr">
-        <is>
-          <t>ABSTAIN · R3 not yet validated</t>
+      <c r="W55" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4193,29 +5669,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A58:Q58"/>
-    <mergeCell ref="A67:Q67"/>
-    <mergeCell ref="A59:Q59"/>
-    <mergeCell ref="A73:Q73"/>
-    <mergeCell ref="A64:Q64"/>
-    <mergeCell ref="A60:Q60"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A6:Q6"/>
-    <mergeCell ref="A70:Q70"/>
-    <mergeCell ref="A69:Q69"/>
-    <mergeCell ref="A65:Q65"/>
-    <mergeCell ref="A66:Q66"/>
-    <mergeCell ref="A74:Q74"/>
-    <mergeCell ref="A3:Q3"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A71:Q71"/>
-    <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A62:Q62"/>
-    <mergeCell ref="A72:Q72"/>
-    <mergeCell ref="A68:Q68"/>
-    <mergeCell ref="A63:Q63"/>
+    <mergeCell ref="A68:W68"/>
+    <mergeCell ref="A67:W67"/>
+    <mergeCell ref="A58:W58"/>
+    <mergeCell ref="A64:W64"/>
+    <mergeCell ref="A59:W59"/>
+    <mergeCell ref="A73:W73"/>
+    <mergeCell ref="A60:W60"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A70:W70"/>
+    <mergeCell ref="A61:W61"/>
+    <mergeCell ref="A6:W6"/>
+    <mergeCell ref="A69:W69"/>
+    <mergeCell ref="A65:W65"/>
+    <mergeCell ref="A66:W66"/>
+    <mergeCell ref="A74:W74"/>
+    <mergeCell ref="A3:W3"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A71:W71"/>
+    <mergeCell ref="A5:W5"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A62:W62"/>
+    <mergeCell ref="A72:W72"/>
+    <mergeCell ref="A63:W63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4227,7 +5703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4235,36 +5711,37 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · every closed position · 2026-09-10</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>58 exits · R1 16 · R2 42   ·   R1 rows are ADVISORY and are excluded from production P&amp;L</t>
+          <t>58 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 21 · STOP-BREACH MARK 11   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🔴 11 of these are STOP-BREACH exits · the stop was passed and the position left CURRENT, but it is NOT sold · price and P&amp;L are today's MARK · avg -5.49% · worst -13.11%</t>
+          <t>📊 REALIZED PRODUCTION PERFORMANCE · 21 closed trade(s) · win 9/21 · avg -0.47%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 11 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
         </is>
       </c>
     </row>
@@ -4296,50 +5773,55 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>Record Type</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Realized P&amp;L %</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>Holding Days</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Entry Confidence %</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Exit Trigger</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4373,42 +5855,47 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>1191</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>1129.5</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>-5.16</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 1149.2286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -4442,42 +5929,47 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>1449.5</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>1391.1</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>-4.03</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -4511,42 +6003,47 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>1413.5</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>1373.6</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>-2.82</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -4580,42 +6077,47 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>381.6</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>369.35</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>-3.21</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 369.75 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>IND-R1-TATAPOWER-20260804-29907f</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -4649,42 +6151,47 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
+          <t>ADMINISTRATIVE</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>454.85</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>454.85</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>454.85</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+15.5pp)</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>IND-R2-SUNTV-20260908-c6e7dc</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -4718,42 +6225,47 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>1048.7</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>1007.2</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>-3.96</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 1011.5999 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>IND-R1-SBIN-20260821-b637f4</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -4787,42 +6299,47 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>1642.5</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>1577.1</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>-3.98</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 1594.6857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -4856,42 +6373,47 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
+          <t>ADMINISTRATIVE</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>289</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>289</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+19.4pp)</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>IND-R2-PETRONET-20260908-f20701</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -4925,42 +6447,47 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>2410</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>2094</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>-13.11</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 2314.8285 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>IND-R1-LUPIN-20260805-71abab</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -4994,42 +6521,47 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>507.9</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>470.4</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="J14" s="6" t="n">
         <v>-7.38</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="K14" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 493.3286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>IND-R1-IRCTC-20260804-afbb8f</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -5063,42 +6595,47 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>2064.9</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>1952</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>-5.47</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 1990.457 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -5132,42 +6669,47 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>385.15</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>369.85</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="J16" s="6" t="n">
         <v>-3.97</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="K16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 377.5071 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>IND-R1-DABUR-20260828-be7819</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -5201,42 +6743,47 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
+          <t>STOP-BREACH MARK</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>5454.5</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>5054.5</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="J17" s="6" t="n">
         <v>-7.33</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="K17" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Stop breached</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
           <t>STOP BREACHED - stop 5283.7143 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>IND-R1-BRITANNIA-20260804-3de31c</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>lifecycle:stop-breach</t>
         </is>
@@ -5270,42 +6817,47 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
+          <t>ADMINISTRATIVE</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>414.35</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>414.35</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>414.35</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+18.2pp)</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>IND-R2-RBLBANK-20260907-a63a75</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -5339,42 +6891,47 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
+          <t>REALIZED EXIT</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>391.3</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>415.35</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>6.15</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="K19" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+17.1pp)</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -5408,42 +6965,47 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
+          <t>ADVISORY/HISTORICAL</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>177.09</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>177.09</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0</v>
+        <v>177.09</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
           <t>Retired-runner cleanup · producer guard added 2026-09-02 · t</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>IND-R1-WIPRO-20260902-25d63c</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>registry:advisory</t>
         </is>
@@ -5477,42 +7039,47 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
+          <t>ADMINISTRATIVE</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>2891.8</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>2891.8</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0</v>
+        <v>2891.8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+57.0pp)</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ADANIENT-20260902-51452a</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -5546,42 +7113,47 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
+          <t>ADVISORY/HISTORICAL</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>347.25</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="I22" s="4" t="n">
         <v>326.5</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="J22" s="6" t="n">
         <v>-5.98</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="K22" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Historical reconciliation</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
           <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>IND-R1-NTPC-20260804-b96a36</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>registry:advisory</t>
         </is>
@@ -5615,42 +7187,47 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
+          <t>REALIZED EXIT</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>2383.9</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="I23" s="4" t="n">
         <v>2160.2</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="J23" s="6" t="n">
         <v>-9.380000000000001</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="K23" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+13.0pp)</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>registry:production</t>
         </is>
@@ -5684,42 +7261,47 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
+          <t>ADMINISTRATIVE</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>398.8</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>398.8</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0</v>
+        <v>398.8</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+52.9pp)</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ABCAPITAL-20260831-d36452</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
         </is>
@@ -5753,42 +7335,47 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
+          <t>ADVISORY/HISTORICAL</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>1955.3</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="I25" s="4" t="n">
         <v>1912</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="J25" s="6" t="n">
         <v>-2.21</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="K25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Historical reconciliation</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
           <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>registry:advisory</t>
         </is>
@@ -5822,42 +7409,47 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
+          <t>ADVISORY/HISTORICAL</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="I26" s="4" t="n">
         <v>268.15</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="J26" s="6" t="n">
         <v>-7.21</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="K26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Historical reconciliation</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
           <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>IND-R1-ITC-20260805-3cdd2a</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>registry:advisory</t>
         </is>
@@ -5891,42 +7483,47 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
+          <t>REALIZED EXIT</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>415.15</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="I27" s="4" t="n">
         <v>402.55</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>-3.04</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="K27" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>Rotation swap</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
           <t>Rotation → GNFC.NS (+14.3pp)</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>registry:p